--- a/Output/Shivraj Singh Chauhan/extracted_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A871"/>
+  <dimension ref="A1:A577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6090 +438,4032 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/illegal-mining-behind-punjab-floods-shivraj/articleshow/123727346.cms</t>
+          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/union-minister-shivraj-singh-chouhan-urges-people-to-buy-swadeshi-products/2900485</t>
+          <t>https://www.ap7am.com/index.php/en/109483/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/minister-shivraj-singh-chouhan-urges-people-to-buy-swadeshi-products-125090901666_1.html</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2165121</t>
+          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://icar.org.in/en/union-agriculture-minister-shri-shivraj-singh-chouhan-hails-success-viksit-krishi-sankalp-abhiyan</t>
+          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/gst-reforms-2025-agriculture-dairy-rural-boost/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-delhi-cm-rekha-gupta-inaugurate-saras-ajeevika-mela-with-over-400-lakhpati-didis/</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/top/vice-president-election-shivraj-singh-chouhan-union-ministers-cast-votes-in-parliament</t>
+          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/fiscal-first-half-end-nears-6-agri-schemes-announced-in-budget-yet-to-hit-ground-10248612/</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3624624-shivraj-singh-chouhan-assures-adequate-fertiliser-supply-for-satna-farmers</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/kerala/kerala-mp-kodikunnil-suresh-seeks-special-central-package-for-kuttanad/article70033326.ece</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/2-day-national-agricultural-conference-to-be-held-from-15-september-1503486047.html/amp</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2165828</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://icar.org.in/en/shri-shivraj-singh-chouhan-performs-yoga-occasion-11th-international-yoga-day</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-assures-adequate-supply-of-fertiliser-and-urea-in-madhya-pradesh/?amp=1</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-on-similar-lines-10246857/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3621585-empowering-women-through-swadeshi-a-path-to-self-reliance</t>
+          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3624282-government-slashes-gst-on-agricultural-equipment-in-revolutionary-move</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://english.dainikjagranmpcg.com/states/madhya-pradesh/union-agriculture-minister-shivraj-singh-chouhan-confronted-by-congress-black-flag/article-4795</t>
+          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/amp_articleshow/123993745.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3620588-union-ministers-vote-in-vice-presidential-election-amid-strengthening-nda-alliance</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mp-cong-claims-fertiliser-shortage-protests-with-black-flags-during-chouhan-s-satna-visit/2906296</t>
+          <t>https://www.aninews.in/news/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-calls-gst-reforms-a-new-growth-chapter-570827</t>
+          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278563647/under-your-leadership-upper-house-will-establish-new-benchmarks-shivraj-chouhan-congratulates-radhakrishnan</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278568693/very-revolutionary-decision-shivraj-singh-chouhan-welcomes-centre-new-gst-reforms</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/union-agriculture-minister-shivraj-singh-chouhan-exhorts-manit-bhopal-students-to-drive-innovations-for-nation</t>
+          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-mp-shivraj-singh-chouhan-arrives-in-satna-receives-rousing-welcome-from-party-workers-7105407.html</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/mama-mama-passengers-cheer-as-union-minister-shivraj-singh-chouhan-travels-in-train-from-bhopal-to-satna</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan/amp/</t>
+          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://menafn.com/1110047997/Rift-Between-Shivraj-Mohan-Yadav-Hurting-Farmers-In-MP-Umang-Singhar</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/congress-mla-stops-shivraj-singh-chouhan-convoy-in-satna-raises-fertiliser-shortage-issue-union-minister-responds-135894167.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/maihar-to-witness-unprecedented-development-says-shivraj-singh-chouhan-as-he-visits-sharda-mata-mandir20250912022337-65993/</t>
+          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/shivraj-singh-chouhan-kisan-samvad-cancelled-satna-congress-workers-strike-over-fertiliser-shortage-clash-with-police-135900267.html</t>
+          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/bhopal-metropolitan-region-to-be-develop-by-cpa-urban-administration-gives-approval-file-stuck-in-cms-secretariat-for-one-year-135875346.html</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/satna/agriculture-minister-convoy-was-stopped-due-to-shortage-of-fertilizers-in-satna-shivraj-singh-chauhan-had-cameras-switched-off/articleshow/123834635.cms</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/satna/news/congress-and-police-clash-over-the-siege-of-agriculture-minister-video-135899538.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://icar.org.in/hi/kaenadaraiya-karsai-mantarai-sarai-saivaraaja-sainha-caauhaana-nae-bhaarata-maen-vaikasaita-dao</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-reach-rewanchal-express-train-compartment-passengers-journey-become-memorable-19935723</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/madhya-pradesh/shivraj-singh-chouhan-satna-visit-stopped-convoy-and-drank-tea-2025-09-11-1162020</t>
+          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/shivraj-singh-chouhan-urea-supply-demand-kharif-season-9266469</t>
+          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/shivraj-singh-chauhan-%E0%A4%85%E0%A4%AC-%E0%A4%AC-%E0%A4%9C-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%95%E0%A4%B2-%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%B6%E0%A4%95-%E0%A4%AC%E0%A5%87%E0%A4%9A%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%9A%E0%A4%B2%E0%A5%87%E0%A4%97-%E0%A4%A1%E0%A4%82%E0%A4%A1-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%AB%E0%A4%B8%E0%A4%B0-%E0%A4%82-%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1JdWvq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/madhya-pradesh/union-minister-shivraj-singh-chauhan-traveled-by-train-and-also-met-passengers-201757584298910.html</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/satna/union-agriculture-minister-shivraj-singh-chauhan-visits-satna-gives-instructions-for-housing-survey-on-villagers-request-pays-tribute-to-security-aides-son-satna-news-c-1-1-noi1431-3392106-2025-09-11</t>
+          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/mohan-government-is-targeting-shivraj-singh-chauhan-big-allegation-of-digvijay-singh-gave-advice-to-chief-minister/articleshow/123851246.cms</t>
+          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/shivraj-singh-chouhan-viral-video-passengers-cheer-rewanchal-express-travels-in-train-from-bhopal-to-satna-one-nation-one-election-9257315</t>
+          <t>https://www.deccanherald.com/amp/story/india%2Fkarnataka%2Fcentre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.icar.org.in/hi/node/2295</t>
+          <t>https://www.deccanherald.com/amp/story/india%2Fagriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/maihar/news/shivraj-singh-chouhan-welcomed-at-maihar-railway-station-135891647.html</t>
+          <t>https://www.devdiscourse.com/article/business/3633463-relief-and-recovery-government-support-for-jks-rural-communities</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/shivraj-singh-chouhan-made-train-journey-memorable-took-selfies-with-passengers-gave-blessings/articleshow/123822181.cms</t>
+          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/shivraj-singh-chauhan-in-maihar-reached-kisan-samvad-program-special-farm-house-will-be-developed-9261297/amp/1</t>
+          <t>https://www.moneycontrol.com/news/india/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k-13561833.html/amp</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/satna/union-minister-shivraj-singh-chouhan-drinks-tea-from-roadside-tea-seller-in-amarpatan-maihar-watch-video/videoshow/123849877.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/satna/union-minister-stopped-convoy-in-maihar-and-enjoy-sip-of-tea-seller-overjoyed-serving-to-shivraj-singh-chouhan/articleshow/123848991.cms</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/shivraj-singh-chauhans-convoy-stopped-in-satna/146293</t>
+          <t>https://www.thehansindia.com/amp/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2165797</t>
+          <t>https://krishijagran.com/news/centre-to-provide-pm-kisan-relief-rs-76-crore-for-shgs-in-flood-hit-jammu-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/satna/farmers-created-a-ruckus-during-shivraj-satna-visit-union-minister-had-to-cancel-the-program/articleshow/123856543.cms</t>
+          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/satna-congress-mla-siddharth-kushwaha-stopped-shivraj-singh-convoy-farmers-fertilizer-problem-madhya-pradesh-news-mps25091102748</t>
+          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276011</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/satna/news/congress-district-president-stopped-shivrajs-convoy-in-satna-135893405.html</t>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/shivraj-singh-chouhan-one-nation-one-election-satna-speech</t>
+          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/satna/congress-mla-stopped-shivraj-singh-chauhans-convoy-congress-workers-protested-against-the-fertilizer-crisis-heated-debate-with-the-union-agriculture-minister-satna-news-c-1-1-noi1431-3392298-2025-09-11?src=top-subnav</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/hindi/the-latest/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A%E0%A5%8C%E0%A4%B9%E0%A4%BE%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%B2%E0%A5%8B%E0%A4%95%E0%A4%B8</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/congress-protests-fertiliser-shortage-shows-black-flags-to-shivraj-lcln-strc-2331298-2025-09-12</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/mp-news-mama-style-prevails-in-rewanchal-express-union-minister-shivraj-seen-mingling-with-passengers-2025-09-11</t>
+          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-bjp-mlas-meet.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/shivraj-singh-chouhan-s-train-journey-goes-viral-union-minister-interacts-with-passengers-takes-selfies-3010901</t>
+          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/maihar/news/shivraj-singh-said-in-maihar-only-swadeshi-will-strengthen-the-country-135899462.html</t>
+          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/congress-district-president-stopped-the-convoy-of-union-agriculture-minister-shivraj-singh-in-satna-9258138</t>
+          <t>https://www.news18.com/amp/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-in-maihar-worshipped-maa-sharda-and-had-discussion-with-farmers-madhya-pradesh-news-mps25091200401</t>
+          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits?amp</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan?amp</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/madhya-pradesh/satna-news/news-shivraj-singh-chauhan-advocated-holding-lok-sabha-and-assembly-elections-together-news-hindi-1-752085-KKN.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-second-phase-of-developed-agriculture-resolution-campaign-is-going-to-start-under-the-leadership-of-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%88-%E0%A4%A1-%E0%A4%B2-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C/ar-AA1M0AyD</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/punjab/video/floods-in-punjab-destroyed-crops-central-minister-shivraj-chauhan-met-affected-people-ytvd-2325394-2025-09-09</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/videos/satna-news/congress-stops-shivraj-singh-chauhan-convoy-farmers-issues-protest-mp-news-19936521</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mp-s-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2165089</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/bhopal-nephews-and-nieces-do-innovation-uncle-is-always-with-you-union-minister-told-manit-students-2025-09-12</t>
+          <t>https://www.devdiscourse.com/article/law-order/3635568-madhya-pradesh-leads-with-one-nation-one-election-resolutions?amp</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/digvijay-singh-said--bjp-government-is-targeting-shivraj-2211664</t>
+          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html/amp</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/punjab-flood-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%87%E0%A4%A8-%E0%A4%B5%E0%A4%9C%E0%A4%B9-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%86%E0%A4%88-%E0%A4%B9%E0%A5%88-%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD%E0%A4%AF%E0%A4%82%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%A2%E0%A4%BC/ar-AA1M0DR3?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/narmadapuram/pipariya/news/shivraj-singhs-personal-visit-to-pachmarhi-135920246.html</t>
+          <t>https://www.ptinews.com/editor-detail/Chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-J-K/2930370</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/union-minister-shivraj-singh-said-that-due-to-the-reform-in-gst-farmers-will-get-a-lot-of-benefits-on-every-front/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.amp.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/shivraj-s-program-cancelled-amid-women-s-uproar-2211674</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/19/del27-jk-chouhan-farmers.amp.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.navodayatimes.in/news/delhi-ncr/shivraj-singh-and-cm-rekha-gupta-inaugurated-saras-ajeevika-mela/275273/</t>
+          <t>https://www.uniindia.com/photoes/638786.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/madhya-pradesh/union-minister-shivraj-singh-unveiled-the-statue-ophp/cid17395895.htm</t>
+          <t>https://www.uniindia.com/photoes/638671.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%95-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-43-%E0%A4%B2-%E0%A4%97-%E0%A4%82-%E0%A4%95-%E0%A4%97%E0%A4%88-%E0%A4%9C-%E0%A4%A8-1-71-%E0%A4%B2-%E0%A4%96-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%AF%E0%A4%B0-%E0%A4%9C%E0%A4%AE-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%89%E0%A4%97-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC%E0%A4%B0%E0%A5%8D%E0%A4%AC-%E0%A4%A6-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%85%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A5%87%E0%A4%9C%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%A6-%E0%A4%B0/ar-AA1LUOIP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.uniindia.com/photoes/638785.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/rewa-news/after-shivraj-mama-who-is-famous-as-jijaji-dildaron-me-dildar-mohan-jijaji-song-19932860</t>
+          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/shivraj-said-if-there-is-no-crisis-of-fertilizer-then-instructions-to-collectors-135901032.html</t>
+          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/shivraj-suddenly-arrived-in-the-sleeper-coach-and-a-crowd-gathered-to-take-self-2210879</t>
+          <t>https://www.uniindia.com/photoes/638668.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/narmadapuram/news/union-agriculture-minister-shivraj-takes-refuge-in-mahadev-in-pachmarhi-135915881.html</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/prime-minister-narendra-modi-will-visit-flood-affected-punjab-and-himachal-pradesh-today/</t>
+          <t>https://theprint.in/india/chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-j-k/2746928/?amp</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/mp-6-%E0%A4%AC%E0%A4%9C%E0%A5%87-6-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%96%E0%A4%AC%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%97%E0%A5%8D-%E0%A4%B5-%E0%A4%B2-%E0%A4%AF%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%9A%E0%A5%82%E0%A4%B9-%E0%A4%82-%E0%A4%95-%E0%A4%86%E0%A4%82%E0%A4%A4%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%8F-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87/ar-AA1M0HhF?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/Farmers-in-queue...-Agriculture-Minister-said---There-is-no-shortage-of-fertilizers-in-any-district-of-Madhya-Pradesh</t>
+          <t>http://www.uniindia.com/photoes/638670.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.dailychhattisgarh.com/latest-news/303197/shivraj-is-in-charge-of-voting-of-mps-from-plain-areas</t>
+          <t>http://www.uniindia.com/photoes/638071.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/congress-workers-showed-black-flags-to-shivraj-over-the-shortage-of-fertilizers-in-satna/867487/?amp</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/madhya-pradesh/congressmen-create-ruckus-over-fertilizer-crisis-in-mp-agriculture-minister-shivraj-program-cancelled-201757703520039.html</t>
+          <t>http://www.uniindia.com/photoes/638735.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/jijaji-is-becoming-popular-after-mama-shivraj-singh-chouhan-mama-mp-cm-dr-mohan-yadav-getting-edge-in-mp-superhit-jija-song-dildaroin-mein-dildar-moha-9241307</t>
+          <t>http://www.uniindia.com/photoes/638794.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/madhya-pradesh/news/the-mp-government-will-take-another-loan-of-4000-crore-rupees-the-funds-will-be-2209682</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/satna/news/shivraj-met-the-passengers-in-rewanchal-express-135892534.html</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/local/mp/vidisha/news/public-outrage-over-the-plight-of-vidisha-shivraj-tandon-held-responsible-for-the-plight-of-the-city-135922679.html</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/27700-metric-tonnes-of-urea-supplied-in-satna-union-minister-said-arrangements-will-be-increased-as-per-requirement/</t>
+          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.khabarfast.com/haryana-jind-vinesh-phogat-lashed-out-at-agriculture-minister-shivraj-singh/participants</t>
+          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.khabarfast.com/haryana-jind-vinesh-phogat-lashed-out-at-agriculture-minister-shivraj-singh/</t>
+          <t>https://neindiabroadcast.com/2025/09/20/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/rajasthan/dungarpur/news/shivraj-and-mahi-selected-at-state-level-in-rifle-shooting-135889944.html</t>
+          <t>https://www.socialnews.xyz/2025/09/16/new-delhi-shivraj-singh-chouhan-addresses-press-conference-gallery-2/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/shivraj-jitu-war-broke-out-jitu-said-how-long-will-the-country-s-agriculture-2210622</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/agriculture-minister-shivraj-singh-chauhans-property-disclosed/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/amp/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/agriculture-minister-shivraj-singh-chouhan-participated-in-one-nation-one-election-program-in-satna-1276218-2025-09-11</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-statement-unturned-in-ensuring-proper-supply-of-fertilizers-1277046-2025-09-13</t>
+          <t>https://www.socialnews.xyz/2025/09/19/new-delhi-shivraj-singh-chouhan-addresses-press-conference-on-gst-reforms-gallery/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/shivraj-singh-chauhan-reached-the-shelter-of-lord-shiva-did-a-photo-shoot-of-monkey-in-the-valleys-of-pachmarhi/</t>
+          <t>https://www.socialnews.xyz/2025/09/16/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/congress-mla-asked-questions-to-shivraj-singh-chauhan-regarding-fertilizer-problem-1276616-2025-09-12</t>
+          <t>https://www.thehawk.in/news/india/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/amp/312704-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A%E0%A5%8C%E0%A4%B9%E0%A4%BE%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%86%E0%A4%9C-%E0%A4%B8%E0%A4%A4%E0%A4%A8%E0%A4%BE-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%BE-%E0%A4%A6%E0%A5%8C%E0%A4%B0%E0%A4%BE-%E0%A4%95%E0%A4%BF%E0%A4%AF%E0%A4%BE</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.enewsmp.com/enewsmp-34566-63.html</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/news/312704-Shivraj-Singh-Chouhan-visits-Satna-in-Madhya-Pradesh</t>
+          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/bhopal-shivraj-singh-chauhan-will-participate-in-the-youth-parliament-program-today-bhopal--4259523</t>
+          <t>https://www.latestly.com/agency-news/india-news-union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative-7122123.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=shivraj-singh-chauhan-reached-the-shelter-of-lord-shiva-did-a-photo-shoot-of-monkey-in-the-valleys-of-pachmarhi-576422</t>
+          <t>https://menafn.com/1110086486/Over-5000-Rural-Houses-In-JK-To-Get-PMAY-Support-Minister</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/politics-heated-up-in-mp-over-fertilizer-crisis-shivrajs-convoy-stopped-in-satna-congress-showed-black-flags/</t>
+          <t>https://www.socialnews.xyz/2025/09/17/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/amp/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/madhya-pradesh/satna-mla-kisan-samasya-shivraj-singh-chouhan-kafila-roka-646115</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/shivraj-singh-chauhan-gave-the-message-of-adopting-swadeshi-to-the-farmers-in-maihar-4260774</t>
+          <t>https://www.latestly.com/agency-news/india-news-shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers-7119994.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-during-shivrajs-visit-to-satna-congress-created-ruckus-over-fertilizer-crisis-clashed-with-police/</t>
+          <t>https://www.latestly.com/agency-news/india-news-will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-7119481.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/shivraj-singh-chauhan-welcomed-gst-reforms-4260577</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/shivraj-singh-chauhan-advocated-for-holding-lok-sabha-and-assembly-elections-together-4260757</t>
+          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html/amp</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/union-minister-shivraj-singh-and-chief-minister-rekha-gupta-inaugurated-saras-livelihood-fair-1275080-2025-09-09</t>
+          <t>https://www.takeonedigitalnetwork.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-hit-farmers-in-rs-pura-assures-full-compensation/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/mp-info/women-stopped-agriculture-minister-shivrajs-convoy-due-to-shortage-of-fertilizers-accused-the-police-of-misbehavior-34848</t>
+          <t>https://mobilenews24x7.com/2025/business/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-suddenly-reached-the-sleeper-coach-of-the-train-the-coach-echoed-with-the-sound-of-mama-mama/</t>
+          <t>https://www.newsdrum.in/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan-10485478</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://bansalnews.com/shivraj-singh-chouhan-satna-kisan-samvad-congress-hindi-news-bps/</t>
+          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://livevns.news/state/madhyapradesh/shivraj-singh-chauhan-will-come-to-satna-on-septemphp/cid17384387.htm</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://livevns.news/state/madhyapradesh/shivraj-singh-chauhan-will-be-in-satna-today-willphp/cid17391154.htm</t>
+          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-chauhan-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A6-%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%A6-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B2%E0%A4%97%E0%A4%A4-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82/ar-AA1G4kSw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/simultaneous-elections-save-money-labour-environment-time-shivraj-singh/?amp=1</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html?utm_source=article_detail&amp;utm_medium=CRE&amp;utm_campaign=latestnews_CRE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/madhya-pradesh/farmers-stopped-the-convoy-of-union-agriculture-minister-shivraj-in-satna-1351890.html/amp</t>
+          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.enewsmp.com/enewsmp-34572-63.html</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-nda-parliamentary-party-meeting-1185963</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/vice-presidential-election-shivraj-singh-chouhan-union-ministers-cast-votes-in-parliament-4256328</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/coming-among-the-public-and-travelling-in-the-train-mama-shivraj-gave-the-people-a-feeling-of-closeness-with-ram-ram-dua-salaam/</t>
+          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/madhya-pradesh/shivraj-singh-chauhan-gave-the-message-of-adopting-swadeshi-to-the-farmers-in-maihar--4260606</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/madhya-pradesh/shivraj-singh-chauhan-advocated-for-holding-lok-sabha-and-assembly-elections-together--4260623</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://livevns.news/state/madhyapradesh/union-minister-shivraj-singh-unveiled-the-statue-ophp/cid17395865.htm</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://hindikhabar.com/jitu-patwari-shivraj-singh-chouhan-farmers-issue-social-media-war/</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/News/after-shivraj-mama-mohan-jijaji-entered-the-politics-of-madhya-pradesh</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9A-%E0%A4%A8%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%A4%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%97%E0%A4%88%E0%A4%82-%E0%A4%B5-%E0%A4%AF%E0%A4%B0%E0%A4%B2/ar-AA1xALne?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://lalluram.com/union-minister-shivraj-worshiped-maa-sharda-with-his-wife-in-maihar-called-for-adopting-swadeshi/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/national-rabi-conference-2025-in-delhi-two-day-event/</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/central-minister-shivraj-vksa-plan-setback-damu-employees-threaten-boycott-1277015-2025-09-13</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/union-minister-shivraj-singh-chauhan-visits-flood-affected-area-budilya-brahman-jammu-region-5608</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/under-your-leadership-the-upper-house-will-set-new-standards-shivraj-chouhan-congratulates-radhakrishnan-4257278</t>
+          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://dainikyashonnati.com/ladli-bahna-yojana-echoes-the-politics-of-madhya-pradesh-and-revolution-in-society/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.yashbharat.com/shivraj-singh-chauhans-very-low-stay-in-katni-today/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/bku-wrote-letter-to-agriculture-minister-shivraj-regarding-gene-edited-paddy-demand-to-ban-1277452-2025-09-14</t>
+          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/many-bjp-leaders-congratulated-cp-radhakrishnan-with-prime-minister-narendra-modi-on-being-elected-17th-vice-president-1348867.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%9F-%E0%A4%B0%E0%A4%97%E0%A5%87%E0%A4%9F-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9-%E0%A4%AE-%E0%A4%B9%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A6%E0%A5%87-%E0%A4%A6-%E0%A4%A8%E0%A4%B8-%E0%A4%B9%E0%A4%A4/ar-AA1MqaDa?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://yashbharat.co.in/%E0%A4%AD%E0%A5%8B%E0%A4%AA%E0%A4%BE%E0%A4%B2-%E0%A4%9C%E0%A4%BE%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%86%E0%A4%9C-%E0%A4%B0%E0%A4%BE%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%BF-%E0%A4%95/</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/central-minister-shivraj-vksa-plan-setback-damu-employees-threaten-boycott-1277015-2025-09-13?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://yashbharat.co.in/%E0%A4%B9%E0%A4%82%E0%A4%97%E0%A4%BE%E0%A4%AE%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%9A%E0%A4%B2%E0%A4%A4%E0%A5%87-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%B6%E0%A4%BF/</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://bansalnews.com/jyotiraditya-scindia-net-worth-shivraj-chouhan-modi-minister-asset-declaration-mp-hindi-news-wks/</t>
+          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/after-shivraj-mama-the-new-brand-cm-mohan-yadav-knows-jijaji-who-gave-the-name-and-what-will-be-the-favorite-of-the-public/</t>
+          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://ahilyawani.com/farmers-talk-alert-government-and-opposition-attack-kaushal-kishore-chaturvedi/</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/raisen-mp-fake-fertilizer-conflicting-statements-shivraj-singh-chouhan-aidal-singh-kansana-shock-farmers-9650353.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/bku-wrote-letter-to-agriculture-minister-shivraj-regarding-gene-edited-paddy-demand-to-ban-1277452-2025-09-14?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/madhya-pradesh/congress-workers-show-black-flags-to-shivraj-singh-chouhan-over-shortage-of-fertilizer-in-satna-3248096.html</t>
+          <t>https://hindi.krishijagran.com/news/gst-reduction-agriculture-machinery-shivraj-singh-meeting-benefits-for-farmers-2025/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/madhya-pradesh/bhopal-progress-of-mnrega-under-the-leadership-of-chief-minister-mohan-yadav-bhopal--4261083</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%AD%E0%A4%B0-%E0%A4%B8-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1u1cBq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://tennews.in/will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan/</t>
+          <t>https://www.sudarshannews.in/news-detail.aspx?id=132584</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-vice-president-election-shivraj-singh-chouhan-union-ministers-cast-votes-in-parliament-7101753.html</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-and-delhi-chief-minister-smt-rekha-gupta-formally-inaugurate-saras-livelihood-fair/</t>
+          <t>https://www.m.khaskhabar.com/news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467215-Shivraj-Singh-Chouhan-visits-Satna-in-Madhya-Pradesh</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.technologyforyou.org/union-minister-shri-shivraj-singh-chouhan-and-delhi-chief-minister-smt-rekha-gupta-formally-inaugurate-saras-livelihood-fair/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE-%E0%A4%A8%E0%A4%B9-%E0%A4%A8-%E0%A4%AE-%E0%A4%AE%E0%A4%B2-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%B0-%E0%A4%B9%E0%A4%A4-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%97%E0%A4%A4-%E0%A4%AA%E0%A5%87%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%9B%E0%A5%82%E0%A4%9F-%E0%A4%9C-%E0%A4%B0-%E0%A4%B0%E0%A4%96/ar-AA1BdzrP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/shivraj-singh-chauhan-in-maihar-reached-kisan-samvad-program-special-farm-house-will-be-developed-9261297</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/political-war-broke-out-on-social-media-shivraj-singh-chouhan-jitu-patwari-clashed-19932361</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2165797</t>
+          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2165089</t>
+          <t>https://www.bhaskar.com/mp/bhopal/pc-sharma-said-shivraj-singh-announced-to-build-sita-mata-temple-in-sri-lanka-01595983.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/satna-scuffling-between-congress-leaders-and-police-going-central-agriculture-minister-shivraj-singh-chauhan-9262293</t>
+          <t>http://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF%E0%A5%82%E0%A4%B0-%E0%A4%AF-%E0%A4%86%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1Mqmi4?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://inshorts.com/hi/news/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8--%E0%A4%B9-%E0%A4%A8--%E0%A4%8F%E0%A4%AE%E0%A4%AA--%E0%A4%AE---%E0%A4%86%E0%A4%AE-%E0%A4%B2-%E0%A4%97---%E0%A4%95--%E0%A4%B8-%E0%A4%A5-%E0%A4%9F-%E0%A4%B0-%E0%A4%A8-%E0%A4%AE---%E0%A4%95-%E0%A4%AF--%E0%A4%B8%E0%A4%AB%E0%A4%B0--%E0%A4%B5-%E0%A4%A1-%E0%A4%AF--%E0%A4%86%E0%A4%AF--%E0%A4%B8-%E0%A4%AE%E0%A4%A8--1757594751489</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/bihar-election-2025-nda-strategy-bjp-focus-obc-youth-women-voters-article-152792919/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%AE%E0%A4%AA-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B0%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B8%E0%A5%81%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%86%E0%A4%9C-%E0%A4%9C-%E0%A4%B0-%E0%A4%B9-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%B5-%E0%A4%B0%E0%A4%82%E0%A4%9F/ar-AA1qUS4m?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-assures-adequate-supply-of-fertiliser-and-urea-in-madhya-pradesh/</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/fertilizer-shortage-crisis-farmers-face-lathi-charge-black-marketing-and-nhrc-takes-notice-across-indian-states-3012164/amp</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://thepublicworld.com/archives/111305</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/politics/congress-leader-umang-singhar-has-criticized-both-the-state-and-central-governments-for-the-fertilizer-shortage-and-black-marketing-in-madhya-pradesh-1351076.html</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://mruganchalexpress.com/certificate-distributed-to-talented-student-student-of-chief-minister-free-scooty/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/pmfby-pradhan-mantri-fasal-bima-yojana-conditions-profit-and-crop-insurance-companies-earnings-1276703-2025-09-12</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%9C-%E0%A4%A4-%E0%A4%87%E0%A4%9C%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%AD-%E0%A4%97-%E0%A4%B2-%E0%A4%AF/ar-AA1Eqc4V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://tfipost.in/2025/09/punjab-floods-when-bjp-held-the-hand-of-the-people/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://indianews.in/state/madhya-pradesh/digvijay-chautala-on-ujjain-kisan-nyay-yatra-farmer-issues-congress-bjp-824996/amp/</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/chief-minister-dr-yadav-is-constantly-working-to-provide-new-identity-to-tourism-in-the-state/</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/466957-Shivraj-Singh-Chouhan-and-Rekha-Gupta-formally-inaugurate-SARAS-Livelihood-Fair</t>
+          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://thepublicworld.com/archives/111327</t>
+          <t>https://vocaltv.in/madhya-pradesh/shivraj-singh-chouhan-on-a-visit-to-raisen-districphp/cid17449225.htm</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://areporterlive.com/bjp-likely-to-announce-new-national-president-soon-as-rss-ties-improve-four-leaders-in-the-race/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%82%E0%A4%B5%E0%A5%87%E0%A4%A6%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-cm-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%95-%E0%A4%9A-%E0%A4%9F%E0%A5%8D%E0%A4%A0/ar-AA1wPCa5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/hi/!state/shivraj-singh-in-maihar-worshipped-maa-sharda-and-had-discussion-with-farmers-madhya-pradesh-news-mps25091200401</t>
+          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B0-%E0%A4%B2-%E0%A4%AC-%E0%A4%9C-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%9B%E0%A5%82%E0%A4%9F-%E0%A4%97%E0%A4%8F-%E0%A4%AA-%E0%A4%9B%E0%A5%87/ar-AA1sCHcC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/shivraj-singh-chouhan-urea-supply-demand-kharif-season-9266469/amp/1</t>
+          <t>https://www.msn.com/hi-in/news/other/india-israel-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%B0-%E0%A4%87%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%AA%E0%A5%82%E0%A4%B8-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B8-%E0%A4%B0%E0%A4%B9/ar-AA1CvKsJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz</t>
+          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/indian-politics-%E0%A4%B9-%E0%A4%A5-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%82%E0%A4%A4-%E0%A4%A6-%E0%A4%96-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%96-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%94%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%AC-%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A4%B9-%E0%A4%AF%E0%A5%87/ar-AA1BmSnU?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/pm-modi-will-give-eight-big-gifts-to-madhya-pradesh-6-lakh-farmers-will-benefit-19937764</t>
+          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.icar.org.in/hi/paiema-kaisaana-samamaana-naidhai-kai-20vain-kaisata-2-agasata-2025-kao-kai-jaaegai-jaarai</t>
+          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/congress-workers-showed-black-flags-to-shivraj-over-the-shortage-of-fertilizers-in-satna/867487/</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-10-11-september-live-updates-vice-president-cp-radhakrishnan-nepal-protests-pm-modi-rahul-gandhi/4133715/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/relief-for-farmers-as-gst-cut-lowers-tractor-and-equipment-prices/</t>
+          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/satna/mppsc-result-2024-son-of-a-farmer-became-a-dsp-and-security-guard-son-treasury-officer-in-satna/articleshow/123869811.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%86%E0%A4%82%E0%A4%A6-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A4%B9-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82/ar-AA1vC8f0?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.khabarfast.com/haryana-jind-vinesh-phogat-lashed-out-at-agriculture-minister-shivraj-singh</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%86%E0%A4%B2-%E0%A4%9A%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1DqpoB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/local/mp/news/mp-evening-bulletin-news-update-ladli-behna-kist-september-2025-135903046.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/21/moral-responsibility-of-every-citizen-to-keep-his.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/news/mp-evening-bulletin-news-update-bhopal-bjp-neta-viral-video-bus-fired-135895003.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/shivraj-singh-chauhan-advocated-for-holding-lok-sabha-and-assembly-elections-together--4260623</t>
+          <t>https://www.msn.com/hi-in/news/other/rural-development-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A8-%E0%A4%B8%E0%A4%82%E0%A4%AD%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B5-%E0%A4%95%E0%A4%B8-%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1wUMo8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/under-your-leadership-upper-house-will-establish-new-benchmarks-shivraj-chouhan-congratulates-radhakrishnan/</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/bku-wrote-letter-to-agriculture-minister-shivraj-regarding-gene-edited-paddy-demand-to-ban-1277452-2025-09-14?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.amarujala.com/amp/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/after-reduction-in-gst-rates-farmers-will-now-get-tractors-and-other-agricultural-equipment-at-these-prices/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A4%A8-%E0%A4%A5-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%9F%E0%A4%B6%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%87%E0%A4%B8-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A6-%E0%A4%97%E0%A5%8D%E0%A4%97%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%AE-%E0%A4%B0-%E0%A4%8F%E0%A4%82%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%9F/ar-AA1z4w81?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/bjp-will-soon-get-a-new-national-president-relations-between-rss-and-bjp-have-softened-names-of-these-ministers-are-ahead-in-the-race-news-295051</t>
+          <t>https://www.msn.com/hi-in/news/other/gst-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%B9-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%82-%E0%A4%B2-%E0%A4%AD/ar-AA1MSiQO?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/vikasit-krishi-sankalp-abhiyaan-rabi-crop-national-conference-2025-prv-1277150-2025-09-13</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/desh-pradesh/haryana/haryana-floods-bhupinder-hooda-demands-70000/article-105755</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.vnationnews.com/bjp-leaders-including-cp-radhakrishnan-pm-modi-who-were-elected-17th-vice-president-of-the-country-congratulated-bjp-leaders/</t>
+          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.saahassamachar.in/union-minister-shivraj-singh-reached-satna-gave-instructions-for-housing-survey-on-the-demand-of-villagers</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1%E0%A4%BC%E0%A4%A6-%E0%A4%94%E0%A4%B0-%E0%A4%A4%E0%A5%81%E0%A4%85%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-msp-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1zzqhC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/madhya-pradesh/11-year-old-girl-dies-of-heart-attack-while-playing-in-school-11--4260682</t>
+          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/mock-drills-to-grouping-up-nda-mps-all-hands-on-deck-as-bjp-aims-to-leave-no-room-for-error-in-vice-president-polls-3718150</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3624418-india-seeks-halt-to-recruitment-of-citizens-into-russian-army?amp</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3624624-shivraj-singh-chouhan-assures-adequate-fertiliser-supply-for-satna-farmers?amp</t>
+          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/union-minister-giriraj-singh-criticizes-sudershan-reddy-s-morality-after-meeting-with-fodder-scam-convict</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3624417-protests-erupt-over-fertiliser-shortage-in-satna</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-in-rabi-festphp/cid17420755.htm</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/national-agricultural-conference-rabi-abhiyan-2025-begins-monday/</t>
+          <t>https://vocaltv.in/Jammu-and-Kashmir/shivraj-chauhan-visits-flood-affected-in-rs-pura-php/cid17443231.htm</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/rajya-sabha-deputy-chairman-casts-vote-to-elect-15th-vice-president20250909120917/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%82%E0%A4%A7%E0%A5%81-%E0%A4%9C%E0%A4%B2-%E0%A4%B8%E0%A4%82%E0%A4%A7-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%B8%E0%A4%82%E0%A4%97%E0%A4%A0%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1F0ALw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/union-minister-shivraj-singh-chouhan-urges-people-to-buy-swadeshi-products-10066812</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/13/viksit-krishi-sankalp-abhiyan-to-guide-production-strategies-for-rabi-season/</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/21/moral-responsibility-of-every-citizen-to-keep-his.php</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-vice-president-election-union-minister-rajnath-singh-nda-mps-cast-votes-in-parliament-7101524.html</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan</t>
+          <t>https://vocaltv.in/national/moral-responsibility-of-every-citizen-to-keep-hisphp/cid17452423.htm</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/punjab/news/politics-sharpens-over-pm-modis-visit-to-flood-affected-punjab-cabinet-minister-barinder-kumar-goyal-urges-centre-135868535.html</t>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://newsriveting.com/two-day-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/vice-presidential-election-food-stalls-crackers-prayers-for-radhakrishnan-in-his-hometown/</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-minister-shivraj-interacts-with-street-vendors-in-raisen-135977689.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%9F-%E0%A4%B0%E0%A4%97%E0%A5%87%E0%A4%9F-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9-%E0%A4%AE-%E0%A4%B9%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A6%E0%A5%87-%E0%A4%A6-%E0%A4%A8%E0%A4%B8-%E0%A4%B9%E0%A4%A4/ar-AA1MqaDa</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.php</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/efforts-to-make-rabi-conference-more-effective-two-day-brainstorming-to-be-held-with-states</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%AE-%E0%A4%B0-%E0%A4%AE-%E0%A4%A6%E0%A5%81%E0%A4%86-%E0%A4%B8%E0%A4%B2-%E0%A4%AE-%E0%A4%86%E0%A4%B6-%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%A6-%E0%A4%94%E0%A4%B0-%E0%A4%A4-%E0%A4%AC%E0%A4%A1%E0%A4%BC%E0%A4%A4-%E0%A4%A1%E0%A4%BC-%E0%A4%B8%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AB-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%A8-%E0%A4%95-%E0%A4%B8%E0%A4%AB%E0%A4%B0-%E0%A4%95-%E0%A4%AF-%E0%A4%A6%E0%A4%97-%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%A6-%E0%A4%AF/ar-AA1MjJoj</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-said-we-will-help-the-farmers-by-conducting-a-survey-135973923.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/punjab/ludhiana/former-madhya-pradesh-cm-shivraj-chauhan-arrives-in-ludhiana-meeting-with-punjab-core-committee-continues-126458919.html</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-next-national-president-rss-deal-top-5-ministers-in-race-all-details-in-hindi-1385409.html?ref_source=OI-HI&amp;ref_medium=Home-Page&amp;ref_campaign=News-Cards</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/no-stone-will-be-left-unturned-to-ensure-adequatephp/cid17395822.htm</t>
+          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/?amp</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/local/mp/news/mp-evening-bulletin-news-update-bhopal-bjp-neta-viral-video-bus-fired-135895003.html</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/cp-radhakrishnan-visited-ram-temple-another-party-was-out-of-the-voting-process-know-what-the-number-game-is-saying-now-19929491</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/rss-dominates-from-president-vice-president-and-pm-modi-to-cms-of-these-states-see-the-full-list-19931567</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.abhitaknews.com/news/14077</t>
+          <t>https://www.inhnews.in/News/after-listening-to-the-farmers-shivraj-singh-called-the-collector</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://english.dainikjagranmpcg.com/states/madhya-pradesh/68c3cdf7a1579/article-4805</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/madhya-pradesh/farmers-stopped-the-convoy-of-union-agriculture-minister-shivraj-in-satna-1351890.html</t>
+          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://ind24.tv/news/shivraj_jeetu</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://ind24.tv/news/MP_Poltician_Lineage</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://ncrsamacharlive.in/latest/madhya-pradesh-youth-congress-leader-arrested-before-meeting-youth-with-farmer-issues-on-arrival-of-union-minister-in-maihar</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16?utm_source=rssfeed</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/satna-political-uproar-on-the-issue-of-farmers-and-fertilizers-1276150-2025-09-11</t>
+          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/new-delhi/delhi-news-vikasit-krshi-sankalp-abhiyaan-ka-doosara-charan-3-se-18-aktoobar-tak-1185955</t>
+          <t>https://upkiran.org/Shivraj-Singh-Chouhan-recounts-a-memorable-anecdote-about-a-side-of-PM-Modi-that-few-people-know</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/amit-shah-rahul-gandhi-sonia-gandhi-cast-votes-for-vice-president-election-4256284</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/preparation-for-rabi-season-developed-agriculture-resolution-campaign-will-run-from-3-to-18-october-national-c</t>
+          <t>https://www.5dariyanews.com/hindi/news/313264-Shivraj-Singh-Chouhan-meets-flood-affected-farmers-of-Jammu</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/digvijay-questions-madhya-pradesh-govts-ladli-behna-scheme-calls-it-a-drop-in-ocean-to-make-women-self-reliant-1903575</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/head-granthi-slams-pm-modi-s-punjab-visit-bjp-fires-back/north/news/3571321.html</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3621647-empowering-delhi-bjps-double-engine-governance</t>
+          <t>https://www.bhaskarhindi.com/other/-110--1189364</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/live-blog/india/vice-president-election-2025-updates-ndas-radhakrishnan-vs-india-blocs-reddy-voting-begins-at-10-am/</t>
+          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/14/madhya-pradesh-government-committed-to-27-obc-quota-cm-yadav-tells-delegation</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/elections/assembly-elections/bihar/bihar-elections-bjps-campaign-mode-on-pm-modi-amit-shah-to-visit-poll-bound-state/amp_articleshow/123837283.cms</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/14/bes8-mp-obc-quota-nath.amp.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189280</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278562569/aap-sanjay-singh-accuses-abstaining-parties-of-backing-bjp-in-vice-presidential-poll</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-mp-shivraj-singh-chouhan-arrives-in-satna-receives-rousing-welcome-from-party-workers-7105407.html/amp</t>
+          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/mp-shivraj-singh-chouhan-arrives-in-satna-receives-rousing-welcome-from-party-workers/</t>
+          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/rift-between-shivraj-mohan-yadav-hurting-farmers-in-mp-umang-singhar</t>
+          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/rss-bjp-veteran-from-tamil-nadu-c-p-radhakrishnan-becomes-vice-president-of-india/</t>
+          <t>https://jantaserishta.com/delhi-ncr/shivraj-singh-chouhan-participated-in-a-cleanliness-drive-in-raisen-as-part-of-the-seva-pakhwada-4277570</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://m.sakshipost.com/amp/news/jyotiraditya-scindia-urges-male-family-members-women-local-panchayat-bodies-not-interfere</t>
+          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-raise-concern-over-bio-stimulant-1278916-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/arrest-warrant-issued-against-bhojpur-mla-surendra-patwa-court-directs-bjp-leader-to-appear-after-repeated-absences-in-cheque-bounce-cases-135883039.html</t>
+          <t>https://www.haribhoomi.com/amp/buzz/buzz/pm-modi-75th-birthday-sewa-pakhwada-week-2025-live-updates-bjp-celebration-news-5913-5913</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>http://www.amarujala.com/madhya-pradesh/bhopal/mp-politics-news-bjp-policy-one-family-one-post-rule-enforced-leader-sons-face-restraint-2025-09-13?position=15&amp;src=tlh</t>
+          <t>https://jantaserishta.com/local/andhra-pradesh/andhra-pradesh-shivraj-singh-chouhan-plants-75-saplings-on-pm-modis-birthday-4270902</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%89%E0%A4%AA%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B2-%E0%A4%A1%E0%A4%B2-%E0%A4%AC%E0%A4%B9%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%B9-%E0%A4%B0%E0%A5%87-bjp-%E0%A4%94%E0%A4%B0-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%9C-%E0%A4%A8-%E0%A4%8F-%E0%A4%B5%E0%A4%9C%E0%A4%B9/ar-AA1tpMwS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-next-national-president-rss-deal-top-5-ministers-in-race-all-details-in-hindi-1385409.html</t>
+          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/national-hindi-news/does-rss-want-to-make-sanjay-joshi-bjp-president-125091300037_1.html</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/vice-presidential-poll-sanjay-singh-accuses-abstaining-parties-of-backing-bjp-hindi-news-hin25090903133</t>
+          <t>https://dainiksaveratimes.com/big-1/government-leave-no-stone-unturned-helping-farmers-shivraj-chauhan-told-flood-victims/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/madhya-pradesh/there-is-a-fierce-battle-in-madhya-pradesh-bjp-over-nepotism-125091200044_1.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/pm-modi-birthday-shivraj-singh-chouhan-launches-healthy-women-strong-family-campaign-plants-75-saplings-in-pus</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-chief-sudhanshu-trivedi-in-bjp-national-president-race-social-media-react-1384019.html</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/vice-president-election-2025-voting-results-live-updates-nda-cp-radhakrishnan-india-bloc-b-sudershan-mps-vote-election-commission-news-in-hindi/4131678/</t>
+          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/fertilizer-crisis-in-mp-leader-of-opposition-umang-singhar-revelation-questions-on-the-government-1382995.html</t>
+          <t>https://makdaiexpress24.com/kisan-aakrosh-morcha-met-union-agriculture-minister-shivraj-singh-chauhan-and-demands-to-start-the-work-of-ganjal-marand-dame/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://upkiran.org/final-round-for-post-of-BJP-president-has-begun-these-4-big-ministers-in-race</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-arrest-warrant-issued-against-former-minister-and-bjp-mla-surendra-patwa/</t>
+          <t>https://dainiksaveratimes.com/national/jammu-kashmir/110-road-works-approved-udhampur-jitendra-singh-expresses-gratitude-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/headlines/mp-fertilizer-crisis-umang-singhar-slams-bjp-government-says-farmers-face-lathi-charge-treated-as-vote-bank-06-816825</t>
+          <t>https://jantaserishta.com/local/madhya-pradesh/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop--4276499</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://indianews.in/state/madhya-pradesh/digvijay-chautala-on-ujjain-kisan-nyay-yatra-farmer-issues-congress-bjp-824996/</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://lagatar.in/vice-presidential-election-pm-modi-casts-first-vote-akhilesh-calls-bjp-a-exploited-party</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/bjp-slams-punjab-government-over-flood-relief-calls-out-cm-bhagwant-mann-in-jalandhar-prv-1276973-2025-09-13?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/chandigarh/pm-modi-visit-punjab-flood-aap-seeks-funds-10237243/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/jammu-and-kashmir-shivraj-singh-chouhan-met-flood-affected-farmers</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/projects-not-politics-pm-modi-resets-manipur-pitch/ar-AA1MvfAk</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/amp/india/all-india/madhya-pradesh-government-to-audit-ladli-behna-beneficiaries-to-remove-ineligible-names-1903332</t>
+          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/fiscal-first-half-end-nears-6-agri-schemes-announced-in-budget-yet-to-hit-ground/</t>
+          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3621648-unity-in-diversity-oppositions-political-success-in-vice-presidential-election?amp</t>
+          <t>https://sehorehulchal.com/news/shivraj-singh-chouhan-noticed-a-cow-sitting-on-the-road-and-said-i-will-come-again-in-the-evening/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278569822/maihar-to-witness-unprecedented-development-says-shivraj-singh-chouhan-as-he-visits-sharda-mata-mandir</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/11/will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan/</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-bihar-election-bjps-new-strategy-no-election-in-charge-focus-on-joint-campaign-committee-24046042.html</t>
+          <t>https://lalluram.com/mp-news-union-agriculture-minister-shivraj-singh-chouhan-called-the-collector-in-sehore-and-directed-him-to-immediately-survey-the-damaged-crops/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/local/mp/satna/news/congress-district-president-stopped-shivrajs-convoy-in-satna-135893405.html</t>
+          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-presidential-election-opposition-candidate-sudarshan-reddy-denies-cross-voting-kharge-says-victory-is-certain/articleshow/123779510.cms</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/satna/congress-mla-stopped-shivraj-singh-chauhans-convoy-congress-workers-protested-against-the-fertilizer-crisis-heated-debate-with-the-union-agriculture-minister-satna-news-c-1-1-noi1431-3392298-2025-09-11</t>
+          <t>https://deshbandhump.com/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%B8%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%95%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/patrika-special/cash-transfer-schemes-not-game-changers-in-vidhansabha-elections-2025-in-bihar-19930337</t>
+          <t>https://www.outlookhindi.com/country/general/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-102444</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/rewa/rewa-controversy-over-the-statue-of-late-former-assembly-speaker-srinivas-tiwari-congress-issues-warning-police-stops-construction-work/articleshow/123852364.cms</t>
+          <t>https://livevns.news/National/agriculture-minister-to-hold-meeting-on-gstphp/cid17435327.htm</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/nation/vice-president-election-uprashtrapati-chunav-live-updates-cp-radhakrishnan-sudarshan-reddy-india-vs-nda-bjp-congress-livenews-9600148.html</t>
+          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.khabarfast.com/delhi-vice-president-election-live-update-voting-begins-for-the-election/56776</t>
+          <t>https://mediapassion.co.in/?p=67079</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/politics/national-vice-president-election-2025-voting-live-cp-radhakrishnan-vs-b-sudershan-reddy-key-highlights-nda-india-lb-24040604.html</t>
+          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/after-shivrajs-mama-brand-a-new-relation-has-come-in-mp-politics-brother-in-laws-entry-649844</t>
+          <t>https://upkiran.org/Government-supports-flood-hit-Jammu-and-Kashmir-farmers</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://lalluram.com/cp-radhakrishnan-or-b-sudarshan-reddy-vice-presidential-election-today-voting-will-start-at-10-am/</t>
+          <t>https://jantaserishta.com/delhi-ncr/shivraj-recalls-meeting-pm-modi-on-his-birthday-4270868</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/andhra-pradesh/super-six-election-promises-to-be-a-superhit-cm-naidu-4260033</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/anand-amul-dairy-board-of-directors-election-bjp-wins-resounding-victory-1276731-2025-09-12</t>
+          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://navyugsandesh.com/india-elects-new-vice-president-cp-radhakrishnan-wins-with-452-votes/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/MP-Cong-claims-fertiliser-shortage-protests-with-black-flags-during-Chouhan-s-Satna-visit/2906296</t>
+          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/11/will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan</t>
+          <t>https://livevns.news/National/shivraj-singh-in-pusaphp/cid17424761.htm</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/madhya-pradesh/news/opposition-attacks-state-government-over-fertilizer-crisis-in-mp-saying--farmer-2210820</t>
+          <t>https://lalluram.com/one-nation-one-election-public-representatives-of-raisen-district-submitted-a-letter-of-support-to-union-minister-shivraj/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sidhi-hain-dildar-ke-dildars-mohan-jija-ji-hmar-sidhi-singer-rakhi-dwivedi-song-viral-cm-mohan-yadav-started-smiling-on-stage-9600698.html</t>
+          <t>https://hindi.newsdanka.com/politics/even-after-years-pm-modi-remains-connected-with-the-workers/115314/amp/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/local/mp/bhopal/news/shivraj-said-if-there-is-no-crisis-of-fertilizer-then-instructions-to-collectors-135901032.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/madhya-pradesh/ladli-behna-yojana-september-28-installment-2025-live-updates-date-time-cm-mohan-yadav-releases-1250-rupees-cmladlibahna-mp-gov-in-ladli-behna-ki-28vi-kist-kab-aayegi/liveblog/123836777.cms</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://newstrack.com/amp/opinion/anand-mantralay-madhya-pradesh-article-by-senior-journalist-yogesh-mishra-541050</t>
+          <t>https://hindi.latestly.com/quickly/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/shivraj-in-maihar-after-visiting-maa-sharda-interacted-with-the-farmers-said-adopt-the-indigenous-formula-in-farming/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mp-news-politics-on-fertilizer-leader-of-opposition-accused-of-black-marketing-took-a-dig-at-cms-scooty-distribution-umang-said/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://thebetterindia.com/tags/hearing-and-speech-impairement</t>
+          <t>https://www.samacharjagat.com/news/national/modi-government-is-now-going-to-bring-this-law-against-them-shivraj-chauhan-has-made-the-announcement-324290?fatafatnews</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/punjab-deluge-shivraj-chouhan-flags-illegal-mining-behind-weak-embankments-assures-multi-term-rehab/ar-AA1LW3yd</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/articles/vice-president-election-shivraj-singh-chouhan-union-ministers-cast-votes-in-parliament</t>
+          <t>https://azadsipahi.in/09/2025/shivraj-chauhan-gave-birthday-wish-to-prime-minister-modi-the-story-of-the-first-meeting.html</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/will-discuss-fertiliser-issue-with-mp-cm-says-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/maihar-to-witness-unprecedented-development-says-shivraj-singh-chouhan-as-he-visits-sharda-mata-mandir/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-minister-in-action-to-ensure-farmers-benefit-from-gst-reduction-learn-more</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.euractiv.com/section/agriculture-food/news/eu-farm-chief-heads-to-india-as-trade-talks-intensify/</t>
+          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/2nd-phase-of-viksit-krishi-sankalp-abhiyan-from-oct-3-two-day-rabi-conference-begins-monday</t>
+          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://theshillongtimes.com/2025/09/14/viksit-krishi-sankalp-abhiyan-to-guide-production-strategies-for-rabi-season/</t>
+          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/mp-cong-claims-fertiliser-shortage-protests-with-black-flags-during-chouhans-satna-visit/2906296</t>
+          <t>https://azadsipahi.in/09/2025/agriculture-minister-shivraj-chauhan-will-meet-tomorrow-for-gst-reforms-on-agricultural-machinery.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://khabarindia.in/new-gst-rates-a-boon-for-agriculture-and-farmers-prosperity/</t>
+          <t>https://makdaiexpress24.com/if-the-state-government-approves-a-big-announcement-of-the-agriculture-minister-soybean-will-be-purchased-on-support-price/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://studycafe.in/historic-gst-reduction-brings-relief-to-agriculture-and-livelihoods-392837.html</t>
+          <t>https://sundayguardianlive.com/news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448-143406/amp/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A6-%E0%A4%9F%E0%A5%82%E0%A4%95-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A4%9D-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1M0IKR</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership?amp</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-gst-2-0-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%B9-%E0%A4%97-%E0%A4%AC%E0%A5%9C-%E0%A4%AC%E0%A4%9A%E0%A4%A4-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%97-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%A8-%E0%A4%B8-%E0%A4%89%E0%A4%AA%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%86%E0%A4%87%E0%A4%8F-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1M02Gr?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/?amp=1&amp;utm_source=AMP&amp;utm_medium=AMP_HOME&amp;utm_campaign=AMP_NAV_LINKS&amp;utm_id=KJ_AMP_PAGES</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/punjab/video/agriculture-minister-shivraj-singh-chouhan-on-the-flood-in-punjab-crops-are-completely-devastated-the-roots-have-rotted-ytvd-2325439-2025-09-08</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.icar.org.in/hi/dao-kaajala-cakaravaratai-kao-karsai-evan-sanbadadha-vaijanaana-maen-navaacaara-kae-laie</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/video/congress-mla-asked-questions-to-shivraj-singh-chauhan-regarding-fertilizer-problem-1276616-2025-09-12</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-appealed-to-the-countrymen/</t>
+          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html/amp</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/punjab/story/punjab-flood-impact-on-rabi-season-crops-due-to-heavy-silt-deposit-in-fields-swm-1274959-2025-09-09</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday?amp</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/congress-workers-and-farmers-protest-over-fertiliser-shortage-in-mauganj-swm-1274214-2025-09-08</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions?amp</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/chhattisgarh/two-day-national-agriculture-conference-to-be-held-in-new-delhi-3251517.html/amp</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/sopa-requests-government-to-impose-10-percent-duty-on-edible-oil-imports-know-why-swm-1274770-2025-09-09</t>
+          <t>https://www.socialnews.xyz/2025/09/17/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/bhupendra-hooda-statement-on-compensation-salt-sprinkled-on-wounds-of-farmers-1277159-2025-09-13</t>
+          <t>https://www.socialnews.xyz/2025/09/16/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://icar.org.in/hi/kaenadaraiya-mantarai-sarai-saivaraaja-sainha-caauhaana-kae-naetartava-maen-vaikasaita-karsai</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.gktoday.in/hindi/saras-%E0%A4%9C%E0%A5%80%E0%A4%B5%E0%A4%A8%E0%A5%8B%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%BE-2025-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A6/</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%A6%E0%A5%8B%E0%A4%AA%E0%A4%B9%E0%A4%B0-%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-541/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/FactsheetDetails.aspx?Id=149270</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/cotton-prices-%E0%A4%95%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A4%B0-%E0%A4%B6%E0%A5%82%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%AF-%E0%A4%A4-%E0%A4%B6%E0%A5%81%E0%A4%B2%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A5%87-%E0%A4%AC%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%AE%E0%A5%81%E0%A4%B6%E0%A5%8D%E0%A4%95-%E0%A4%B2/ar-AA1M6xGQ?ocid=finance-verthp-feeds</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/state/jharkhand/giridih/mla-met-the-union-minister</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://cnewsbharat.com/hindi/news/alirajpur-142655</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/9/Tanishaa-breaks-her-silence-on-her-breakup-with-Ud.html</t>
+          <t>https://www.msn.com/hi-in/news/other/pm-kisan-20th-installment-%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%9D-%E0%A4%B2-%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%A8%E0%A4%A6-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87%E0%A4%97-20500-%E0%A4%95%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%8F/ar-AA1JA7Hp</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B2-%E0%A4%B2-%E0%A4%AE-%E0%A4%A3-%E0%A4%A8%E0%A5%87-vc-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%97-%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%87%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A4%B9-56-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-fir-%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%AE-%E0%A4%A8-%E0%A4%9F%E0%A4%B0-%E0%A4%82%E0%A4%97-%E0%A4%94%E0%A4%B0/ar-AA1KyF3w?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-weather-change-again-in-himachal-heavy-rain-in-these-districts-today-1275758-2025-09-11</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-upates-weather-news-in-hindi-agriculture-latest-updates-imd-alerts-in-hindi-1276921-2025-09-13</t>
+          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weater-updates-in-hindi-imd-weather-alert-news-in-hindi-punjab-flood-news-1275199-2025-09-10</t>
+          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=maa-narmada-and-devi-ahilya-bai-have-a-deep-and-unbreakable-relationship-with-indore-panchayat-and-rural-development-minister-patel-576401</t>
+          <t>https://www.kisantak.in/amp/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=chief-secretary-to-the-chief-minister-reviewed-the-development-work-in-naxal-affected-districts-576167</t>
+          <t>https://mradubhashi.com/news.php?id=relief-from-farming-to-pocket-government-to-procure-these-5-major-kharif-crops-in-karnataka-577744</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/punjab/operation-rahat-changed-the-picture-punjab-governments-help-reached-every-village/</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-and-delhi-chief-minister-rekha-gupta-formally-inaugurate-saras-livelihood-fair/</t>
+          <t>https://makdaiexpress24.com/harda-district-congress-committee-submitted-a-memorandum-to-union-agriculture-minister-shivraj-singh-regarding-6-point-demands-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%A6%E0%A5%8B-%E0%A4%A6%E0%A4%BF%E0%A4%B5%E0%A4%B8%E0%A5%80%E0%A4%AF-%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%80%E0%A4%AF-%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-icars-impact-on-indian-farmers-bridging-the-gap-between-research-and-reality-24042637.html</t>
+          <t>https://www.kisantak.in/crops/story/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-says-pralhad-joshi-swm-1280394-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-food-reserves-are-full-but-nutrition-and-productivity-are-a-challenge-24041715.html</t>
+          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-icars-role-in-indias-food-security-addressing-nutrition-gaps-and-productivity-24041446.html</t>
+          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/madhya-pradesh/news/cm-went-to-the-fields-and-took-stock-of-the-damaged-soybean-crop-2211449</t>
+          <t>https://www.5dariyanews.com/news/467983-Shivraj-Singh-Chouhan-visits-flood-affected-border-village-of-Badyal-Brahmana-in-RS-Pura-Jammu</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/two-day-seminar-on-agriculture-in-delhiphp/cid17410728.htm</t>
+          <t>https://www.5dariyanews.com/amp/467914-Shivraj-Singh-Chouhan-chairs-key-meeting-on-GST-reforms-for-agricultural-machinery</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=organize-multipurpose-agricultural-fairs-to-promote-agriculture-based-industries-chief-minister-dr-yadav-576495</t>
+          <t>https://www.betulupdate.com/tractor-gst-price-cut-new-machinery-rates-2025/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.tarunmitra.in/national/national-agricultural-conference-rabi-abhiyan-in-pusa-today-and-tomorrow/article-105072</t>
+          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/national-agriculture-conference-preparations-for-rabi-abhiyan-2025-to-be-discussed-for-two-days</t>
+          <t>https://news24online.com/india/latest-news-trending-today-real-time-live-pm-modi-apple-iphone-17-sale-rrts-metro-corridor-rahul-gandhi-weather-update-russia-earthquake-donald-trump/635732/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/haryana-agriculture-minister-announces-indigenous-fairs-to-be-organised-for-farmers-swm-1275313-2025-09-10</t>
+          <t>https://www.business-standard.com/amp/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://sauhardsandesh.com/committed-to-welfare-farmers-and-youth-mp-trivendra-singh-rawat-met-cm-yogi/</t>
+          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/news/312467-PM-should-announce-release-of-%E2%82%B92000-crore-package-for-Ajnala-flood-victims-and-%E2%82%B960000-crore-due-to</t>
+          <t>https://www.jammulinksnews.com/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/union-minister-shobha-karandlaje-visited-the-flood-affected-areas-of-gurdaspur-promises-repair/99031/</t>
+          <t>https://www.newsdrum.in/national/chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-j-k-10479980</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/14092025/pm-kisan-yojana/</t>
+          <t>https://hindi.news18.com/amp/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/business/ladli-behna-yojana-28th-installment-date-28vi-kist-kab-aayegi-ladli-behna-yojana-news-in-hindi/4131025/</t>
+          <t>https://www.etvbharat.com/amp/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/kaimoor-cm-mahila-rojgar-yojana-get-10000-for-self-employment-24044397.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/business/ladli-behna-yojana-28th-installment-2025-released-cm-mohan-yadav-transfered-1541-crores-mp-news-business-news-in-hindi/4139320/</t>
+          <t>https://hindi.news18.com/amp/news/madhya-pradesh/raisen-mp-fake-fertilizer-conflicting-statements-shivraj-singh-chouhan-aidal-singh-kansana-shock-farmers-9650353.html</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-news-digvijaya-singh-questions-on-ladli-behna-yojana-does-this-money-come-from-their-mama-house-19941697</t>
+          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20?src=top-subnav-amp</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/madhya-pradesh/cm-mohan-yadav-distribute-scooty-to-7832-topper-students-under-free-scooty-scheme-and-transfer-money-into-girl-students-account/articleshow/123826305.cms</t>
+          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128/amp</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/pmfby-crop-insurance-scam-pradhan-mantri-fasal-bima-yojana-farmers-ntcpmm-dskc-2331965-2025-09-12</t>
+          <t>https://m-hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://postmanindia.in/chief-minister-pushkar-singh-dhami-participated-in-the-intellectuals-conference-in-kashipur/</t>
+          <t>https://www.msn.com/hi-in/news/other/mp-6-%E0%A4%AC%E0%A4%9C%E0%A5%87-6-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%96%E0%A4%AC%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%97%E0%A5%8D-%E0%A4%B5-%E0%A4%B2-%E0%A4%AF%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%9A%E0%A5%82%E0%A4%B9-%E0%A4%82-%E0%A4%95-%E0%A4%86%E0%A4%82%E0%A4%A4%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%8F-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87/ar-AA1M0HhF?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.indianewscalling.com/himachal/news/174202-news-received-from-dpro-una-focusing-dc-una-sh-and-other-events.aspx</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/himachal-pradesh/cm-sukhu-said-cbse-curriculum-decision-is-historic-9849-crores-for-education-this-year-2025-09-14</t>
+          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/uttarakhandchief-minister-enquired-about-the-health-of-journalist-mohan-bhulani/</t>
+          <t>https://navbharattimes.indiatimes.com/breaking-news-in-hindi/liveblog/58166012.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/cm-pushkar-dhami-approved-government-service-appointments-for-dependents-of-two-martyred-soldiers-uttarakhand-news-uts25091006877</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20?src=top-subnav</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/money/ladki-bahin-yojana-august-installment-1500-rupees-women-account-deposite-adititatkare-241757589852116.html</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/rajasthan/jaipur/rajasthan-news-cm-anuprati-free-coaching-scheme-apply-by-september-30-for-free-coaching-in-competitive-exams-2025-09-13</t>
+          <t>https://hindi.news18.com/amp/news/haryana/chandigarh-city-rahul-gandhi-habit-of-making-false-allegations-then-running-away-haryana-cm-nayab-singh-saini-on-vote-chori-9647747.html</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.munaadi.com/news-details/Government-is-determined-to-achieve-Sustainable-Development-Goals-%E2%80%93-Chief-Minister-Progress-report-will-prove-to-be-a-guide-in-policy-decisions-and-planning-in-the-coming-years-%E2%80%93-Finance-Minister-OP-Choudhary</t>
+          <t>https://www.etvbharat.com/amp/hi/!bharat/centre-emphases-on-crop-diversification-for-sustainable-agricultural-system-hindi-news-hin25091803739</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/basti/kajari-festival-in-harraiya-today-deputy-chief-minister-will-attend-basti-news-c-207-1-sgkp1006-143678-2025-09-12</t>
+          <t>https://www.prabhatkhabar.com/education/current-affairs/todays-current-affairs-in-hindi-for-21-september-2025</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/featured/ladli-behna-yojana-update-for-1-26-crore-mp-beneficiaries-29th-kist-will-come-in-october-rs-1500-instead-1250-in-nov-04-818057</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/featured/127-crore-ladli-behna-yojana-mp-beneficiaries-28th-kist-come-on-12-september-friday-will-get-rs-1500-instead-of-1250-in-oct-04-816791</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218/amp</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/featured/gift-t-127-crore-ladli-behna-yojana-mp-beneficiaries-will-get-28th-kist-today-will-get-rs-1250-again-450-for-gas-cylinder-04-817098</t>
+          <t>https://www.inhnews.in/News/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://delhiuptodate.com/good-news-will-come-on-12-september-28th-installment-of-ladli-bahna-yojana-will-send-rs-1250/</t>
+          <t>https://paliwalwani.com/delhi/shivraj-singh-chauhan-told-the-story-of-first-meeting-with-modi-ji</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/ladli-behna-yojana-digvijaya-singh-questions-1250-rupees-mohan-yadav-10455223</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=well-being-of-sisters-is-the-mission-of-the-government-chief-minister-dr-yadav-576159</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/sopa-requests-government-to-impose-10-percent-duty-on-edible-oil-imports-know-why-swm-1274770-2025-09-09</t>
+          <t>https://www.kisantak.in/amp/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://dakhalchhattisgarh.com/unicef-india-will-provide-technical-support-in-the-construction-of-developed-chhattisgarh/</t>
+          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/amp/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=society-should-also-join-the-government-in-pm-janman-yojana-governor-patel-575524</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html/amp</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://liveskgnews.com/uttarakhand/government-road-connectivity-health-facilities-education-tourism-in-the-state-to-strengthen-infrastructure-like-tourism-drinking-water-and-energy/</t>
+          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html/amp</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://newsheight.com/big-breaking-chief-minister-pushkar-singh-dhami-to-inspect-doon-hospital-by-interacting-with-patients-directly-to-the-status-of-their-health-services/</t>
+          <t>https://jantaserishta.com/local/jammu-and-kashmir/on-the-instructions-of-pm-modi-the-central-government-became-active-in-helping-the-flood-affected-farmers-4275101</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/former-cm-digvijay-singh-raised-serious-questions-on-amount-of-ladli-behna-yojana-650416</t>
+          <t>https://www.khabarwala24.com/national/raisen-mein-shivraj-singh-ne-ek-rashtr-ek-chunav-ke-liye-janpratinidhiyon-ko-dilai-shapath/103967/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://hillspost.com/%E0%A4%9C%E0%A4%82%E0%A4%97%E0%A4%B2%E0%A5%80-%E0%A4%9C%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%85%E0%A4%AC-%E0%A4%A8%E0%A4%B9%E0%A5%80%E0%A4%82-%E0%A4%95%E0%A4%B0-%E0%A4%AA%E0%A4%BE%E0%A4%8F/56842/</t>
+          <t>https://www.saahassamachar.in/shivraj-issues-stern-message-to-farmers-on-their-plight-issues-strict-instructions-to-sehore-collector</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=bihar-has-picked-up-the-pace-of-development-nda-government-will-be-formed-again-anurag-singh-thakur-576210</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://devbhoomimedia.com/cm-dhami-in-kashipur-sammelan/</t>
+          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/jitu-patwari-slams-cm-mohan-yadav-on-farmers-issue-says-working-for-reels-photos-1277266-2025-09-13</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630162-strategizing-himalayan-agriculture-calls-for-specialized-policies-and-education</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/politics/story/punjab-aap-balginder-singh-dhillon-agriculture-reform-cold-storage-food-processing-prv-1276983-2025-09-13</t>
+          <t>https://www.ptinews.com/editor-detail/centre-to-procure-green-gram--black-gram--sunflower-from-karnataka--union-minister-pralhad-joshi/2933070</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/rewari-cm-urban-housing-scheme-consent-register-by-september-10/</t>
+          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/cong-threatens-nyay-adhikar-yatra-over-farmer-issues/articleshow/123752203.cms</t>
+          <t>https://www.knskashmir.com/centre-always-stands-by-people-of-jandk-in-crisis--union-minister-198242</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/50-days-of-silence-oppn-question-former-vp-dhankhars-absence-on-polling-day-3718730</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/punjab-floods-unwell-cm-bhagwant-mann-welcomes-pm-narendra-modis-visit-toll-51/articleshow/123777869.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/after-aerial-survey-of-landslide-hit-himachal-pm-to-visit-punjab-tomorrow/articleshow/123752293.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/10/pm-modi-to-inaugurate-purnea-airport-launch-rs-45000-crore-projects-in-bihar-on-sep-15/</t>
+          <t>https://www.indiatodayne.in/amp/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://thepublicworld.com/archives/111332</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/mds18-ka-joshi-crops.amp.html</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.samaykhabar.com/2025/09/blog-post_9.html</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/midday-news-545/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/aap-rajya-sabha-mp-sanjay-singh-house-arrest-in-srinagar-jammu-kashmir-aam-aadmi-party-mla-mehraj-malik-1276194-2025-09-11</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/haryana/rohtak/video-on-the-75th-foundation-day-of-saini-sanstha-in-rohtak-chief-minister-naib-singh-laid-the-foundation-stone-of-the-new-building-of-saini-public-school-2025-09-14-1757841061</t>
+          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=social-justice-minister-kushwaha-gave-instructions-to-investigate-de-addiction-centres-576163</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-emphasises-crop-diversification-for-a-sustainable-agricultural-system-enn25091803601</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://livevns.news/state/uttrakhand/focus-on-law-and-order-and-public-facilities-cmphp/cid17376202.htm</t>
+          <t>https://thekashmirhorizon.com/2025/09/20/union-agri-minister-chauhan-pledges-full-support-to-jk-farmers/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-flood-health-infrastructure-suffers-loss-of-rs-780-crore-seeks-rs-20-000-crore-aid-from-centre</t>
+          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/others/triple-engine-government-has-failed-in-delhi-there-is-garbage-everywhere-ankush-narang-4260747</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634626-central-approval-boosts-karnataka-farmers-with-price-support-scheme?amp</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.babushahi.com/full-news.php?id=210415</t>
+          <t>https://aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://news24online.com/india/vice-president-election-2025-india-voting-live-updates-nda-c-p-radhakrishnan-faces-india-bloc-sudarshan-reddy-jagdeep-dhankar-resignation-bjp-congress-opposition/629007/</t>
+          <t>http://www.uniindia.com/photoes/638734.html</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278562357/rajya-sabha-deputy-chairman-casts-vote-to-elect-15th-vice-president</t>
+          <t>https://www.ptinews.com/editor-detail/Bhagwant-Mann-assures-to-raise-arhtiyas-demands-with-Centre/2931607</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278562307/vice-president-election-union-minister-rajnath-singh-nda-mps-cast-votes-in-parliament</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-politics-news-bjp-policy-one-family-one-post-rule-enforced-leader-sons-face-restraint-2025-09-13</t>
+          <t>https://statetimes.in/jda-cracks-down-on-unauthorised-construction-at-domana-nardani/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/bihar-election-2025-nda-strategy-bjp-focus-obc-youth-women-voters-article-152792919</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=rss-has-a-deep-impact-on-top-leaders-including-pm-modi-575599</t>
+          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/tamil-nadu/vice-presidential-election-food-stalls-crackers-and-prayers-in-radhakrishnans-hometown-4256252</t>
+          <t>https://www.thekashmirmonitor.net/pm-stands-by-people-of-jk-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/sanjay-singh-accuses-parties-abstaining-from-voting-in-vice-president-election-of-supporting-bjp-4256868</t>
+          <t>https://m.sakshipost.com/amp/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/more-than-700-members-of-parliament-exercised-their-right-to-vote-in-the-election-for-the-next-vice-president-4256928</t>
+          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/delhi-news/vice-president-election-so-far-67-percent-voting-hema/cid17382351.htm</t>
+          <t>https://www.thehawk.in/news/economy-and-business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://dainikdehat.com/india/vice-presidential-election-prime-minister-modi-congratulates-cp-radhakrishnan/</t>
+          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/hi/!state/pachmarhi-shivraj-singh-chauhan-reached-mahadev-temple-click-monkey-photo-posted-on-social-media-madhya-pradesh-news-mps25091400387</t>
+          <t>https://www.newsdrum.in/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-10478477</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AA%E0%A4%B0-%E0%A4%AE%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%A8-%E0%A4%9C-%E0%A4%B2-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%98%E0%A4%9F-%E0%A4%AF-%E0%A4%96%E0%A4%B0%E0%A4%AA%E0%A4%A4%E0%A4%B5-%E0%A4%B0-%E0%A4%A8-%E0%A4%B6%E0%A4%95-%E0%A4%95-%E0%A4%AC-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0-%E0%A4%95-%E0%A4%97%E0%A4%88/ar-AA1KRKhB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/pachmarhi-shivraj-singh-chauhan-reached-mahadev-temple-click-monkey-photo-posted-on-social-media-madhya-pradesh-news-mps25091400387</t>
+          <t>https://www.thehawk.in/news/india/jitu-patwari-plays-down-internal-rift-claims-in-madhya-pradesh-congress</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/bhopal-there-is-shortage-of-fertilizers-in-the-state-the-leader-of-opposition-accused-of-black-marketing-sa-2025-09-11</t>
+          <t>https://www.5dariyanews.com/amp/467664-National-Conference-on-Agriculture-%E2%80%93-Rabi-Campaign-2025-concludes-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-fatal-car-container-collision-on-bhopal-vip-road-speeding-driver-dies-24040694.html</t>
+          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/amp/bhopal-news/mp-news-pwd-minister-called-90-degree-bridge-correct-high-court-responded-then-contractors-should-be-given-medals-again-19936522</t>
+          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%91%E0%A4%AA%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%B8-%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%B0-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AA-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%81%E0%A4%9F%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%87%E0%A4%95-%E0%A4%A6-%E0%A4%8F-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1Lb4oe</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/bhopal-railway-employee-used-to-force-for-unnatural-relation-by-posing-as-transgender-19929438</t>
+          <t>https://www.editorji.com/amp/business-news/gst-reduction-on-farm-equipment-benefits-farmers-1758261712044</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/news/cm-forgot-to-announce-restart-of-cpa-135875096.html</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/people-of-chhatarpur-of-mp-told-the-story-of-nepal-19934402</t>
+          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/indore-news/indore-to-mumbai-journey-is-now-faster-tejas-special-train-frequency-increased-see-schedule-19932392</t>
+          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision?amp</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/madhya-pradesh/news/geeta-bhawan-is-being-built-in-every-urban-body-of-madhya-pradesh-2212632?amp</t>
+          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/bhopal-strict-action-against-love-jihad-accused-in-bhopal-bhopal--4261176</t>
+          <t>https://www.devdiscourse.com/article/business/3633463-relief-and-recovery-government-support-for-jks-rural-communities?amp</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/bhopal-weather-department-expressed-the-possibility-of-possible-rain-bhopal--4259526</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/bhopal-police-busted-a-gang-of-robbers-4260342</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rate-cut-agri-minister-to-meet-farm-equipment-industry-on-sep-19-125091800798_1.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/bhopal-krishna-gaur-called-education-the-basis-of-development-bhopal--4259446</t>
+          <t>https://www.wionews.com/business-economy/goods-and-services-tax-reforms-how-cheaper-will-tractors-get-minister-reveals-1758282747902/amp</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/high-speed-car-collides-with-motorcycle-35-year-old-dies-brother-seriously-injured-4259892</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630162-strategizing-himalayan-agriculture-calls-for-specialized-policies-and-education?amp</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-heavy-rain-alert-in-up-bihar-uttarakhand-also-receive-rain-1276357-2025-09-12</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/politics/bjp-president-sanjay-joshi-modi-bhagwat</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rsss-acceptance-grows-under-chief-mohan-bhagwats-leadership/articleshow/123836861.cms</t>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/c-p-radhakrishnan-to-be-the-15th-vice-president-of-india/</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.babushahi.com/view-news.php?id=210415&amp;headline=Vice-Presidential-Election:-Food-stalls,-crackers,-prayers-for-Radhakrishnan-in-his-hometown</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630300-punjabs-plea-for-aid-restoring-flood-damaged-farmlands?amp</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278562987/choice-of-candidates-is-reminder-of-who-cares-for-country-dmk-saravanan-annadurai-on-vp-elections</t>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/13/jyotiraditya-scindia-urges-male-family-members-of-women-in-local-panchayat-bodies-not-to-interfere-in-official-works/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=jyotiraditya-scindia-urges-male-family-members-of-women-in-local-panchayat-bodies-not-to-interfere-in-official-works</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448?amp=1</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/13/viksit-krishi-sankalp-abhiyan-to-guide-production-strategies-for-rabi-season/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=viksit-krishi-sankalp-abhiyan-to-guide-production-strategies-for-rabi-season</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/08/punjab-minister-seeks-help-of-pm-modi-for-flood-victims/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=punjab-minister-seeks-help-of-pm-modi-for-flood-victims</t>
+          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation/amp-11758032543012.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/opinion/why-modi-shah-and-rss-are-locking-horns-over-naddas-successor/865606/</t>
+          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/ujjain-news/mp-news-farmers-union-to-hold-major-show-of-strength-in-ujjain-against-land-pooling-19940062</t>
+          <t>https://www.lokmattimes.com/business/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/amp/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://newstrack.com/amp/india/bjp-national-president-can-be-announced-anytime-these-names-are-leading-540955</t>
+          <t>https://menafn.com/1110088234/Agriculture-Minister-Meets-Industry-Associations-On-Recent-GST-Cuts-For-Farm-Machinery</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/bjp-national-president-announced-soon-obstacle-removed/index.php</t>
+          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://theruralpress.in/2025/09/13/what-will-happen-in-1250-rupees/</t>
+          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://bhilwaratimes.in/2025/31039/14/09/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.gandivlive.com/bjp-national-president-announced-soon-these-4-ministers-join-the-race/</t>
+          <t>https://www.latestly.com/agency-news/india-news-will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-7119481.html/amp</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://upuklive.com/national/these-4-legendary-ministers-will-be-announced-by-bjps-new-national-president-soon-22009.html</t>
+          <t>https://www.lokmattimes.com/business/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister-1/amp/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/vice-president-elections-voting-results-reactions-live-updates-september-9-2025/article70028318.ece</t>
+          <t>https://www.socialnews.xyz/2025/09/19/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2025/09/09/mud-bridges-night-vigils-how-punjab-is-surviving-its-flood-crisis</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/banka-bihar-election-2025-no-leader-achieved-three-house-record-in-banka-24045407.html</t>
+          <t>https://www.latestly.com/agency-news/india-news-union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative-7122123.html/amp</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/kamalnath-digvijay-singh-met-in-delhi-differences-dismissed-political-activities-intensify-bhopal-in-mp/2918872</t>
+          <t>https://newsable.asianetnews.com/amp/business/farmers-to-gain-as-agri-minister-pushes-gst-cut-benefit-for-tractors-equipment-articleshow-lipd50k</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/23-cm-in-bihar-politics-shri-krishna-singh-lalu-yadav-rabri-devi-nitish-kumar-complet-full-tenure-hindi-news-brn25091203684</t>
+          <t>https://vocaltv.in/national/agriculture-minister-to-hold-meeting-on-gstphp/cid17435350.htm</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/bihar-election-2025-india-many-political-parties-that-gave-prime-minister-and-chief-minister-now-oblivion-hindi-news-brn25091104892</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/mp-bjp-cracks-down-on-nepotism-relatives-of-leaders-resign-sons-also-denied-tickets/articleshow/123847330.cms</t>
+          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/?amp</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/shimla-pm-modis-himachal-pradesh-visit-aerial-survey-and-relief-directives-tomorrow-24039661.html</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/politics/bjp-leaders-in-manipur-join-congress/articleshow/123779144.cms</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/dmk-is-not-a-movement-that-disrupts-public-life-chief-minister-stalin/868170/?amp</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://newsheight.com/big-breaking-teachers-of-uttarakhand-announced-the-battle-of-cross-cross/</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/index.php</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/central-minister-shivraj-vksa-plan-setback-damu-employees-threaten-boycott-1277015-2025-09-13</t>
+          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/nepal-border-uttarakhand-security-cmphp/cid17384963.htm</t>
+          <t>https://www.aajsamaaj.com/agriculture-minister-asks-centre-to-help-in-removing-sand-from-fields-and-providing-wheat-seeds/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://chhattisgarhkiawaaz.com/50688</t>
+          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278562262/met-fodder-scam-convict-and-talks-about-morality-giriraj-singh-slams-vp-candidate-sudershan-reddy</t>
+          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/amp/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/madhya-pradesh-meet-of-commissioners-collectors-in-bhopal-after-dussehra</t>
+          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html/amp</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
+          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.timesbull.com/business/gst-2-0-farmers-to-get-direct-benefit-from-new-gst-know-how-much-they-will-save-601472.html</t>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/gorakhpur/bansgaon/news/panchayat-committee-meeting-in-bansgaon-area-135869586.html</t>
+          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://chhapratoday.com/saran/several-proposals-were-passed-in-the-meeting-of-the-20-point-program-implementation-committee-in-riwilganj-block/</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://webvarta.com/states/uttar-pradesh/kushinagar-journalists-six-demands-cm-yogi/</t>
+          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/be-magnanimous-punjab-minister-asks-pm-for-rs-25000cr-flood-relief/articleshow/123766832.cms</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://mobilenews24x7.com/2025/national-news/punjab-minister-seeks-help-of-pm-modi-for-flood-victims/</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/statement-by-a-senior-congress-leader-from-madhya-pradesh-2210896</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/mp/gwalior/mp-gwa-hmu-mat-latest-gwalior-news-030503-2019409-nor.html</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-congress-opposition-leader-umang-singhar-big-statement-on-nepal-protest-local18-9608793.html</t>
+          <t>https://www.etvbharat.com/hi/!bharat/agriculture-roadmap-prepared-according-to-geographical-and-climatic-conditions-of-states-hindi-news-hin25091703030</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A4%AE%E0%A4%B2%E0%A4%A8-%E0%A4%A5-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%97-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AE%E0%A4%9A%E0%A5%87-%E0%A4%B8-%E0%A4%AF-%E0%A4%B8-%E0%A4%AC%E0%A4%B5-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%AC-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%B8-%E0%A4%B8-%E0%A4%B2-%E0%A4%B5%E0%A4%9F-%E0%A4%95-%E0%A4%8F%E0%A4%82%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%82%E0%A4%A7-%E0%A4%AF-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%A6-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC-%E0%A4%A4/ar-AA1LfczO</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.starsamachar.com/aaj-ki-surkhiyan-patakhe-tariff-dhamki-tax-chori</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/madhya-pradesh/cm-mohan-yadav-says-government-is-committed-to-giving-27-percent-obc-reservation-3012228/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0%E0%A4%AC-%E0%A4%95-%E0%A4%A8%E0%A5%8D%E0%A4%AB%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%B8-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-250-%E0%A4%B2-%E0%A4%96-%E0%A4%AE-%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%AC-%E0%A4%9C-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B0%E0%A4%96-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF/ar-AA1MEprL</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/amp/madhyapardesh/what-happened-in-nepal-we-will-never-let-it-happen-in-india-rahul-gandhi-is-fighting-to-protect-voting-rights-patwari-267712</t>
+          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/punjab/chandigarh-pm-modi-punjab-visit-pm-modi-will-come-to-punjab-tomorrow-aap-ministers-demanded-a-special-package-of-20-thousand-crores-from-the-prime-minister-24040090.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://politalks.news/breaking-news-and-will-continue-to-fight-digvijay-singh-gave-a-big-statement-after-meeting-kamal-nath</t>
+          <t>https://hindi.theprint.in/india/economy/3-7-percent-growth-in-agriculture-sector-in-first-quarter-is-the-highest-in-the-world-chauhan/869080/?noamp=mobile&amp;amp</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/etawah-news/shivpal-singh-yadav-said-many-assembly-tickets-finalized-by-akhilesh-yadav-19942676?cb_rec=djRfMl8xXzhfN18wXzFfMF8</t>
+          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/amp/news/madhya-pradesh/bhopal-mp-congress-opposition-leader-umang-singhar-said-there-will-be-soon-takhtapalat-in-india-local18-9608793.html</t>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=cm-mohan-yadavs-retort-on-umang-singhars-statement-575921</t>
+          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/west-bengal-bjp-leader-arjun-singh-controversial-statement-on-nepal-sparks-row-with-tmc-1351804.html</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=india-is-alert-on-nepal-crisis-pm-modis-big-appeal-575597</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://npg.news/amp/madhya-pradesh/mp-mein-khaad-par-vivaad-kaalaabaajaaree-ke-aarop-se-garamaee-pradesh-kee-siyaasat-madhya-pradesh-politics-news-1295165</t>
+          <t>https://www.5dariyanews.com/hindi/news/312967-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://npg.news/politics/obch-aarakshan-par-chm-ka-bada-bayaan-27-pheesadee-kota-dene-ke-lie-sarakaar-taiyaar-1295388</t>
+          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/bhupendra-hooda-statement-on-compensation-salt-sprinkled-on-wounds-of-farmers-1277159-2025-09-13</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=%E2%80%9Cit-is-disappointing-when-your-rights-are-taken-away%E2%80%9D-%E2%80%93-iyer%E2%80%99s-statement-on-being-ruled-out-of-asia-cup-goes-viral-575265</t>
+          <t>https://jantaserishta.com/amp/national/agriculture-minister-raised-the-issue-at-the-national-conference-on-agriculture-rabi-campaign-4273805</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=ban-on-firecrackers-big-statement-by-the-chief-justice-questions-raised-on-the-splendor-of-diwali-576132</t>
+          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=conspiracy-to-reduce-the-number-of-hindus-in-the-world-monarchy-should-be-established-in-nepal-dhirendra-shastris-statement-576469</t>
+          <t>https://statetimes.in/amp/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=netanyahu-approves-e1-settlement-project-in-west-bank-says-palestinian-state-will-not-be-formed-576217</t>
+          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=trumps-tone-changed-gave-good-news-about-india-575598</t>
+          <t>https://www.etvbharat.com/hi/!bharat/centre-emphases-on-crop-diversification-for-sustainable-agricultural-system-hindi-news-hin25091803739</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=les-tarifs-douaniers-am%C3%A9ricains-sur-le-commerce-p%C3%A9trolier-entre-linde-et-la-russie-zelenskyy-apporte-son-soutien-575209</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/uttar-pradesh/moradabad/moradabad-dr-st-hasan-ind-vs-pak-controversy/article-105656</t>
+          <t>https://www.msn.com/hi-in/news/other/procurement-%E0%A4%AE%E0%A5%82%E0%A4%82%E0%A4%97%E0%A4%AB%E0%A4%B2-%E0%A4%94%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%AC-%E0%A4%A8-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%85%E0%A4%B5%E0%A4%A7-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%81%E0%A4%85%E0%A4%B0-%E0%A4%AE%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1%E0%A4%BC%E0%A4%A6-%E0%A4%95-%E0%A4%B9-%E0%A4%97-100-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%96%E0%A4%B0-%E0%A4%A6/ar-AA1yKSox?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=gujarat-explosion-in-amuls-biogas-plant-7-employees-injured-576431</t>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/automobile/october-2025-will-launch-the-new-hyundai-venue-smart-features/article-106343</t>
+          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/agriculture/kitchen-garden-tips-grive-green-chilli-in-kitchen-garden-get/article-105732</t>
+          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/automobile/hondas-bike-and-scooter-after-gst-2025-reforms-now-big/article-106328</t>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=congress-vote-chor-gaddi-chhod-conference-in-bilaspur-signature-campaign-also-started-575405</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=on-the-charge-of-molestation-a-woman-chased-and-beat-a-pradhan-candidate-in-gorakhpur-on-the-middle-of-the-road-a-crowd-of-passersby-gathered-575941</t>
+          <t>https://eng.ruralvoice.in/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=kanpurs-dreadful-case-brother-came-in-sisters-dream-and-told-the-truth-about-the-murder-sensation-as-soon-as-it-was-revealed-575717</t>
+          <t>https://www.prameyanews.com/news-post/nation/two-day-national-agriculture-conference-begins-to-strategise-for-rabi-season-2025</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/noida-agritech-startup-ai-platforms-crop-carbon-tracking-125091000434_1.html</t>
+          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/build-bridges-of-harmony-between-hills-and-valley-prime-minister-modi-in-manipur/ar-AA1Mui9x</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nitish-launches-451-development-projects-worth-rs-1-343-crore-in-bhojpur-buxar/ar-AA1M1mx0</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/telangana-cm-revanth-reddy-appeals-railways-for-rapid-road-and-rail-connectivity-between-hyderabad-and-amaravati20250912071537-66116/</t>
+          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-government-approves-146-17-crore-for-development-projects-201757684998036.html</t>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/haryana/haryana-cm-nayab-singh-saini-takes-serious-note-of-delays-in-projects-orders-detailed-review-2025-09-09-1161589</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/politics/controversy-over-delhi-cm-rekha-gupta-husband-presence-in-official-meeting-sanjay-singh-said-rekha-gupta-is-cm-her-husband-is-super-cm/articleshow/123769595.cms</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.munaadi.com/news-details/Chief-Secretary-to-the-Chief-Minister-reviewed-the-development-works-in-Naxal-affected-districts-emphasis-on-effective-implementation-of-development-schemes:-Instructions-to-ensure-reach-of-schemes-to-every-village</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/bihar/munger/story-foundation-laid-for-pcc-road-and-drainage-in-khargpur-by-jd-u-mla-rajiv-kumar-singh-201757796743607.html</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://uttarakhanduday.com/uttarakhand-news/uttarakhand-chief-minister-dhami-approves-various-development-schemes-of-146-19-crore/</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://mukhyadhara.in/the-chief-minister-provided-financial-approval-for-various-development-schemes-worth-rs-146-19-crore/</t>
+          <t>https://mediapassion.co.in/?p=66795</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/states/uttarakhand/uttarakhand-cm-pushkar-singh-dhami-approved-an-amount-of-rs-14619-crore-for-development-projects-10453573</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/others/delhi-cm-reviews-development-projects-in-chandni-chowk-lok-sabha-constituency-4260731</t>
+          <t>https://www.kisantak.in/amp/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://topkikhabar.com/kashipur-cm-pushkar-dhami-participated-in-the-enlightened-conference-and-gave-information-about-the-achievements-of-the-government-and-development-schemes-from-mass-media/</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gave-financial-approval-for-various-development-schemes-worth-rs-136-68-crore-for-champawat-dehradun-bageshwar-and-tehri/</t>
+          <t>https://www.msn.com/hi-in/news/other/pusa-fourth-convocation-bihar-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B5-%E0%A4%9A-%E0%A4%B0-%E0%A4%94%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%95-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%B5-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9/ar-AA1IMIBJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/chhattisgarh/cm-sai-visited-korba-held-an-important-meeting-regarding-tribal-welfare-and-tourism-development-several-schemes-were-discussed-in-detail-52-816285</t>
+          <t>https://www.newspuran.com/blogs/mismanagement-of-fertilizer-without-assessment</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/gurugram-news-chief-minister-takes-strict-action-on-irregularities-in-basai-stp-project-orders-to-chargesheet-chief-engineer/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/delhi-ncr/delhi/delhi-cms-shalimar-bagh-area-received-hotline-maintenance-van-without/article-105995</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/delhi-ncr/chief-minister-reviews-development-plans-of-south-delhi-4262464</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/evening-news-513/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://hillvani.com/100-crore-amount-approved-by-chief-minister-for-various-development-schemes/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/punjab-floods-minister-balbir-singh-highlights-rs-780-cr-health-infra-loss-seeks-urgent-aid-from-centre/articleshow/123777370.cms</t>
+          <t>https://www.patrika.com/bhopal-news/khategaon-mahila-bal-vikas-supervisor-amita-jat-and-project-officer-pranay-maheshwar-dispute-19950165</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://jagratilahar.com/hindi/health/120505/Dr-balbir-singh-health-minister-bhagwant-mann-cabinet-</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B2-%E0%A4%B2-%E0%A4%AE-%E0%A4%A3-%E0%A4%A8%E0%A5%87-vc-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%97-%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%87%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A4%B9-56-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-fir-%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%AE-%E0%A4%A8-%E0%A4%9F%E0%A4%B0-%E0%A4%82%E0%A4%97-%E0%A4%94%E0%A4%B0/ar-AA1KyF3w?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://asarnewz.com/?p=55225</t>
+          <t>https://www.tractorjunction.com/agriculture-news/krishi-mela-rabi-2025-to-be-held-in-hisar-on-september-21-22/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/himachal-pradesh/himachal-pradesh-cm-sukhvinder-singh-sukhu-met-16th-finance-commission-chairman-pangariya-to-discuss-state-financial-situation-ann-3011199</t>
+          <t>https://www.khabarwala24.com/national/kendriya-mantri-shivraj-ne-kisanon-ke-soybean-ki-fasal-kharab-hone-ki-shikayat-par-adhikari-ko-survey-ka-diya-nirdesh/103594/</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/punjab-government-will-give-compensation-to-flood-victims-in-45-days-cm-bhagwant-singh-mann-gave-strict-orders/</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%85%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%A8-%E0%A4%95%E0%A5%81%E0%A4%AE-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B5-%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%AF-%E0%A4%AA%E0%A5%88%E0%A4%95%E0%A5%87%E0%A4%9C-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97-%E0%A4%95/ar-AA1LXS5F</t>
+          <t>https://www.kisantak.in/amp/news/trending/story/bijnor-farmer-electrocuted-in-field-villagers-block-highway-with-body-1280227-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/education/news/story/india-literacy-milestone-himachal-joins-fully-literate-states-education-amnr-dskc-2329843-2025-09-10</t>
+          <t>https://www.msn.com/hi-in/news/other/paddy-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B2-%E0%A4%A8%E0%A5%8D%E0%A4%9A-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE-%E0%A4%8F%E0%A4%A1-%E0%A4%9F%E0%A5%87%E0%A4%A1-%E0%A4%A7-%E0%A4%A8-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%97-30-%E0%A4%A4%E0%A4%95-%E0%A4%87%E0%A4%9C-%E0%A4%AB-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1E8rJq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/hi/!state/851-crore-contract-approved-in-the-meeting-of-hppc-and-hpwpc-haryana-news-hrs25091205183</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers?amp</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/sukhu-met-the-chairman-of-the-16th-finance-commission-urged-to-continue-rdg/amp/?utm=relatedarticles</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/business/business-news/new-gst-rates-list-2025-on-cars-bikes-mobile-phones-tv-paper-gold-medicines-clothes-solar-insurance-food-items-check-education-electronics-healthcare-automobile-agriculture-daily-essentials-sectors-live-updates/liveblog/123689422.cms</t>
+          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/himachal-pradesh/kangra-hh-dalai-lama-letter-to-cmphp/cid17389225.htm</t>
+          <t>https://www.thehawk.in/news/economy-and-business/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/pm-modi-aerial-survey-of-disaster-affected-areas-of-himachal-19930789</t>
+          <t>https://hindi.theprint.in/india/economy/3-7-percent-growth-in-agriculture-sector-in-first-quarter-is-the-highest-in-the-world-chauhan/869080/</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://www.jagmarg.com/punjab/punjab-floods-health-infrastructure-worth-780-crore-rupees-damaged-in-the-state</t>
+          <t>https://www.amarujala.com/haryana/chandigarh-haryana/haryana-is-making-a-big-contribution-in-food-security-shyam-singh-rana-chandigarh-haryana-news-c-16-1-pkl1095-820762-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/punjab-cm-bhagwant-mann-cabinet-meeting-regarding-floods-relief-work-take-big-decision-know-full-details-1276770-2025-09-12</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/blog/india/floods-disrupt-developing-india-b668/</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://asarnewz.com/?p=55250</t>
+          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/hp-cm-sukhu-demanded-rs-10-thousand-crore-annual-rdg-for-himachal-from-finance-commission-chairman-dr-arvind-panagariya-himachal-pradesh-news-hps25091105987</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13763</t>
+          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://shikharhimalaya.com/dehradun-mlas-met-the-chief-minister-regarding-regional-demands/</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://gkmnews.in/cm-gave-financial-approval-to-various-development-schemes-of-146-19-crore/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A4%BC-%E0%A4%98-%E0%A4%9F-%E0%A4%B2-700-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A5%82%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-150-%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-158-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2-%E0%A4%B8%E0%A4%AC%E0%A5%8D%E0%A4%B8-%E0%A4%A1/ar-AA1MCt9k</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1185809</t>
+          <t>https://www.bhaskar.com/amp/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://uttarakhandcitynews.com/many-public-representatives-including-mlas/</t>
+          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-pm-modi-will-visit-uttarakhand-on-september-11-will-do-an-aerial-survey-of-the-disaster-affected-areas-and-will-also-hold-a-review-meeting/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://newsheight.com/anand-vardhan-chief-secretary-of-construction-to-be-done-to-organize-big-breaking-2027-kumbh-mela-in-a-divine-and-grand-manner/</t>
+          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/chief-minister-sukhwinder-singh-sukhu-demand-for-special-fund-for-himachal-from/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/22/Uttarakhand-UKSSSC-Exam-Viral.html</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/punjab/pm-modi-released-rs-1600-crore-amount-for-punjab-flood-victims/</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/12/punjab-governments-focus-on-medical-aid-and-restoration-of-infrastructure/</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/andhra-government-started-work-on-model-shield-for-farmers-from-american-tariffs-1277038-2025-09-13</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://hindikhabar.com/punjab-cm-bhagwant-man-compensation-flood-victims-45-days/</t>
+          <t>https://www.kisantak.in/amp/knowledge/story/international-rice-conference-to-be-held-at-bharat-mandapam-october-30-and-31-1280579-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/14/punjab-government-launches-massive-operation/</t>
+          <t>https://www.kisantak.in/amp/latest-news/story/scientific-banana-ripening-facility-in-north-goa-to-boost-trade-swm-1280684-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/12/every-flood-victim-will-get-compensation-cm-mann/</t>
+          <t>https://www.msn.com/en-in/money/topstories/gst-reforms-to-inject-rs-2-lakh-cr-into-economy-boost-demand-across-sectors/ar-AA1MPDtb?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/punjab/high-hopes-of-flood-relief-package-on-pm-modis-punjab-visit/</t>
+          <t>https://smestreet.in/sectors/agriculture/gst-on-agricultural-machinery-tractors-tillers-harvesters-slashed-to-5-from-sept-22-10479641</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/chouhan-urges-buying-swadeshi-products/33399020250909</t>
+          <t>https://www.kisantak.in/amp/latest-news/story/punjab-cm-bhagwant-mann-announces-price-cuts-for-verka-s-milk-and-cooperative-products-swm-1280239-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/hooda-flays-govt-over-crop-compensation/articleshow/123855508.cms</t>
+          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://theprint.in/opinion/punjab-floods-test-for-parties-must-act-together-fast/2738071/</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-ministrys-special-campaign-5-0-will-start-from-october-2-work-will-be-done-on-e-waste-and-complaints/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/pm-modi-to-visit-punjab-on-september-9-to-review-flood-situation/</t>
+          <t>https://hindi.krishijagran.com/news/north-india-heavy-rainfall-update-himachal-uttarakhand-cloudburst-landslide-dehradun-deaths-delhi-up-bihar-maharashtra-weather-alert-2025/</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://tennews.in/pm-modi-to-inaugurate-purnea-airport-launch-rs-45000-crore-projects-in-bihar-on-sep-15/</t>
+          <t>https://jantaserishta.com/business/indian-agriculture-will-achieve-top-global-growth-of-37-in-q1-2025-26-4269188</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.bizzbuzz.news/politics/ab-tak-chappan-gabbar-singh-tax-gone-but-1371506</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A4%E0%A5%87%E0%A4%9C-%E0%A4%AF-%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-75-%E0%A4%9C-%E0%A4%B2-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%B5-%E0%A4%95%E0%A4%B8-%E0%A4%A4-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8/ar-AA1MJ8ti</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/punjab-floods-pm-conducts-aerial-survey-meets-affected-people-in-gurdaspur-10065855</t>
+          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/bajaj-chetak-scooter-to-range-rover-know-what-ministers-owns-in-the-modi-government/articleshow/123845477.cms</t>
+          <t>https://samacharsamrat.com/agriculture-ministry-to-inform-farmers-about-the-benefits-of-gst-rate-revision/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/punjab-news/pm-modi-punjab-visit/</t>
+          <t>https://jantaserishta.com/national/agriculture-minister-raised-the-issue-at-the-national-conference-on-agriculture-rabi-campaign-4273805</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/politics-on-pm-narendra-modi-punjab-visit-on-sep-9-mp-sanjay-singh-2025-09-08</t>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html/amp</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/nation/political-signal-ravneet-bittu-will-accompany-pm-modi-during-his-visit-to-flood-affected-areas/</t>
+          <t>https://annews.co.in/15476/</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/pm-modi-will-visit-himachal-and-punjab-tomorrow-will-take-stock-of-flood-situation-19928622</t>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/pm-modi-will-visit-punjab-on-tuesday-to-review-the-flood-situation/</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/punjab/kapurthala-bjp-to-celebrate-modis-birthday-by-helping-flood-victims-in-kapurthala-punjab-24043648.html</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/pm-modi-visit-punjab-and-himachal-pradesh-to-review-flood-situation-hindi-news-hin25090804985</t>
+          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/national-news/pm-kisan-samman-nidhi-yojana-e-kyc-land-varification-aadhar-linking-must-be-done-for-21st-installment-19929843</t>
+          <t>https://shekhawatilive.com/agriculture/gst-cut-tractors-farm-equipment-cheaper-farmers-benefit.html/</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://boltahindustan.in/trending-stories/thousands-of-people-protest-on-streets-of-assam-for-schedule-tribes-st-status/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198/amp</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/haryana/chandigarh-haryana/video-three-trucks-of-relief-material-left-for-punjab-from-bjp-state-office-panchkamal-2025-09-09</t>
+          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://jagratilahar.com/hindi/politics/120500/Pm-must-show-generosity-in-extending-aid-to-flood-hit-punjab-barinder-kumar-goyal</t>
+          <t>https://www.tractorjunction.com/tractor-news/auspicious-time-to-buy-a-tractor-from-navratri-to-diwali/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://newstrack.com/punjab/punjab-flood-crisis-2025-modi-action-vs-missing-leaders-539599</t>
+          <t>https://www.tractorjunction.com/tractor-news/top-3-john-deere-tractor-models-in-india-price-and-features/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/vice-president-election-2025-voting-and-results-live-updates-who-wins-uprashtrapati-chunav-nda-cp-radhakrishnan-india-sudershan-reddy/liveblog/123776712.cms</t>
+          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/modi-announced-a-relief-package-of-rs-1200-crore-for-the-disaster-hit-areas-of-uttarakhand/867485/?amp</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/news/pm-modi-will-visit-flood-affected-states/503599.html</t>
+          <t>https://www.kisantak.in/amp/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/politics-3/punjab-politics-chief-minister-bhagwant-singh-pm-modi/503770.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/punjab-govt-to-allow-flood-hit-farmers-to-mine-sand-from-their-fields-swm-1274251-2025-09-08</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/punjab/pm-modi-will-meet-flood-affected-families-and-relief-workers-in-kangra-and-gurdaspur-today-4256164</t>
+          <t>https://www.amarujala.com/amp/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=education-is-most-important-for-the-progress-and-development-of-any-society-deputy-chief-minister-deora-576499</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/CM-Dr-Yadav-congratulated-PM-Modi-on-his-birthday.php</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/punjab/punjab-seeks-rs-20000-crore-flood-relief-package-from-centre-pm-modi-to-visit-state-today-4256058</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/main-objective-of-skill-development-schemes-is-to.php</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/triple-engine-government-has-failed-in-delhi-there-is-garbage-everywhere-ankush-narang-4260747</t>
+          <t>https://www.agniban.com/chief-minister-nitish-kumar-expanded-the-chief-ministers-determination-self-help-allowance-scheme-in-bihar/</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modi-aerial-survey-of-flood-affected-areas-in-himachal-563737</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/desh-pradesh/bihar/government-issued-order-for-morbihar-contract-workers-reinstatement-appeal-process-7000-staff-relief/article-105794</t>
+          <t>https://www.business-standard.com/amp/industry/agriculture/gst-rate-cut-agri-minister-to-meet-farm-equipment-industry-on-sep-19-125091800798_1.html</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://prabhattimes.com/news/pm-modi-visit-punjab-flood-situation-review/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/delhi-national-agriculture-conference-rabi-campaign-2025-to-be-held-on/99312/</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/2-day-national-agricultural-conference-to-be-held-from-15-september-1503486047.html</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://ianslive.in/viksit-krishi-sankalp-abhiyan-to-guide-production-strategies-for-rabi-season--20250914094317</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267881</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://www.fnbnews.com/Policy-Regulations/new-gst-rates-a-boon-for-agriculture-and-farmers-prosperity-84744</t>
+          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-stands-with-jk-flood-victims-agriculture-minister-4275258</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3626888-second-phase-of-viksit-krishi-sankalp-abhiyan-begins-with-rabi-conference-2025</t>
+          <t>https://www.aninews.in/videos/national/CVBNCVBCVB</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shri-shivraj-singh-chouhan-visits-satna-in-madhya-pradesh-assures-supply-of-fertiliser-and-urea/</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/amp/local/chhattisgarh/agriculture-minister-ramvichar-netam-on-delhi-tour-4264726</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>https://www.aajsamaaj.com/punjab-government-will-allow-flood-affected-farmers-to-mine-sand-from-their-fields-they-will-also-be-allowed-to-sell-it-manish-sisodia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/baat-pate-ki/apna-paisa/budget-2025-6-new-agriculture-schemes-stuck-even-after-half-a-financial-year</t>
-        </is>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/india/mantris-reveal-assets-from-scooters-to-crypto/articleshow/123845772.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/headlines/3627395-frances-fnsea-gears-up-for-major-protest-against-eu-mercosur-deal-and-us-tariffs?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/uttarakhand/%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8%E0%A4%9C-%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A3-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA%E0%A4%AC%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0/ar-AA1M0cOp</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-dehradun-city-news-cm-dhami-attends-jain-samaj-sammelan-assures-support-24039856.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>https://www.jansatta.com/rajya/exclusive-interview-why-did-we-lose-congress-haryana-assembly-elections-know-what-former-cm-bhupinder-singh-hooda-said/4140386/</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>https://jharkhandstatenews.com/article/hindi-news/2873/Jesova-invited-Chief-Minister-Hemant-Soren-and-MLA-Kalpana-Soren-to-attend-Diwali-Mela-Morhabadi-Ground</t>
-        </is>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>https://www.grenonews.com/?p=104729</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/cm-gupta-announces-committees-for-organising-ramlila-durga-puja-festivals-in-delhi/867493/</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/bhopal/ladli-behna-yojana-update-1-26-crore-sisters-will-get-rs-1500-in-their-accounts-check-payment-sta-1383443.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/uttarakhand-news-15-%E0%A4%B8%E0%A4%B9-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A4%95-%E0%A4%82-%E0%A4%95-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%A7-%E0%A4%AE-%E0%A4%A8%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%AA-%E0%A4%A8-%E0%A4%AF%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A4%B9-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8%E0%A4%9C-%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%A3-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA%E0%A4%AC%E0%A4%A6%E0%A5%8D%E0%A4%A7/ar-AA1M48l7</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>https://rajpanchhi.com/posts/68c6b2c9a09cd6cfc14b2fe2--8xc_9-Delegation-of-Khatik-community-met-Chief-Minister-Bhajanlal-Sharma-with-a-courtesy-meeting-called-upon-him-to-take-advantage-of-the-schemes</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>https://rajpanchhi.com/posts/68c59395a09cd6cfc142f704-qizEIX-Yogi-Nath-and-Siddha-community-delegation-met-Chief-Minister-Bhajanlal-Sharma-and-BJP-President-Madan-Rathore-and-expressed-gratitude-for-the-social-upliftment</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>https://thenewspost.in/News-Update/officers-wives-association-invited-chief-minister-hemant-soren-for-diwali-fair-Pz5EurDKWb</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>https://corbetthalchal.in/chief-minister-announced-the-message-of-unity-and-non-violence-of-jain-society-in-uttarakhand/</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>https://lagatar.in/ias-officers-wives-association-invited-cm-for-diwali-mela</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>https://thebikanernews.in/rajasthan/rajasthan-delegation-of-siddha-samaj-met-chief-minister/cid17411756.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>https://liveskgnews.com/uttarakhand/bharat-ratna-pandit-govind-ballabh-pant-celebrated-with-grandeur-in-irdt-auditorium/</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>https://nayabharat.live/minister-smt-lakshmi-rajwade-took-a-joint-meeting-of-officials-of-women-and-child-development-social-welfare-department-in-jashpur/</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>https://brightpost.in/2025/09/09/achievements-of-dhami-government-in-uttarakhand-focus-on-disaster-management-education-and-investment/</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>https://nayabharat.live/saint-asanga-dev-ji-who-was-revered-by-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>https://khabarcell.com/jharkhand/chief-minister-invited-for-five-day-diwali-fair-to-be-held-in-morhabadi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>https://dainikbharat24.com/2025/09/jesova-invited-the-chief-minister-to-attend-the-diwali-fair/</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/gurugram/ncr-news-gurugram-will-become-number-one-in-cleanliness-with-public-participation-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/bihar/gaya/story-bhola-paswan-shastri-s-legacy-the-ongoing-struggle-for-social-justice-and-political-participation-in-bihar-201757507715060.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/haryana/chandigarh-news/news-gurugram-has-to-be-made-number-one-in-cleanliness-ranking-with-public-participation-chief-minister-news-hindi-1-751850-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>https://newstrack.com/uttar-pradesh/samarth-uttar-pradesh-2047-public-participation-education-ai-541273</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>https://dainiksaveratimes.com/national/haryana/cm-did-shramdaan-in-cleanliness-drive-pledged-to-make-gurugram-number-one-in-cleanliness-ranking-through-public-participation/</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>https://www.thehawk.in/news/india/jyotiraditya-scindia-urges-male-family-members-of-women-in-local-panchayat-bodies-not-to-interfere-in-official-works</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/state-government-new-promotion-policy-for-employees-remains-on-hold/articleshow/123849435.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>https://www.tv9hindi.com/india/green-signal-to-jiska-khet-uski-sand-policy-cm-bhagwant-mann-decision-in-favor-of-flood-victims-3473305.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/dehradun/uttarakhand-cabinet-decision-poultry-feed-subsidy-scheme-will-be-implemented-in-the-hilly-districts-of-the-sta-2025-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>https://jagratilahar.com/hindi/politics/120526/Bhagwant-Mann-Led-Punjab-Cabinet-Takes-Historic-Decisions-To-Give-Healing-Touch-To-Flood-Affected-Residents</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/851-crore-contract-approved-in-the-meeting-of-hppc-and-hpwpc-haryana-news-hrs25091205183</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/ujjain-news/mp-congress-attack-on-bjp-government-mohan-yadav-amit-shah-on-mp-farmers-major-issues-19939361</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>https://kelopravah.news/government-is-determined-to-achieve-sustainable-development-goals-cm-say/</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>https://www.naidunia.com/madhya-pradesh/bhopal-congress-kisan-nyay-yatra-in-ujjain-today-leaders-including-sachin-pilot-digvijay-singh-will-participate-8405072</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/punjab/punjab-chandigarh-news/news-punjab-cabinet-led-by-cm-mann-took-historic-decisions-green-signal-to-jiska-khet-uski-sand-policy-news-hindi-1-751137-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>https://www.tv9hindi.com/videos/tv9-digital-bihar-baithak-deputy-cm-vijay-sinha-nda-bihar-assembly-election-2025-3479304.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>https://garimatimes.in/punjab-news-cabinet-meeting-approves-prosecution-against-bikram-majithia-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-flood-cabinet-decision-mera-khet-meri-ret-policy-implemented-farmers-will-get-ownership-rights</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/madhya-pradesh/ujjain/congress-kisan-nyay-yatra-ujjain-october-2023-18-817300</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>https://www.thejbt.com/state-news/punjab-cabinet-took-historic-decisions-under-the-leadership-of-cm-mann-green-signal-to-jiska-khet-uski-sand-policy-news-294683</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/state/punjab/many-historic-decisions-taken-in-punjab-cabinet-meeting-green-signal-to-jiska-khet-uski-ret-news-93212</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>https://rewariupdate.com/haryana-basai-water-treatment-project-tender-irregularities/</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>https://apnuuttarakhand.com/uttarakhand-government-gave-big-relief-to-the-employees-increased/</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%86%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A4%9D-%E0%A4%A4-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1M0LYh</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-date-2025-do-not-make-these-mistakes-while-filing-itr-or-else-you-will-not-get-money-amar-2025-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-change-in-gst-rates-will-prove</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>https://hindi.moneycontrol.com/india/mallikarjun-kharge-video-pulling-up-farmers-viral-on-social-media-agriculture-minister-and-bjp-targeted-congress-article-2149008.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>https://www.punjabkesari.in/national/news/pm-kisan-s-21st-installment-may-get-stuck-if-you-have-not-done-these-important-2210389</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/headlines/%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%9F-%E0%A4%95-06-816</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>https://samarsaleel.com/food-processing-sector-deputy-chief-minister-will-increase-the-income-of-farmers-and-youth/496097</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>https://himachalnownews.com/%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%95%E0%A5%83%E0%A4%A4%E0%A4%BF%E0%A4%95-%E0%A4%96%E0%A5%87%E0%A4%A4%E0%A5%80-%E0%A4%B8%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%AD%E0%A5%8B%E0%A4%95%E0%A5%8D.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>https://krishijagran.com/news/ncel-apeda-join-hands-to-boost-india-s-cooperative-led-agricultural-exports/</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>https://krishijagran.com/news/india-s-seafood-exports-get-boost-eu-approves-102-fishery-establishments/</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/agriculture-news-live-upates-weather-news-in-hindi-agriculture-latest-updates-imd-alerts-in-hindi-1276921-2025-09-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/gaon-post/drishtikon/cotton-cultivation-cotton-price-cotton-msp-cotton-farmers-cotton-production-cotton-import-cotton-export</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/crops/story/vikasit-krishi-sankalp-abhiyaan-rabi-crop-national-conference-2025-prv-1277150-2025-09-13?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/shimla/two-day-national-cooperative-conference-begins-in-shimla-deputy-chief-minister-inaugurates-it-2025-09-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>https://www.abplive.com/states/up-uk/up-news-big-relief-for-farmers-in-up-chief-minister-yogi-adityanath-gave-important-instructions-3011627</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>https://hindi.webdunia.com/uttar-pradesh/state-cooperative-college-will-be-established-in-the-state-research-will-be-encouraged-125091300072_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>https://vocaltv.in/himachal-pradesh/cooperative-banks-27thousand-crore-deposit-dycmphp/cid17411159.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/state-cooperative-college-will-be-established-to-promote-research-in-cooperatives-yogi/867921/</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/lucknow/cm-yogi-said-state-cooperative-college-will-be-opened-in-up-in-review-of-cooperative-department-2025-09-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>https://vocaltv.in/uttar-pradesh/murlidhar-mohol-the-cooperative-sector-is-gettingphp/cid17406881.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>https://www.dotookmedia.com/2025/09/lucknowthe-cooperative-department-is.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>https://dainiksaveratimes.com/punjab/punjab-government-launched-crop-residue-management-loan-scheme-through-cooperative-banks/</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/himachal-pradesh/use-central-assistance-in-a-transparent-manner-bjp-leader-told-cm-sukhu-4265006</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>https://www.haribhoomi.com/amp/state-local/haryana/kurukshetra/international-gita-festival-bali-kurukshetra-land-demand-shri-krishna-message-646332</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>https://dailyuttarakhand.com/cooperation-will-change-the-fate-of-himalayan-states-dr-dhan-singh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>https://www.theindiadaily.com/state/punjab/punjab-launches-revised-crop-residue-loan-scheme-to-curb-stubble-burning-and-boost-sustainable-farming-news-93602</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!bharat/first-national-women-empowerment-conference-held-in-tirupati-andhra-pradesh-hindi-news-hin25091403438</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/bihar/patna-city-chief-minister-nitish-kumar-flagged-off-80-pink-buses-for-women-24039705.html?utm_source=article_detail&amp;utm_medium=CRE&amp;utm_campaign=latestnews_CRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/hapur/story-women-empowerment-awareness-program-held-in-hapur-under-beti-bachao-beti-padhao-scheme-201757453830319.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>https://www.statemirror.com/state/bihar/bihar-chief-minister-women-employment-scheme-lifesaver-for-nitish-kumar-who-will-get-benefittd-bihar-chunav-2025-150923</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/bhopal-news/ladli-behna-yojana-update-installment-know-how-to-register-your-name-19927104</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/women-will-get-50-percent-reservation-in-vita-booths/</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>https://kelopravah.news/unicef-india-will-provide-technical-support-in-building-a-developed-chhattisgarh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/south-asia-largest-drone-hub-to-be-built-in-sisay-hisar-drone-pilot-convocation-in-chandigarh-agriculture-drone-pavilion-haryana-news-hrs25090900509</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-will-become-a-powerhouse-of-drone-technology-cm-saini/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>https://samacharnama.com/states/bihar-news/bihar-government-launches-chief-ministers-women-employment/cid17404205.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>https://www.gnewsportal.com/rajasthan/ghoomar-utsav-2025-will-be-organized-on-the-initiative-of-deputy-chief-minister-dia-kumari</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>https://mradubhashi.com/news.php?id=women-in-bihar-will-get-10000-rupees-government-started-a-new-scheme-575961</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>https://royalbulletin.in/uttar-pradesh/saharanpur/poxo-act-and-awareness-of-women-empowerment-schemes-to-girls/article-105452</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/amp/local/andhra-pradesh/harivansh-singh-highlights-ntrs-impact-on-women-empowerment-at-tirupati-conference-4265120</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>https://knn24.in/%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B5%E0%A4%BF%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A5%81%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/others/rajasthan-ghoomar-festival-will-be-held-for-the-first-time-in-jaipur-on-november-15-4260734</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>https://cgnn24.in/?p=111351</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>https://nayabharat.live/chhattisgarh-government-sets-an-example-in-the-empowerment-of-special-articles/</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>https://makdaiexpress24.com/meeting-will-be-held-in-the-state-from-17-september-to-2-october/</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/bihar/emphasis-on-education-and-skill-development-in-bihar-minister-targets-rjd-and-mamta-banerjee--4255685</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>https://cgmitan.com/divine-power-urn-brought-from-shanti-kunj-haridwar-108-kundiya-vishwa-kalyan-gayatri-maha-yagya-will-be-held-in-silghat-from-10-to-13-december/</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>https://kirandoot.com/?p=68079</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>https://webvarta.com/states/uttar-pradesh/kushinagar-mission-shakti-discussion-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>https://krishijagran.com/news/pm-kisan-samman-nidhi-govt-advises-farmers-to-update-mobile-numbers-ahead-of-21st-instalment/</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-if-farmer-brothers-do-not-do-this-work-then-the-installment-wil-2025-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/mau/story-rakesh-singh-demands-resolution-of-farmers-issues-regarding-pm-kisan-samman-nidhi-201757701198149.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>https://www.naidunia.com/chhattisgarh/raipur-99-percent-people-in-maoist-affected-areas-have-aadhaar-card-28-lakh-farmers-benefit-from-pm-kisan-scheme-8405248</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-know-these-important-updates-before-the-21st-installment-arrive-2025-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/upi-new-rules-from-september-15-these-rules-of-upi-transactions-will-change-you-will-be-able-to-transact-lak-2025-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/ayushman-bharat-yojana-know-these-rules-related-to-ayushman-bharat-yojana-how-can-you-get-free-treatment-2025-09-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/delhi-thar-news-new-car-got-damaged-at-the-time-of-delivery-will-it-get-insurance-or-not-delhi-women-thar-2025-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/these-women-will-not-get-2100-rupees-haryana-lado-lakshmi-yojana-cm-nayab-singh-saini-utility-2025-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/spice-jet-plane-emergency-landing-wheel-got-loose-on-the-runway-plane-took-off-how-did-it-land-safely-2025-09-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-card-if-you-want-to-go-to-aadhaar-centre-you-can-take-an-appointment-from-home-like-this-uidai-a-2025-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>https://hindi.latestly.com/india/pm-kisan-samman-nidhi-21st-installment-date-kyc-bank-land-verification-update-2025-2749988.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>https://bhartiyabasti.com/basti-news-live-in-hindi/strict-instructions-given-to-officers-in-deputy-chief-minister-basti/article-22685</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>http://mirroruttarakhand.com/news-uttarakhand-chief-minister-gave-financial-approval-for-various-development-schemes-worth-rs-146-19-crore-for-nainital-bageshwar-and-haridwar/</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/politics/story/jitu-patwari-slams-cm-mohan-yadav-on-farmers-issue-says-working-for-reels-photos-1277266-2025-09-13?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
-        </is>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>https://www.deccanchronicle.com/nation/madhya-pradesh-government-to-audit-ladli-behna-beneficiaries-to-remove-ineligible-names-1903328</t>
-        </is>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/mp-ladli-behna-yojana-money-increased-to-1500-rupees-mohan-yadav-govt-not-adding-new-names-madhya-pradesh-news-mps25090801561</t>
-        </is>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>https://www.indiatoday.in/world/story/eu-negotiators-head-to-delhi-as-india-us-trade-tensions-rise-2784093-2025-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>https://www.moneycontrol.com/news/business/india-eu-speed-up-talks-for-fta-says-commerce-minister-piyush-goyal-13533552.html/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>https://organiser.org/2025/09/08/314716/world/high-profile-eu-delegation-to-land-in-new-delhi-aims-to-consolidate-india-eu-fta-deal-amid-spiking-trump-tariffs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>https://hindi.news24online.com/state/chhattisgarh/cm-vishnu-deo-sai-thakur-joharni-program-special-focus-on-bastar-division-new-industrial-policy/1320505/</t>
-        </is>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/economy/government-is-committed-to-strengthen-the-agricultural-marketing-system-chief-minister-sharma/865844/</t>
-        </is>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/india/chief-minister-vishnu-dev-sai-attends-thakur-joharni-event-in-narharpur-012-1385715.html?ref_source=AdSlot[300x250]&amp;ref_medium=PVA&amp;ref_campaign=ArticlePromoUnfilled</t>
-        </is>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>https://uttarakhandkesari.in/chief-minister-pushkar-singh-dhami-attended-the-prabuddhan-samvad-programme/</t>
-        </is>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>https://kelopravah.news/changes-in-gst-will-give-new-impetus-to-the-economy-of-the-state-and-the-country/</t>
-        </is>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/india/gujarat-jan-vishwas-amendment-bill-2025-012-1382451.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>https://theguptchar.com/bastar-sarguja-development-cm-vishnudev-sai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/khad-beej/story/bio-stimulants-regulation-india-2025-fco-update-shivraj-singh-chouhan-1277400-2025-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>https://sbharatnews.com/?p=138049</t>
-        </is>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>https://mradubhashi.com/news.php?id=many-important-decisions-were-taken-in-sebi-board-meeting-companies-got-the-benefit-of-new-time-limit-576350</t>
-        </is>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>https://alivenews.co.in/two-youths-from-haryana-stranded-on-ukraine-border/</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>https://alivenews.co.in/sachin-thakur-became-the-district-president-of-faridabad-bjp-yuva-morcha/</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>https://kirandoot.com/?p=68112</t>
-        </is>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>https://www.tribuneindia.com/news/punjab/modi-announces-rs-1600-cr-for-flood-hit-punjab-oppn-farmers-call-it-cruel-joke/</t>
-        </is>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/en/!bharat/live-blog--vice-president-election-2025-live-updates-c-p-radhakrishnan-vs-b-sudershan-reddy-nda-bjp-india-congress-enn25090900526</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>https://www.indianewsstream.com/radhakrishnan-elected-vice-president-oppositions-unity-claims-questioned/</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>https://aninews.in/news/national/general-news/vice-president-election-union-minister-rajnath-singh-nda-mps-cast-votes-in-parliament20250909114516/</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/hi-in/news/india/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%B5-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%89%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%8D%E0%A4%A1-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%9F-%E0%A4%82%E0%A4%97-%E0%A4%B8%E0%A5%87-%E0%A4%87%E0%A4%A8%E0%A4%95-%E0%A4%B0-%E0%A4%96%E0%A4%A1%E0%A4%BC%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%9C-%E0%A4%A4-%E0%A4%A4%E0%A4%AF/ar-AA1May5t?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/ashok-gehlot-alleges-extra-cameras-in-house-to-record-oppositions-conversation-demands-investigation-rajasthan-news-rjs25091004202</t>
-        </is>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>https://ndtv.in/cricket/saim-ayub-dismissed-for-golden-duck-vs-oman-fakhar-zaman-said-for-saim-ayub-that-he-is-updated-version-of-babar-azam-ind-vs-pak-asia-cup-2025-hindi-9266759/amp/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>https://www.divyahimachal.com/2025/09/opposition-parties-surrounded-the-central-government-on-the-issue-of-aid-chief-minister-alleged-that-bjp-leaders-are-doing-politics-instead-of-helping-the-flood-victims/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/jaipur-news/rajasthan-assembly-adjourned-indefinitely-2-important-bills-passed-on-last-day-19934152</t>
-        </is>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/himachal-pradesh/chamba-mla-responded-to-oppositions-criticism-4265014</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/haryana/haryana-good-management-of-flood-relief-opposition-should-focus-on-its-role-mp-barala-4262961</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/national/vice-presidential-election-opposition-candidate-sudarshan-reddy-denies-cross-voting-kharge-says-victory-is-certain-4255993</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/rajasthan/former-rajasthan-chief-minister-vasundhara-raje-pays-courtesy-call-on-new-vice-president-cp-radhakrishnan-4263897</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/amp/local/himachal-pradesh/use-central-assistance-in-a-transparent-manner-bjp-leader-told-cm-sukhu-4265006</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/state/bihar/patna/bihar-news-cm-was-changed-more-than-vice-chancellor-his-tenure-was-the-shortest-in-bihar/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>https://firstbihar.com/politics/bihar-cm-shortest-tenure-5-to-13-days-news-622897</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-politics-nitish-kumar-became-chief-minister-in-2005-first-with-the-help-of-bjp-arun-jaitley/articleshow/123798206.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/patrika-special/in-madhya-pradesh-57-mps-and-mlas-come-from-political-families-adr-report-reveals-19944241</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/madhya-pradesh-bjp-faces-criticism-over-double-standards-on-dynasty-politics-hindi-news-2025-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!bharat/story-of-satish-prasad-singh-who-was-bihar-chief-minister-for-just-five-days-hindi-news-brn25090802879</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/education/general-knowledge/bihar-chunav-gk-know-who-was-chief-minister-for-only-17-days</t>
-        </is>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/state/bihar/patna/bihar-news-cm-was-changed-more-than-vice-chancellor-his-tenure-was-the-shortest-in-bihar</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>https://www.timesnowhindi.com/india/who-will-be-the-next-vice-president-of-india-decision-will-be-taken-today-know-what-is-the-equation-of-nda-and-india-for-victory-article-152729962</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>https://mp.punjabkesari.in/madhya-pradesh/news/digvijay-singh-met-kamal-nath-2211302</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>https://www.lokmatnews.in/india/bihar-polls-siyasat-pariwarwad-politics-nepotism-mla-in-jail-son-daughter-and-wife-in-politics-whenever-crisis-power-ticket-and-position-b507/</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/amp/local/mp/news/57-mps-and-mlas-in-mp-have-family-connections-135915533.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-9-september-2025-3473506.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/bhopal/former-cm-digvijay-singh-and-kamal-nath-delhi-meeting-beginning-of-reconciliation-political-maste-1383847.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/chhattisgarh/how-digvijaya-singh-prediction-about-ajit-jogi-became-true/2918254/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>https://delhiuptodate.com/cm-mohan-yadav-got-new-identity-in-politics-after-shivraj-mama/</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186084</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/-15--1185971</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/news-1185434</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/bengaluru-council-session-at-vidhana-soudha-1185905</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/kerala-cm-vijayan-must-shed-ostrich-like-attitude-says-lop-satheesan-1185872</t>
-        </is>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/news-1185712</t>
-        </is>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/patna-tejashwi-yadav-at-atipichhra-jagao-rally-1186003</t>
-        </is>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>https://www.uttranews.com/the-country-will-get-a-new-vice-president-the-secrets-of-votes-will-be-revealed-today-all-eyes-are-on-the-winning-strategy-of-nda-and-the-opposition/</t>
-        </is>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>https://upkiran.org/Seven-days-Chief-Minister-know-how-Nitish-Kumars-first-coronation-collapsed</t>
-        </is>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>https://raftartoday.com/the-politics-of-renaming-sadullapur-village-caught-up-from-panchayat-to-former-chief-minister-akhilesh-yadav-hinted-at-coming-to-the-village-a-new-front-of-politics-from-village-to-city-discussion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>https://knewsindia.in/rajya/%E0%A4%B0%E0%A4%BE%E0%A4%B9%E0%A4%A4-%E0%A4%AA%E0%A4%B0-%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%A8%E0%A5%80%E0%A4%A4%E0%A4%BF/</t>
-        </is>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>https://www.newsnationtv.com/india/aap-mp-sanjay-singh-climbed-the-gate-and-former-chief-minister-farooq-abdullah-seen-in-front-10440728</t>
-        </is>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>https://www.primetvindia.com/gaurav-gogoi-assam-politics-is-raging-chief-ministers-post-is-making-a-mockery-of-sarma-gogois-big-statement/</t>
-        </is>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>https://viratvasundhara.in/2025/09/14/rewa-mp-vindhyas-politics-of-sikandar-shri-yut-srinivas-tiwaris-statue-ends/</t>
-        </is>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>https://www.moneycontrol.com/news/india/abstaining-parties-backing-bjp-in-vice-presidential-poll-says-aap-leader-sanjay-singh-13532847.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/india/videos-amit-shah-rahul-gandhi-sonia-gandhi-among-leaders-who-cast-votes-in-vice-presidential-election-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/cong-leader-rahul-gandhi-to-visit-flood-hit-punjab-on-monday-10464288</t>
-        </is>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>https://thenewsmill.com/2025/09/sonia-gandhi-kharge-other-congress-leaders-cast-their-votes-for-15th-vice-presidential-elections/</t>
-        </is>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/ujjain-congress-kisan-adhikar-yatra-sachin-pilot-digvijay-singh-jeetu-patwari-raise-farmers-problems-madhya-pradesh-news-mps25091201207</t>
-        </is>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/bhopal-there-is-shortage-of-fertilizers-in-the-state-the-leader-of-opposition-accused-of-black-marketing-sa-2025-09-11?src=top-subnav</t>
-        </is>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/police-lathicharged-the-farmers-of-neendar-who-were-going-to-gherao-the-cm-residence-in-jaipur-rajasthan-news-rjs25091310332</t>
-        </is>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/hi-in/news/other/mp-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB%E0%A5%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%97%E0%A5%81%E0%A4%B8%E0%A5%8D%E0%A4%B8-%E0%A4%9F-%E0%A4%B2-%E0%A4%AB%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%AC%E0%A4%A8-%E0%A4%AE%E0%A4%9C-%E0%A4%95-%E0%A4%86%E0%A4%82%E0%A4%A6-%E0%A4%B2%E0%A4%A8-%E0%A4%95-%E0%A4%9A%E0%A5%87%E0%A4%A4-%E0%A4%B5%E0%A4%A8/ar-AA1Iafyt?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/save-nindrad-movement-farmers-came-out-to-surround-cm-house-in-protest-against-land-acquisition-for-residential-colony-rajasthan-news-rjs25091306866</t>
-        </is>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/jaipur-news/save-nindrad-movement-farmers-who-went-out-to-surround-cm-residence-were-stopped-19942209</t>
-        </is>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/ratlam-soybean-crop-destroyed-farmers-protest-demanding-compensation-mohan-yadav-assessed-loss-in-field-madhya-pradesh-news-mps25091306755</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/ujjain-congress-vote-chor-gaddi-chhod-kisan-nyay-yatra-sachin-pilot-demand-land-acquisition-bill-madhya-pradesh-news-mps25091307009</t>
-        </is>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>https://www.chinimandi.com/haryana-government-should-fix-the-rate-of-sugarcane-at-rs-500-per-quintal-former-chief-minister-bhupendra-hooda-in-hindi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
-        <is>
-          <t>https://lalluram.com/mp-news-satna-congress-leaders-scuffled-with-police-who-went-to-stop-the-protest/</t>
-        </is>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/politics/story/farmers-anger-erupts-on-adarsh-mandi-police-station-demand-suspension-of-sho-in-shamli-up-1277417-2025-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
-        <is>
-          <t>https://samacharnama.com/states/uttar-pradesh-news/akhilesh-yadav-suddenly-reached-the-farmers-protest-saw-in/cid17376433.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
-        <is>
-          <t>https://dainikathah.com/?p=61344</t>
-        </is>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/khad-beej/story/bio-stimulants-regulation-india-2025-fco-update-shivraj-singh-chouhan-1277400-2025-09-14?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
-        </is>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
-        <is>
-          <t>https://avnews.in/tomorrow-congress-will-take-out-farmers-with-two-groups-and-raise-farmers-issues-in-the-public-meeting/</t>
-        </is>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/punjab-govt-starts-special-girdawari-to-assess-losses-due-to-floods-1277483-2025-09-14?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
-        </is>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
-        <is>
-          <t>https://www.thehawk.in/news/economy-and-business/viksit-krishi-sankalp-abhiyan-to-guide-production-strategies-for-rabi-season</t>
-        </is>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
-        <is>
-          <t>https://www.inhnews.in/News/cm-vishnudev-sais-press-conference-gst-20-gives-big-relief-to-farmers</t>
-        </is>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
-        <is>
-          <t>https://mradubhashi.com/news.php?id=pappu-yadav-expressed-concern-over-the-law-and-order-and-foreign-policy-of-bihar-576026</t>
-        </is>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
-        <is>
-          <t>https://knewsindia.in/rajya/panchayats-are-an-effective-medium-for-improving-socio-economic-standards-of-living-chief-minister-mohan-yadav/</t>
-        </is>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
-        <is>
-          <t>https://bccnews24.com/raipur-changes-in-gst-will-give-new-impetus-to-the-economy-of-the-state-and-the-country-businessmen-and-the-common-man-will-benefit-chief-minister-vishnu-dev-sai-2/</t>
-        </is>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B0%C2%B8%C3%8E%C2%B4%C2%B2%C2%B6&amp;fontname=Mangal&amp;LocID=32&amp;pubdate=08%20Sep%202025</t>
-        </is>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-himalayan-save-mission-2025-environmental-protection-awards-in-dehradun-201757333983241.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/delhi/story/delhi-government-3k-heater-rwa-mazdoor-pradushan-lclcn-rptc-2331914-2025-09-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-himalayan-biodiversity-conservation-cms-call-for-collective-effort-24040889.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
-        <is>
-          <t>https://mbmnewsnetwork.com/himachal-pradesh/853311/%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%B5%E0%A4%BE%E0%A4%AF%E0%A5%81-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-2025-%E0%A4%AE%E0%A5%87</t>
-        </is>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/shimla/himachal-s-parwanoo-municipal-council-ranks-second-in-the-country-s-clean-air-survey-2025-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>https://www.jansatta.com/national/delhi-govt-to-work-with-corporates-to-clean-yamuna-and-tackle-pollution/4131722/</t>
-        </is>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-nature-worship-program-in-mansarovar-pledged-to-protect-by-worshipping-the-tree-news-hindi-1-752700-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/uttarakhand/uttarakhand-cm-pushkar-singh-dhami-himalaya-bachao-abhiyan-2025-201757462627706.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-himalaya-day-celebrated-collective-responsibility-for-conservation-amidst-challenges-201757342384712.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-pushkar-singh-dhami-emphasizes-himalayan-conservation-and-sustainable-tourism-201757415716705.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
-        <is>
-          <t>https://hilllive.in/chief-minister-wished-the-people-of-the-state-on-himalayan-day/.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
-        <is>
-          <t>https://thetruefact.com/government-is-working-committed-to-himalaya-protection-chief-minister-dhami/</t>
-        </is>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>https://mradubhashi.com/news.php?id=urban-bodies-are-being-encouraged-to-dispose-of-waste-in-the-state-576498</t>
-        </is>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/others/puri-under-the-initiative-one-tree-in-the-name-of-mother-sudarshan-patnaik-created-a-sand-sculpture-said-environment-is-an-invaluable-heritage-4264045</t>
-        </is>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
-        <is>
-          <t>https://livevns.news/amp/state/uttrakhand/governor-and-cm-gave-wishes-for-himalaya-dayphp/cid17379177.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
-        <is>
-          <t>https://www.aajsamaaj.com/mahendragarh-news-it-is-very-important-to-include-cleanliness-in-our-nature-mla-kanwar-singh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
-        <is>
-          <t>https://mediapassion.co.in/?p=66702</t>
-        </is>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
-        <is>
-          <t>https://dailyuttarakhand.com/tourism-should-be-developed-in-harmony-with-nature-maharaj/</t>
-        </is>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
-        <is>
-          <t>https://best24news.com/haryana/haryana-news-chief-minister-naib-singh/</t>
-        </is>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
-        <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/evening-news-504/</t>
-        </is>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
-        <is>
-          <t>https://mobilenews24x7.com/2025/natural-disaster/ahead-of-pm-modis-visit-punjab-aap-seeks-rs-20000-crore-flood-relief-package/</t>
-        </is>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A4%A8-%E0%A4%B7-%E0%A4%B8-%E0%A4%B8-%E0%A4%A6-%E0%A4%AF-%E0%A4%95-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-60-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%95%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%95-%E0%A4%AF/ar-AA1M3nSx?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
-        <is>
-          <t>https://upkiran.org/Prime-Minister-visit-to-flood-affected-states-today-focus-on-relief-work</t>
-        </is>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
-        <is>
-          <t>https://azadsipahi.in/09/2025/punjab-asked-the-central-government-25-thousand-crores-in-compensation-for-the-damage-caused-by-floods.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
-        <is>
-          <t>https://khabrimedia.com/punjab-news-center-showed-step-motherly-behavior-even-in-natural-disaster-aman-arora/</t>
-        </is>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
-        <is>
-          <t>https://boldnewsonline.com/national-agricultural-conference-to-begin-on-september-15-for-two-days/</t>
-        </is>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
-        <is>
-          <t>https://orissadiary.com/union-agriculture-minister-shri-shivraj-singh-chouhan-visits-satna-in-madhya-pradesh-assures-supply-of-fertiliser-and-urea/</t>
-        </is>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>https://orissadiary.com/new-gst-rates-a-boon-for-agriculture-and-farmers-prosperity/</t>
-        </is>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/satna/farmers-created-a-ruckus-during-shivraj-satna-visit-union-minister-had-to-cancel-the-program/amp_articleshow/123856543.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/mohan-government-is-targeting-shivraj-singh-chauhan-big-allegation-of-digvijay-singh-gave-advice-to-chief-minister/amp_articleshow/123851246.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/chhattisgarh/agriculture-minister-ramvichar-netam-on-delhi-tour-4264726</t>
-        </is>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>https://guwahatiplus.com/farmers-to-benefit-as-second-phase-of-viksit-krishi-sankalp-abhiyan-targets-rabi-season</t>
-        </is>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/haryana/karnal/scientists-and-officers-will-go-to-the-farmers-doorsteps-and-do-research-as-per-demand-karnal-news-c-18-knl1008-734875-2025-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>https://makdaiexpress24.com/shivraj-singh-chauhan-reached-shivas-shelter-a-photo-shoot-of-a-monkey-in-pachmarhis-litigants/</t>
-        </is>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>https://www.global-agriculture.com/india-region/new-gst-rates-a-boon-for-agriculture-and-farmers-prosperity/</t>
-        </is>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>https://chetaktimes.com/news-in-hindi-sardarpur-dhar-congress-gyapan-fasal-beema/</t>
-        </is>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/haryana/chandigarh-haryana/video-bhupender-singh-hooda-visit-flood-affected-areas-by-driving-tractor-2025-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/uttar-pradesh/bareilly/video-sp-mla-absent-from-annual-sugarcane-committee-meeting-in-baheri-2025-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/news/trending/story/pm-modi-lays-foundation-of-thenzawl-sialsuk-road-will-benefit-paddy-and-horticulture-farmers-swm-1277040-2025-09-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%B0-%E0%A4%B9%E0%A4%A4-%E0%A4%A6%E0%A5%87%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8-%E0%A4%B8-%E0%A4%A6-%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%95-%E0%A4%B2-%E0%A4%B8%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE-%E0%A4%B0%E0%A5%87%E0%A4%A4/ar-AA1M3ZXW</t>
-        </is>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>https://uditvani.in/jharkhand/jharkhand-kharif-crop-insurance-date-extended/</t>
-        </is>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/economy/swadeshi-fairs-will-be-organised-for-farmers-haryana-agriculture-minister/866319/</t>
-        </is>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/hi-in/news/other/gst-%E0%A4%B8%E0%A5%81%E0%A4%A7-%E0%A4%B0-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%AE-%E0%A4%B2-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%B0-%E0%A4%B9%E0%A4%A4-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%AA%E0%A4%B0-63000-%E0%A4%A4%E0%A4%95-%E0%A4%95-%E0%A4%B9-%E0%A4%97-%E0%A4%AC%E0%A4%9A%E0%A4%A4/ar-AA1M0EjD?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/arunachal-pradesh-cm-launches-kiwi-mission-calls-it-agriculture-revolution/865602/</t>
-        </is>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/news/relief-amount-reached-the-accounts-of-456-farmers-of-38-affected-villages-of-burhanpur-district/</t>
-        </is>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/news/five-day-krishi-sakhi-training-concluded-in-ujjain/</t>
-        </is>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/news/chhindwara-collector-inspected-the-cultivation-of-blueberry-and-g-9-banana/</t>
-        </is>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" t="inlineStr">
-        <is>
-          <t>https://www.timesnowhindi.com/photos/auto/gst-reform-2025-tractor-price-also-drop-you-will-get-a-direct-discount-of-this-much-rupees-photo-gallery-152735032</t>
-        </is>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/haryana/panchkula-how-much-compensation-will-be-given-in-case-of-death-and-damage-to-house-in-flood-cm-naib-saini-has-set-the-standards-for-compensation-24040313.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/india/madhya-pradesh-chief-minister-mohan-yadav-farmers-support-012-1384195.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/shimla-cooperation-himachal-economy-support-2212680</t>
-        </is>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="inlineStr">
-        <is>
-          <t>https://dnewsnetwork.in/%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%95%E0%A5%83%E0%A4%A4%E0%A4%BF%E0%A4%95-%E0%A4%96%E0%A5%87%E0%A4%A4%E0%A5%80-%E0%A4%B8%E0%A5%87-%E0%A4%89%E0%A4%AA%E0%A4%AD%E0%A5%8B%E0%A4%95%E0%A5%8D/</t>
-        </is>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
-        <is>
-          <t>https://www.totaltv.in/farmer-leader-gurnam-singh-chaduni-met-cm-nayab-saini/</t>
-        </is>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2165828</t>
-        </is>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2165121</t>
-        </is>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/haryana/panipat/flood-affected-farmers-should-upload-their-data-on-the-portal-panipat-news-c-244-1-pnp1011-143419-2025-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/haryana/story/haryana-rain-deaths-compensation-relief-fund-nayab-singh-saini-lclnt-dskc-2328418-2025-09-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttar-pradesh/noida-ncr-noida-news-yamuna-embankment-in-disrepair-minister-orders-action-24042218.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" t="inlineStr">
-        <is>
-          <t>https://m.mp.punjabkesari.in/madhya-pradesh/news/enemies-of-farmers-caught-by-police-cooperative-bank-employee-and-transport-com-2212257?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>https://barabankiexpress.in/?p=26293</t>
-        </is>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>https://www.agniban.com/mention-the-case-in-your-resume-too-supreme-court-orders-university-vc-in-sexual-harassment-case/index.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" t="inlineStr">
-        <is>
-          <t>https://peoplesupdate.com/collector-public-hearing-multiple-people-repeated-applications-no-solution-103215</t>
-        </is>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/news/madhya-pradesh-government-is-with-the-farmers-every-loss-will-be-compensated-cm-yadav/</t>
-        </is>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" t="inlineStr">
-        <is>
-          <t>https://www.abplive.com/states/up-uk/up-news-big-relief-for-farmers-in-up-chief-minister-yogi-adityanath-gave-important-instructions-3011627/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="846">
-      <c r="A846" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/india/chhattisgarh-ten-maoist-cadres-including-cpi-maoist-central-committees-sixth-member-neutralized-66019/</t>
-        </is>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" t="inlineStr">
-        <is>
-          <t>https://www.citiupdate.com/news/detailNews/104776</t>
-        </is>
-      </c>
-    </row>
-    <row r="848">
-      <c r="A848" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/bareilly-news/strong-uttar-pradesh-developed-uttar-pradesh-2047-campaign-launched-from-bareilly-19928758</t>
-        </is>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/amp/local/uttar-pradesh/siddharthnagar/news/vision-document-2047-seminar-concluded-in-siddharthnagar-135909778.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="850">
-      <c r="A850" t="inlineStr">
-        <is>
-          <t>https://thetruefact.com/big-breaking-chief-minister-pushkar-singh-dhami-participated-in-the-enlightened-conference-in-kashipur/</t>
-        </is>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=89935</t>
-        </is>
-      </c>
-    </row>
-    <row r="852">
-      <c r="A852" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/videos/raipur-news/chhattisgarh-farmers-will-get-direct-benefit-from-gst-reform-cm-sai-19940419</t>
-        </is>
-      </c>
-    </row>
-    <row r="853">
-      <c r="A853" t="inlineStr">
-        <is>
-          <t>https://mradubhashi.com/news.php?id=gst-rates-reduced-on-medicines-and-medical-equipment-nppa-asked-to-ensure-benefits-reach-the-general-public-576342</t>
-        </is>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/amp/sarkari-yojana/story/pmfby-pradhan-mantri-fasal-bima-yojana-conditions-profit-and-crop-insurance-companies-earnings-1276703-2025-09-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="855">
-      <c r="A855" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/amp/others/shivraj-singh-chauhan-advocated-for-holding-lok-sabha-and-assembly-elections-together-4260757</t>
-        </is>
-      </c>
-    </row>
-    <row r="856">
-      <c r="A856" t="inlineStr">
-        <is>
-          <t>https://www.munaadi.com/news-details/GST-reform-is-the-beginning-of-a-new-revolutionary-economic-era:-Chief-Minister-Say-GST-reform-will-make-the-life-of-the-people-easier:-Chief-Minister-Say</t>
-        </is>
-      </c>
-    </row>
-    <row r="857">
-      <c r="A857" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/agriculture/agriculture-minister-shivraj-singh-chouhan-gave-detailed-information-about-how-much-benefit-farmers-will-get-from-which-component-1477675.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="858">
-      <c r="A858" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/sakal-money/personal-finance/gst-reform-tractor-price-cut-farm-equipment-discount-farmers-benefit-india-2025-ymk86</t>
-        </is>
-      </c>
-    </row>
-    <row r="859">
-      <c r="A859" t="inlineStr">
-        <is>
-          <t>https://ahmednagarlive24.com/spacial/gst-rate-good-news-for-farmers-you-can-save-up-to-rs-63000-on-buying-a-tractorhow-to-read-it/</t>
-        </is>
-      </c>
-    </row>
-    <row r="860">
-      <c r="A860" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/bhopal-news/mahatma-gandhi-national-rural-employment-guarantee-scheme-manrega-become-boon-for-schedule-tribes-mp-is-number-one-in-terms-of-employment-19941565</t>
-        </is>
-      </c>
-    </row>
-    <row r="861">
-      <c r="A861" t="inlineStr">
-        <is>
-          <t>https://hindi.news18.com/amp/news/rajasthan/bharatpur-center-will-be-built-for-beekeeping-in-bharatpur-local18-ws-kl-9617934.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="862">
-      <c r="A862" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/business/urban-company-ipo-retail-demand-explodes-whats-behind-the-record-breaking-subscription-numbers-65831/</t>
-        </is>
-      </c>
-    </row>
-    <row r="863">
-      <c r="A863" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/business/shringar-house-of-mangalsutra-ipo-why-retail-investors-are-rushing-on-day-1-check-details-64590/</t>
-        </is>
-      </c>
-    </row>
-    <row r="864">
-      <c r="A864" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/india/indias-longest-glass-skywalk-in-vizag-with-explicit-view-of-bay-of-bengal-opening-soon-62908/</t>
-        </is>
-      </c>
-    </row>
-    <row r="865">
-      <c r="A865" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/india/delhi-police-freeze-illegally-acquired-property-of-a-known-drug-offender-in-delhis-bharat-nagar-area20250908130751-61623/</t>
-        </is>
-      </c>
-    </row>
-    <row r="866">
-      <c r="A866" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/sports/historic-win-rishab-yadav-after-winning-gold-at-world-archery-championships-202520250912031800-66000/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="867">
-      <c r="A867" t="inlineStr">
-        <is>
-          <t>https://www.newsx.com/education/rrb-group-d-exam-date-2025-out-check-official-cbt-exam-schedule-cbt-city-slip-cbt-admit-card-direct-link-62470/</t>
-        </is>
-      </c>
-    </row>
-    <row r="868">
-      <c r="A868" t="inlineStr">
-        <is>
-          <t>https://www.millenniumpost.in/nation/lop-singhar-criticises-mp-govt-over-fertiliser-crisis-police-action-on-farmers-626920</t>
-        </is>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/bhopal-digvijay-raised-questions-on-the-amount-being-given-to-the-ladli-sisters-said-does-this-money-come-f-2025-09-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/amp/bhopal-news/mp-news-digvijaya-singh-questions-on-ladli-behna-yojana-does-this-money-come-from-their-mama-house-19941697</t>
-        </is>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" t="inlineStr">
-        <is>
-          <t>https://www.ibc24.in/chhattisgarh/raipur/cg-news-tribal-development-authoritys-budget-increased-to-75-crores-3246057.html</t>
+          <t>https://mradubhashi.com/news.php?id=questions-about-the-functioning-of-municipal-corporations-cm-yogi-orders-review-of-mayors-powers-which-may-be-curtailed-576957</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A577"/>
+  <dimension ref="A1:A731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,35 +438,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
+          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ap7am.com/index.php/en/109483/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan</t>
+          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
+          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
@@ -480,63 +480,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
+          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
+          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
         </is>
       </c>
     </row>
@@ -557,14 +557,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/amp_articleshow/123993745.cms</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
@@ -585,28 +585,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
         </is>
       </c>
     </row>
@@ -634,3836 +634,4914 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167786</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/?amp=1</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
+          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday</t>
+          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/?amp=1</t>
+          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
+          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
+          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276011</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/amp/story/india%2Fkarnataka%2Fcentre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/amp/story/india%2Fagriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
+          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633463-relief-and-recovery-government-support-for-jks-rural-communities</t>
+          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
+          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k-13561833.html/amp</t>
+          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
+          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits?amp</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/amp/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/centre-to-provide-pm-kisan-relief-rs-76-crore-for-shgs-in-flood-hit-jammu-shivraj-singh-chouhan/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276011</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
+          <t>https://www.ptinews.com/detail/national/Local-bodies-in-MP-s-Raisen-passed-resolutions-supporting-One-Nation-One-Election-Chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.uniindia.com/photoes/638785.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://www.ptinews.com/detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pm-s-blessings-chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
+          <t>https://www.ptinews.com/editor-detail/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-bjp-mlas-meet.html</t>
+          <t>https://www.crosstownnews.in/post/147010/central-and-state-governments-take-all-necessary-steps-to-restore-livelihoods-bring-sufferers-out-of-this-disaster-shivraj-singh.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.news18.com/amp/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits?amp</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan?amp</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
+          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
+          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://www.socialnews.xyz/2025/09/16/new-delhi-shivraj-singh-chouhan-addresses-press-conference-gallery-2/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/local-bodies-in-mp-s-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3635568-madhya-pradesh-leads-with-one-nation-one-election-resolutions?amp</t>
+          <t>https://english.newsnationtv.com/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html/amp</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-J-K/2930370</t>
+          <t>https://english.newsnationtv.com/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.amp.html</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/19/del27-jk-chouhan-farmers.amp.html</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638786.html</t>
+          <t>https://www.latestly.com/agency-news/india-news-pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra-7115311.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638671.html</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638785.html</t>
+          <t>https://english.newsnationtv.com/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
+          <t>https://english.newsnationtv.com/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
+          <t>https://www.newsdrum.in/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan-10485478</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638668.html</t>
+          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-j-k/2746928/?amp</t>
+          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638670.html</t>
+          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638071.html</t>
+          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638735.html</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638794.html</t>
+          <t>https://indiapublickhabar.com/Agriculture/shivraj-singh-agricultural-growth-food-basket-india-2025/4795</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://neindiabroadcast.com/2025/09/20/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/new-delhi-shivraj-singh-chouhan-addresses-press-conference-gallery-2/</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/amp/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/new-delhi-shivraj-singh-chouhan-addresses-press-conference-on-gst-reforms-gallery/</t>
+          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/union-minister-shivraj-singh-chauhan-visits-flood-affected-area-budilya-brahman-jammu-region-5608</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday</t>
+          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AF%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95%E0%A5%87-%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2-%E0%A4%95%E0%A4%AE-%E0%A4%A8/ar-AA1tKoCZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative-7122123.html</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://menafn.com/1110086486/Over-5000-Rural-Houses-In-JK-To-Get-PMAY-Support-Minister</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/17/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/amp/</t>
+          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A5%88%E0%A4%B0-%E0%A4%AB-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%AA%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%8F%E0%A4%95%E0%A4%9C%E0%A5%81%E0%A4%9F-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1LuZyz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers-7119994.html</t>
+          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-7119481.html</t>
+          <t>https://www.msn.com/hi-in/news/other/kartikeya-wedding-photo-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%AF-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7%E0%A5%82%E0%A4%AE-%E0%A4%A5-%E0%A4%B0%E0%A4%95%E0%A4%A4-%E0%A4%A8%E0%A4%9C%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%A6-%E0%A4%A8-%E0%A4%82-%E0%A4%AC%E0%A4%B9%E0%A5%82/ar-AA1Aq18G?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%B6%E0%A4%95-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A4%B2-%E0%A4%97%E0%A4%88-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%A4-%E0%A4%88-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C%E0%A4%97-%E0%A4%A6-%E0%A4%B7-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%B8%E0%A4%96%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88/ar-AA1KGssn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html/amp</t>
+          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.takeonedigitalnetwork.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-hit-farmers-in-rs-pura-assures-full-compensation/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%9C%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A5%87%E0%A4%98%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%B2-%E0%A4%97-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87%E0%A4%AE%E0%A4%B2%E0%A4%AA-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%97-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%82%E0%A4%B8%E0%A5%82-%E0%A4%AA-%E0%A4%82%E0%A4%9B%E0%A4%95%E0%A4%B0-9-%E0%A4%B2-%E0%A4%96-%E0%A4%95-%E0%A4%AE%E0%A4%A6%E0%A4%A6-%E0%A4%A6/ar-AA1DBLvQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://mobilenews24x7.com/2025/business/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister/</t>
+          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan-10485478</t>
+          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-chauhan-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%AE%E0%A4%82%E0%A4%9A-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A6-%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%A6-%E0%A4%B2-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B2%E0%A4%97%E0%A4%A4-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82/ar-AA1G4kSw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html?utm_source=article_detail&amp;utm_medium=CRE&amp;utm_campaign=latestnews_CRE</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A5%82-%E0%A4%95%E0%A4%B6%E0%A5%8D%E0%A4%AE-%E0%A4%B0-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AB%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%B0%E0%A5%8D%E0%A4%AC-%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%82%E0%A4%A6%E0%A4%97-%E0%A4%B9-%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A4%E0%A4%AC-%E0%A4%B9/ar-AA1MT4zW</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%85%E0%A4%9A-%E0%A4%A8%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%A4%E0%A4%B8%E0%A5%8D%E0%A4%B5-%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%97%E0%A4%88%E0%A4%82-%E0%A4%B5-%E0%A4%AF%E0%A4%B0%E0%A4%B2/ar-AA1xALne?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
+          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/union-minister-shivraj-singh-chauhan-visits-flood-affected-area-budilya-brahman-jammu-region-5608</t>
+          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
+          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%9F-%E0%A4%B0%E0%A4%97%E0%A5%87%E0%A4%9F-%E0%A4%95%E0%A4%B0-%E0%A4%B0%E0%A4%B9-%E0%A4%AE-%E0%A4%B9%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A6%E0%A5%87-%E0%A4%A6-%E0%A4%A8%E0%A4%B8-%E0%A4%B9%E0%A4%A4/ar-AA1MqaDa?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/raisen-mp-fake-fertilizer-conflicting-statements-shivraj-singh-chouhan-aidal-singh-kansana-shock-farmers-9650353.html</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AF%E0%A5%87-%E0%A4%A8%E0%A4%9F%E0%A4%B5%E0%A4%B0%E0%A4%B2-%E0%A4%B2-%E0%A4%B9%E0%A5%88-%E0%A4%AB-%E0%A4%B0-%E0%A4%A7-%E0%A4%96%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%A4-%E0%A4%86%E0%A4%A8-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%9C%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%B8-%E0%A4%A7/ar-AA1xUk9d?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/gst-reduction-agriculture-machinery-shivraj-singh-meeting-benefits-for-farmers-2025/</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%94%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%89%E0%A4%AA%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%AD%E0%A4%B0-%E0%A4%B8-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87/ar-AA1u1cBq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.sudarshannews.in/news-detail.aspx?id=132584</t>
+          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.m.khaskhabar.com/news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%A4-%E0%A4%B8-%E0%A4%8F-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AF-%E0%A4%A6%E0%A4%97-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1MHFyB</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE-%E0%A4%A8%E0%A4%B9-%E0%A4%A8-%E0%A4%AE-%E0%A4%AE%E0%A4%B2-%E0%A4%B8%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%A6-%E0%A4%B0-%E0%A4%B9%E0%A4%A4-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%97%E0%A4%A4-%E0%A4%AA%E0%A5%87%E0%A4%B6-%E0%A4%B8%E0%A5%87-%E0%A4%9B%E0%A5%82%E0%A4%9F-%E0%A4%9C-%E0%A4%B0-%E0%A4%B0%E0%A4%96/ar-AA1BdzrP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/mp/bhopal/pc-sharma-said-shivraj-singh-announced-to-build-sita-mata-temple-in-sri-lanka-01595983.html</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF%E0%A5%82%E0%A4%B0-%E0%A4%AF-%E0%A4%86%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%97/ar-AA1Mqmi4?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.msn.com/hi-in/news/other/mgnrega-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AE%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6-%E0%A4%A4-%E0%A4%94%E0%A4%B0-%E0%A4%9C%E0%A4%B5-%E0%A4%AC%E0%A4%A6%E0%A5%87%E0%A4%B9-%E0%A4%95-%E0%A4%B8%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1uZF53?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
+          <t>https://hindi.krishijagran.com/news/strict-action-on-fake-fertilizers-seeds-only-quality-biostimulants-rabi-abhiyaan-2025-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%8F%E0%A4%AE%E0%A4%AA-%E0%A4%95%E0%A5%87-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%B8%E0%A4%B9-%E0%A4%A4-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%B0%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%B8%E0%A5%81%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%86%E0%A4%9C-%E0%A4%9C-%E0%A4%B0-%E0%A4%B9-%E0%A4%9A%E0%A5%81%E0%A4%95-%E0%A4%B9%E0%A5%88-%E0%A4%B5-%E0%A4%B0%E0%A4%82%E0%A4%9F/ar-AA1qUS4m?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
+          <t>https://www.bhaskarhindi.com/other/-110--1189364</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%9C-%E0%A4%A4-%E0%A4%87%E0%A4%9C%E0%A4%B0-%E0%A4%AF%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%A4-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%B9-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%AD-%E0%A4%97-%E0%A4%B2-%E0%A4%AF/ar-AA1Eqc4V?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/18/Agriculture-minister-to-hold-meeting-on-gst.php</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189280</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.php</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/madhya-pradesh/shivraj-singh-chouhan-on-a-visit-to-raisen-districphp/cid17449225.htm</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%88-%E0%A4%B8%E0%A4%82%E0%A4%B5%E0%A5%87%E0%A4%A6%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-cm-%E0%A4%86%E0%A4%A4-%E0%A4%B6-%E0%A4%95-%E0%A4%9A-%E0%A4%9F%E0%A5%8D%E0%A4%A0/ar-AA1wPCa5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B0-%E0%A4%B2-%E0%A4%AC-%E0%A4%9C-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%9B%E0%A5%82%E0%A4%9F-%E0%A4%97%E0%A4%8F-%E0%A4%AA-%E0%A4%9B%E0%A5%87/ar-AA1sCHcC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-said-we-will-help-the-farmers-by-conducting-a-survey-135973923.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/india-israel-%E0%A4%87%E0%A4%B8%E0%A5%8D%E0%A4%B0-%E0%A4%87%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%AA%E0%A5%82%E0%A4%B8-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%B8-%E0%A4%B0%E0%A4%B9/ar-AA1CvKsJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://rashtriyahindimail.in/posts/111331</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/Shivraj-singh-in-pusa.php</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AE%E0%A5%8D%E0%A4%B8%E0%A4%9F%E0%A5%87%E0%A4%95-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%95%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A5%81%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A4%88-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A/ar-AA1Cwv9k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
+          <t>https://www.msn.com/hi-in/news/other/mp-by-election-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%B0-%E0%A4%AE%E0%A4%A8-%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%A4-%E0%A4%B0/ar-AA1syDww?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
+          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/?amp</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
+          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%86%E0%A4%82%E0%A4%A6-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%AF-%E0%A4%A8-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%96%E0%A5%81%E0%A4%B2%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A4%B9-%E0%A4%AF%E0%A5%87-%E0%A4%AC-%E0%A4%A4%E0%A5%87%E0%A4%82/ar-AA1vC8f0?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%B2-%E0%A4%97-%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2-%E0%A4%B5-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%86%E0%A4%B2-%E0%A4%9A%E0%A4%A8-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1DqpoB?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskar.com/local/mp/vidisha/news/mla-tandon-submitted-a-6-point-demand-letter-for-the-development-of-vidisha-135938909.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/21/moral-responsibility-of-every-citizen-to-keep-his.html</t>
+          <t>https://www.bhaskar.com/local/punjab/amritsar/jandialaguru/news/meeting-with-the-union-minister-to-expand-the-scope-of-the-pradhan-mantri-awas-yojana-135954129.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rural-development-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A8-%E0%A4%B8%E0%A4%82%E0%A4%AD%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B5-%E0%A4%95%E0%A4%B8-%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1wUMo8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/amp/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6-%E0%A4%AE-%E0%A4%B2-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%AF-%E0%A4%97-%E0%A4%86%E0%A4%A6-%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A4%A8-%E0%A4%A5-%E0%A4%94%E0%A4%B0-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%9F%E0%A4%B6%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%87%E0%A4%B8-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%A6-%E0%A4%97%E0%A5%8D%E0%A4%97%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%AE-%E0%A4%B0-%E0%A4%8F%E0%A4%82%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%96%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A4%9F/ar-AA1z4w81?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/gst-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%B9-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%8F%E0%A4%82-%E0%A4%B2-%E0%A4%AD/ar-AA1MSiQO?ocid=finance-verthp-feeds</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1%E0%A4%BC%E0%A4%A6-%E0%A4%94%E0%A4%B0-%E0%A4%A4%E0%A5%81%E0%A4%85%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-msp-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1zzqhC?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.prabhasakshi.com/national/good-news-for-farmers-gst-saves-lakhs-on-tractors-and-harvester-shivraj-singh-chouhan-statement</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
+          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
+          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-in-rabi-festphp/cid17420755.htm</t>
+          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-raise-concern-over-bio-stimulant-1278916-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/Jammu-and-Kashmir/shivraj-chauhan-visits-flood-affected-in-rs-pura-php/cid17443231.htm</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%82%E0%A4%A7%E0%A5%81-%E0%A4%9C%E0%A4%B2-%E0%A4%B8%E0%A4%82%E0%A4%A7-%E0%A4%95-%E0%A4%B2%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%B8-%E0%A4%AE%E0%A4%B5-%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%B8%E0%A4%82%E0%A4%97%E0%A4%A0%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8/ar-AA1F0ALw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/21/moral-responsibility-of-every-citizen-to-keep-his.php</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/moral-responsibility-of-every-citizen-to-keep-hisphp/cid17452423.htm</t>
+          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/union-minister-shivraj-interacts-with-street-vendors-in-raisen-135977689.html</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.php</t>
+          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-said-we-will-help-the-farmers-by-conducting-a-survey-135973923.html</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/?amp</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
+          <t>https://lalluram.com/gst-new-slab-agricultural-equipment-union-agriculture-minister-shivraj-singh-on-new-gst-slabs/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
+          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/News/after-listening-to-the-farmers-shivraj-singh-called-the-collector</t>
+          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
+          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
+          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16?utm_source=rssfeed</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://upkiran.org/Shivraj-Singh-Chouhan-recounts-a-memorable-anecdote-about-a-side-of-PM-Modi-that-few-people-know</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/news/313264-Shivraj-Singh-Chouhan-meets-flood-affected-farmers-of-Jammu</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-110--1189364</t>
+          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-minister-in-action-to-ensure-farmers-benefit-from-gst-reduction-learn-more</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189280</t>
+          <t>https://makdaiexpress24.com/if-the-state-government-approves-a-big-announcement-of-the-agriculture-minister-soybean-will-be-purchased-on-support-price/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
+          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/shivraj-singh-chouhan-participated-in-a-cleanliness-drive-in-raisen-as-part-of-the-seva-pakhwada-4277570</t>
+          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday?amp</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-raise-concern-over-bio-stimulant-1278916-2025-09-17</t>
+          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/amp/buzz/buzz/pm-modi-75th-birthday-sewa-pakhwada-week-2025-live-updates-bjp-celebration-news-5913-5913</t>
+          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/andhra-pradesh/andhra-pradesh-shivraj-singh-chouhan-plants-75-saplings-on-pm-modis-birthday-4270902</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://thenewsmill.com/2025/09/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.thehawk.in/news/india/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/big-1/government-leave-no-stone-unturned-helping-farmers-shivraj-chauhan-told-flood-victims/</t>
+          <t>https://www.5dariyanews.com/news/467914-Shivraj-Singh-Chouhan-chairs-key-meeting-on-GST-reforms-for-agricultural-machinery</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/pm-modi-birthday-shivraj-singh-chouhan-launches-healthy-women-strong-family-campaign-plants-75-saplings-in-pus</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
+          <t>https://www.bhaskarhindi.com/other/new-delhi-mps-at-parliament-during-monsoon-session-1186493</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/kisan-aakrosh-morcha-met-union-agriculture-minister-shivraj-singh-chauhan-and-demands-to-start-the-work-of-ganjal-marand-dame/</t>
+          <t>https://divyakirti.com/archives/5675</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/jammu-kashmir/110-road-works-approved-udhampur-jitendra-singh-expresses-gratitude-shivraj-singh/</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop--4276499</t>
+          <t>https://www.bhaskar.com/mp-oth-mat-latest-neemuch-news-024503-2124969-nor.html</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/jammu-and-kashmir-shivraj-singh-chouhan-met-flood-affected-farmers</t>
+          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://www.5dariyanews.com/news/467662-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-held-in-Delhi-under-the-chairmanship-of-Shivra</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
+          <t>https://news24online.com/india/latest-news-trending-today-real-time-live-pm-modi-apple-iphone-17-sale-rrts-metro-corridor-rahul-gandhi-weather-update-russia-earthquake-donald-trump/635732/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
+          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/shivraj-singh-chouhan-noticed-a-cow-sitting-on-the-road-and-said-i-will-come-again-in-the-evening/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://lalluram.com/mp-news-union-agriculture-minister-shivraj-singh-chouhan-called-the-collector-in-sehore-and-directed-him-to-immediately-survey-the-damaged-crops/</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%AE-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%A4-%E0%A4%B9%E0%A4%AB-%E0%A4%9C%E0%A4%AE-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%9C-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-pm-kisan-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1N2dx0?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>http://www.msn.com/hi-in/news/other/karnataka-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%A8-%E0%A4%9F%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%87%E0%A4%A8-%E0%A4%AA-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1MXeLi?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%B8%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%95%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95/</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.outlookhindi.com/country/general/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-102444</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/agriculture-minister-to-hold-meeting-on-gstphp/cid17435327.htm</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://mediapassion.co.in/?p=67079</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://upkiran.org/Government-supports-flood-hit-Jammu-and-Kashmir-farmers</t>
+          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/shivraj-recalls-meeting-pm-modi-on-his-birthday-4270868</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
+          <t>https://www.aajsamaaj.com/agriculture-minister-asks-centre-to-help-in-removing-sand-from-fields-and-providing-wheat-seeds/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/?amp=1</t>
+          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
+          <t>https://hindi.latestly.com/india/school-assembly-news-headlines-for-18-september-national-international-sports-2756435.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://livevns.news/National/shivraj-singh-in-pusaphp/cid17424761.htm</t>
+          <t>https://www.betulupdate.com/tractor-gst-price-cut-new-machinery-rates-2025/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://lalluram.com/one-nation-one-election-public-representatives-of-raisen-district-submitted-a-letter-of-support-to-union-minister-shivraj/</t>
+          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/even-after-years-pm-modi-remains-connected-with-the-workers/115314/amp/</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.msn.com/en-in/news/India/farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-shivraj-singh-chouhan/ar-AA1MAvVi</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/quickly/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.samacharjagat.com/news/national/modi-government-is-now-going-to-bring-this-law-against-them-shivraj-chauhan-has-made-the-announcement-324290?fatafatnews</t>
+          <t>https://www.knskashmir.com/centre-always-stands-by-people-of-jandk-in-crisis--union-minister-198242</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://azadsipahi.in/09/2025/shivraj-chauhan-gave-birthday-wish-to-prime-minister-modi-the-story-of-the-first-meeting.html</t>
+          <t>https://www.aninews.in/news/national/general-news/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation20250922140426</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
+          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-minister-in-action-to-ensure-farmers-benefit-from-gst-reduction-learn-more</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
+          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
+          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://azadsipahi.in/09/2025/agriculture-minister-shivraj-chauhan-will-meet-tomorrow-for-gst-reforms-on-agricultural-machinery.html</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-emphasises-crop-diversification-for-a-sustainable-agricultural-system-enn25091803601</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/if-the-state-government-approves-a-big-announcement-of-the-agriculture-minister-soybean-will-be-purchased-on-support-price/</t>
+          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448-143406/amp/</t>
+          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership?amp</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/?amp=1&amp;utm_source=AMP&amp;utm_medium=AMP_HOME&amp;utm_campaign=AMP_NAV_LINKS&amp;utm_id=KJ_AMP_PAGES</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
+          <t>https://www.bignewsnetwork.com/news/278582056/defence-minister-rajnath-singh-shares-my-modi-story-on-pm-75th-birthday-praises-his-discipline-profound-knowledge</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html/amp</t>
+          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday?amp</t>
+          <t>https://www.socialnews.xyz/2025/09/20/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions?amp</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
+          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/17/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
+          <t>https://english.newsnationtv.com/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%A6%E0%A5%8B%E0%A4%AA%E0%A4%B9%E0%A4%B0-%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-541/</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
+          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
+          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/pm-kisan-20th-installment-%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%B8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%9D-%E0%A4%B2-%E0%A4%87%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%A8%E0%A4%A6-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A%E0%A5%87%E0%A4%97-20500-%E0%A4%95%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B0%E0%A5%81%E0%A4%AA%E0%A4%8F/ar-AA1JA7Hp</t>
+          <t>https://english.newsnationtv.com/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
+          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.etvbharat.com/hi/!bharat/centre-emphases-on-crop-diversification-for-sustainable-agricultural-system-hindi-news-hin25091803739</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=relief-from-farming-to-pocket-government-to-procure-these-5-major-kharif-crops-in-karnataka-577744</t>
+          <t>https://www.inhnews.in/News/bjp-leaders-of-the-country-shared-memorable-stories-of-pm-modi-you-should-also-read-them</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://www.msn.com/hi-in/news/other/agriculture-%E0%A4%A6%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%A4-%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%A6-%E0%A4%B5-%E0%A4%B0-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%B9-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%B0-%E0%A4%A1%E0%A4%AE%E0%A5%88%E0%A4%AA/ar-AA1MEFla?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/harda-district-congress-committee-submitted-a-memorandum-to-union-agriculture-minister-shivraj-singh-regarding-6-point-demands-of-farmers/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/agriculture-roadmap-prepared-according-to-geographical-and-climatic-conditions-of-states-hindi-news-hin25091703030</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-says-pralhad-joshi-swm-1280394-2025-09-20</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467983-Shivraj-Singh-Chouhan-visits-flood-affected-border-village-of-Badyal-Brahmana-in-RS-Pura-Jammu</t>
+          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/amp/467914-Shivraj-Singh-Chouhan-chairs-key-meeting-on-GST-reforms-for-agricultural-machinery</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.betulupdate.com/tractor-gst-price-cut-new-machinery-rates-2025/</t>
+          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://news24online.com/india/latest-news-trending-today-real-time-live-pm-modi-apple-iphone-17-sale-rrts-metro-corridor-rahul-gandhi-weather-update-russia-earthquake-donald-trump/635732/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://www.kisantak.in/crops/story/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-says-pralhad-joshi-swm-1280394-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://deshbandhump.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%BE-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.jammulinksnews.com/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://deshbandhump.com/%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%BE-%E0%A4%AA%E0%A4%96%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A4%BC%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-j-k-10479980</t>
+          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/amp/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.khabarwala24.com/national/seva-pakhwada-bjp-ruled-states-to-organize-various-programs-on-prime-minister-modis/101297/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://www.5dariyanews.com/news/467582-We-will-make-India-food-basket-of-the-world-Shivraj-Singh-Chouhan</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/amp/news/madhya-pradesh/raisen-mp-fake-fertilizer-conflicting-statements-shivraj-singh-chouhan-aidal-singh-kansana-shock-farmers-9650353.html</t>
+          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20?src=top-subnav-amp</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128/amp</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://m-hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-6-%E0%A4%AC%E0%A4%9C%E0%A5%87-6-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%96%E0%A4%AC%E0%A4%B0%E0%A5%87%E0%A4%82-%E0%A4%97%E0%A5%8D-%E0%A4%B5-%E0%A4%B2-%E0%A4%AF%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AD-%E0%A4%9A%E0%A5%82%E0%A4%B9-%E0%A4%82-%E0%A4%95-%E0%A4%86%E0%A4%82%E0%A4%A4%E0%A4%95-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%8F-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87/ar-AA1M0HhF?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.inhnews.in/news/bjp-leaders-of-the-country-shared-memorable-stories-of-pm-modi-you-should-also-read-them</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
+          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/breaking-news-in-hindi/liveblog/58166012.cms</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20?src=top-subnav</t>
+          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/amp/news/haryana/chandigarh-city-rahul-gandhi-habit-of-making-false-allegations-then-running-away-haryana-cm-nayab-singh-saini-on-vote-chori-9647747.html</t>
+          <t>https://rashtriyahindimail.in/posts/111292</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/hi/!bharat/centre-emphases-on-crop-diversification-for-sustainable-agricultural-system-hindi-news-hin25091803739</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/education/current-affairs/todays-current-affairs-in-hindi-for-21-september-2025</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218/amp</t>
+          <t>https://www.5dariyanews.com/hindi/news/312967-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/News/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://paliwalwani.com/delhi/shivraj-singh-chauhan-told-the-story-of-first-meeting-with-modi-ji</t>
+          <t>https://www.currentcrime.com/video-of-zubeen-garg-makes-everyone-cry/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation/amp-11758032543012.html</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.devdiscourse.com/article/politics/3628306-rahul-gandhi-visits-flood-hit-areas-in-amritsar-gurdaspur</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.socialnews.xyz/2025/09/15/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/amp/</t>
+          <t>https://www.socialnews.xyz/2025/09/17/surjewala-urges-centre-to-quickly-release-pending-3-36-lakh-mt-urea-to-karnataka-farmers/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html/amp</t>
+          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html/amp</t>
+          <t>https://www.socialnews.xyz/2025/09/18/cm-mohan-yadav-inaugurates-sandipani-school-in-katni-joins-cleanliness-drive-in-jabalpur/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/jammu-and-kashmir/on-the-instructions-of-pm-modi-the-central-government-became-active-in-helping-the-flood-affected-farmers-4275101</t>
+          <t>https://www.socialnews.xyz/2025/09/17/cong-observes-ex-mp-assembly-speaker-srinivas-tiwaris-100th-birth-anniversary-in-rewa/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/raisen-mein-shivraj-singh-ne-ek-rashtr-ek-chunav-ke-liye-janpratinidhiyon-ko-dilai-shapath/103967/</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.saahassamachar.in/shivraj-issues-stern-message-to-farmers-on-their-plight-issues-strict-instructions-to-sehore-collector</t>
+          <t>https://vocaltv.in/national/gst-bachat-utsav-begins-centre-leaderphp/cid17455799.htm</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630162-strategizing-himalayan-agriculture-calls-for-specialized-policies-and-education</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/centre-to-procure-green-gram--black-gram--sunflower-from-karnataka--union-minister-pralhad-joshi/2933070</t>
+          <t>https://www.msn.com/en-in/news/India/nath-began-bulldozer-action-after-honey-trap-case-shivraj-mohan-too-went-for-it-in-bhopal/ar-AA1u1IuG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
+          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.knskashmir.com/centre-always-stands-by-people-of-jandk-in-crisis--union-minister-198242</t>
+          <t>https://hindi.oneindia.com/videos/fertilizer-and-seed-shortage-in-vidisha-shivraj-singh-chouhan-cm-mohan-yadav-4264565.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267881</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.indiatodayne.in/amp/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
+          <t>https://www.ibc24.in/madhya-pradesh/peoples-representatives-of-raisen-district-passed-resolution-in-support-of-one-nation-one-election-shivraj-singh-chouhan-3262147.html</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/mds18-ka-joshi-crops.amp.html</t>
+          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/midday-news-545/</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-emphasises-crop-diversification-for-a-sustainable-agricultural-system-enn25091803601</t>
+          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://thekashmirhorizon.com/2025/09/20/union-agri-minister-chauhan-pledges-full-support-to-jk-farmers/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
+          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634626-central-approval-boosts-karnataka-farmers-with-price-support-scheme?amp</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%A6%E0%A5%8B%E0%A4%AA%E0%A4%B9%E0%A4%B0-%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-541/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1MOmec?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638734.html</t>
+          <t>https://hindi.etnownews.com/personal-finance/pm-kisan-21st-installment-without-land-documents-border-areas-farmers-can-still-benefit-from-pm-kisan-yojana-check-details-heree-article-152876946</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Bhagwant-Mann-assures-to-raise-arhtiyas-demands-with-Centre/2931607</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://statetimes.in/jda-cracks-down-on-unauthorised-construction-at-domana-nardani/</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.thekashmirmonitor.net/pm-stands-by-people-of-jk-chouhan/</t>
+          <t>https://www.tv9hindi.com/state/punjab/floods-wreak-havoc-in-punjab-farmland-disappear-demarcation-of-more-than-one-lakh-acres-land-is-over-3488020.html</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://m.sakshipost.com/amp/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
+          <t>https://www.amarujala.com/haryana/hisar/chief-minister-naib-singh-saini-said-adopt-diversification-in-agriculture-give-priority-to-coarse-cereals-hisar-news-c-21-hsr1020-715039-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
+          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/economy-and-business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-10478477</t>
+          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
+          <t>https://www.kisantak.in/politics/story/haryana-farmer-schemes-agriculture-diversification-nayab-singh-saini-prv-1280721-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/jitu-patwari-plays-down-internal-rift-claims-in-madhya-pradesh-congress</t>
+          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/amp/467664-National-Conference-on-Agriculture-%E2%80%93-Rabi-Campaign-2025-concludes-in-New-Delhi</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
+          <t>https://eng.ruralvoice.in/opinion/talks-on-us-tariffs-begin-again-will-tariffs-upend-indian-agriculture.html</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
+          <t>https://www.millenniumpost.in/business/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-says-chouhan-627425</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.editorji.com/amp/business-news/gst-reduction-on-farm-equipment-benefits-farmers-1758261712044</t>
+          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision?amp</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633463-relief-and-recovery-government-support-for-jks-rural-communities?amp</t>
+          <t>https://www.amarujala.com/business/business-diary/business-updates-fpi-rbi-share-market-usd-inr-value-commerce-trade-import-export-hindi-news-2025-09-23</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/gst-rate-cut-agri-minister-to-meet-farm-equipment-industry-on-sep-19-125091800798_1.html</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.wionews.com/business-economy/goods-and-services-tax-reforms-how-cheaper-will-tractors-get-minister-reveals-1758282747902/amp</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630162-strategizing-himalayan-agriculture-calls-for-specialized-policies-and-education?amp</t>
+          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630300-punjabs-plea-for-aid-restoring-flood-damaged-farmlands?amp</t>
+          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448?amp=1</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://www.prajasatta.in/himachal-news/cm-sukhu-said-that-punjab-and-haryana-should-play-a-role-in-supporting-the-interests-of-himachal/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation/amp-11758032543012.html</t>
+          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.msn.com/en-in/politics/government/brics-nations-launch-land-restoration-partnership-to-stop-desertification-and-soil-fertility-loss/ar-AA1Dbt7Q?ocid=BingNewsSerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/amp/</t>
+          <t>https://patnapress.com/bihar-self-employment-schemes-entrepreneurs/amp/?noamp=mobile</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://menafn.com/1110088234/Agriculture-Minister-Meets-Industry-Associations-On-Recent-GST-Cuts-For-Farm-Machinery</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
+          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu-7119481.html/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%B8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95-%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%B8/ar-AA1tsiMG?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister-1/amp/</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative-7122123.html/amp</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/amp/business/farmers-to-gain-as-agri-minister-pushes-gst-cut-benefit-for-tractors-equipment-articleshow-lipd50k</t>
+          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/agriculture-minister-to-hold-meeting-on-gstphp/cid17435350.htm</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/bhadohi/gyanpur/news/women-empowerment-campaign-in-bhadohi-135934797.html</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/?amp</t>
+          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
+          <t>https://www.livehindustan.com/bihar/banka/story-nda-workers-grand-meeting-in-shambhugan-bihar-development-and-women-empowerment-highlighted-201758491360340.html</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.amarujala.com/delhi-ncr/noida/positive-news-in-district-na-news-c-121-1-pbt1011-144312-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/index.php</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/hathras/chhauragadaua/news/special-honor-in-national-women-empowerment-workshop-135976706.html</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/?amp=1</t>
+          <t>https://www.amarujala.com/haryana/sonipat/gift-of-gymnasiums-indoor-gyms-and-womens-cultural-centre-sonipat-news-c-197-1-snp1001-142698-2025-09-23</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/agriculture-minister-asks-centre-to-help-in-removing-sand-from-fields-and-providing-wheat-seeds/</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/sultanpur/news/bike-rally-under-mission-shakti-in-sultanpur-135977475.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
+          <t>https://www.punjabkesari.com/uttar-pradesh/mission-shakti-5-0/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/amp/</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/gauriganj/story-mission-shakti-phase-5-launched-in-amethi-focus-on-women-s-safety-and-empowerment-201758384351430.html</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html/amp</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/agra/saiyan/news/mission-shakti-live-broadcast-of-chief-minister-from-lucknow-135969992.html</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
+          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://janaagaj.in/the-government-will-continue-to-work-with-dedication-for-women-empowerment-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
+          <t>https://khabardigital.com/india/what-did-prime-minister-modi-give-to-women-on-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://mpbreakingnews.in/chhattisgarh/annapurna-devi-met-cm-vishnudev-sai-discussed-women-empowerment-and-child-development-52-819875</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/agriculture-roadmap-prepared-according-to-geographical-and-climatic-conditions-of-states-hindi-news-hin25091703030</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0%E0%A4%AC-%E0%A4%95-%E0%A4%A8%E0%A5%8D%E0%A4%AB%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%B8-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-250-%E0%A4%B2-%E0%A4%96-%E0%A4%AE-%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%AC-%E0%A4%9C-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B0%E0%A4%96-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF/ar-AA1MEprL</t>
+          <t>https://lalluram.com/punjab-government-women-empowerment-scheme-1100-rupees-monthly-allowance/</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
+          <t>https://www.dotookmedia.com/2025/09/50_20.html</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://jantaserishta.com/delhi-ncr/delhi-cm-stresses-on-womens-health-and-empowerment-at-aiims-4279950</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/3-7-percent-growth-in-agriculture-sector-in-first-quarter-is-the-highest-in-the-world-chauhan/869080/?noamp=mobile&amp;amp</t>
+          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/</t>
+          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+          <t>https://sbharatnews.com/?p=139033</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
+          <t>https://janaagaj.in/teachers-should-develop-the-habit-of-reading-books-in-children-governor/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://federalbharat.com/national-resolution-of-healthy-women-strong-family-witness-gadkari-shared-the-historic-moment-of-noida/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://cg24news.in/cm-20949</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/news/312967-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
+          <t>https://newsheight.com/big-breaking-healthy-women-social-family/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/national/agriculture-minister-raised-the-issue-at-the-national-conference-on-agriculture-rabi-campaign-4273805</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://statetimes.in/amp/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
+          <t>https://devbhoomimedia.com/cm-dhami-in-kashipur-sammelan/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/centre-emphases-on-crop-diversification-for-sustainable-agricultural-system-hindi-news-hin25091803739</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
+          <t>https://bharat24live.com/news/bihar-nitish-government-will-transfer-5000-to-the-accounts-of-50-lakh-women-today</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/procurement-%E0%A4%AE%E0%A5%82%E0%A4%82%E0%A4%97%E0%A4%AB%E0%A4%B2-%E0%A4%94%E0%A4%B0-%E0%A4%B8-%E0%A4%AF-%E0%A4%AC-%E0%A4%A8-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%85%E0%A4%B5%E0%A4%A7-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A4%E0%A5%81%E0%A4%85%E0%A4%B0-%E0%A4%AE%E0%A4%B8%E0%A5%82%E0%A4%B0-%E0%A4%89%E0%A4%A1%E0%A4%BC%E0%A4%A6-%E0%A4%95-%E0%A4%B9-%E0%A4%97-100-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%96%E0%A4%B0-%E0%A4%A6/ar-AA1yKSox?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://bolchhattisgarh.in/chief-minister-sai-laid-the-foundation-stone-and-inaugurated-77-development-works-of-development-works-worth-rs-245-crore-80-lakh/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
+          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
+          <t>https://hindi.lifeberrys.com/state/delhi-ncr/the-modi-shah-duo-is-reportedly-preparing-to-pull-off-another-surprise-move--sudha-yadav-could-become-the-partys-first-female-national-president-243441.html</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+          <t>https://www.hindektatimes.com/204154/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://webvarta.com/states/other-state/sonipat-lado-lakshmi-yojana-mega-camp-2025/</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi</t>
+          <t>https://webvarta.com/states/other-state/haryana-cm-nayab-saini-sonipat-projects/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.prameyanews.com/news-post/nation/two-day-national-agriculture-conference-begins-to-strategise-for-rabi-season-2025</t>
+          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
+          <t>https://rajkajlive.com/chief-minister-dhami-inaugurated-the-exhibition-in-the-municipal-corporation/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+          <t>https://www.saahassamachar.in/fifth-phase-of-mission-shakti-to-commence-from-sharad-navratri-chief-minister</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
+          <t>https://www.rewariyasat.com/business/ladli-bahna-yojana-28th-installment-mp-484313</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
+          <t>https://news24online.com/business/pm-kisan-samman-nidhi-yojana-government-eases-rules-for-border-area-farmers-when-will-rs-2000-be-credited-details/638726/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://upstox.com/news/business-news/latest-updates/india-us-trade-talks-back-on-track-amid-tariff-tensions-positive-forward-looking/article-181419/</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://upstox.com/news/business-news/latest-updates/mother-dairy-to-pass-100-gst-benefit-cuts-prices-on-milk-paneer-butter-ghee-and-safal-foods/article-181384/</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://mediapassion.co.in/?p=66795</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15?utm_source=Internal_AT&amp;utm_medium=Article&amp;utm_name=Read_More</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/pusa-fourth-convocation-bihar-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%B5-%E0%A4%9A-%E0%A4%B0-%E0%A4%94%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%95-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%B5-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9/ar-AA1IMIBJ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.newspuran.com/blogs/mismanagement-of-fertilizer-without-assessment</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
+          <t>https://thebharatnow.in/others-state/centres-relief-plan-punjab-floods-declared-extreme-disaster-farmers-to-get-compensation-state-to-get-loan/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/evening-news-513/</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+          <t>https://www.timesbull.com/business/lado-laxmi-yojana-married-and-unmarried-women-will-get-rs-2100-govt-makes-big-announcement-608380.html</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/khategaon-mahila-bal-vikas-supervisor-amita-jat-and-project-officer-pranay-maheshwar-dispute-19950165</t>
+          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%B0-%E0%A4%A1%E0%A4%BC-%E0%A4%B2-%E0%A4%B2-%E0%A4%AE-%E0%A4%A3-%E0%A4%A8%E0%A5%87-vc-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%97-%E0%A4%A8%E0%A4%B5-%E0%A4%88-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%87%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A4%B9-56-%E0%A4%95%E0%A4%82%E0%A4%AA%E0%A4%A8-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-fir-%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%AE-%E0%A4%A8-%E0%A4%9F%E0%A4%B0-%E0%A4%82%E0%A4%97-%E0%A4%94%E0%A4%B0/ar-AA1KyF3w?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/krishi-mela-rabi-2025-to-be-held-in-hisar-on-september-21-22/?amp=1</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/kendriya-mantri-shivraj-ne-kisanon-ke-soybean-ki-fasal-kharab-hone-ki-shikayat-par-adhikari-ko-survey-ka-diya-nirdesh/103594/</t>
+          <t>https://m.economictimes.com/news/india/bollywoods-go-to-travel-destinations-youll-want-to-visit/london/slideshow/123943268.cms</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/news/trending/story/bijnor-farmer-electrocuted-in-field-villagers-block-highway-with-body-1280227-2025-09-20</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/paddy-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%B2-%E0%A4%A8%E0%A5%8D%E0%A4%9A-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A4%B2-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE-%E0%A4%8F%E0%A4%A1-%E0%A4%9F%E0%A5%87%E0%A4%A1-%E0%A4%A7-%E0%A4%A8-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%97-30-%E0%A4%A4%E0%A4%95-%E0%A4%87%E0%A4%9C-%E0%A4%AB-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1E8rJq?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.sakshipost.com/news/india-remains-heart-growth-journey-tech-firm-nothing-raises-200-million-452836</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers?amp</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/satna-maihar-daylight-robbery-8-lakh-lclk-strc-2333321-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
+          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/economy-and-business/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan</t>
+          <t>https://awaaz24x7.com/news/haryana-a-program-was-organized-in-panchkula-to-commemorate-maharaja-agrasen-jayanti-chief-minister-nayab-singh-saini-attended-and-extended-greetings-for-the-sharadiya-navratri</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/3-7-percent-growth-in-agriculture-sector-in-first-quarter-is-the-highest-in-the-world-chauhan/869080/</t>
+          <t>https://kalikumaunkhabar.com/uttarakhand/lohaghat-the-color-of-the-traders-brought-the-police-in-action-parking-passers-by-roads-of-municipality-and-pwd-upset</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/chandigarh-haryana/haryana-is-making-a-big-contribution-in-food-security-shyam-singh-rana-chandigarh-haryana-news-c-16-1-pkl1095-820762-2025-09-17</t>
+          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://himachalnownews.com/%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%97-%E0%A4%A8%E0%A5%80%E0%A4%A4%E0%A4%BF.html</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://hindi.theprint.in/india/rahul-gandhi-visits-flood-affected-areas-in-amritsar-and-gurdaspur-meets-victims/869119/</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A4%BC-%E0%A4%98-%E0%A4%9F-%E0%A4%B2-700-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%B2-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%A5-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%B8%E0%A5%82%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%82-150-%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-158-%E0%A4%95-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AE-%E0%A4%B2-%E0%A4%B8%E0%A4%AC%E0%A5%8D%E0%A4%B8-%E0%A4%A1/ar-AA1MCt9k</t>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
+          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://jantaserishta.com/delhi-ncr/when-did-the-opposition-talk-about-reforms-gajendra-singh-shekhawat-4279867</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
+          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/22/Uttarakhand-UKSSSC-Exam-Viral.html</t>
+          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
+          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/knowledge/story/international-rice-conference-to-be-held-at-bharat-mandapam-october-30-and-31-1280579-2025-09-21</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/latest-news/story/scientific-banana-ripening-facility-in-north-goa-to-boost-trade-swm-1280684-2025-09-21</t>
+          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/money/topstories/gst-reforms-to-inject-rs-2-lakh-cr-into-economy-boost-demand-across-sectors/ar-AA1MPDtb?ocid=finance-verthp-feeds</t>
+          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://smestreet.in/sectors/agriculture/gst-on-agricultural-machinery-tractors-tillers-harvesters-slashed-to-5-from-sept-22-10479641</t>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/latest-news/story/punjab-cm-bhagwant-mann-announces-price-cuts-for-verka-s-milk-and-cooperative-products-swm-1280239-2025-09-20</t>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-ministrys-special-campaign-5-0-will-start-from-october-2-work-will-be-done-on-e-waste-and-complaints/</t>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/north-india-heavy-rainfall-update-himachal-uttarakhand-cloudburst-landslide-dehradun-deaths-delhi-up-bihar-maharashtra-weather-alert-2025/</t>
+          <t>https://www.bhaskar.com/chh-rai-hmu-mat-latest-raipur-news-050504-1407740-nor.html</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/business/indian-agriculture-will-achieve-top-global-growth-of-37-in-q1-2025-26-4269188</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%A4%E0%A5%87%E0%A4%9C-%E0%A4%AF-%E0%A4%97-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-75-%E0%A4%9C-%E0%A4%B2-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%B5-%E0%A4%95%E0%A4%B8-%E0%A4%A4-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%AA-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8/ar-AA1MJ8ti</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://samacharsamrat.com/agriculture-ministry-to-inform-farmers-about-the-benefits-of-gst-rate-revision/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/agriculture-minister-raised-the-issue-at-the-national-conference-on-agriculture-rabi-campaign-4273805</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html/amp</t>
+          <t>https://www.bhaskarhindi.com/other/-75--1188144</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://annews.co.in/15476/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1186696</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.bhaskarhindi.com/other/pm-modi-addresses-the-nation-1189723</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
+          <t>https://sanjeevanisamachar.com/story-of-former-bihar-chief-minister-daroga-prasad-rai/</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://shekhawatilive.com/agriculture/gst-cut-tractors-farm-equipment-cheaper-farmers-benefit.html/</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198/amp</t>
+          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
+          <t>https://npg.news/amp/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/auspicious-time-to-buy-a-tractor-from-navratri-to-diwali/?amp=1</t>
+          <t>https://swatvasamachar.com/news/nawada-news-2224/</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/top-3-john-deere-tractor-models-in-india-price-and-features/?amp=1</t>
+          <t>https://rightnewsindia.com/himachal-pradesh-chief-ministers-advisor-launches-a-scathing-attack-on-politics/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/amp/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
+          <t>https://www.bhaskarhindi.com/other/news-1187827</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/amp/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/CM-Dr-Yadav-congratulated-PM-Modi-on-his-birthday.php</t>
+          <t>https://www.rajyasameeksha.com/politics</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/main-objective-of-skill-development-schemes-is-to.php</t>
+          <t>https://jantaserishta.com/local/telangana/the-chief-justice-of-the-high-court-urged-the-chief-minister-to-enhance-facilities-in-the-courts-4277697</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/chief-minister-nitish-kumar-expanded-the-chief-ministers-determination-self-help-allowance-scheme-in-bihar/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/industry/agriculture/gst-rate-cut-agri-minister-to-meet-farm-equipment-industry-on-sep-19-125091800798_1.html</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://khabarsameeksha.com/increased-facilities-in-doon-hospital-within-two-days-on-the-instructions-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
+          <t>https://theprint.in/india/hallmark-of-modis-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-bjp-leaders/2745143/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267881</t>
+          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-stands-with-jk-flood-victims-agriculture-minister-4275258</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/videos/national/CVBNCVBCVB</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=questions-about-the-functioning-of-municipal-corporations-cm-yogi-orders-review-of-mayors-powers-which-may-be-curtailed-576957</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/dewas-news-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%A8%E0%A5%8D-%E0%A4%A8-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%A8%E0%A4%97%E0%A5%8D%E0%A4%A8-%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%81%E0%A4%9F%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%B2-%E0%A4%B8%E0%A5%9C%E0%A4%95-%E0%A4%AA%E0%A4%B0-%E0%A4%9A%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%95%E0%A5%8D-%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9C%E0%A4%B0/ar-AA1It9zG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Rain-havoc-continues-in-Dehradun-one-student-died.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Security-forces-recovered-looted-weapons-in-Manipu.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Aim-to-make-India-a-leader-in-biofuel-and-green-tr.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>https://e-webcareit.com/cooperation-in-cooperation-programme-organised-at-raj-bhavan-two-important-agreements-signed-in-the-presence-of-governor-and-chief-minister</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Engineers-Research-and-Training-Institute-will-be.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>https://inanews.org/lucknow-agriculture-minister-attended-the-national-agriculture-conference--rabi-abhiyan-2025-in-new-delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>https://www.cnbctv18.com/economy/gst-new-rates-india-live-updates-two-slab-system-september-22-nirmala-sitharaman-gst-2-0-itc-council-reforms-5-18-40-pc-liveblog-19681684.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/stock-re-categorization/slideshow/123940116.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/india/cm-pushkar-singh-dhami-expressed-gratitude-to-the-cag-report-on-the-achievement-of-revenue-surplus-3493975.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>https://firstbihar.com/bihar/patna-news/advocates-will-get-5000-rs-per-month-stipend-in-bihar-nitish-kumar-government-announced-879143</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278588801/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>https://postmanindia.in/chief-minister-inaugurated-the-swachh-utsav-programme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/cms-emphasis-on-speeding-up-implementation-of-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/-75--1187799</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>https://rajpanchhi.com/posts/68d0f60ba09cd6cfc1b3f89e-H1QpM_-Ek-tree-%E2%80%94-mother-s-name-campaign-Chief-Minister-Bhajanlal-Sharma-gave-a-message-of-environmental-protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>https://shouryagatha.com/main-stories/himalayan-environmental-dialogue-program-speakers-took-various-measures-for-environmental-balance-in-the-desamvivi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>https://bolpanipat.com/cleanliness-is-the-only-way-to-have-a-healthy-and-prosperous-life-ceo-dr-kiran-singh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>https://knewsindia.in/big-breaking-2/major-relief-for-festivals-in-delhi-rekha-gupta-government-allows-loudspeakers-to-be-played-till-12-midnight/</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/chief-minister-wishes-the-people-of-the-state-on-himalaya-day-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>https://apnuuttarakhand.com/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>https://media24news.in/?p=90140</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>https://media24news.in/?p=90048</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>https://www.prameyanews.com/index.php/two-day-national-agriculture-conference-begins-to-strategise-for-rabi-season-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>https://media24news.in/?p=90190</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>https://www.5dariyanews.com/news/467745-Chander-Kumar-participates-in-national-conference-on-Kharif-Rabi-Campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>https://livevns.news/National/shivraj-singh-in-pusaphp/cid17424761.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/heavy-damage-to-soybean-crop-due-to-continuous-rain-and-waterlogging-in-sehore-135984420.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>https://sehorehulchal.com/news/farmers-devastated-by-double-attack-cm-helpline-flooded-with-complaints/</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/ces28-ar-agriculture-minister.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-yogi-adityanath-said-up-working-towards-viksit-uttar-pradesh-vision2047-24055474.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/raipur-news/cm-claims-gst-2-0-provides-relief-to-all-sections-tractors-19964857</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/video/madhya-pradesh/rewa/the-chief-minister-gave-a-gift-of-rs16231-crore-to-tyonthar-rewa-news-c-1-1-noi1337-3425344-2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-providing-the-best-fertilizers-seeds-and-pesticides-to-farmers-is-our-priority-dr-kirori-lal-news-hindi-1-753391-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>https://best24news.com/haryana/haryana-news-haryana-cm-saini-gave-a-big/</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>https://www.krishakjagat.org/national-news/gst-2-0-implemented-75-hp-tractors-will-be-cheaper-by-%E2%82%B963000-from-today-reducing-the-burden-on-farmers-pockets/</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%B9-%E0%A4%97-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A4-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%97-%E0%A4%B0-%E0%A4%B5%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9-%E0%A4%97-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1MTb2R?ocid=finance-verthp-feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/gst-cuts-from-22nd-september-ensure-benefits-reach-farmers-says-agriculture-minister-shivraj-singh-chouhan-ddb79</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>https://www.drishtiias.com/statepcs/17-09-2025/bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>https://dainiksaveratimes.com/national/national-agriculture-conference-rabi-abhiyan-2025-union-agriculture-minister-shivraj-chauhan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>https://spokesmanhindi.com/national/punjab/170925/central-government-releases-sdrf-funds-punjab-receives-advance-instal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-approves-110-road-projects-worth-rs-2000-crore-for-udhampur-4278710</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>https://makdaiexpress24.com/devotees-climbed-1063-stairs-to-seek-the-blessings-of-maihars-mother-sharda-and-pooja-mais-blessings-in-brahmamuhurta/</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A731"/>
+  <dimension ref="A1:A645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
@@ -466,42 +466,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630797-union-minister-chouhans-birthday-tribute-and-memoir-reflecting-on-modis-leadership</t>
+          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
         </is>
       </c>
     </row>
@@ -522,28 +522,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
+          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
         </is>
       </c>
     </row>
@@ -564,98 +564,98 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
+          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
+          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
+          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
@@ -669,98 +669,98 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/</t>
+          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
+          <t>https://krishijagran.com/news/centre-to-provide-pm-kisan-relief-rs-76-crore-for-shgs-in-flood-hit-jammu-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
+          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
+          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276011</t>
+          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
@@ -774,238 +774,238 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits?amp</t>
+          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
+          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276221</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Local-bodies-in-MP-s-Raisen-passed-resolutions-supporting-One-Nation-One-Election-Chouhan/2936291</t>
+          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638785.html</t>
+          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pm-s-blessings-chouhan/2929985</t>
+          <t>https://www.uniindia.com/photoes/638785.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
+          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.crosstownnews.in/post/147010/central-and-state-governments-take-all-necessary-steps-to-restore-livelihoods-bring-sufferers-out-of-this-disaster-shivraj-singh.html</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://www.uniindia.com/shivraj-assesses-damages-of-crops-in-jammu-announces-relief-measures-for-farmers-disaster-victims/north/news/3583526.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.uniindia.com/photoes/638787.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday/</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/new-delhi-shivraj-singh-chouhan-addresses-press-conference-gallery-2/</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
+          <t>https://menafn.com/1110074178/Shivraj-Singh-Chouhan-Plants-75-Saplings-To-Mark-PM-Modis-Birthday</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu20250919170904</t>
+          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
+          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/india-news-pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra-7115311.html</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan-10485478</t>
+          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits</t>
         </is>
       </c>
     </row>
@@ -1026,56 +1026,56 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
+          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
+          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://indiapublickhabar.com/Agriculture/shivraj-singh-agricultural-growth-food-basket-india-2025/4795</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
         </is>
       </c>
     </row>
@@ -1089,91 +1089,91 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111289</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/union-minister-shivraj-singh-chauhan-visits-flood-affected-area-budilya-brahman-jammu-region-5608</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-politics-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AD-%E0%A4%B0%E0%A5%8D%E0%A4%97%E0%A4%B5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%AF%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5-%E0%A4%B8-%E0%A4%8F%E0%A4%AE-%E0%A4%95%E0%A5%87-%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2-%E0%A4%95%E0%A4%AE-%E0%A4%A8/ar-AA1tKoCZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
@@ -1187,854 +1187,854 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/shivraj-singh-%E0%A4%85%E0%A4%AE%E0%A5%87%E0%A4%B0-%E0%A4%95-%E0%A4%9F%E0%A5%88%E0%A4%B0-%E0%A4%AB-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%9A-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B5%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%AA%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%85%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%8F%E0%A4%95%E0%A4%9C%E0%A5%81%E0%A4%9F-%E0%A4%B9-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9-%E0%A4%8F/ar-AA1LuZyz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
+          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/kartikeya-wedding-photo-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%A1%E0%A4%BC%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%AF-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7%E0%A5%82%E0%A4%AE-%E0%A4%A5-%E0%A4%B0%E0%A4%95%E0%A4%A4-%E0%A4%A8%E0%A4%9C%E0%A4%B0-%E0%A4%86%E0%A4%88-%E0%A4%A6-%E0%A4%A8-%E0%A4%82-%E0%A4%AC%E0%A4%B9%E0%A5%82/ar-AA1Aq18G?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%95-%E0%A4%9F%E0%A4%A8-%E0%A4%B6%E0%A4%95-%E0%A4%A1-%E0%A4%B2%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C%E0%A4%B2-%E0%A4%97%E0%A4%88-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%9C%E0%A4%A4-%E0%A4%88-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C%E0%A4%97-%E0%A4%A6-%E0%A4%B7-%E0%A4%AF-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%B8%E0%A4%96%E0%A5%8D%E0%A4%A4-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A4%B5-%E0%A4%88/ar-AA1KGssn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/lifestyle/travel/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A5%87%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B6-%E0%A4%A6-%E0%A4%9C-%E0%A4%A7%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A5%87-%E0%A4%87%E0%A4%B8-%E0%A4%AE%E0%A4%B9%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%81%E0%A4%88-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AA%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B0-%E0%A4%AF-%E0%A4%B2-%E0%A4%96-%E0%A4%82-%E0%A4%B0%E0%A5%81%E0%A4%95%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-100-%E0%A4%AC-%E0%A4%B0-%E0%A4%B8-%E0%A4%9A%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87/ar-AA1AqGiS?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%9C%E0%A4%A1%E0%A4%BC-%E0%A4%AC%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A5%87%E0%A4%98%E0%A4%B0-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%B2-%E0%A4%97-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87%E0%A4%AE%E0%A4%B2%E0%A4%AA-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%97-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%82%E0%A4%B8%E0%A5%82-%E0%A4%AA-%E0%A4%82%E0%A4%9B%E0%A4%95%E0%A4%B0-9-%E0%A4%B2-%E0%A4%96-%E0%A4%95-%E0%A4%AE%E0%A4%A6%E0%A4%A6-%E0%A4%A6/ar-AA1DBLvQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A5%82-%E0%A4%95%E0%A4%B6%E0%A5%8D%E0%A4%AE-%E0%A4%B0-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AD-%E0%A4%B5-%E0%A4%A4-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%AB%E0%A4%B8%E0%A4%B2%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%B0%E0%A5%8D%E0%A4%AC-%E0%A4%A6-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%82%E0%A4%A6%E0%A4%97-%E0%A4%B9-%E0%A4%A4-%E0%A4%B9%E0%A5%88-%E0%A4%A4%E0%A4%AC-%E0%A4%B9/ar-AA1MT4zW</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
+          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
+          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
+          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
+          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/short-video/jammu-3/union-minister-shivraj-singh-chouhan-arrives-at-jammu-airport-receives-a-grand-welcome-from-bjp-workers-19958336</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
+          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AF%E0%A5%87-%E0%A4%A8%E0%A4%9F%E0%A4%B5%E0%A4%B0%E0%A4%B2-%E0%A4%B2-%E0%A4%B9%E0%A5%88-%E0%A4%AB-%E0%A4%B0-%E0%A4%A7-%E0%A4%96%E0%A5%87-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AE%E0%A4%A4-%E0%A4%86%E0%A4%A8-%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%9A-%E0%A4%B9-%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%9C%E0%A4%B0-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%B6-%E0%A4%A8-%E0%A4%B8-%E0%A4%A7/ar-AA1xUk9d?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-on-womenphp/cid17431466.htm</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
+          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%B8-%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%A4-%E0%A4%B8-%E0%A4%8F-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%81%E0%A4%A8-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%AF-%E0%A4%A6%E0%A4%97-%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95-%E0%A4%95-%E0%A4%B8%E0%A5%8D%E0%A4%B8/ar-AA1MHFyB</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
+          <t>https://vocaltv.in/national/agriculture-minister-to-hold-meeting-on-gstphp/cid17435350.htm</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.php</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/Shivraj-singh-in-pusa.php</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mgnrega-%E0%A4%97%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%A3-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%AE%E0%A4%A8%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%95-%E0%A4%B8%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6-%E0%A4%A4-%E0%A4%94%E0%A4%B0-%E0%A4%9C%E0%A4%B5-%E0%A4%AC%E0%A4%A6%E0%A5%87%E0%A4%B9-%E0%A4%95-%E0%A4%B8%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%A6-%E0%A4%8F-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6/ar-AA1uZF53?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/strict-action-on-fake-fertilizers-seeds-only-quality-biostimulants-rabi-abhiyaan-2025-shivraj-singh/</t>
+          <t>https://www.bhaskarhindi.com/other/-2025-26-36250--1187634</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
+          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://www.inhnews.in/news/after-listening-to-the-farmers-shivraj-singh-called-the-collector</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-110--1189364</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
+          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
+          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/18/Agriculture-minister-to-hold-meeting-on-gst.php</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189280</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.php</t>
+          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-said-we-will-help-the-farmers-by-conducting-a-survey-135973923.html</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111331</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/Shivraj-singh-in-pusa.php</t>
+          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AE%E0%A5%8D%E0%A4%B8%E0%A4%9F%E0%A5%87%E0%A4%95-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%95-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%95%E0%A4%B2-%E0%A4%A8%E0%A5%87%E0%A4%AA-%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A5%81%E0%A4%9F%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A4%88-%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B9-%E0%A4%97-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A/ar-AA1Cwv9k?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mp-by-election-%E0%A4%AC%E0%A5%81%E0%A4%A7%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B0%E0%A4%AE-%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95%E0%A5%87-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%A7-%E0%A4%95-%E0%A4%B0-%E0%A4%B5-%E0%A4%9C%E0%A4%AF%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%B0-%E0%A4%AE%E0%A4%A8-%E0%A4%B5-%E0%A4%B8-%E0%A4%95-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%A8%E0%A5%87-%E0%A4%89%E0%A4%A4-%E0%A4%B0/ar-AA1syDww?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/?amp</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
+          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%B8%E0%A4%AE%E0%A5%87%E0%A4%A4-%E0%A4%B8%E0%A4%AD-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%AA-%E0%A4%A1%E0%A4%BC-%E0%A4%A4-%E0%A4%82-%E0%A4%95-%E0%A4%A6%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-pm-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%AC-%E0%A4%AE-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B2-%E0%A4%AD-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1MIJWd</t>
+          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
+          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/vidisha/news/mla-tandon-submitted-a-6-point-demand-letter-for-the-development-of-vidisha-135938909.html</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/amritsar/jandialaguru/news/meeting-with-the-union-minister-to-expand-the-scope-of-the-pradhan-mantri-awas-yojana-135954129.html</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://www.gaonjunction.com/khabar-junction/jammu-and-kashmir-shivraj-singh-chouhan-met-flood-affected-farmers</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/good-news-for-farmers-gst-saves-lakhs-on-tractors-and-harvester-shivraj-singh-chouhan-statement</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://lalluram.com/gst-new-slab-agricultural-equipment-union-agriculture-minister-shivraj-singh-on-new-gst-slabs/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
+          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/madhya-pradesh/union-minister-shivraj-singh-chouhan-praises-one-nation-one-election-bill-4277664</t>
+          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/shivraj-singh-chouhan-raise-concern-over-bio-stimulant-1278916-2025-09-17</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
+          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/agriculture-minister-shivraj-chauhan-important-meeting-benefit-from-gst/</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/others/shivraj-singh-chouhan-directed-officials-to-conduct-a-survey-on-complaints-of-damaged-soybean-crop-4276576</t>
+          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://lalluram.com/gst-new-slab-agricultural-equipment-union-agriculture-minister-shivraj-singh-on-new-gst-slabs/</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/government-stands-with-the-flood-affected-farmers-agriculture-minister-shivraj-chauhan/</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-narendra-modi-shivraj-singh-chouhan-milk-dairy-farmers-sugarcane-farmers-yogi-adityanath-live</t>
+          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
@@ -2048,3500 +2048,2898 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
+          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
+          <t>https://www.5dariyanews.com/news/467697-Shivraj-Singh-Chouhan-Plants-75-Saplings-at-ICAR-to-Mark-PM-Modis-75th-Birthday</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-minister-in-action-to-ensure-farmers-benefit-from-gst-reduction-learn-more</t>
+          <t>https://www.5dariyanews.com/news/467914-Shivraj-Singh-Chouhan-chairs-key-meeting-on-GST-reforms-for-agricultural-machinery</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
+          <t>https://www.5dariyanews.com/news/467662-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-held-in-Delhi-under-the-chairmanship-of-Shivra</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/if-the-state-government-approves-a-big-announcement-of-the-agriculture-minister-soybean-will-be-purchased-on-support-price/</t>
+          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.patrika.com/bhopal-news/notification-issued-to-change-the-name-of-alirajpur-district-to-aalirajpur-19947549</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3630799-tales-of-leadership-rajnath-singh-and-others-share-modi-stories-on-pms-75th-birthday?amp</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative/</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467914-Shivraj-Singh-Chouhan-chairs-key-meeting-on-GST-reforms-for-agricultural-machinery</t>
+          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
+          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-mps-at-parliament-during-monsoon-session-1186493</t>
+          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://divyakirti.com/archives/5675</t>
+          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
+          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/rewa-cm-mohan-yadav-jijaji-song-by-lokgayika-rakhi-local18-9622572.html</t>
+          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/mp-oth-mat-latest-neemuch-news-024503-2124969-nor.html</t>
+          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>http://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
+          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467662-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-held-in-Delhi-under-the-chairmanship-of-Shivra</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://news24online.com/india/latest-news-trending-today-real-time-live-pm-modi-apple-iphone-17-sale-rrts-metro-corridor-rahul-gandhi-weather-update-russia-earthquake-donald-trump/635732/</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Cente-J-K-govt-will-bring-farmers-out-of-flood-disaster-with-PM-s-blessings-Chouhan/2929985</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
+          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://www.newsdrum.in/national/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-union-minister-pralhad-joshi-10482514</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.thehawk.in/news/economy-and-business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B8-%E0%A4%AE-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95-%E0%A4%A4-%E0%A4%B9%E0%A4%AB-%E0%A4%9C%E0%A4%AE-%E0%A4%A8-%E0%A4%95%E0%A5%87-%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%9C-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B0-%E0%A4%AD-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%97-pm-kisan-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1N2dx0?ocid=finance-verthp-feeds</t>
+          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/karnataka-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%A8-%E0%A4%9F%E0%A4%95-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%85%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%87%E0%A4%A8-%E0%A4%AA-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%96%E0%A4%B0-%E0%A4%AB-%E0%A4%AB%E0%A4%B8%E0%A4%B2-%E0%A4%82-%E0%A4%95-%E0%A4%96%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%97-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1MXeLi?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
+          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
+          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
+          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://hindi.ianslive.in/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali--20250922133554</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/agriculture-minister-asks-centre-to-help-in-removing-sand-from-fields-and-providing-wheat-seeds/</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/school-assembly-news-headlines-for-18-september-national-international-sports-2756435.html</t>
+          <t>https://mradubhashi.com/news.php?id=relief-from-farming-to-pocket-government-to-procure-these-5-major-kharif-crops-in-karnataka-577744</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.betulupdate.com/tractor-gst-price-cut-new-machinery-rates-2025/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
+          <t>https://dainiksaveratimes.com/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-shivraj-singh-chouhan/ar-AA1MAvVi</t>
+          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
+          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.knskashmir.com/centre-always-stands-by-people-of-jandk-in-crisis--union-minister-198242</t>
+          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
+          <t>https://www.5dariyanews.com/news/467582-We-will-make-India-food-basket-of-the-world-Shivraj-Singh-Chouhan</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation20250922140426</t>
+          <t>https://patnapress.com/bihar-assembly-horse-trading-scandal-bjp-mla-questioned/amp/?noamp=mobile</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
+          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-emphasises-crop-diversification-for-a-sustainable-agricultural-system-enn25091803601</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Arrest-of-Mehraj-Malik-is-illegal.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
+          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://www.patrika.com/bhopal-news/mp-got-golden-banyan-award-honoured-by-union-minister-gajendra-singh-shekhawat-at-heritage-tourism-best-state-category-19945617</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rain-alert-in-8-districts-imd-issues-warning-19964265</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278582056/defence-minister-rajnath-singh-shares-my-modi-story-on-pm-75th-birthday-praises-his-discipline-profound-knowledge</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rainfall-in-next-12-hours-alert-issued-in-3-districts-warns-imd-19953418</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://rashtriyahindimail.in/posts/111292</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://www.patrika.com/bhopal-news/2-big-mines-of-mp-will-yield-gold-after-singrauli-this-district-is-preparing-gold-mine-in-mp-19951211</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-northlines/20250920/281487872510068</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://mradubhashi.com/news.php?id=forest-minister-kedar-kashyap-paid-tribute-to-bharat-ratna-visvesvaraya-576675</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
+          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
+          <t>https://www.currentcrime.com/video-of-zubeen-garg-makes-everyone-cry/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
+          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://www.dailypioneer.com/2025/india/chouhan-inspects-damaged-farms-in-j-k.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
+          <t>https://patnapress.com/eci-mandates-ai-election-content-labels/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
+          <t>https://patnapress.com/foreign-pilgrims-russia-ukraine-gaya-ancestral-rites/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://patnapress.com/solar-eclipse-live-stream-2025/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://patnapress.com/pawan-singh-bihar-2025-elections-reality-show-exit/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
+          <t>https://patnapress.com/solar-eclipse-september-2025/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://patnapress.com/navratri-2025-goddess-shailputri-traditional-offerings/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://patnapress.com/nitish-kumar-construction-workers-aid/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
+          <t>https://www.socialnews.xyz/2025/09/19/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/centre-emphases-on-crop-diversification-for-sustainable-agricultural-system-hindi-news-hin25091803739</t>
+          <t>https://patnapress.com/patna-ipsowa-tree-festival-bihta/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/News/bjp-leaders-of-the-country-shared-memorable-stories-of-pm-modi-you-should-also-read-them</t>
+          <t>https://www.socialnews.xyz/2025/09/20/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/agriculture-%E0%A4%A6%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%A4-%E0%A4%B2%E0%A4%B9%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%A6-%E0%A4%B5-%E0%A4%B0-%E0%A4%AC%E0%A4%A2%E0%A4%BC-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%B9-%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B2-%E0%A4%A8-%E0%A4%82%E0%A4%97-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%B0-%E0%A4%A1%E0%A4%AE%E0%A5%88%E0%A4%AA/ar-AA1MEFla?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/agriculture-roadmap-prepared-according-to-geographical-and-climatic-conditions-of-states-hindi-news-hin25091703030</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
+          <t>https://www.socialnews.xyz/2025/09/17/cong-observes-ex-mp-assembly-speaker-srinivas-tiwaris-100th-birth-anniversary-in-rewa/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
+          <t>https://patnapress.com/pawan-kumar-bhimappa-bajantri-sworn-in-patna-high-court-chief-justice/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/this-is-how-agriculture-minister-shivraj-chauhan-met-pm-modi-for-the-first-time/</t>
+          <t>https://vocaltv.in/national/gst-bachat-utsav-begins-centre-leaderphp/cid17455799.htm</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://www.newstak.in/bihar/story/chirag-paswan-bihar-nda-seat-sharing-statement-3203457-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-says-pralhad-joshi-swm-1280394-2025-09-20</t>
+          <t>https://insiderlive.in/bihar-election-2025-congress-candidate-selection-seat-sharing/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AE%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%BE-%E0%A4%85%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%87%E0%A4%A8-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80/</t>
+          <t>https://insiderlive.in/bihar-goreyakothi-vidhansabha-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B8%E0%A5%87%E0%A4%B5%E0%A4%BE-%E0%A4%AA%E0%A4%96%E0%A4%B5%E0%A4%BE%E0%A4%A1%E0%A4%BC%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
+          <t>https://insiderlive.in/bihar-baniapur-vidhan-sabha-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
+          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/seva-pakhwada-bjp-ruled-states-to-organize-various-programs-on-prime-minister-modis/101297/</t>
+          <t>https://mp.punjabkesari.in/national/news/scindia-s-statement-regarding-the-roads-of-mp-2213041</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467582-We-will-make-India-food-basket-of-the-world-Shivraj-Singh-Chouhan</t>
+          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
+          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/bjp-leaders-of-the-country-shared-memorable-stories-of-pm-modi-you-should-also-read-them</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111292</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://ianslive.in/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister--20250919175149</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/hindi/news/312967-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
+          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
+          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.currentcrime.com/video-of-zubeen-garg-makes-everyone-cry/</t>
+          <t>https://www.newsdrum.in/business/farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan-10467830</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation/amp-11758032543012.html</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628306-rahul-gandhi-visits-flood-hit-areas-in-amritsar-gurdaspur</t>
+          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/17/surjewala-urges-centre-to-quickly-release-pending-3-36-lakh-mt-urea-to-karnataka-farmers/</t>
+          <t>https://theindianawaaz.com/gst-cut-on-farm-equipment-must-benefit-farmers-directly-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
+          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/18/cm-mohan-yadav-inaugurates-sandipani-school-in-katni-joins-cleanliness-drive-in-jabalpur/</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/17/cong-observes-ex-mp-assembly-speaker-srinivas-tiwaris-100th-birth-anniversary-in-rewa/</t>
+          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/gst-bachat-utsav-begins-centre-leaderphp/cid17455799.htm</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13875</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/nath-began-bulldozer-action-after-honey-trap-case-shivraj-mohan-too-went-for-it-in-bhopal/ar-AA1u1IuG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/fertilizer-and-seed-shortage-in-vidisha-shivraj-singh-chouhan-cm-mohan-yadav-4264565.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267881</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/madhya-pradesh/peoples-representatives-of-raisen-district-passed-resolution-in-support-of-one-nation-one-election-shivraj-singh-chouhan-3262147.html</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/shadol-umariya-senior-citizen-pensioners-association-demand-for-payment-of-dearness-allowance-memorandum-to-chief-minister/</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
+          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.aajsamaaj.com/agriculture-minister-asks-centre-to-help-in-removing-sand-from-fields-and-providing-wheat-seeds/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
+          <t>https://www.newspuran.com/blogs/mismanagement-of-fertilizer-without-assessment</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/</t>
+          <t>https://www.kadwaghut.com/?p=260993</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%A6%E0%A5%8B%E0%A4%AA%E0%A4%B9%E0%A4%B0-%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-541/</t>
+          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%B8%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%87-%E0%A4%AE-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-gst-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%8F%E0%A4%95%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1MOmec?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://hindi.etnownews.com/personal-finance/pm-kisan-21st-installment-without-land-documents-border-areas-farmers-can-still-benefit-from-pm-kisan-yojana-check-details-heree-article-152876946</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://hindi.krishijagran.com/news/gst-reduction-agriculture-machinery-shivraj-singh-meeting-benefits-for-farmers-2025/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://birsabhumi.com/gst-reduction-agricultural-machinery-prices-drop/</t>
+          <t>https://www.millenniumpost.in/business/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-says-chouhan-627425</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/punjab/floods-wreak-havoc-in-punjab-farmland-disappear-demarcation-of-more-than-one-lakh-acres-land-is-over-3488020.html</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/hisar/chief-minister-naib-singh-saini-said-adopt-diversification-in-agriculture-give-priority-to-coarse-cereals-hisar-news-c-21-hsr1020-715039-2025-09-22</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.ptinews.com/editor-detail/kerala-governor--cm-wish-pm-modi-on-his-75th-birthday/2921961</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/haryana-farmer-schemes-agriculture-diversification-nayab-singh-saini-prv-1280721-2025-09-21</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
+          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/opinion/talks-on-us-tariffs-begin-again-will-tariffs-upend-indian-agriculture.html</t>
+          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/business/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-says-chouhan-627425</t>
+          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://thebikanernews.in/rajasthan/to-address-the-legitimate-demands-of-the-employees-working/cid17435615.htm</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://www.kadwaghut.com/?p=260445</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/business-updates-fpi-rbi-share-market-usd-inr-value-commerce-trade-import-export-hindi-news-2025-09-23</t>
+          <t>https://samacharnama.com/states/himachal-pradesh-news/punjab-haryana-should-work-like-big-brothers-to-support/cid17420227.htm</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://www.global-agriculture.com/india-region/prime-minister-modi-lays-foundation-stone-of-indias-first-pm-mitra-park-in-madhya-pradesh/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
+          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
+          <t>https://thecsrjournal.in/bihar-mukhyamantri-mahila-rojgar-yojana-hindi/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.prajasatta.in/himachal-news/cm-sukhu-said-that-punjab-and-haryana-should-play-a-role-in-supporting-the-interests-of-himachal/</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/politics/government/brics-nations-launch-land-restoration-partnership-to-stop-desertification-and-soil-fertility-loss/ar-AA1Dbt7Q?ocid=BingNewsSerp&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://patnapress.com/bihar-self-employment-schemes-entrepreneurs/amp/?noamp=mobile</t>
+          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/hathras/chhauragadaua/news/special-honor-in-national-women-empowerment-workshop-135976706.html</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://www.jagran.com/bihar/patna-city-bihar-govt-jobs-women-entrepreneurship-nitish-kumar-employement-drive-24050839.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%A6-%E0%A4%B5-%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%86%E0%A4%AF-%E0%A4%AE-%E0%A4%9D-%E0%A4%B2%E0%A4%A1%E0%A4%BC%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A8-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%95-%E0%A4%AA%E0%A5%88%E0%A4%B8-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A5%88%E0%A4%B8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95-%E0%A4%95%E0%A4%B0-%E0%A4%B8%E0%A4%95%E0%A4%A4%E0%A5%87-%E0%A4%B9%E0%A5%88%E0%A4%82-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%9F%E0%A4%B8/ar-AA1tsiMG?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://khabardigital.com/india/what-did-prime-minister-modi-give-to-women-on-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/bhadohi/gyanpur/news/women-empowerment-campaign-in-bhadohi-135934797.html</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
+          <t>https://livevns.news/Top-Headlines/cm-yogi-launches-mission-shakti-50-special-program-in/cid17447412.htm</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/bihar/banka/story-nda-workers-grand-meeting-in-shambhugan-bihar-development-and-women-empowerment-highlighted-201758491360340.html</t>
+          <t>https://khatpatnews.com/?p=61931</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
+          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/delhi-ncr/noida/positive-news-in-district-na-news-c-121-1-pbt1011-144312-2025-09-21</t>
+          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/hathras/chhauragadaua/news/special-honor-in-national-women-empowerment-workshop-135976706.html</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/sonipat/gift-of-gymnasiums-indoor-gyms-and-womens-cultural-centre-sonipat-news-c-197-1-snp1001-142698-2025-09-23</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/sultanpur/news/bike-rally-under-mission-shakti-in-sultanpur-135977475.html</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/uttar-pradesh/mission-shakti-5-0/</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/gauriganj/story-mission-shakti-phase-5-launched-in-amethi-focus-on-women-s-safety-and-empowerment-201758384351430.html</t>
+          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/agra/saiyan/news/mission-shakti-live-broadcast-of-chief-minister-from-lucknow-135969992.html</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
+          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
+          <t>https://amanyatralive.com/%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C%E0%A4%BC-5-%E0%A4%95%E0%A4%BE-%E0%A4%B6%E0%A5%81%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://janaagaj.in/the-government-will-continue-to-work-with-dedication-for-women-empowerment-chief-minister/</t>
+          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/what-did-prime-minister-modi-give-to-women-on-his-birthday/</t>
+          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
+          <t>https://www.hindektatimes.com/204154/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/chhattisgarh/annapurna-devi-met-cm-vishnudev-sai-discussed-women-empowerment-and-child-development-52-819875</t>
+          <t>https://aavaj.com/jaunpur/jaunpur-news-%E0%A4%9C%E0%A5%8C%E0%A4%A8%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C-5-0-%E0%A4%95/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://www.rewariyasat.com/business/ladli-bahna-yojana-28th-installment-mp-484313</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://www.newstak.in/utility-news/story/pm-kisan-21st-installment-update-notification-2025-3202470-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://lalluram.com/punjab-government-women-empowerment-scheme-1100-rupees-monthly-allowance/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.dotookmedia.com/2025/09/50_20.html</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/delhi-cm-stresses-on-womens-health-and-empowerment-at-aiims-4279950</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://sbharatnews.com/?p=139033</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://janaagaj.in/teachers-should-develop-the-habit-of-reading-books-in-children-governor/</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://federalbharat.com/national-resolution-of-healthy-women-strong-family-witness-gadkari-shared-the-historic-moment-of-noida/</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://cg24news.in/cm-20949</t>
+          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://newsheight.com/big-breaking-healthy-women-social-family/</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
+          <t>https://www.timesbull.com/business/lado-laxmi-yojana-married-and-unmarried-women-will-get-rs-2100-govt-makes-big-announcement-608380.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
+          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
+          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://devbhoomimedia.com/cm-dhami-in-kashipur-sammelan/</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://bharat24live.com/news/bihar-nitish-government-will-transfer-5000-to-the-accounts-of-50-lakh-women-today</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://bolchhattisgarh.in/chief-minister-sai-laid-the-foundation-stone-and-inaugurated-77-development-works-of-development-works-worth-rs-245-crore-80-lakh/</t>
+          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://hindi.lifeberrys.com/state/delhi-ncr/the-modi-shah-duo-is-reportedly-preparing-to-pull-off-another-surprise-move--sudha-yadav-could-become-the-partys-first-female-national-president-243441.html</t>
+          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.hindektatimes.com/204154/</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://webvarta.com/states/other-state/sonipat-lado-lakshmi-yojana-mega-camp-2025/</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://webvarta.com/states/other-state/haryana-cm-nayab-saini-sonipat-projects/</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://rajkajlive.com/chief-minister-dhami-inaugurated-the-exhibition-in-the-municipal-corporation/</t>
+          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.saahassamachar.in/fifth-phase-of-mission-shakti-to-commence-from-sharad-navratri-chief-minister</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.rewariyasat.com/business/ladli-bahna-yojana-28th-installment-mp-484313</t>
+          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://news24online.com/business/pm-kisan-samman-nidhi-yojana-government-eases-rules-for-border-area-farmers-when-will-rs-2000-be-credited-details/638726/</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/business-news/latest-updates/india-us-trade-talks-back-on-track-amid-tariff-tensions-positive-forward-looking/article-181419/</t>
+          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/business-news/latest-updates/mother-dairy-to-pass-100-gst-benefit-cuts-prices-on-milk-paneer-butter-ghee-and-safal-foods/article-181384/</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://vocaltv.in/madhya-pradesh/the-chief-minister-will-unveil-the-statue-of-a-conphp/cid17426496.htm</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
+          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/others-state/centres-relief-plan-punjab-floods-declared-extreme-disaster-farmers-to-get-compensation-state-to-get-loan/</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.timesbull.com/business/lado-laxmi-yojana-married-and-unmarried-women-will-get-rs-2100-govt-makes-big-announcement-608380.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/bollywoods-go-to-travel-destinations-youll-want-to-visit/london/slideshow/123943268.cms</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/india-remains-heart-growth-journey-tech-firm-nothing-raises-200-million-452836</t>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/satna-maihar-daylight-robbery-8-lakh-lclk-strc-2333321-2025-09-15</t>
+          <t>https://rightnewsindia.com/himachal-pradesh-chief-ministers-advisor-launches-a-scathing-attack-on-politics/</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+          <t>https://insiderlive.in/rjd-family-dispute-rohini-acharya-controversy/</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://awaaz24x7.com/news/haryana-a-program-was-organized-in-panchkula-to-commemorate-maharaja-agrasen-jayanti-chief-minister-nayab-singh-saini-attended-and-extended-greetings-for-the-sharadiya-navratri</t>
+          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://kalikumaunkhabar.com/uttarakhand/lohaghat-the-color-of-the-traders-brought-the-police-in-action-parking-passers-by-roads-of-municipality-and-pwd-upset</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+          <t>https://insiderlive.in/giriraj-singh-attack-opposition-bihar-politics/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://himachalnownews.com/%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%88-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A5%8B%E0%A4%97-%E0%A4%A8%E0%A5%80%E0%A4%A4%E0%A4%BF.html</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
+          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/rahul-gandhi-visits-flood-affected-areas-in-amritsar-and-gurdaspur-meets-victims/869119/</t>
+          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
+          <t>https://www.newsdrum.in/national/hallmark-of-modis-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-bjp-leaders-10473104</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/delhi-ncr/when-did-the-opposition-talk-about-reforms-gajendra-singh-shekhawat-4279867</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%A6%E0%A5%8B%E0%A4%AA%E0%A4%B9%E0%A4%B0-%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-538/</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/rahul-gandhi-punjab-visit.html</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Armys-winter-storage-train-returns-with-753-tonnes.html</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/ED-notice-to-Yuvraj-Singh-Robin-Uthappa-Sonu-Sood.html</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/chh-rai-hmu-mat-latest-raipur-news-050504-1407740-nor.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+          <t>https://www.jagmarg.com/sonipat/chief-minister-nayab-singh-saini-gave-a-big-gift-inaugurated-557-projects-worth-about-rs-117-crore</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-75--1188144</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186696</t>
+          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/pm-modi-addresses-the-nation-1189723</t>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://m.economictimes.com/markets/stocks/stock-liveblog/tech-mahindra-share-price-today-live-updates-16-sep-2025/liveblog/123911873.cms</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://sanjeevanisamachar.com/story-of-former-bihar-chief-minister-daroga-prasad-rai/</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
+          <t>https://m.economictimes.com/markets/stocks/news/7-penny-stocks-surge-up-to-55-in-just-5-days-did-you-invest-in-any/kesoram-industries/slideshow/124024203.cms</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://npg.news/amp/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
+          <t>https://m.economictimes.com/markets/stocks/news/redington-among-7-stocks-that-closed-above-vwap-on-sept-16/bullish-trend/slideshow/123934660.cms</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://swatvasamachar.com/news/nawada-news-2224/</t>
+          <t>https://m.economictimes.com/markets/stocks/news/garden-reach-shipbuilders-among-4-stocks-that-formed-bullish-white-marubozu-pattern/zen-technologies/slideshow/123962841.cms</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/himachal-pradesh-chief-ministers-advisor-launches-a-scathing-attack-on-politics/</t>
+          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/new-entrants/slideshow/123940009.cms</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://m.economictimes.com/markets/stocks/news/15-mfs-add-these-10-stocks-in-august-25-4-stocks-rally-over-50-in-fy26/mankind-pharma/slideshow/123896518.cms</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1187827</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.rajyasameeksha.com/politics</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-dhami-visited-the-disaster-affected-areas-and-directed-to-provide-immediate-financial-assistance-and-basic-services-to-all-affected-families-as-per-disaster-standards/</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/telangana/the-chief-justice-of-the-high-court-urged-the-chief-minister-to-enhance-facilities-in-the-courts-4277697</t>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://firstindia.co.in/news/madhya-pradesh/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://khabarsameeksha.com/increased-facilities-in-doon-hospital-within-two-days-on-the-instructions-of-the-chief-minister/</t>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/hallmark-of-modis-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-bjp-leaders/2745143/</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/dewas-news-%E0%A4%A6%E0%A5%87%E0%A4%B5-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%95%E0%A4%A8%E0%A5%8D-%E0%A4%A8-%E0%A4%A6-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%A8%E0%A4%97%E0%A5%8D%E0%A4%A8-%E0%A4%B9-%E0%A4%95%E0%A4%B0-%E0%A4%98%E0%A5%81%E0%A4%9F%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC%E0%A4%B2-%E0%A4%B8%E0%A5%9C%E0%A4%95-%E0%A4%AA%E0%A4%B0-%E0%A4%9A%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%95%E0%A5%8D-%E0%A4%AF-%E0%A4%B9%E0%A5%88-%E0%A4%AE-%E0%A4%9C%E0%A4%B0/ar-AA1It9zG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskarhindi.com/other/news-1188553</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://samvadjanhvi.com/dehradun-the-first-meeting-of-the-state-level-disha-committeechaired-by-cm-dhamidiscussed-the-progress-of-schemes-related-to-agriculture-rural-developmenturban-developmenthealth-and-educationas-well-a/</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Rain-havoc-continues-in-Dehradun-one-student-died.html</t>
+          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Security-forces-recovered-looted-weapons-in-Manipu.html</t>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
+          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
+          <t>https://samvaad365.com/dehradun-cm-dhami-wishes-pm-modi-on-his-birthday-and-launches-swachh-utsav-2025/</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Aim-to-make-India-a-leader-in-biofuel-and-green-tr.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://e-webcareit.com/cooperation-in-cooperation-programme-organised-at-raj-bhavan-two-important-agreements-signed-in-the-presence-of-governor-and-chief-minister</t>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Engineers-Research-and-Training-Institute-will-be.php</t>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://inanews.org/lucknow-agriculture-minister-attended-the-national-agriculture-conference--rabi-abhiyan-2025-in-new-delhi</t>
+          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
+          <t>https://media24news.in/?p=90140</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/economy/gst-new-rates-india-live-updates-two-slab-system-september-22-nirmala-sitharaman-gst-2-0-itc-council-reforms-5-18-40-pc-liveblog-19681684.htm</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/stock-re-categorization/slideshow/123940116.cms</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/cm-pushkar-singh-dhami-expressed-gratitude-to-the-cag-report-on-the-achievement-of-revenue-surplus-3493975.html</t>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://firstbihar.com/bihar/patna-news/advocates-will-get-5000-rs-per-month-stipend-in-bihar-nitish-kumar-government-announced-879143</t>
+          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278588801/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://postmanindia.in/chief-minister-inaugurated-the-swachh-utsav-programme/</t>
+          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/evening-news-513/</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/ces28-ar-agriculture-minister.html</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cms-emphasis-on-speeding-up-implementation-of-schemes/</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628939-haryana-cm-meets-union-minister-pralhad-joshi-to-discuss-farmer-welfare-and-procurement-issues?amp</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-75--1187799</t>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://rajpanchhi.com/posts/68d0f60ba09cd6cfc1b3f89e-H1QpM_-Ek-tree-%E2%80%94-mother-s-name-campaign-Chief-Minister-Bhajanlal-Sharma-gave-a-message-of-environmental-protection</t>
+          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://shouryagatha.com/main-stories/himalayan-environmental-dialogue-program-speakers-took-various-measures-for-environmental-balance-in-the-desamvivi/</t>
+          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://bolpanipat.com/cleanliness-is-the-only-way-to-have-a-healthy-and-prosperous-life-ceo-dr-kiran-singh/</t>
+          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://knewsindia.in/big-breaking-2/major-relief-for-festivals-in-delhi-rekha-gupta-government-allows-loudspeakers-to-be-played-till-12-midnight/</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://dailyuttarakhand.com/chief-minister-wishes-the-people-of-the-state-on-himalaya-day-2/</t>
+          <t>https://makdaiexpress24.com/in-the-name-of-a-garden-mother-the-campaign-deputy-commissioner-mnrega-council-mr-singh-reviewed-the-works/</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://apnuuttarakhand.com/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+          <t>https://spokesmanhindi.com/national/punjab/170925/central-government-releases-sdrf-funds-punjab-receives-advance-instal.html</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=90140</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=90048</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>https://thebharatnow.in/business/great-news-for-the-crop-wheat-production-could-see-a-record-increase-next-year/</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>https://www.prameyanews.com/index.php/two-day-national-agriculture-conference-begins-to-strategise-for-rabi-season-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>https://media24news.in/?p=90190</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>https://www.5dariyanews.com/news/467745-Chander-Kumar-participates-in-national-conference-on-Kharif-Rabi-Campaign</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>https://livevns.news/National/shivraj-singh-in-pusaphp/cid17424761.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/mp/sehore/news/heavy-damage-to-soybean-crop-due-to-continuous-rain-and-waterlogging-in-sehore-135984420.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>https://sehorehulchal.com/news/farmers-devastated-by-double-attack-cm-helpline-flooded-with-complaints/</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
-        </is>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
-        </is>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/ces28-ar-agriculture-minister.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
-        </is>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
-        </is>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
-        </is>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>https://pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
-        </is>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
-        </is>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>https://makdaiexpress24.com/stagnation-of-15-trains-was-increased-for-devotees-visiting-maihar-in-navratri/</t>
-        </is>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-yogi-adityanath-said-up-working-towards-viksit-uttar-pradesh-vision2047-24055474.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/raipur-news/cm-claims-gst-2-0-provides-relief-to-all-sections-tractors-19964857</t>
-        </is>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/rewa/the-chief-minister-gave-a-gift-of-rs16231-crore-to-tyonthar-rewa-news-c-1-1-noi1337-3425344-2025-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-providing-the-best-fertilizers-seeds-and-pesticides-to-farmers-is-our-priority-dr-kirori-lal-news-hindi-1-753391-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>https://best24news.com/haryana/haryana-news-haryana-cm-saini-gave-a-big/</t>
-        </is>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
-        </is>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>https://www.krishakjagat.org/national-news/gst-2-0-implemented-75-hp-tractors-will-be-cheaper-by-%E2%82%B963000-from-today-reducing-the-burden-on-farmers-pockets/</t>
-        </is>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%85%E0%A4%AC-%E0%A4%96%E0%A5%87%E0%A4%A4-%E0%A4%B9-%E0%A4%97-%E0%A4%95-%E0%A4%AB-%E0%A4%AF%E0%A4%A4-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%AE%E0%A4%A4-%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%97-%E0%A4%B0-%E0%A4%B5%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AC%E0%A4%A4-%E0%A4%AF-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9-%E0%A4%97-%E0%A4%AB-%E0%A4%AF%E0%A4%A6/ar-AA1MTb2R?ocid=finance-verthp-feeds</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/gst-cuts-from-22nd-september-ensure-benefits-reach-farmers-says-agriculture-minister-shivraj-singh-chouhan-ddb79</t>
-        </is>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>https://www.drishtiias.com/statepcs/17-09-2025/bihar</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/sheopur-farmers-pelt-stones-at-fertilizer-distribution-center-lcln-strc-2333824-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/morena-three-farmers-injured-in-fertilizer-centre-clash-lcln-dskc-2333935-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>https://dainiksaveratimes.com/national/national-agriculture-conference-rabi-abhiyan-2025-union-agriculture-minister-shivraj-chauhan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>https://spokesmanhindi.com/national/punjab/170925/central-government-releases-sdrf-funds-punjab-receives-advance-instal.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/jammu-and-kashmir/centre-approves-110-road-projects-worth-rs-2000-crore-for-udhampur-4278710</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>https://makdaiexpress24.com/devotees-climbed-1063-stairs-to-seek-the-blessings-of-maihars-mother-sharda-and-pooja-mais-blessings-in-brahmamuhurta/</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A645"/>
+  <dimension ref="A1:A719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,35 +438,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
+          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
+          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
@@ -480,28 +480,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
         </is>
       </c>
     </row>
@@ -515,56 +515,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
+          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
+          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://www.deccanherald.com/india/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-3736063</t>
         </is>
       </c>
     </row>
@@ -578,252 +578,252 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
+          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
+          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
+          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/centre-to-provide-pm-kisan-relief-rs-76-crore-for-shgs-in-flood-hit-jammu-shivraj-singh-chouhan/</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
+          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985/0</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/ensure-timely-relief/</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/delhi/centre-to-adopt-rajasthans-farm-initiatives-says-chouhan</t>
+          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
+          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
+          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
+          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276221</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
@@ -837,287 +837,287 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638785.html</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://boldnewsonline.com/jammu-flood-victims-to-receive-relief-under-chouhans-package/</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/shivraj-assesses-damages-of-crops-in-jammu-announces-relief-measures-for-farmers-disaster-victims/north/news/3583526.html</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638787.html</t>
+          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://menafn.com/1110074178/Shivraj-Singh-Chouhan-Plants-75-Saplings-To-Mark-PM-Modis-Birthday</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
+          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.bhaskar.com/local/mp/balaghat/news/on-september-22-shivraj-singh-chauhan-will-come-to-malajkhand-will-be-involved-in-the-program-130343967.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits</t>
+          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/union-minister-shivraj-singh-chauhan-visits-flood-affected-area-budilya-brahman-jammu-region-5608</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
+          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
+          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
+          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111289</t>
+          <t>https://www.bhaskar.com/local/mp/gwalior/news/union-agriculture-minister-shivraj-singh-in-gwalior-today-135763757.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
+          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
+          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
@@ -1131,28 +1131,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
@@ -1166,210 +1166,210 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
+          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
+          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AC-%E0%A4%AF-%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%81%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%9F-%E0%A4%95-%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%B0-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%B8-%E0%A4%82%E0%A4%B9-%E0%A4%B9%E0%A5%81%E0%A4%8F-%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%A5-%E0%A4%A8%E0%A4%B9-%E0%A4%82-%E0%A4%B9-%E0%A4%97-%E0%A4%A7-%E0%A4%96/ar-AA1IGUm4</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
@@ -1383,189 +1383,189 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
+          <t>https://www.bhaskar.com/local/mp/vidisha/news/shivraj-participated-in-cycle-rally-in-vidisha-135798900.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
+          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AA%E0%A4%82%E0%A4%9C-%E0%A4%AC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%A2%E0%A4%BC-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A4%A8-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%A8%E0%A5%81%E0%A4%95%E0%A4%B8-%E0%A4%A8-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%95-%E0%A4%B0-%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%B8-%E0%A4%82%E0%A4%AA%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AE-%E0%A4%AE-%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%B8%E0%A4%82%E0%A4%97-%E0%A4%96%E0%A4%A1%E0%A4%BC-%E0%A4%B9%E0%A5%88-%E0%A4%95%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0/ar-AA1LY8vz?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
+          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189485</t>
+          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/agriculture-minister-to-hold-meeting-on-gstphp/cid17435350.htm</t>
+          <t>https://www.bhaskarhindi.com/city/new-delhi/delhi-news-dalahan-aur-tilahan-ka-utpaadan-badhaane-ke-lie-rodamaip-banaakar-hoga-kaamah-shivaraaj-1187595</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.php</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/Shivraj-singh-in-pusa.php</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
+          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/Shivraj-singh-in-pusa.php</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B6-%E0%A4%B5%E0%A4%B0-%E0%A4%9C-%E0%A4%A8%E0%A5%87-%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%88%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%A4-%E0%A4%93%E0%A4%82-%E0%A4%B8%E0%A5%87-%E0%A4%9C-%E0%A4%8F%E0%A4%B8%E0%A4%9F-%E0%A4%95%E0%A4%9F-%E0%A4%A4-%E0%A4%95-%E0%A4%B2-%E0%A4%AD-%E0%A4%95-%E0%A4%B8-%E0%A4%A8-%E0%A4%82-%E0%A4%A4%E0%A4%95-%E0%A4%AA%E0%A4%B9%E0%A5%81%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%B9/ar-AA1MSa6R?ocid=finance-verthp-feeds</t>
+          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-2025-26-36250--1187634</t>
+          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://www.bhaskar.com/local/mp/ujjain/news/will-attend-the-statue-unveiling-program-of-swami-satyamitranand-giri-maharaj-130328756.html</t>
         </is>
       </c>
     </row>
@@ -1579,63 +1579,63 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/after-listening-to-the-farmers-shivraj-singh-called-the-collector</t>
+          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
+          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
+          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/gst-reforms-make-farming-cheaper-profitable-shivraj-singh/</t>
+          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
@@ -1691,35 +1691,35 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://mediawala.in/shivraj-singh-chouhan-told-the-story-of-his-first-meeting-with-modi/</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/extensive-discussions-rabi-conference-yield-good-results-rabi-crops-season-shivraj-singh/</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
@@ -1733,3211 +1733,3729 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/shivraj-singh-chouhan-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers-3258778.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
+          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/jammu-and-kashmir-shivraj-singh-chouhan-met-flood-affected-farmers</t>
+          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://lalluram.com/gst-new-slab-agricultural-equipment-union-agriculture-minister-shivraj-singh-on-new-gst-slabs/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
+          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
+          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
+          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://divyakirti.com/archives/5675</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-minister-shivraj-singh-chouhan-virtually-attends-the-launch-of-the-swasth-nari-sashakt-parivaar-abhiyaan-from-new-delhi/</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
+          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
+          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467697-Shivraj-Singh-Chouhan-Plants-75-Saplings-at-ICAR-to-Mark-PM-Modis-75th-Birthday</t>
+          <t>https://sundayguardianlive.com/news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654-140171/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467914-Shivraj-Singh-Chouhan-chairs-key-meeting-on-GST-reforms-for-agricultural-machinery</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467662-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-held-in-Delhi-under-the-chairmanship-of-Shivra</t>
+          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
+          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
+          <t>https://statetimes.in/will-discuss-plying-of-all-vehicular-types-on-jmu-sgr-nh-with-gadkari-cm/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
+          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/midday-news-545/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/notification-issued-to-change-the-name-of-alirajpur-district-to-aalirajpur-19947549</t>
+          <t>https://www.heraldgoa.in/globe-nation/punjab-police-clears-farmer-protest-sites-at-shambhu-and-khanauri-borders-arrests-leaders/14647/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://statetimes.in/from-safe-houses-to-subterranean-sanctuaries-terror-outfits-change-tactics/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/ces28-ar-agriculture-minister.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/</t>
+          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://statetimes.in/peace-prerequisite-for-tourism-sports-sectors-to-flourish-in-jk-cm/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
+          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
+          <t>https://www.newsdrum.in/national/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-union-minister-pralhad-joshi-10482514</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
+          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://www.thehawk.in/news/india/jitu-patwari-plays-down-internal-rift-claims-in-madhya-pradesh-congress</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
+          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.indiatodayne.in/arunachal-pradesh/video/arunachal-agriculture-minister-calls-for-state-specific-policies-at-national-rabi-conference-1279202-2025-09-18</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/agricultural-machinery-and-tractors-to-become-cheaper--minister-1758348113097</t>
+          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
+          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
+          <t>https://hindi.ianslive.in/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali--20250922133554</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-union-minister-pralhad-joshi-10482514</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/economy-and-business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
+          <t>https://www.agniban.com/several-events-were-held-in-bjp-ruled-states-on-prime-minister-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://indianlooknews.com/?p=56810</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
+          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/legislative-trojan-horse-mallikarjun-kharge-slams-bjp-over-bill-on-removal-of-pm-cm-ministers/articleshow/123893656.cms</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://hindi.ianslive.in/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali--20250922133554</t>
+          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=relief-from-farming-to-pocket-government-to-procure-these-5-major-kharif-crops-in-karnataka-577744</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/good-news-for-karnataka-farmers-central-government-to-procure-five-major-kharif-crops</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://bccnews24.com/raipur-minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://rashtriyahindimail.in/posts/111292</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
+          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467582-We-will-make-India-food-basket-of-the-world-Shivraj-Singh-Chouhan</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://patnapress.com/bihar-assembly-horse-trading-scandal-bjp-mla-questioned/amp/?noamp=mobile</t>
+          <t>https://www.currentcrime.com/video-of-zubeen-garg-makes-everyone-cry/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/22/jk-flood-victims-to-get-comprehensive-package-lop-sunil-sharma/</t>
+          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
+          <t>https://www.ptinews.com/editor-detail/CPI-must-emerge-as-a-strong-force-that-can-shape-India-s-political-course-D-Raja/2936350</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
+          <t>https://www.socialnews.xyz/2025/09/20/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
+          <t>https://www.socialnews.xyz/2025/09/17/cong-observes-ex-mp-assembly-speaker-srinivas-tiwaris-100th-birth-anniversary-in-rewa/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Arrest-of-Mehraj-Malik-is-illegal.html</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-got-golden-banyan-award-honoured-by-union-minister-gajendra-singh-shekhawat-at-heritage-tourism-best-state-category-19945617</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rain-alert-in-8-districts-imd-issues-warning-19964265</t>
+          <t>https://mp.punjabkesari.in/national/news/scindia-s-statement-regarding-the-roads-of-mp-2213041</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://www.bhaskar.com/local/mp/vidisha/news/mla-tandon-submitted-a-6-point-demand-letter-for-the-development-of-vidisha-135938909.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-weather-heavy-rainfall-in-next-12-hours-alert-issued-in-3-districts-warns-imd-19953418</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111292</t>
+          <t>https://www.business-standard.com/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/2-big-mines-of-mp-will-yield-gold-after-singrauli-this-district-is-preparing-gold-mine-in-mp-19951211</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=forest-minister-kedar-kashyap-paid-tribute-to-bharat-ratna-visvesvaraya-576675</t>
+          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=shraddha-of-dashami-tithi-of-pitru-paksha-and-worship-of-hanumanji-these-acts-will-do-good-to-the-ancestors-and-son-of-wind-576661</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.currentcrime.com/video-of-zubeen-garg-makes-everyone-cry/</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
+          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.dailypioneer.com/2025/india/chouhan-inspects-damaged-farms-in-j-k.html</t>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://patnapress.com/eci-mandates-ai-election-content-labels/</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://patnapress.com/foreign-pilgrims-russia-ukraine-gaya-ancestral-rites/</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://patnapress.com/solar-eclipse-live-stream-2025/</t>
+          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://patnapress.com/pawan-singh-bihar-2025-elections-reality-show-exit/</t>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://patnapress.com/solar-eclipse-september-2025/</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://patnapress.com/navratri-2025-goddess-shailputri-traditional-offerings/</t>
+          <t>https://ianslive.in/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister--20250919175149</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://patnapress.com/nitish-kumar-construction-workers-aid/</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister/</t>
+          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://patnapress.com/patna-ipsowa-tree-festival-bihta/</t>
+          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/17/cong-observes-ex-mp-assembly-speaker-srinivas-tiwaris-100th-birth-anniversary-in-rewa/</t>
+          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://patnapress.com/pawan-kumar-bhimappa-bajantri-sworn-in-patna-high-court-chief-justice/</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
+          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/gst-bachat-utsav-begins-centre-leaderphp/cid17455799.htm</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111216</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/bihar/story/chirag-paswan-bihar-nda-seat-sharing-statement-3203457-2025-09-22</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/bihar-election-2025-congress-candidate-selection-seat-sharing/</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/bihar-goreyakothi-vidhansabha-election-2025/</t>
+          <t>https://www.msn.com/hi-in/news/other/agri-rural-news-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B2%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B8%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7-%E0%A4%A8-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0%E0%A4%9C-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%B5-%E0%A4%B0%E0%A5%8D%E0%A4%AF/ar-AA1MMI5R</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/bihar-baniapur-vidhan-sabha-election-2025/</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/scindia-s-statement-regarding-the-roads-of-mp-2213041</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/ar-AA1MVTvG</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+          <t>https://upuklive.com/business/the-21st-installment-of-pm-farmer-will-come-soon-for-the-farmers-a-gift-of-rs-2000-will-come-soon-23960.html</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
+          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
+          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://ianslive.in/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister--20250919175149</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
+          <t>https://statetimes.in/former-hurriyat-chief-abdul-gani-bhat-passes-away/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision</t>
+          <t>https://statetimes.in/cme-cum-brainstorming-session-organised-by-mru-gmc-jammu/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/business/farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan-10467830</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
+          <t>https://himachaldastak.com/chief-minister-tourism-start-up-scheme-gets-approval/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://timetv.news/national/2025/09/22/registration-of-cashless-treatment-up-to-rs-10-lakh-under-chief-ministers-health-scheme-will-start-from-september-23-cm-mann/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/gst-cut-on-farm-equipment-must-benefit-farmers-directly-agriculture-minister/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
+          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/himachal-government-will-bear-the-expenses-of-marriage-of-orphan-children-2216300</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
+          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
+          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-govt-makes-ekyc-mandatory-for-beneficiaries-of/cid17441579.htm</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://www.theindiadaily.com/state/punjab/cashless-treatment-up-to-rs-10-lakh-punjab-first-state-in-the-country-to-launch-the-chief-minister-s-health-scheme-news-94860</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://starsamachar.com/sidhi-sp-shailendra-singh-crime-control-police-action</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://www.livehindustan.com/uttarakhand/rudrapur/story-uttarakhand-cm-pushkar-singh-dhami-visits-khatima-listens-to-public-concerns-201758294392599.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
+          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-21-september-2025-in-hindi-todays-top-news</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/2-more-doctors-appointed-in-dhaneta-hospital-2213561</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/farmers-will-benefit-from-gst-reduction-agriculture-minister/</t>
+          <t>https://hindi.moneycontrol.com/jobs/sarkari-naukri-government-jobs-in-himachal-recruitment-in-electricity-revenue-health-and-panchayati-raj-departments-article-2162823.html</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/agriculture-minister-asks-centre-to-help-in-removing-sand-from-fields-and-providing-wheat-seeds/</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.newspuran.com/blogs/mismanagement-of-fertilizer-without-assessment</t>
+          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/?p=260993</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/aligarh/story-aligarh-wholesalers-demand-action-against-fake-drug-dealers-at-cdf-up-annual-meeting-201758578893110.html</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-holds-review-meeting-with-public-representatives-on-new-gst-rates-and-swadeshi-campaign-expresses-gratitude-to-pm-modi-and-finance-minister/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
+          <t>https://raigarhtopnews.com/chief-minister-vishnudev-sai-attended-2/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
+          <t>https://uttarakhandmorningpost.com/dehradun-chief-ministers-instructions-ready-on-dm-ground-zero-in-disaster-affected-areas/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/gst-reduction-agriculture-machinery-shivraj-singh-meeting-benefits-for-farmers-2025/</t>
+          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
+          <t>https://acn18.com/%E0%A4%B8%E0%A4%9A%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%BE%E0%A4%AF%E0%A4%B2%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
+          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.millenniumpost.in/business/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-says-chouhan-627425</t>
+          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/himachal-education-reform-cbse-curriculum-rajiv-gandhi-schools-student-loan-scheme-54-818476</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/setback-for-congress-karnataka-hc-invalidates-malur-mlas-election-orders-recounting-of-votes/articleshow/123923092.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/PM-Mitra-Park-is-a-symbol-of-the-industrial-power.html</t>
+          <t>https://newsarenaindia.com/nation/rajnath-shares-my-modi-story-praises-discipline-knowledge/56623</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/kerala-governor--cm-wish-pm-modi-on-his-75th-birthday/2921961</t>
+          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/alirajpur-district-renamed-aalirajpur-in-hindi-official-notification-issued-lcln-strc-2334595-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/nitish-kumar-opened-his-treasure-for-women-voters-in-bihar-elections-hindi-news-brn25091900519</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/a-driver-was-bitten-by-a-snake-and-taken-to-the-hospital-but-was-released-as-soon-as-he-was-shown-to-a-doctor-in-ujjain/articleshow/123980598.cms</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/vidisha/stone-pelting-news-on-maa-kali-tableau-in-muslim-locality-committee-resolved-matter-amicably/articleshow/124053496.cms</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/mahakal-mandir-pandit-pujari-appointments-controversy-indore-high-court-seeks-answers-ujjain-collector-in-3-months/articleshow/123947146.cms</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://thebikanernews.in/rajasthan/to-address-the-legitimate-demands-of-the-employees-working/cid17435615.htm</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/ujjain-railway-station-accident-army-truck-caught-fire-loaded-in-goods-train-railway-staff-control-no-casualty-reported/articleshow/124024940.cms</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/?p=260445</t>
+          <t>https://insiderlive.in/ujiyarpur-vidhan-sabha-chunav-analysis/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/himachal-pradesh-news/punjab-haryana-should-work-like-big-brothers-to-support/cid17420227.htm</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/haryana-women-given-priority-in-vita-booths/</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/there-will-be-6-main-and-3-recreational-games-in-mp-sports-festival-registration-starts-today-135939182.html</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/prime-minister-modi-lays-foundation-stone-of-indias-first-pm-mitra-park-in-madhya-pradesh/</t>
+          <t>https://ianslive.in/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal--20250915134402</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://www.freepressjournal.in/bhopal/bhopal-gandhi-medical-college-students-raise-concern-over-language-mismatch-in-internal-exams</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/morena-mp-live-news-today-21-september-2025-madhya-pradesh-breaking-update-crime-education-politics-samachar-aaj-ki-taza-khabar-livenews-9648356.html</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
+          <t>https://hindi.oneindia.com/news/bhopal/bjp-mp-alok-sharma-sharp-statement-ban-on-non-veg-shops-is-right-1390405.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/bihar-mukhyamantri-mahila-rojgar-yojana-hindi/</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/organizations-protested-saying-the-government-used-societies-135963056.html</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
+          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://www.ptinews.com/editor-detail/RSS-leader-stresses-on-strengthening-Hindu-society-to-counter-global-conspiracies/2938144</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Governor-Mangubhai-Patel-wishes-Prime-Minister-Mod.html</t>
+          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/uttarakhandonly-with-the-strength-of-modi-dhami-will-the-next-decade-belong-to-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/hathras/chhauragadaua/news/special-honor-in-national-women-empowerment-workshop-135976706.html</t>
+          <t>https://mbmnewsnetwork.com/himachal-pradesh/854552/%E0%A4%B0%E0%A4%BF%E0%A4%9C-%E0%A4%AA%E0%A4%B0-13-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%8B-%E0%A4%B9%E0%A5%8B%E0%A4%97%E0%A4%BE-%E0%A4%B5%E0%A5%80%E0%A4%B0</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-bihar-govt-jobs-women-entrepreneurship-nitish-kumar-employement-drive-24050839.html</t>
+          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/jind/suman-sharma-became-the-womens-district-president-of-jjp-jind-news-c-198-1-rew1001-226085-2025-09-21</t>
+          <t>https://humarabikaner.com/india/pm-modi-birthday-prime-ministers-75th-birthday-today/cid17427895.htm</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/what-did-prime-minister-modi-give-to-women-on-his-birthday/</t>
+          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
+          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
+          <t>https://deshbandhump.com/congress-factionalism-came-out-in-the-open-in-front-of-the-leader-of-opposition/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.gyanwani.com/33520/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://navbharatlive.com/maharashtra/nashik/trimbakeshwar-parking-dispute-journalist-attack-case-nashik-1362570.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://livevns.news/Top-Headlines/cm-yogi-launches-mission-shakti-50-special-program-in/cid17447412.htm</t>
+          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://khatpatnews.com/?p=61931</t>
+          <t>https://www.prabhatkhabar.com/business/new-gst-rates-2025-leaders-reactions-gst-reform-india</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/india/jharkhand/healthy-women-strong-families-campaign/504213.html</t>
+          <t>https://www.tv9hindi.com/india/raja-bhaiya-wife-bhanvi-singh-dispute-son-statement-big-reveals-3492379.html</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.surajvarta.in/2025/09/mission-shakti-50-dedicated-to-womens.html</t>
+          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
+          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://thechenabtimes.com/2025/09/22/government-approves-rs-1955-65-crore-for-110-roads-project-in-udhampur-kathua-doda-constituency/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
+          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-provided-financial-approval-of-rs-127-crore-for-various-development-schemes/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
+          <t>https://citiupdate.com/news/detailNews/104931</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
+          <t>https://www.tv9hindi.com/india/cm-nitish-kumar-patna-mauryalok-comprehensive-urban-development-schemes-3493262.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
+          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://amanyatralive.com/%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C%E0%A4%BC-5-%E0%A4%95%E0%A4%BE-%E0%A4%B6%E0%A5%81%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%82/</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://youthindiatoday.com/awareness-program-on-dowry-prohibition-and-women-empowerment-in-kampil-under-seva-pakhwada/</t>
+          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
+          <t>https://shikharhimalaya.com/dehradun-expedite-implementation-of-development-plans-cm/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://www.hindektatimes.com/204154/</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://www.sabkuchgyan.com/editorial-%E0%A4%85%E0%A4%AD%E0%A5%80-%E0%A4%AA%E0%A4%A2%E0%A4%BC%E0%A5%87%E0%A4%82-%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%B0%E0%A4%A5-%E0%A4%AE%E0%A4%B9/</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://aavaj.com/jaunpur/jaunpur-news-%E0%A4%9C%E0%A5%8C%E0%A4%A8%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%AE%E0%A4%BF%E0%A4%B6%E0%A4%A8-%E0%A4%B6%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%BF-%E0%A4%AB%E0%A5%87%E0%A4%9C-5-0-%E0%A4%95/</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.rewariyasat.com/business/ladli-bahna-yojana-28th-installment-mp-484313</t>
+          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/utility-news/story/pm-kisan-21st-installment-update-notification-2025-3202470-2025-09-17</t>
+          <t>https://rewariupdate.com/haryana-gets-a-gift-of-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
+          <t>https://www.babushahi.com/business.php?id=210834</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/uae-firms-keen-to-invest-in-indian-infra-banking-startups-logistics-sectors-commerce-minister-piyush-goyal/articleshow/124001887.cms</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://samvadjanhvi.com/dehradun-cm-dhami-returned-from-delhimlas-and-public-representatives-made-a-courtesy-visit/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.punjabkesari.in/national/news/foundation-stone-laid-for-eight-major-connectivity-road-projects-2216961</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/cm-nayab-singh-saini-mega-road-upgradation-project-647580</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
+          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.timesbull.com/business/lado-laxmi-yojana-married-and-unmarried-women-will-get-rs-2100-govt-makes-big-announcement-608380.html</t>
+          <t>https://www.sabguru.com/haryana-cm-nayab-singh-saini-inaugurates-557-projects-worth-about-rs-117-crore-in-sonipat</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
+          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/delhi-cm-rekha-gupta-launches-song-for-pm-narendra-modis-birthday/articleshow/123921234.cms</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://scroll.in/latest/1086674/how-bjp-governments-companies-celebrated-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/srinagar-jk-disaster-pm-modi-will-visit-the-devastation-in-jammu-and-kashmir-omar-abdullah-looking-at-the-relief-package-24054487.html</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
+          <t>https://hindi.news18.com/blogs/amish-devgan/pm-narendra-modi-75th-birthday-reason-behind-indian-prime-minister-power-and-popularity-writes-amish-devgan-9632298.html</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/jammu-and-kashmir-flood-damage-report-cm-asks-officials-to-speed-up-assessment-ahead-of-pms-expected-visit-hindi-news-hin25092204098</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
+          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
+          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
+          <t>https://vocaltv.in/national/n-a-conference-in-pusa-today-and-tomorrowphp/cid17416096.htm</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://cnin.co.in/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A4%BE%E0%A4%AE-%E0%A4%A8%E0%A4%88-%E0%A4%A6%E0%A4%BF%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%BF%E0%A4%A4.../70480</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://cnewsbharat.com/hindi/news/sultanpur-143182</t>
+          <t>https://media24news.in/?p=90140</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-mann-warned-the-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan?amp</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/madhya-pradesh/the-chief-minister-will-unveil-the-statue-of-a-conphp/cid17426496.htm</t>
+          <t>https://www.dainiktribuneonline.com/news/rohtak/chief-minister-vishwakarma-samman-yojana-launched-artisans-will-get-a-top-up-incentive-of-rs-5000/</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
+          <t>https://www.etvbharat.com/hi/!bharat/tamilnadu-chief-minister-stalin-launches-anbu-karangal-scheme-hindi-news-hin25091503706</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
+          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-viksit-bharat-viksit-uttar-pradesh-2047-workshop-in-gorakhpur-24049561.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
+          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/dehradun-pushkar-singh-dhami-holds-meeting-1189512</t>
+          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://cnin.co.in/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%BE-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80-%E0%A4%AA%E0%A4%B0-%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%BF%E0%A4%95.../70476</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
+          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/himachal-pradesh-chief-ministers-advisor-launches-a-scathing-attack-on-politics/</t>
+          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/rjd-family-dispute-rohini-acharya-controversy/</t>
+          <t>https://rghnews.com/cg-news-raipur-62/</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
+          <t>https://rghnews.com/cg-news-today-89/</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/giriraj-singh-attack-opposition-bihar-politics/</t>
+          <t>https://www.outlookbusiness.com/planet/industry/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-chouhan</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://www.newsgram.com/india/2025/09/16/sc-seeks-statess-responses-on-pleas-against-anti-conversion-laws</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
+          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
+          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/hallmark-of-modis-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-bjp-leaders-10473104</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13875</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
+          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
+          <t>https://smefutures.com/moil-starts-manganese-exports-as-state-trading-enterprise/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/%E0%A4%A6%E0%A5%8B%E0%A4%AA%E0%A4%B9%E0%A4%B0-%E0%A4%B8%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%BE%E0%A4%B0-538/</t>
+          <t>https://indiaeducationdiary.in/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/rahul-gandhi-punjab-visit.html</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Armys-winter-storage-train-returns-with-753-tonnes.html</t>
+          <t>https://dainiksaveratimes.com/national/national-agriculture-conference-rabi-abhiyan-2025-union-agriculture-minister-shivraj-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/ED-notice-to-Yuvraj-Singh-Robin-Uthappa-Sonu-Sood.html</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/maharashtra-urges-centre-to-double-onion-export-subsidy-to-support-farmers</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/haridwareducationshantikunjInternational-Conferenc.html</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Titagarh-rail-system-Navy-airport.html</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/country-has-made-rapid-progress-in-renewable-energ.html</t>
+          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/NMMS-scholarship-application-last-date-extended-to.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/17/Female-cheetah-Dheera-successfully-released-in-Gan.html</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bird-watching-tour-bird-species-MP-tourism.html</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
+          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.jagmarg.com/sonipat/chief-minister-nayab-singh-saini-gave-a-big-gift-inaugurated-557-projects-worth-about-rs-117-crore</t>
+          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://narmadanchal.com/angered-by-the-fertilizer-crisis-and-neglect-the-bharatiya-kisan-sangh-will-launch-a-major-agitation-on-september-26/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
+          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://www.kisantak.in/news/trending/story/amit-shah-advises-farmers-to-reduce-use-of-pesticides-and-fertilizers-swm-1281204-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/stock-liveblog/tech-mahindra-share-price-today-live-updates-16-sep-2025/liveblog/123911873.cms</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/7-penny-stocks-surge-up-to-55-in-just-5-days-did-you-invest-in-any/kesoram-industries/slideshow/124024203.cms</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/redington-among-7-stocks-that-closed-above-vwap-on-sept-16/bullish-trend/slideshow/123934660.cms</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/garden-reach-shipbuilders-among-4-stocks-that-formed-bullish-white-marubozu-pattern/zen-technologies/slideshow/123962841.cms</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/amfi-reshuffle-poonawalla-fincorp-gillette-india-among-6-smallcap-stocks-that-may-get-midcap-status/new-entrants/slideshow/123940009.cms</t>
+          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/15-mfs-add-these-10-stocks-in-august-25-4-stocks-rally-over-50-in-fy26/mankind-pharma/slideshow/123896518.cms</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://indiapublickhabar.com/Country/sam-pitroda-pakistan-statement-clarification-2025/4940</t>
+          <t>https://www.aajtak.in/uttar-pradesh/story/yogi-adityanath-writes-pm-narendra-modi-birthday-wishes-ntc-dskc-2335103-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-dhami-visited-the-disaster-affected-areas-and-directed-to-provide-immediate-financial-assistance-and-basic-services-to-all-affected-families-as-per-disaster-standards/</t>
+          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/madhya-pradesh/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/hathras/chhauragadaua/news/special-honor-in-national-women-empowerment-workshop-135976706.html</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+          <t>https://khatpatnews.com/?p=61931</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1188553</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/dehradun-the-first-meeting-of-the-state-level-disha-committeechaired-by-cm-dhamidiscussed-the-progress-of-schemes-related-to-agriculture-rural-developmenturban-developmenthealth-and-educationas-well-a/</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/haryana-news/haryana-is-the-first-state-to-launch-an-environment-plan/cid17430072.htm</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://samvaad365.com/dehradun-cm-dhami-wishes-pm-modi-on-his-birthday-and-launches-swachh-utsav-2025/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/india-us-ties-tested-after-trump-attack-yet-still-stronger-than-chinas-trust-gap-says-us-foreign-policy-expert/articleshow/123939627.cms</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://smefutures.com/india-oman-trade-agreement-fta-oman-trade-deal/</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/eu-eyes-deeper-india-partnership-despite-concerns-over-moscow-ties/articleshow/123943367.cms</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90140</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/indias-exports-likely-to-grow-6-per-cent-this-year-piyush-goyal/articleshow/123947681.cms</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90048</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/igf-qetci-sign-pact-to-develop-uk-india-quantum-value-chain-map/articleshow/123996773.cms</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/us-revokes-sanctions-exemption-on-irans-chabahar-port-what-it-means-for-indias-strategic-gateway/articleshow/123979793.cms</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://m.economictimes.com/news/economy/foreign-trade/india-in-advanced-talks-with-oman-for-fta-open-to-trade-deals-with-other-gcc-nations-piyush-goyal/articleshow/124001364.cms</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/tripura-opposition-unhappy-with-no-business-in-assembly-on-sept-22-due-to-pm-modis-visit/articleshow/123999325.cms</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/govt-sets-record-wheat-output-target-at-119-mn-tons-for-2025-26/</t>
+          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
+          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+          <t>https://hindi.news18.com/news/bihar/patna-pm-narendra-modi-purnia-rally-nitish-kumar-statement-on-lalan-singh-nda-politics-analysis-bihar-chunav-9628128.html</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/evening-news-513/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
+          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+          <t>https://www.etvbharat.com/hi/!bharat/politics-on-bhura-baal-saaf-karo-in-bihar-election-2025-hindi-news-brn25091604889</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/ces28-ar-agriculture-minister.html</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-cm-mohan-yadav-list-of-corporations-and-boards-ready-before-cabinet-expansion-bjp-organization-1390793.html</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628939-haryana-cm-meets-union-minister-pralhad-joshi-to-discuss-farmer-welfare-and-procurement-issues?amp</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.agniban.com/bihar-chief-minister-nitish-kumar-met-union-home-minister-amit-shah/</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/shivraj-singh-chouhan-seed-availability-exceeds-demand-fertilizer-concerns-persist-sai29</t>
+          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://makdaiexpress24.com/in-the-name-of-a-garden-mother-the-campaign-deputy-commissioner-mnrega-council-mr-singh-reviewed-the-works/</t>
+          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation-11758032543012.html</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://spokesmanhindi.com/national/punjab/170925/central-government-releases-sdrf-funds-punjab-receives-advance-instal.html</t>
+          <t>https://www.etvbharat.com/hi/!state/morena-mock-drill-exercise-before-farmers-protest-kailaras-sugar-mill-police-lathicharge-and-firing-madhya-pradesh-news-mps25092101046</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/tech/newsletters/morning-dispatch/the-h-1b-silver-lining-festive-sales-day-1-surge/articleshow/124059068.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>https://www.cnbctv18.com/economy/gst-new-rates-india-live-updates-two-slab-system-september-22-nirmala-sitharaman-gst-2-0-itc-council-reforms-5-18-40-pc-liveblog-19681684.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/small-biz/sustainability/bizarre-climate-ideas-show-how-far-off-track-we-are/articleshow/123965955.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/cms-emphasis-on-speeding-up-implementation-of-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/other/-75--1187799</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>https://awaaz24x7india.com/news/uttarakhand-events-were-held-across-the-state-on-prime-minister-modis-birthday-cm-dhami-inaugurated-the-swachh-utsav-2025-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>https://nayabharat.live/uttarakhand-news-the-first-meeting-of-the-state-level-direction-committee-in-the-secretariat-chaired-by-chief-minister-dhami-said-that-the-implementation-of-the-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>https://statetimes.in/dc-jammu-reviews-functioning-of-swd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>https://www.punjabnewsexpress.com/business/news/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-297667</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>https://cg24news.in/bjp-20925</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276221</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>https://spokesmanhindi.com/national/punjab/170925/central-government-releases-sdrf-funds-punjab-receives-advance-instal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
         </is>

--- a/Output/Shivraj Singh Chauhan/extracted_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A719"/>
+  <dimension ref="A1:A782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,126 +438,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
+          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.newsgram.com/politics/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter</t>
+          <t>https://www.ndtv.com/india-news/shivraj-singh-chouhan-on-when-pm-modi-touched-everyone-with-his-humility-9287303</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
+          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
+          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/agriculture-minister-shivraj-chouhan-promises-approval-of-package-for-5000-flood-hit-rural-houses-in-jammu-and-kashmir/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
+          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
+          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/punjab/preparing-contingency-plan-for-flood-ravaged-punjab-chouhan/</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/lcv-hcv/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/articleshow/123993745.cms</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
@@ -571,49 +571,49 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
+          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/business/Shivraj-Singh-Chouhan-urges-tractor-makers-to-pass-on-GST-cuts-to-farmers-from-Sept-22/2929091</t>
+          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
+          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/pm-modis-75th-birthday-shivraj-chouhan-recalls-meeting-during-bjps-ekta-yatra20250917101241</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
@@ -627,49 +627,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
+          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2166972</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
+          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
+          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
@@ -683,21 +683,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
         </is>
       </c>
     </row>
@@ -718,35 +718,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://risingkashmir.com/relief-rehab-efforts-underway-in-jk-shivraj-singh/</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://sundayguardianlive.com/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813-142577/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/shivraj-singh-wants-gst-benefits-to-reach-farmers-1503488785.html</t>
+          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
+          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
         </is>
       </c>
     </row>
@@ -760,378 +760,378 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
+          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813</t>
+          <t>https://krishijagran.com/news/centre-to-provide-pm-kisan-relief-rs-76-crore-for-shgs-in-flood-hit-jammu-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
+          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
+          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
+          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633348-government-pledges-support-to-flood-hit-jammu-farmers</t>
+          <t>https://www.uniindia.com/photoes/638789.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://tennews.in/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3633036-gst-slashed-to-boost-farm-mechanization-ministers-urge-direct-farmer-benefits</t>
+          <t>http://www.uniindia.com/photoes/638736.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
+          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/balaghat/news/on-september-22-shivraj-singh-chauhan-will-come-to-malajkhand-will-be-involved-in-the-program-130343967.html</t>
+          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
+          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/union-minister-shivraj-singh-chauhan-visits-flood-affected-area-budilya-brahman-jammu-region-5608</t>
+          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169829</t>
+          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%95%E0%A5%83%E0%A4%B7%E0%A4%BF-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%9A-16/</t>
+          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
+          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeejkladakh/jammu/shivraj-singh-chouhan-jammu-visit-flood-affected-farmers-5595</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/gwalior/news/union-agriculture-minister-shivraj-singh-in-gwalior-today-135763757.html</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
@@ -1152,343 +1152,343 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
+          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168649</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
+          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.bhaskarhindi.com/other/-110--1189364</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169829</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/videos/shivraj-singh-chauhan-on-gst-2-0-4264863.html</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/state/madhya-pradesh/pm-modi-75th-birthday-shivraj-singh-chouhan-shares-32-years-old-story-ekta-yatra/articleshow-l0ktxfg</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/vidisha/news/shivraj-participated-in-cycle-rally-in-vidisha-135798900.html</t>
+          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/shivraj-singh-chauhan-post-on-social-mediaphp/cid17427824.htm</t>
+          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/shivraj-asks-tractor-manufacturers-to-pass-on-gst-cut-benefits-to-farmers/870614/</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
+          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
         </is>
       </c>
     </row>
@@ -1502,357 +1502,357 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
+          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
+          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/new-delhi/delhi-news-dalahan-aur-tilahan-ka-utpaadan-badhaane-ke-lie-rodamaip-banaakar-hoga-kaamah-shivaraaj-1187595</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-said-we-will-help-the-farmers-by-conducting-a-survey-135973923.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.hindusthansamachar.in/Encyc/2025/9/16/Shivraj-singh-in-pusa.php</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
+          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/ujjain/news/will-attend-the-statue-unveiling-program-of-swami-satyamitranand-giri-maharaj-130328756.html</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.prabhasakshi.com/national/shivraj-singh-chouhan-became-emotional-after-seeing-the-suffering-of-farmers-in-jammu</t>
+          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
+          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%B6%E0%A4%BF%E0%A4%B5%E0%A4%B0%E0%A4%BE%E0%A4%9C-%E0%A4%B8%E0%A4%BF%E0%A4%82%E0%A4%B9-%E0%A4%A8%E0%A5%87-%E0%A4%B8%E0%A5%8B%E0%A4%AF%E0%A4%BE%E0%A4%AC%E0%A5%80%E0%A4%A8-%E0%A4%95%E0%A5%80/</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
+          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/video/agriculture-minister-tells-about-corruption-in-govt-offices-1278914-2025-09-17</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
+          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
@@ -1866,21 +1866,21 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
         </is>
       </c>
     </row>
@@ -1894,126 +1894,126 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
+          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
+          <t>https://divyakirti.com/archives/5675</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://divyakirti.com/archives/5675</t>
+          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
+          <t>https://www.etvbharat.com/hi/!state/after-vijayvargiya-meeting-with-home-minister-amit-shah-bjp-held-high-level-meeting-at-cm-house-madhya-pradesh-news-mps25092003187</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
+          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
+          <t>https://www.5dariyanews.com/news/467662-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-held-in-Delhi-under-the-chairmanship-of-Shivra</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-17-18-september-live-updates-pm-narendra-modi-75th-birthday-bihar-election-bjp-amit-shah-rahul-gandhi-supreme-court/4145200/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
         </is>
       </c>
     </row>
@@ -2041,3423 +2041,3864 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
+          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
+          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654-140171/</t>
+          <t>https://www.newsonair.gov.in/bulletins-detail/midday-news-545/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://statetimes.in/jkdfa-representatives-meet-union-agriculture-minister-present-detail-of-challenges-faced-by-dairy-farmers/</t>
+          <t>https://www.heraldgoa.in/globe-nation/punjab-police-clears-farmer-protest-sites-at-shambhu-and-khanauri-borders-arrests-leaders/14647/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/punjab-floods-centre-renews-push-for-crop-insurance-asks-state-to-join-pmfby20250916140301</t>
+          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://statetimes.in/will-discuss-plying-of-all-vehicular-types-on-jmu-sgr-nh-with-gadkari-cm/</t>
+          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/midday-news-545/</t>
+          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/punjab-police-clears-farmer-protest-sites-at-shambhu-and-khanauri-borders-arrests-leaders/14647/</t>
+          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://statetimes.in/from-safe-houses-to-subterranean-sanctuaries-terror-outfits-change-tactics/</t>
+          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/ces28-ar-agriculture-minister.html</t>
+          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
+          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://statetimes.in/peace-prerequisite-for-tourism-sports-sectors-to-flourish-in-jk-cm/</t>
+          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://www.bhaskarhindi.com/other/new-delhi-mps-at-parliament-during-monsoon-session-1186493</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-union-minister-pralhad-joshi-10482514</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
+          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/jitu-patwari-plays-down-internal-rift-claims-in-madhya-pradesh-congress</t>
+          <t>https://hindi.ianslive.in/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali--20250922133554</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
+          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
+          <t>https://dainiksaveratimes.com/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://studycafe.in/union-agriculture-minister-likely-to-chair-a-meeting-today-on-gst-reforms-for-agricultural-machinery-393526.html</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
+          <t>https://indianlooknews.com/?p=56810</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://www.knskashmir.com/jandk-flood-victims-to-get-comprehensive-package--lop-sunil-sharma-198290</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/madhya-pradesh/story/some-own-vintage-cars-some-own-weapons-how-wealthy-are-madhya-pradesh-union-ministers-details-revealed-3202452-2025-09-17</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/arrest-warrant-issued-against-bhojpur-mla-surendra-patwa-court-directs-bjp-leader-to-appear-after-repeated-absences-in-cheque-bounce-cases-135883039.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://hindi.ianslive.in/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali--20250922133554</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/several-events-were-held-in-bjp-ruled-states-on-prime-minister-modis-75th-birthday/</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://www.etvbharat.com/hi/!state/bjp-mla-rajeev-singh-parichha-and-mla-ravi-sharma-came-face-to-face-over-inspector-in-jhansi-uttar-pradesh-news-ups25091500787</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.etvbharat.com/hi/!state/sub-inspector-sunil-kumar-rai-slaps-bjp-worker-in-mirzapur-ssp-suspended-departmental-inquiry-started-uttar-pradesh-news-ups25092003608</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://indianlooknews.com/?p=56810</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-bjp-divisional-president-amit-chauhan-blame-naveen-dhul-haryana-135939831.html</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.khabarwala24.com/national/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali/104403/</t>
+          <t>https://mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
+          <t>https://www.bhaskar.com/local/haryana/gurugram/news/political-upheaval-7-rebel-councillors-return-bjp-gurugram-135982046.html</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/legislative-trojan-horse-mallikarjun-kharge-slams-bjp-over-bill-on-removal-of-pm-cm-ministers/articleshow/123893656.cms</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Hallmark-of-Modi-s-strong-leadership-lies-in-ability-to-take-decisions-in-difficult-circumstances-BJP-leaders/2923219</t>
+          <t>https://www.prabhatkhabar.com/business/new-gst-rates-2025-leaders-reactions-gst-reform-india</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
+          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
+          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
+          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111292</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
+          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://firstindia.co.in/articles/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://mp.punjabkesari.in/national/news/scindia-s-statement-regarding-the-roads-of-mp-2213041</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.currentcrime.com/video-of-zubeen-garg-makes-everyone-cry/</t>
+          <t>https://www.wionews.com/business-economy/goods-and-services-tax-reforms-how-cheaper-will-tractors-get-minister-reveals-1758282747902</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/CPI-must-emerge-as-a-strong-force-that-can-shape-India-s-political-course-D-Raja/2936350</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
+          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/17/cong-observes-ex-mp-assembly-speaker-srinivas-tiwaris-100th-birth-anniversary-in-rewa/</t>
+          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111216</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13875</t>
+          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation-11758032543012.html</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/scindia-s-statement-regarding-the-roads-of-mp-2213041</t>
+          <t>https://ianslive.in/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister--20250919175149</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/vidisha/news/mla-tandon-submitted-a-6-point-demand-letter-for-the-development-of-vidisha-135938909.html</t>
+          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
+          <t>https://eng.ruralvoice.in/national/ghaziabad-farmer-neelam-tyagi-honoured-with-dr-norman-e-borlaug-innovative-farmer-award-2025.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/markets/capital-market-news/agriculture-sector-growing-at-impressive-pace-125091600244_1.html</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
+          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
+          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://ianslive.in/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister--20250919175149</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3631949-gst-cuts-on-farm-equipment-to-boost-atmanirbhar-bharat-vision</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
+          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://vocaltv.in/national/n-a-conference-in-pusa-today-and-tomorrowphp/cid17416096.htm</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
+          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
+          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
+          <t>https://www.kisantak.in/knowledge/story/food-grain-production-expected-to-increase-by-24-percent-despite-floods-and-disasters-1278860-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
+          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/india-may-impose-import-duties-on-pulses-to-protect-farmers-from-falling-prices</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/agri-rural-news-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%B2%E0%A4%AF-%E0%A4%9A%E0%A4%B2-%E0%A4%8F%E0%A4%97-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%85%E0%A4%AD-%E0%A4%AF-%E0%A4%A8-%E0%A4%9B%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B8%E0%A4%97%E0%A4%A2%E0%A4%BC-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%A7-%E0%A4%A8-%E0%A4%96%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%B0%E0%A4%9C-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%B5-%E0%A4%B0%E0%A5%8D%E0%A4%AF/ar-AA1MMI5R</t>
+          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
+          <t>https://eng.ruralvoice.in/state/ap-govt-offers-rs-800-incentive-per-bag-to-farmers-who-cut-urea-use.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india-plans-rs-2-billion-fund-to-boost-infrastructure-finance/78815</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
+          <t>https://statetimes.in/cbi-chargesheets-anil-ambani-rana-kapoor-in-rs-2796-crore-corruption-case/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/agriculture-sector-grows-by-37-per-cent-in-first-quarter-highest-in-the-world-chouhan-3253682.html</t>
+          <t>https://www.tv9hindi.com/state/haryana/haryana-lado-laxmi-yojana-launched-women-will-get-2100-rupees-per-month-from-25-september-3492755.html</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://navbharattimes.indiatimes.com/state/punjab-and-haryana/chandigarh/registration-for-cashless-treatment-rs-10-lakh-under-chief-minister-health-scheme-will-start-from-september-23-bhagwant-mann-announces/articleshow/124050803.cms</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-uttarakhand-government-schemes-review-cm-dhami-focuses-on-swift-implementation-24052708.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://rightnewsindia.com/pm-kisan-21st-installment-flood-affected-farmers-will-get-special-relief/</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://upuklive.com/business/the-21st-installment-of-pm-farmer-will-come-soon-for-the-farmers-a-gift-of-rs-2000-will-come-soon-23960.html</t>
+          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
+          <t>https://www.bhaskar.com/career/news/union-cabinet-approves-bio-ride-scheme-atishi-will-take-oath-as-chief-minister-on-september-21-133669316.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
+          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
+          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://statetimes.in/former-hurriyat-chief-abdul-gani-bhat-passes-away/</t>
+          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cme-cum-brainstorming-session-organised-by-mru-gmc-jammu/</t>
+          <t>https://argusenglish.in/national/pm-modi-to-inaugurate-purnea-airport-launch-rs-45000-crore-projects-in-bihar-on-sep-15</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://english.publictv.in/maharashtra-indian-railways-renames-ahmednagar-railway-station-as-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://starsamachar.com/sidhi-sp-shailendra-singh-crime-control-police-action</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/darbhanga/news/darbhanga-cricket-associations-annual-general-meeting-was-held-new-district-committee-was-elected-135989912.html</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://himachaldastak.com/chief-minister-tourism-start-up-scheme-gets-approval/</t>
+          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/registration-of-cashless-treatment-up-to-rs-10-lakh-under-chief-ministers-health-scheme-will-start-from-september-23-cm-mann/</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-gst-new-rates-uttarakhand-cm-launches-awareness-campaign-for-public-benefit-24055038.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
+          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
+          <t>https://www.bhaskar.com/local/bihar/rohtas/nokha/news/jan-suraj-partys-public-relations-campaign-in-nokha-135969085.html</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/himachal-government-will-bear-the-expenses-of-marriage-of-orphan-children-2216300</t>
+          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
+          <t>https://www.bhaskar.com/local/jharkhand/bokaro/news/pandal-on-the-lines-of-ashta-kastabhanjan-in-bokaro-135942281.html</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/states/maharashtra-news/maharashtra-govt-makes-ekyc-mandatory-for-beneficiaries-of/cid17441579.htm</t>
+          <t>https://www.bhaskar.com/local/haryana/charkhi-dadri/news/charkhi-dadri-mla-sunil-satpal-sangwan-monsoon-session-assembly-dadri-rohtak-road-tender-construction-issue-public-works-department-minister-ranbir-gangwa-135735700.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.theindiadaily.com/state/punjab/cashless-treatment-up-to-rs-10-lakh-punjab-first-state-in-the-country-to-launch-the-chief-minister-s-health-scheme-news-94860</t>
+          <t>https://bolchhattisgarh.in/divisional-level-nuakhai-milan-ceremony-of-dhurwa-samaj-in-jagdalpur-and-the-inauguration-program-of-newly-constructed-social-building-olerse/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/sidhi-sp-shailendra-singh-crime-control-police-action</t>
+          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/rudrapur/story-uttarakhand-cm-pushkar-singh-dhami-visits-khatima-listens-to-public-concerns-201758294392599.html</t>
+          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
+          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
+          <t>https://www.theweek.in/wire-updates/business/2025/09/19/dcm13-biz-chouhan-gst.html</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://eng.ruralvoice.in/cooperatives/kribhco-elects-v-sudhakar-chowdary-chairman-chandrapal-singh-yadav-vice-chairman.html</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-21-september-2025-in-hindi-todays-top-news</t>
+          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/2-more-doctors-appointed-in-dhaneta-hospital-2213561</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://hindi.moneycontrol.com/jobs/sarkari-naukri-government-jobs-in-himachal-recruitment-in-electricity-revenue-health-and-panchayati-raj-departments-article-2162823.html</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/alirajpur-district-renamed-aalirajpur-in-hindi-official-notification-issued-lcln-strc-2334595-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/pawan-singh-will-be-active-in-bihar-elections-2025-135981717.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
+          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/aligarh/story-aligarh-wholesalers-demand-action-against-fake-drug-dealers-at-cdf-up-annual-meeting-201758578893110.html</t>
+          <t>https://www.etvbharat.com/hi/!state/bhopal-artist-anjan-unique-gift-pm-narendra-modi-75th-birthday-1-painting-depicts-entire-life-madhya-pradesh-news-mps25091702758</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-holds-review-meeting-with-public-representatives-on-new-gst-rates-and-swadeshi-campaign-expresses-gratitude-to-pm-modi-and-finance-minister/</t>
+          <t>https://www.etvbharat.com/hi/!state/ashoknagar-woman-slapped-patwari-removal-cm-helpline-complaint-land-demarcation-case-madhya-pradesh-news-mps25091902940</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://raigarhtopnews.com/chief-minister-vishnudev-sai-attended-2/</t>
+          <t>https://www.etvbharat.com/hi/!state/balaghat-naxalites-kidnapping-youth-suspicion-informer-police-hawk-force-searching-forest-madhya-pradesh-news-mps25091703326</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/dehradun-chief-ministers-instructions-ready-on-dm-ground-zero-in-disaster-affected-areas/</t>
+          <t>https://www.etvbharat.com/hi/!state/rajasthan-manganiyar-singer-roze-khan-talk-etv-bharat-save-folk-music-madhya-pradesh-news-mps25091905402</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://www.etvbharat.com/hi/!state/ratlam-vijay-shah-kalika-mata-darshan-tree-planting-gabbar-style-dialogues-madhya-pradesh-news-mps25091801698</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://acn18.com/%E0%A4%B8%E0%A4%9A%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%BE%E0%A4%AF%E0%A4%B2%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82/</t>
+          <t>https://www.etvbharat.com/hi/!state/ratlam-theft-case-thief-trapped-in-chiller-unit-pipe-police-saves-life-madhya-pradesh-news-mps25091900829</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
+          <t>https://ianslive.in/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal--20250915134402</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/himachal-education-reform-cbse-curriculum-rajiv-gandhi-schools-student-loan-scheme-54-818476</t>
+          <t>https://www.freepressjournal.in/bhopal/bhopal-gandhi-medical-college-students-raise-concern-over-language-mismatch-in-internal-exams</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/setback-for-congress-karnataka-hc-invalidates-malur-mlas-election-orders-recounting-of-votes/articleshow/123923092.cms</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/morena-mp-live-news-today-21-september-2025-madhya-pradesh-breaking-update-crime-education-politics-samachar-aaj-ki-taza-khabar-livenews-9648356.html</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/nation/rajnath-shares-my-modi-story-praises-discipline-knowledge/56623</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/guest-teachers-want-regularization-as-guru-dakshina-135933602.html</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/organizations-protested-saying-the-government-used-societies-135963056.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/cm-will-inaugurate-the-buildings-of-animal-science-university-tomorrow-135971701.html</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
+          <t>https://www.bhaskar.com/local/punjab/bathinda/news/on-the-birthday-of-shaheed-bhagat-singh-we-will-surround-the-chief-ministers-residence-hakam-singh-dhanetha-135947665.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/alirajpur-district-renamed-aalirajpur-in-hindi-official-notification-issued-lcln-strc-2334595-2025-09-16</t>
+          <t>https://hindi.oneindia.com/news/bhopal/bjp-mp-alok-sharma-sharp-statement-ban-on-non-veg-shops-is-right-1390405.html</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/nitish-kumar-opened-his-treasure-for-women-voters-in-bihar-elections-hindi-news-brn25091900519</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/awareness-campaign-of-chief-minister-women-employment-scheme-started-135925182.html</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://hindi.oneindia.com/news/bhopal/demonstration-of-mp-guest-teachers-gathered-in-bhopal-ambedkar-park-demand-for-regularization-1386979.html</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/a-driver-was-bitten-by-a-snake-and-taken-to-the-hospital-but-was-released-as-soon-as-he-was-shown-to-a-doctor-in-ujjain/articleshow/123980598.cms</t>
+          <t>https://www.krishakjagat.org/news/onions-sold-at-just-rs-50-quintal-in-this-madhya-pradesh-market-know-todays-latest-rates/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/vidisha/stone-pelting-news-on-maa-kali-tableau-in-muslim-locality-committee-resolved-matter-amicably/articleshow/124053496.cms</t>
+          <t>https://vocaltv.in/rajasthan/amrita-haat-will-be-inaugurated-on-sundayphp/cid17448002.htm</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/mahakal-mandir-pandit-pujari-appointments-controversy-indore-high-court-seeks-answers-ujjain-collector-in-3-months/articleshow/123947146.cms</t>
+          <t>https://vocaltv.in/bihar/safety-standards-checked-operation-of-patna-metrophp/cid17426826.htm</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/ujjain-railway-station-accident-army-truck-caught-fire-loaded-in-goods-train-railway-staff-control-no-casualty-reported/articleshow/124024940.cms</t>
+          <t>https://www.newspuran.com/preparations-for-payment-of-more-than-rs-2-crore-to-acss-favorite-firm-ey</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
+          <t>https://www.eurasiareview.com/19092025-modi-at-75-the-statesman-the-swayamsevak-and-the-question-of-succession-oped/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
+          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/ujiyarpur-vidhan-sabha-chunav-analysis/</t>
+          <t>https://navbharatlive.com/maharashtra/pune/congress-harshwardhan-sapkal-devendra-fadnavis-rss-constitution-statement-1362143.html</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/kabirdham/news/dharna-in-kawardha-against-fir-against-journalist-135970021.html</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/there-will-be-6-main-and-3-recreational-games-in-mp-sports-festival-registration-starts-today-135939182.html</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://ianslive.in/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal--20250915134402</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/durg-bhilai/news/big-meetings-of-bjp-and-congress-on-the-same-day-in-durg-135965362.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/bhopal-gandhi-medical-college-students-raise-concern-over-language-mismatch-in-internal-exams</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ashoknagar/congress-mla-gopal-singh-chauhan-secretly-met-with-the-cm-mohan-yadav-in-ashok-nagar-sparking-speculation-about-his-entry-into-the-bjp-/articleshow/124019641.cms</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/morena-mp-live-news-today-21-september-2025-madhya-pradesh-breaking-update-crime-education-politics-samachar-aaj-ki-taza-khabar-livenews-9648356.html</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/bjp-mp-alok-sharma-sharp-statement-ban-on-non-veg-shops-is-right-1390405.html</t>
+          <t>https://www.indiatv.in/bihar/tejashwi-will-be-cm-face-no-second-option-congress-mp-big-statement-for-bihar-election-2025-09-20-1163974</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/organizations-protested-saying-the-government-used-societies-135963056.html</t>
+          <t>https://www.etvbharat.com/hi/!state/rewa-pandit-srinivas-tiwari-100th-birth-anniversary-statue-unveiling-congress-convention-madhya-pradesh-news-mps25091800671</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/RSS-leader-stresses-on-strengthening-Hindu-society-to-counter-global-conspiracies/2938144</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal</t>
+          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
+          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://humarabikaner.com/india/pm-modi-birthday-prime-ministers-75th-birthday-today/cid17427895.htm</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
+          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
+          <t>https://ganadesh.com/salute-to-sadanand-singhs-legacy-cm-nitish-will-unveil-the-statue-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/uttarakhandonly-with-the-strength-of-modi-dhami-will-the-next-decade-belong-to-uttarakhand/</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
+          <t>https://www.gyanwani.com/33520/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://mbmnewsnetwork.com/himachal-pradesh/854552/%E0%A4%B0%E0%A4%BF%E0%A4%9C-%E0%A4%AA%E0%A4%B0-13-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%8B-%E0%A4%B9%E0%A5%8B%E0%A4%97%E0%A4%BE-%E0%A4%B5%E0%A5%80%E0%A4%B0</t>
+          <t>https://navbharatlive.com/maharashtra/nashik/trimbakeshwar-parking-dispute-journalist-attack-case-nashik-1362570.html</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
+          <t>https://www.jagran.com/uttarakhand/haridwar-haridwar-news-saints-donate-34-lakh-to-cm-relief-fund-24055800.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://humarabikaner.com/india/pm-modi-birthday-prime-ministers-75th-birthday-today/cid17427895.htm</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/katni-who-is-katni-barwara-mla-dhirendra-singh-dhiru-gifted-gold-ring-cm-mohan-yadav-9643451.html</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
+          <t>https://www.prabhatkhabar.com/state/jharkhand/khunti/cm-and-chief-justice-in-khunti-today</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
+          <t>https://www.bhaskar.com/local/bihar/kaimur/news/bihar-has-taken-a-new-direction-under-the-leadership-of-chief-minister-nitish-135966397.html</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/congress-factionalism-came-out-in-the-open-in-front-of-the-leader-of-opposition/</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/today-is-the-24th-anniversary-of-the-bihar-state-womens-commission-135956535.html</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-potholes-roads-premix-material-135970302.html</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.gyanwani.com/33520/</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/hansi/news/hisar-hansi-market-encroachment-removal-drive-municipal-council-update-135951308.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nashik/trimbakeshwar-parking-dispute-journalist-attack-case-nashik-1362570.html</t>
+          <t>https://www.bhaskar.com/local/himachal/shimla/news/himachal-cabinet-meeting-decision-cm-sukhvinder-sukhu-doctor-staff-nurses-recruitment-shimla-135923978.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.bhaskar.com/bihar-election/news/pappu-yadav-talks-to-pm-on-stage-both-laugh-out-loud-135932167.html</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-protest-against-rajya-sabha-mp-ramchandra-jangra-meham-haryana-135924292.html</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/business/new-gst-rates-2025-leaders-reactions-gst-reform-india</t>
+          <t>https://22scope.com/chief-minister-launched-the-web-portal-of-mukhyamantri-pratiya-yojana-under-bihar-bhavan-and-other-construction-workers-welfare-board/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/raja-bhaiya-wife-bhanvi-singh-dispute-son-statement-big-reveals-3492379.html</t>
+          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
+          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-news-digvijay-singh-s-reply-to-siddharth-tiwari-s-statement-son-can-be-son-or-daughter-father-is-not-ang-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/education-minister-sunil-kumars-big-statement-on-tre-4-135982974.html</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://thechenabtimes.com/2025/09/22/government-approves-rs-1955-65-crore-for-110-roads-project-in-udhampur-kathua-doda-constituency/</t>
+          <t>https://www.tv9hindi.com/india/raja-bhaiya-wife-bhanvi-singh-dispute-son-statement-big-reveals-3492379.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
+          <t>https://www.bhaskar.com/local/himachal/mandi/news/himachal-news-mandi-maha-yagya-mp-kangana-ranaut-pm-modi-135940705.html</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-provided-financial-approval-of-rs-127-crore-for-various-development-schemes/</t>
+          <t>https://www.bhaskar.com/local/himachal/shimla/news/mandi-mp-kangana-ranaut-visit-disaster-affected-kullu-manikaran-pm-modi-birthday-himachal-135957922.html</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://citiupdate.com/news/detailNews/104931</t>
+          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/cm-nitish-kumar-patna-mauryalok-comprehensive-urban-development-schemes-3493262.html</t>
+          <t>https://www.bhaskar.com/local/haryana/sonipat/news/harsh-chhikara-supports-uttar-kumar-rape-allegation-statement-135965440.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-harshita-soni-missing-case-update-harshita-found-delhi-135957260.html</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/inox-neo-energies-to-acquire-640-mw-hybrid-portfolio-from-evergreen-group-/78793</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/psp-projects-sets-world-record-with-umiya-dham-foundation/79013</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://shikharhimalaya.com/dehradun-expedite-implementation-of-development-plans-cm/</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/wastewater-and-sewage-treatment/ramky-wins-rs-20.85-billion-godavari-water-project/79057</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://www.constructionworld.in/latest-construction-technology/tekla-user-days-2025-highlights-collaboration-and-tech-led-construction-/78852</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/ntpc-plans-nuclear-power-projects-via-jv-and-standalone-routes/78900</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/highways-and-roads-infrastructure/govt-approves-rs-4.45-billion-mokama-munger-highway-project/78743</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/goa-approves-rs-1.92-billion-mapusa-bus-stand-projec/78876</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/metro-rail-and-railways-infrastructure/gwalior-railway-station-redevelopment-set-for-swift-completion/78894</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://rewariupdate.com/haryana-gets-a-gift-of-rs-117-crore/</t>
+          <t>https://www.thehawk.in/news/india/cm-mohan-yadav-inaugurates-sandipani-school-in-katni-joins-cleanliness-drive-in-jabalpur</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.babushahi.com/business.php?id=210834</t>
+          <t>https://www.bhaskarenglish.in/national/news/pm-modi-arunachal-tripura-hydropower-project-itanagar-tripura-sundari-temple-135981681.html</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/uae-firms-keen-to-invest-in-indian-infra-banking-startups-logistics-sectors-commerce-minister-piyush-goyal/articleshow/124001887.cms</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
+          <t>https://www.deshsewak.org/hindi/news/218872</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/dehradun-cm-dhami-returned-from-delhimlas-and-public-representatives-made-a-courtesy-visit/</t>
+          <t>https://www.jagran.com/uttar-pradesh/ghaziabad-ncr-ghaziabad-news-robot-assisted-sewer-cleaning-pilot-project-launched-24053307.html</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.in/national/news/foundation-stone-laid-for-eight-major-connectivity-road-projects-2216961</t>
+          <t>https://www.bhaskar.com/local/bihar/motihari/news/cm-nitish-kumar-will-come-to-motihari-tomorrow-135984378.html</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
+          <t>https://www.dainiktribuneonline.com/news/nation/pm-modi-turns-75-haryana-cm-saini-launches-seva-pakhwada-in-rohtak/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
+          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/cm-nayab-singh-saini-mega-road-upgradation-project-647580</t>
+          <t>https://www.chinimandi.com/gujarat-handles-49-of-total-national-cargo-chief-minister-bhupendra-patel-lauds-pm-modis-vision-for-the-maritime-sector-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
+          <t>https://www.livemint.com/hindi/money/rs-10000-will-be-deposited-in-accounts-of-50-lakh-women-on-september-22nd-under-bihar-mukhyamantri-mahila-rojgar-yojana-241758295360592.html</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.sabguru.com/haryana-cm-nayab-singh-saini-inaugurates-557-projects-worth-about-rs-117-crore-in-sonipat</t>
+          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
+          <t>https://haryana.punjabkesari.in/haryana/news/haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-2214274</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/delhi-cm-rekha-gupta-launches-song-for-pm-narendra-modis-birthday/articleshow/123921234.cms</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/hisar/agriculture-university-hau-rabi-fair-cm-nayab-singh-saini-647591</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
+          <t>https://shikharhimalaya.com/dehradun-expedite-implementation-of-development-plans-cm/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1086674/how-bjp-governments-companies-celebrated-pm-modis-75th-birthday</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
+          <t>https://vasundharadeep.news/two-day-programs-dedicated-to-public-service-and-cleanliness-started-in-the-vending-zone/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
+          <t>https://devbhoomidarshan.in/cm-dhami-honored-the-artisans-and-weavers-of-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/srinagar-jk-disaster-pm-modi-will-visit-the-devastation-in-jammu-and-kashmir-omar-abdullah-looking-at-the-relief-package-24054487.html</t>
+          <t>https://uttarakhandcitynews.com/bade-kadidehradun-chief-minister-made-craftsmen-of-11-places-including-halduchod-haldwani-nainital-with-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/blogs/amish-devgan/pm-narendra-modi-75th-birthday-reason-behind-indian-prime-minister-power-and-popularity-writes-amish-devgan-9632298.html</t>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-today-19-september-program-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/jammu-and-kashmir-flood-damage-report-cm-asks-officials-to-speed-up-assessment-ahead-of-pms-expected-visit-hindi-news-hin25092204098</t>
+          <t>https://tejastoday.com/loans-provided-to-the-beneficiaries-of-chief-minister-youth-entrepreneur-scheme/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
+          <t>https://garimatimes.in/a-big-gift-to-artisans-in-haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-rohtak-news-updates/</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
+          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
+          <t>https://www.kadwaghut.com/?p=260635</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://insiderlive.in/jp-ganga-path-koilwar-expansion-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/n-a-conference-in-pusa-today-and-tomorrowphp/cid17416096.htm</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-announces-formation-of-monitoring-committees/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90048</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/transrail-expands-footprint-in-africa-with-new-epc-project/78806</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/smart-cities-projects/global-south-diplomats-visit-bhubaneswar-smart-city/78934</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://cnin.co.in/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A4%BE%E0%A4%AE-%E0%A4%A8%E0%A4%88-%E0%A4%A6%E0%A4%BF%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%BF%E0%A4%A4.../70480</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/cerc-proposes-stricter-grid-deviation-rules-for-renewable-projects-/78995</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90140</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/c-dot-joins-pnb-to-drive-it-upgrade-and-digital-banking/78763</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/15/cm-mann-warned-the-pm-modi/</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/coal-and-mining/government-to-promote-underground-coal-gasification-in-auctions/79070</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan?amp</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-ldb-2.0-to-boost-digital-logistics-tracking/79079</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/defence/indian-army-rolls-out-first-overhauled-arv-vt-72b-with-jcbl-group-partnership/79056</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-leads-2025-to-benchmark-state-logistics/79078</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/vikram-solar-secures-200-mw-order-to-expand-india---s-solar-capacity/78863</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://hindi.theprint.in/india/permanent-infrastructure-for-simhastha-will-be-built-only-with-consensus-farmers-will-be-protected-chief-minister-yadav/869129/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/rohtak/chief-minister-vishwakarma-samman-yojana-launched-artisans-will-get-a-top-up-incentive-of-rs-5000/</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/tamilnadu-chief-minister-stalin-launches-anbu-karangal-scheme-hindi-news-hin25091503706</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-praadeshik-sadak-utthaan-pariyojana-inauguration-update-135976694.html</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
+          <t>https://www.abplive.com/states/himachal-pradesh/himachal-floods-rs-20000-crore-loss-cm-sukhvinder-singh-sukhu-statement-on-relief-efforts-ann-3013837</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/gorakhpur-city-viksit-bharat-viksit-uttar-pradesh-2047-workshop-in-gorakhpur-24049561.html</t>
+          <t>https://ddnews.gov.in/200-students-rescued-from-submerged-institute-in-dehradun-after-heavy-rains-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
+          <t>https://www.dainikjagranmpcg.com/opinion/prime-minister-narendra-modi-is-the-champion-of-technology/article-33454</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
+          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/engineer-s-day-will-be-celebrated-with-the-resolution-of-public-welfare-survey-app-and-public-project-manage-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
+          <t>https://www.khaskhabar.com/local/haryana/hisar-news/news-public-money-will-be-used-for-the-public-good-nayab-singh-saini-news-hindi-1-754587-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
+          <t>https://www.tv9hindi.com/state/bihar/bihar-cm-nitish-kumar-mukhyamantri-gramin-setu-yojana-construction-of-703-new-bridges-started-across-the-state-3491602.html</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://cnin.co.in/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%BE-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4%E0%A5%80-%E0%A4%AA%E0%A4%B0-%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%A7%E0%A4%BE%E0%A4%A8%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A5%8D%E0%A4%B0%E0%A4%AE%E0%A4%BF%E0%A4%95.../70476</t>
+          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/the-chief-minister-will-launch-the-app-for-the-deendayal-ladli-laxmi-yojana-scheme-on-september-25/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/jammu-and-kashmir-flood-damage-report-cm-asks-officials-to-speed-up-assessment-ahead-of-pms-expected-visit-hindi-news-hin25092204098</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
+          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/foundation-stone-laid-for-8-link-road-projects-worth-rs-1215-crore-135988387.html</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://krantiodishanews.in/post/13872</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
+          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
+          <t>https://devbhoomimedia.com/mla-meat-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://rghnews.com/cg-news-raipur-62/</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://rghnews.com/cg-news-today-89/</t>
+          <t>https://navpradesh.com/chhattisgarh-silver-jubilee-2/</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
+          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
+          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://www.outlookbusiness.com/planet/industry/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-chouhan</t>
+          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.newsgram.com/india/2025/09/16/sc-seeks-statess-responses-on-pleas-against-anti-conversion-laws</t>
+          <t>https://sundayguardianlive.com/news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448-143406/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
+          <t>https://scroll.in/latest/1086674/how-bjp-governments-companies-celebrated-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/economy/government-sets-record-wheat-production-target-of-119-million-tonnes-for-2025-26/869431/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
+          <t>https://www.newsonair.gov.in/pm-modis-vision-realised-as-gst-council-slashes-tax-on-agricultural-equipment/</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/srinagar-jk-disaster-pm-modi-will-visit-the-devastation-in-jammu-and-kashmir-omar-abdullah-looking-at-the-relief-package-24054487.html</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+          <t>https://www.bhaskar.com/local/bihar/purnia/news/pm-will-inaugurate-airport-and-hold-public-meeting-in-3-hours-135923374.html</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/news/modi-government-reduced-gst-rates-135928493.html</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/flood-fury-devastates-punjab-45-lakh-acres-of-paddy-destroyed-mandis-deserted-farmers-face-triple-crisis</t>
+          <t>https://www.bhaskar.com/career/news/pm-modi-launches-odisha-governments-subhadra-yojana-education-minister-atishi-marlena-will-be-the-new-chief-minister-of-delhi-133658792.html</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
+          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://mp.punjabkesari.in/national/news/pm-modi-said-dhar-s-textiles-will-shine-in-the-world-pm-mitra-park-will-become-2214028</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://smefutures.com/moil-starts-manganese-exports-as-state-trading-enterprise/</t>
+          <t>https://www.bhaskar.com/local/bihar/jehanabad/news/tejashwi-bihar-adhikar-yatra-start-from-jehanabad-135927540.html</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://www.punjabkesari.in/business/news/3-7-growth-in-agriculture-sector-in-first-quarter-is-highest-2213431</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/national-agriculture-conference-rabi-abhiyan-2025-union-agriculture-minister-shivraj-chauhan/</t>
+          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/maharashtra-urges-centre-to-double-onion-export-subsidy-to-support-farmers</t>
+          <t>https://www.ruralvoice.in/agribusiness/mother-dairy-reduces-prices-to-pass-on-gst-benefits-to-consumers.html</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://cnin.co.in/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A4%BE%E0%A4%AE-%E0%A4%A8%E0%A4%88-%E0%A4%A6%E0%A4%BF%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%BF%E0%A4%A4.../70480</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
+          <t>https://media24news.in/?p=90140</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
+          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
+          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://www.aajtak.in/uttar-pradesh/story/viksit-uttar-pradesh-summit-2025-yogi-adityanath-brajesh-pathak-malini-awasthi-ntc-dskc-2339107-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://lalluram.com/govt-is-continuously-committed-to-upliftment-of-deprived-class-expansion-of-public-facilities/</t>
+          <t>https://www.dainiktribuneonline.com/news/gurugram/labour-service-and-awareness-function-on-28th-cm-will-be-the-chief-guest/</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/amit-shah-advises-farmers-to-reduce-use-of-pesticides-and-fertilizers-swm-1281204-2025-09-22</t>
+          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-lado-lakshmi-yojana-app-will-be-launched-from-25-september-trial-will-start-haryana-news-hrs25091603418</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
+          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://delhiuptodate.com/mukhyamantri-vishwakarma-samman-yojana-launch-artisans-will-get-a-topup-incentive-of-%E2%82%B9-5000/</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
+          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttar-pradesh/maharajganj/women-empowerment-is-the-priority-of-the-government-maharajganj-news-c-206-1-sgkp1021-160093-2025-09-21</t>
+          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/uttar-pradesh/story/yogi-adityanath-writes-pm-narendra-modi-birthday-wishes-ntc-dskc-2335103-2025-09-17</t>
+          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/reoti/news/chief-minister-yogi-adityanath-emphasizes-on-women-empowerment-135967270.html</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/balrampur/news/30-crore-government-building-became-dilapidated-135927497.html</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://www.outlookbusiness.com/planet/industry/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-chouhan</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://www.newsgram.com/india/2025/09/16/sc-seeks-statess-responses-on-pleas-against-anti-conversion-laws</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kaithal/chief-minister-will-launch-lado-laxmi-yojana-on-25th-kaithal-news-c-18-1-knl1004-743259-2025-09-21</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
+          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/hathras/chhauragadaua/news/special-honor-in-national-women-empowerment-workshop-135976706.html</t>
+          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/chief-minister-inaugurated-mission-shakti-phase-5-0-dedicated-to-women-empowerment/</t>
+          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://www.swatantraprabhat.com/article/155542/chief-minister-inaugurated-newly-established-mission-shakti-kendras-in-1663</t>
+          <t>https://www.lokmattimes.com/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.cnbctv18.com/economy/gst-new-rates-india-live-updates-two-slab-system-september-22-nirmala-sitharaman-gst-2-0-itc-council-reforms-5-18-40-pc-liveblog-19681684.htm</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://khatpatnews.com/?p=61931</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://www.jansatta.com/videos/news-video/muslim-side-happy-with-supreme-courts-decision-on-waqf-act-2025/4144695/</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://hilllive.in/i-copy-mafia-will-not-be-spared-chief-minister/.html</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/dehradun-chief-minister-launched-the-service-fortnight-exhibition-in-municipal-corporation/</t>
+          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
+          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://www.etvbharat.com/hi/!state/bhopal-bharatiya-kisan-sangh-protest-against-land-acquisition-ujjain-simhastha-2028-mohan-yadav-assured-madhya-pradesh-news-mps25091505407</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
+          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.mahanagartimes.com/post/bhajanlal-sharma-announced-construction-new-training-building-at-rpa</t>
+          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/piyush-goyal-to-visit-uae-for-13th-india-uae-high-level-task-force-on-investments/78929</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/income-tax-return-filing-last-date-news-last-chance-to-file-itr-do-it-quickly-or-else-itr-2025-2025-09-15</t>
+          <t>https://www.jagran.com/himachal-pradesh/shimla-himachal-cm-sukhu-disgruntled-with-punjab-and-haryana-over-bbmb-and-shanan-project-24047696.html</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://www.punjabkesari.com/top-news/cm-vishnu-deo-sai/</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/india-us-ties-tested-after-trump-attack-yet-still-stronger-than-chinas-trust-gap-says-us-foreign-policy-expert/articleshow/123939627.cms</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://smefutures.com/india-oman-trade-agreement-fta-oman-trade-deal/</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/eu-eyes-deeper-india-partnership-despite-concerns-over-moscow-ties/articleshow/123943367.cms</t>
+          <t>https://newsheight.com/big-breaking-chief-minister-pushkar-singh-dhami-impressed-by-the-overflows/</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/indias-exports-likely-to-grow-6-per-cent-this-year-piyush-goyal/articleshow/123947681.cms</t>
+          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/igf-qetci-sign-pact-to-develop-uk-india-quantum-value-chain-map/articleshow/123996773.cms</t>
+          <t>https://ibgnews.com/2025/09/20/shri-h-m-bangur-chairman-shree-cement-conferred-honorary-doctorate-by-kiit-university/</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/us-revokes-sanctions-exemption-on-irans-chabahar-port-what-it-means-for-indias-strategic-gateway/articleshow/123979793.cms</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/foreign-trade/india-in-advanced-talks-with-oman-for-fta-open-to-trade-deals-with-other-gcc-nations-piyush-goyal/articleshow/124001364.cms</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/sukma/news/awareness-was-also-created-about-women-empowerment-in-the-workshop-135978839.html</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/russia-india-business-dialogue-2025-to-be-organised-at-up-international-trade-show/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/tripura-opposition-unhappy-with-no-business-in-assembly-on-sept-22-due-to-pm-modis-visit/articleshow/123999325.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-yogi-adityanath-in-lucknow-kick-starts-mission-shakti-5-former-govts-jobs-to-females-uttar-pradesh-news-ups25092003463</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167813</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/mp-leaders-got-political-power-from-family-revealed-adr-report-on-political-dynasty-madhya-pradesh-news-mps25091505793</t>
+          <t>https://www.amarujala.com/lucknow/mission-shakti-5-0-launched-in-up-cm-yogi-releases-sop-booklets-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/barabanki/ramsnehi-ghat/news/mission-shakti-50-launched-135966763.html</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
+          <t>https://www.bhaskar.com/local/haryana/sonipat/news/sonipat-updates-haryana-cm-saaini-seva-pakhwada-dcrsut-murahtal-program-135981755.html</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/bihar/patna-pm-narendra-modi-purnia-rally-nitish-kumar-statement-on-lalan-singh-nda-politics-analysis-bihar-chunav-9628128.html</t>
+          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
+          <t>https://clipper28.com/union-women-and-child-development-minister-annapurna-devi-paid-a-courtesy-call-on-chief-minister-vishnu-dev-sai/</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
+          <t>https://crimejasoos.in/news/up-news/82978/</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/karnataka-cm-siddaramaiah-says-socio-educational-survey-of-backward-castes-to-not-be-postponed-2025-09-19</t>
+          <t>https://garimatimes.in/uttarakhand-cm-dhami-inaugurated-exhibition-in-dehradun-as-part-of-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/politics-on-bhura-baal-saaf-karo-in-bihar-election-2025-hindi-news-brn25091604889</t>
+          <t>https://khatpatnews.com/?p=61931</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
+          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/dehradun/cm-pushkar-singh-dhami-shared-my-modi-story-on-social-media-when-pm-modi-went-surprise-inspection-midnight/2924358</t>
+          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/mp-cm-mohan-yadav-list-of-corporations-and-boards-ready-before-cabinet-expansion-bjp-organization-1390793.html</t>
+          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
+          <t>https://www.bhaskar.com/local/bihar/siwan/news/beneficiaries-of-pm-kisan-samman-nidhi-yojana-should-get-their-kyc-done-135962013.html</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
+          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/bihar-chief-minister-nitish-kumar-met-union-home-minister-amit-shah/</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
+          <t>https://www.krishakjagat.org/news/animal-husbandry-farmers-benefited-from-the-chief-ministers-dairy-plus-scheme/</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
+          <t>https://www.krishakjagat.org/news/cm-yadav-went-to-the-fields-and-inspected-the-affected-crops-said-farmers-should-not-worry-every-field-will-be-surveyed/</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation-11758032543012.html</t>
+          <t>https://www.krishakjagat.org/national-news/todays-weather-very-heavy-rain-alert-in-northeast-and-maharashtra-monsoon-returns-to-rajasthan-punjab-gujarat/</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
+          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/morena-mock-drill-exercise-before-farmers-protest-kailaras-sugar-mill-police-lathicharge-and-firing-madhya-pradesh-news-mps25092101046</t>
+          <t>https://www.financialexpress.com/policy/economy-india-us-agree-to-step-up-efforts-for-early-bta-3979894/</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india--new-zealand-fta-talks-advance-in-queenstown/79087</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
+          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/tech/newsletters/morning-dispatch/the-h-1b-silver-lining-festive-sales-day-1-surge/articleshow/124059068.cms</t>
+          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/economy/gst-new-rates-india-live-updates-two-slab-system-september-22-nirmala-sitharaman-gst-2-0-itc-council-reforms-5-18-40-pc-liveblog-19681684.htm</t>
+          <t>https://www.facebook.com/BBCnewsHindi/posts/%E0%A4%9C%E0%A4%AF%E0%A4%B0%E0%A4%BE%E0%A4%AE-%E0%A4%B0%E0%A4%AE%E0%A5%87%E0%A4%B6-%E0%A4%AC%E0%A5%8B%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%95%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%87%E0%A4%95%E0%A4%BC%E0%A4%B2%E0%A5%8C%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A5%E0%A5%87%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%80-%E0%A4%96%E0%A4%BC%E0%A4%AC%E0%A4%B0-h/905180755408570/</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
+          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/small-biz/sustainability/bizarre-climate-ideas-show-how-far-off-track-we-are/articleshow/123965955.cms</t>
+          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
+          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
+          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan?amp</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
+          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
+          <t>https://www.patrika.com/bhopal-news/nepotism-in-mp-politics-many-leaders-including-scindia-digvijay-inherited-politics-adr-report-19949471</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
+          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/delhi/other-news/marking-of-leelas-should-also-be-done-on-basis-of-cleanliness-and-environment-said-cm/articleshow/124038453.cms</t>
+          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+          <t>https://www.jagran.com/haryana/panchkula-haryana-politics-birendra-singh-created-an-atmosphere-for-kumari-selja-bhupendra-hooda-turned-tables-said-neither-tired-nor-retired-24056405.html</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-giriraj-singh-ignited-another-fire-in-the-mahagathbandhan-saying-rahul-took-political-advantage-of-tejashwi/articleshow/123979673.cms</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+          <t>https://www.bhaskar.com/local/haryana/panchkula/news/chandigarh-asks-haryana-school-teachers-135958903.html</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cms-emphasis-on-speeding-up-implementation-of-schemes/</t>
+          <t>https://www.gnttv.com/india/story/bihar-politics-lalu-prasad-yadav-did-not-get-the-cms-chair-easily-ram-sundar-das-and-raghunath-jha-were-also-in-the-race-to-become-the-chief-minister-1279641-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-75--1187799</t>
+          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+          <t>https://www.etvbharat.com/hi/!state/marathon-in-kurukshetra-namo-youth-run-2025-cm-nayab-saini-on-parivarvad-haryana-news-hrs25092100814</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+          <t>https://www.bhaskarhindi.com/other/delhi-cm-rekha-gupta-inaugurates-first-large-scale-biogas-plant-at-nangli-dairy-targets-kejriwal-1189076</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/haryana/kurukshetra/namo-yuva-run-will-be-held-on-21st-september-at-brahmasarovar-chief-minister-will-participate-kurukshetra-news-c-45-1-knl1024-142106-2025-09-15</t>
+          <t>https://www.timesnowhindi.com/elections/tejashwi-yadav-will-be-cm-face-of-mahagathbandhan-in-bihar-elections-says-congress-mp-akhilesh-prasad-singh-article-152861720</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
+          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/uttarakhand-events-were-held-across-the-state-on-prime-minister-modis-birthday-cm-dhami-inaugurated-the-swachh-utsav-2025-program</t>
+          <t>https://ind24.tv/news/scindia_MP</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>https://nayabharat.live/uttarakhand-news-the-first-meeting-of-the-state-level-direction-committee-in-the-secretariat-chaired-by-chief-minister-dhami-said-that-the-implementation-of-the-schemes/</t>
+          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/government-teachers-marched-to-the-chief-ministers-residence-to-raise-their-demands/</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
+          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-nabha-farmers-protest-dispute-female-dsp-mandeep-news-135984706.html</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-bathinda-court-again-issues-summons-bjp-mp-actor-kangana-ranaut-news-135933597.html</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
+          <t>https://www.etvbharat.com/hi/!state/farmers-protest-against-land-pooling-scheme-in-ujjain-simhastha-2028-madhya-pradesh-news-mps25091604176</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
+          <t>https://hindi.oneindia.com/news/bhopal/farmers-agitation-against-land-pooling-act-demonstration-by-bharatiya-kisan-sangh-and-karni-sena-1386239.html</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+          <t>https://inanews.org/lucknow-agriculture-minister-attended-the-national-agriculture-conference--rabi-abhiyan-2025-in-new-delhi</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+          <t>https://krishijagran.com/news/dr-jitendra-singh-calls-biotechnology-india-s-next-industrial-revolution-highlights-bio-e3-policy-and-ai-healthcare-initiative/</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/indian-real-estate-draws--80bn-in-15-years--57-per-cent-from-foreigners/78892</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>https://statetimes.in/dc-jammu-reviews-functioning-of-swd/</t>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>https://www.punjabnewsexpress.com/business/news/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-297667</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/niti-aayog-launches-ai-roadmap-and-frontier-tech-repository/78832</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>https://cg24news.in/bjp-20925</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/asm-tech-to-invest-rs-2.50-bn-in-tamil-nadu/78907</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/newsite/erelcontent.aspx?relid=276221</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/godrej-finance--muthoot-join-hands-to-boost-msme-lending/79061</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+          <t>https://www.bhaskar.com/local/punjab/amritsar/news/amritsar-durgiana-temple-langoor-mela-navratri-2025-135978487.html</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>https://upkiran.org/GST-cut-bring-huge-relief-to-farmers-tractors-and-agricultural-equipment-now-be-cheaper</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+          <t>https://dainikdehat.com/states/uttar-pradesh/problems-of-farmers-cows-and-h1b-visa-holders-persist-akhilesh-targets-bjp</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>https://spokesmanhindi.com/national/punjab/170925/central-government-releases-sdrf-funds-punjab-receives-advance-instal.html</t>
+          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
+          <t>https://www.jagran.com/haryana/panchkula-13-solid-waste-management-plants-to-be-set-up-in-haryana-e-waste-collection-centres-in-every-district-375-electric-buses-to-arrive-24049075.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/chief-minister-naib-singh-saini-launched-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/haryana/panchkula/news/cm-launched-haryana-state-environment-plan-2025-135934095.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-utensils-bank-135983940.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/jogapatti/news/one-tree-in-the-name-of-mother-tree-plantation-program-in-machhargaon-135969599.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-news-rao-narbir-singh-said-namo-van-will-be-established-at-75-places-in-haryana-during-seva-pakhwada/</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/haryana/panchkula-haryana-state-environment-plan-2025-launched-by-cm-nayab-singh-saini-know-benefits-24048895.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>https://avikaluttarakhand.com/uttarakhand/cms-emphasis-on-speeding-up-implementation-of-schemes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>https://panchjanya.com/2025/09/17/435757/bharat/uttarakhand/cm-dhami-launched-a-cleanliness-drive-on-pm-modi-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/haryana-cm-nayab-saini-seva-pakhwada-swachhata-abhiyan-on-pm-modi-birthday-in-rohtak-mdu-haryana-news-hrs25091700782</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>https://garimatimes.in/chief-minister-nayab-singh-saini-launched-state-environment-plan-2025-appealed-to-citizens-to-save-water-plant-trees-and-keep-environment-clean/</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/dap-shortage-for-rabi-crops-agra-agriculture-officer-says-npk-provide-better-yield-uttar-pradesh-news-ups25091900464</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>https://eng.ruralvoice.in/latest-news/10-eminent-agricultural-scientists-urge-pm-modi-to-expedite-clearance-for-gm-mustard.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>https://cg24news.in/bjp-20925</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B5%C2%B3%C2%B7&amp;fontname=Mangal&amp;LocID=32&amp;pubdate=19%20Sep%202025</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-22-september-2025-3492207.html</t>
         </is>
       </c>
     </row>

--- a/Output/Shivraj Singh Chauhan/extracted_links.xlsx
+++ b/Output/Shivraj Singh Chauhan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A782"/>
+  <dimension ref="A1:A655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,77 +459,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-chouhan-pulses-oilseeds-production-policy-reforms-125091501403_1.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
+          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
+          <t>https://www.indiatvnews.com/news/india/shivraj-singh-chouhan-extends-birthday-wishes-to-pm-modi-shares-emotional-story-of-their-first-meeting-during-ekta-yatra-of-1992-2025-09-17-1008565</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
+          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
+          <t>https://m.economictimes.com/news/economy/agriculture/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-shivraj-singh-chouhan/articleshow/123904924.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/foodgrain-fruit-and-vegetable-yield-rose-this-year-says-agriculture-minister/article70058267.ece</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-chairs-key-meeting-on-gst-reforms-for-agriculture-machinery/126805</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/adequate-supply-of-seeds-fertilisers-for-the-rabi-season-minister-shivraj-singh-chouhan-3730932</t>
+          <t>https://www.ptinews.com/story/business/shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22/2929091</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-plants-75-saplings-to-mark-pm-modis-birthday-1007339</t>
+          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/india-news-live-updates-h1-b-visa-trump-pm-modi-delhi-zubeen-garg-weather-news-breaking-news-live-21-september-liveblog-13563395.html</t>
+          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
+          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-plants-sapling-at-pusa-greets-pm-modi-on-75th-birthday/</t>
+          <t>https://www.business-standard.com/industry/agriculture/shivraj-singh-chouhan-pm-kisan-benefits-border-farmers-125091900905_1.html</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
@@ -571,5334 +571,4445 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167392</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/j-k/will-rebuild-5000-houses-in-flood-hit-areas-says-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
+          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/news/india/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.newsonair.gov.in/shivraj-singh-chouhan-hails-pm-modis-leadership-as-swasth-nari-campaign-takes-off/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/delhi-confidential/delhi-confidential-ministers-meet-10254247/</t>
+          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2166972</t>
+          <t>https://www.thehindu.com/opinion/op-ed/a-leader-who-has-connected-power-to-the-people/article70077834.ece</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/economy/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-friday-to-ensure-gst-benefits-are-passed-on-to-farmers/126758</t>
+          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative20250921163119</t>
+          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-shivraj-singh-chouhan-assures-support-to-flood-hit-farmers-in-jammus-r-s-pura/</t>
+          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/362-50-million-tonne-foodgrain-production-target-set-for-2025-26-shivraj-singh-chouhan-1503487179.html</t>
+          <t>https://sundayguardianlive.com/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813-142577/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
+          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.news18.com/business/economy/gst-rate-cut-to-benefit-farmers-as-farm-machinery-prices-to-fall-says-shivraj-singh-chouhan-ws-l-9583330.html</t>
+          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/union-minister-shivraj-singh-chouhan-sets-food-grain-production-target-at-362-5-mt-for-rabi-season-2025-26/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
+          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/shivraj-singh-chouhan-speaks-with-farm-mechanisation-associations-urges-transfer-of-reduced-gst-benefits-to-farmers/</t>
+          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/indias-agriculture-grows-at-world-s-fastest-37-rate-shivraj-singh-appreciates-farmers-scientists-and-government-policies-at-rabi-abhiyan-2025-conference/</t>
+          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/gst-cut-a-boon-for-farmers-machinery-to-get-cheaper/</t>
+          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/govt-sets-rabis-crops-production-target-36250-million-tonnes-shivraj-singh-chauhan-453111</t>
+          <t>https://www.aninews.in/news/national/general-news/one-nation-one-election-is-in-the-interest-of-the-country-union-minister-shivraj-singh-chouhan-hails-onoe-bill20250921171136</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-sets-2025-26-rabi-food-grain-production-target-at-362-5-million-tonnes-shivraj-singh-chouhan/</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/union-agriculture-minister-shivraj-singh-chouhan-announces-gst-reforms-on-agricultural-machinery-cheaper-equipment-direct-farmer-benefits-and-awareness-drive-under-viksit-krishi-sankalp-ab/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/union-agriculture-minister-mr-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/agriculture-minister-asks-farm-equipment-amp-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers20250919111813-142577/</t>
+          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/union-agriculture-minister-shivraj-singh-chouhan-to-hold-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/shivraj-singh-chouhan-chairs-meeting-with-farm-machinery-associations-to-ensure-gst-benefits-reach-farmers-from-sept-22/</t>
+          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.crosstownnews.in/post/147010/union-minister-shivraj-chouhan-in-jammu-minister-mp-bjp-chiefmlas-accompany.html</t>
+          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
+          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167249</t>
+          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-shivraj-1008224</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bom16-mp-polls-resolution.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/centre-to-provide-pm-kisan-relief-rs-76-crore-for-shgs-in-flood-hit-jammu-shivraj-singh-chouhan/</t>
+          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/union-minister-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-jk-101758310893588.html</t>
+          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
+          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
+          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/chouhan-promises-approval-of-package-for-5-000-flood-hit-rural-houses-in-j-k/2930370</t>
+          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://arunachalobserver.org/2025/09/17/wangsu-urges-goi-for-state-specific-policy-interventions-for-himalayan-hilly-states-in-national-agri-conference/</t>
+          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3633787-centre-announces-relief-for-flood-hit-farmers-in-jk-says-shivraj-chouhan</t>
+          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168625</t>
+          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
+          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/mr-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
+          <t>http://www.uniindia.com/photoes/638071.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/economy/agri-business/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj/article70053700.ece</t>
+          <t>https://www.uniindia.com/photoes/638794.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/local-bodies-in-mps-raisen-passed-resolutions-supporting-one-nation-one-election-chouhan/2936291</t>
+          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/agri-minister-urges-farm-equipment-makers-to-pass-on-gst-cut-benefits-572263</t>
+          <t>https://tennews.in/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3633021-agricultural-boost-gst-cuts-lead-to-tractor-price-reductions</t>
+          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/farm-machinery-manufacturers-must-bypass-middlemen-to-ensure-benefits-reach-farmers-shivraj-singh-chouhan.html</t>
+          <t>https://www.greaterkashmir.com/gk-top-news/centre-approves-110-road-projects-worth-rs-2000-cr-for-udhampur-ls-segment/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/second-phase-of-viksit-krishi-sankalp-abhiyan-to-begin-under-the-leadership-of-union-agriculture-minister-mr-shivraj-singh-chouhan/</t>
+          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/centre-sets-362-50-million-tonne-foodgrain-target-for-2025-26-at-rabi-conference/</t>
+          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
+          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
+          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/chouhan-announces-relief-package-for-flood-hit-jammu-villages-1503488859.html</t>
+          <t>https://kashmirdespatch.com/national-agriculture-conference-rabi-abhiyan-2025-inaugurated-by-union-agriculture-minister-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/agriculture-minister-holds-delhi-meet-to-ensure-gst-relief-reaches-farmers/</t>
+          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/chouhan-to-visit-rs-pura-today/</t>
+          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/rabi-2025-national-agriculture-conference-delhi/</t>
+          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638072.html</t>
+          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/rabi-conference-2025-two-day-national-agriculture-conference-begins-in-delhi-today/</t>
+          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/photoes/638789.html</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://tennews.in/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>http://www.uniindia.com/photoes/638736.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/rs-1-3-lakh-under-pmay-full-crop-insurance-rs-76-cr-for-shgs-compensation-for-crops-animals/</t>
+          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-press-conference-gallery/</t>
+          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278592969/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation</t>
+          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/19/jammu-shivraj-singh-chouhan-inspects-crop-damage-gallery/</t>
+          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/will-spare-no-effort-in-providing-assistance-to-farmers-union-minister-shivraj-chouhan-visits-flood-hit-areas-in-jammu/</t>
+          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/india-sets-362-50-mt-foodgrain-goal-at-rabi-abhiyan-2025/</t>
+          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467555-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-begins-in-New-Delhi</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/national-agriculture-conference-shivraj-singh-chouhans-announcement-in-rabi-abhiyan-2025-adulterated-fertilizers-and-seeds-will-be-banned-farmers-interests-are-paramount/</t>
+          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/shivraj-singh-chauhan-called-the-collector-in-front-of-the-farmers-19961271</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/news/harda-shivraj-singh-chouhan-farmers-women-visit-135967899.html</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-shivraj-singh-chouhan-should-pass-on-the-benefits-of-gst-reduction-on-agricultural-equipment-to-farmers-24053412.html</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169829</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-birthday-shivraj-singh-chouhan-narrated-story-of-his-first-meeting-at-lal-chowk-9291324</t>
+          <t>https://rashtriyahindimail.in/posts/111289</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/sehore-union-minister-shivraj-singh-chouhan-orders-crop-survey-in-sehore-after-farmers-plea-9647667.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jammu/j-k-union-minister-shivraj-singh-chauhan-visited-flood-affected-areas-assured-all-possible-help-2025-09-19</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/harda-if-state-government-gives-a-proposal-soybean-will-be-purchased-at-support-price-agriculture-minister-shivraj-singh-chouhan-said-in-harda-8406397</t>
+          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168649</t>
+          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-says-in-raisen-one-nation-one-election-is-in-best-interest-of-country-madhya-pradesh-news-mps25092102747</t>
+          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111289</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-shivraj-singh-chouhan-will-come-to-khirkia-tomorrow-135960835.html</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/sehore/union-agriculture-minister-shivraj-singh-chouhan-directed-the-sehore-collector-to-conduct-a-survey-after-heari-2025-09-20</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-jammu-news-farmers-voice-grievances-to-agriculture-minister-shivraj-singh-chouhan-24053223.html</t>
+          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169829</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/union-agriculture-minister-shivraj-singh-chouhan-in-raisen-tomorrow-135967051.html</t>
+          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167220</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/there-should-be-a-system-for-farmers-to-sell-the-sand-from-their-fields-themselves-135959821.html</t>
+          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
+          <t>https://www.agniban.com/mp-shivraj-singh-chouhan-takes-a-tough-stand-on-farmers-plight-calls-collector-and-issues-a-major-order/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167390</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/union-agriculture-minister-shivraj-singh-chouhan-holds-meeting-on-gst-reforms-for-agricultural-machinery/</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/harda-news/shivraj-singhs-statement-on-the-purchase-of-soybeans-at-the-support-price-in-mp-19962070</t>
+          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/shivraj-singh-chouhan-and-sadhana-visit-pachmarhi-photoshoot-at-high-peak-dhoopgarh-madhya-pradesh-news-mps25091501320</t>
+          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/agriculture-minister-shivraj-singh-explained-the-math-behind-the-new-gst-slabs-19966618</t>
+          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
+          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168432</t>
+          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/india/national/shivraj-singh-chouhan-narrated-story-of-first-meeting-with-pm-narendra-modi-on-his-75th-birthday-2025-09-17-1163196</t>
+          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-pm-modi-remembers-the-workers-even-after-years-shivraj-singh-chauhan-shared-an-old-anecdote-news-hindi-1-752882-KKN.html</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167570</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168538</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/pm-modi-75th-birthday-shivraj-singh-shares-idea-behind-ekta-yatra-ytvd-2335154-2025-09-17</t>
+          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/regional-hindi-news/union-agriculture-minister-shivraj-singh-chauhan-participated-in-cleanliness-programme-in-raisen-125092100031_1.html</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/madhya-pradesh/harda/union-minister-shivraj-singh-assured-farmers-of-satellite-survey-harda-news-c-1-1-noi1224-3428329-2025-09-20</t>
+          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://mpcg.ndtv.in/madhya-pradesh-news/union-agriculture-minister-shivraj-singh-chouhan-call-the-collector-to-immediately-survey-of-damaged-soybean-crop-in-sehore-fasal-bima-9312362</t>
+          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167681</t>
+          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/shivraj-singh-chouhan-met-the-farmers-of-jammu-and-said-modi-government-is-with-you-in-every-difficulty-article-152857128</t>
+          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/business/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-1357112.html</t>
+          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/-110--1189364</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/Shivraj-singh-chauhan-in-rabi-fest.html</t>
+          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/photos/news-bulletin/bhopal-union-minister-shivraj-singh-chouhan-participated-in-the-procession-of-badi-mata-of-karuna-dham-temple-at-platinum-plaza-photo-subhash-thakur-19966300</t>
+          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-will-hold-a-high-level-meeting-regarding-gst-reforms-on-agricultural-machinery/</t>
+          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8-%E0%A4%95%E0%A4%BE/</t>
+          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/jammu-shivraj-singh-chouhan-assures-aid-to-flood-hit-farmers-in-rs-pura-24052755.html</t>
+          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
+          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/2025-26-%E0%A4%95%E0%A5%87-%E0%A4%B2%E0%A4%BF%E0%A4%8F-%E0%A4%96%E0%A4%BE%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%BE%E0%A4%A8%E0%A5%8D%E0%A4%A8-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A4%BE%E0%A4%A6%E0%A4%A8/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
+          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/agriculture-minister-shivraj-singh-chouhan-urges-tractor-makers-to-pass-on-gst-cuts-to-farmers-from-sept-22-233198</t>
+          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/rajasthan/jaipur/news/rajasthan-appreciated-in-national-agriculture-conference-union-agriculture-minister-shivraj-singh-chouhan-rajasthan-agriculture-minister-dr-kirodi-lal-meena-135936751.html</t>
+          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/shivraj-singh-chouhan-holds-discussions-with-agricultural-mechanization-organizations-appeals-to-pass-on-the-benefits-of-reduced-gst-to-farmers/</t>
+          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/shivraj-directs-agri-machinery-industry-dealers-to-ensure-gst-benefits-reach-farmers-holds-meeting-with-representatives.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/union-agriculture-ministry-has-set-production-target-of-362-50-million-tonnes-for-the-year-2025-26-shivraj-singh-chauhan-punjab-flood-9293184</t>
+          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/agriculture-minister-shivraj-singh-chouhan-met-flood-affected-farmers-in-jammu-and-said-we-will-not-let-the-farmers-suffer-and-be-ruined/</t>
+          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/raisen-news/raisen-supports-one-nation-one-election-congress-protest-mp-news-19964957</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/india-news/pm-kisan-yojana-21th-installment-big-update-when-farmer-gets-2000-rupees-in-bank-account-here-latest-details-10481059</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/congress-rahul-gandhi-press-conference-amit-shah-patna-visit-dusu-election-today-us-firing-pakistan-saudi-arab-all-live-updates-9297734</t>
+          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://hindi.economictimes.com/news/gst-rate-cut-impact-on-agricultural-sector-agriculture-minister-shivraj-chauhan-told-what-is-going-to-become-cheaper/articleshow/123998169.cms</t>
+          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-chouhan-visits-raisen-says-gst-reforms-will-make-farming-cheaper-and-profitable/</t>
+          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/union-minister-shivraj-singh-said-a-target-of-362-50-million-tonnes-production-has-been-set-for-the-year-2025-26/</t>
+          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/sehore/news/shivraj-called-the-collector-on-the-complaint-of-the-farmer-135966577.html</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/news/congress-protests-ahead-of-union-ministers-visit-to-raisen-135974897.html</t>
+          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/bhopal/guest-teachers-and-outsource-health-workers-regularization-protest-in-bhopal-angry-on-jyotiraditya-and-shivraj-singh-chouhan/articleshow/123934502.cms</t>
+          <t>https://www.inhnews.in/news/shivraj-singh-narrated-the-story-of-pm-modi-and-laxmi-narayan-gupta</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166948</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/pm-modi-and-several-other-leaders-paid-tribute-to-maharaja-agrasen-on-his-birth-anniversary/</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agricultural-conference-rabi-abhiyan-2025-completed-minister-shivraj-said-kisan-call-center-will-be-effective/</t>
+          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/the-target-of-production-of-more-than-362-million-tonnes-for-the-year-2025-26-set-mr-shivraj-singh/</t>
+          <t>https://khabardigital.com/madhya-pradesh/shivraj-singh-chouhan-congress-comment-icar-bhopal/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/fake-or-sub-standard-fertilizers-seeds-pesticides-will-not-be-allowed-to-be-sold-at-any-price-shivraj-singh-chouhan/</t>
+          <t>https://khabardigital.com/madhya-pradesh/modi75-shivraj-singh-chouhan-first-meeting-narendra-modi-story-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/gst-cut-on-tractors-agricultural-equipment-shivraj-singh-chouhan-farmers-will-pocket-lakhs-of-rupay-1391343.html</t>
+          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/planning-will-be-done-with-the-states-to-increase-the-production-of-pulses-and-oilseeds-2025-09-16</t>
+          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/peoples-representatives-of-raisen-district-passed-a-resolution-in-support-of-one-nation-one-election-shivraj/871639/</t>
+          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/gst-cut-will-make-tractors-cheaper-agriculture-minister-told-companies-to-pass-on-the-benefits-to-farmers-2025-09-19</t>
+          <t>https://www.gaonjunction.com/khabar-junction/pm-modi-birthday-shivraj-singh-chouhan-launches-healthy-women-strong-family-campaign-plants-75-saplings-in-pus</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-will-start-from-today-in-pusa/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-agricultural-growth-rate-increased-by-3-7-in-the-first-quarter-of-2025-26-shivraj-said-this-is-the-result-of-the-hard-work-of-farmers/</t>
+          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/harda/khirkiya/news/union-minister-said-we-will-help-the-farmers-by-conducting-a-survey-135973923.html</t>
+          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/national-rabi-conference-2025-chhattisgarh-agriculture-minister-raised-demand-for-msp-and-procurement-for-millets-and-kulthi/</t>
+          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/blog/narendra-modi-the-peoples-leader-who-challenged-the-political-elite-3262161.html</t>
+          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/helpless-due-to-governments-indifference-13-boards-could-not-take-care-of-their-own-welfare-10483265</t>
+          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-will-become-cheaper-by-thousands-of-rupees-after-the-gst-cut-minister-shivraj-said-this-much-money-will-be-saved-directly-for-the-farmers/</t>
+          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthans-campaign-against-substandard-fertilizers-will-benefit-farmers-says-union-minister-chouhan/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/good-news-for-karnataka-farmers-the-central-government-will-buy-these-five-major-kharif-crops-2025-09-20</t>
+          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-from-today/</t>
+          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/rabi-abhiyan-2025-national-agricultural-conference-launched-with-one-nation-ek-agriculture-ek-team/</t>
+          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/there-will-be-a-reduction-of-7-to-13-percent-in-the-prices-of-agricultural-equipment-union-agriculture-minister-will-hold-an-important-meeting/</t>
+          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/pm-narendra-modi-75th-birthday-celebration-today-on-17-september-live-updates-celeb-politician-wishes/liveblog/123932939.cms</t>
+          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://thesootr.com/state/madhya-pradesh/indore-truck-accident-dcp-arvind-tiwari-abused-jhabua-sp-shivraj-removed-10470429</t>
+          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/raisen/sanchi/news/union-minister-chauhan-inaugurated-namo-vatika-in-sanchi-135979357.html</t>
+          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/shivraj-singh-chouhan-pulses-crop-strategy-toboost-area-prv-1278259-2025-09-16</t>
+          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-will-hold-meeting-regarding-gst-reforms-on-agricultural-machinery-1279511-2025-09-18</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-reality-check-agri-minister-called-700-beneficiaries-and-caught-corruption-swm-1278467-2025-09-16</t>
+          <t>http://www.uniindia.com/photoes/638072.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-government-set-target-for-rabi-season-2025-26-production-shivraj-singh-chouhan-swm-1278488-2025-09-16</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/agriculture-minister-shivraj-singh-chouhan-says-no-compromise-with-farmers-interests-1280554-2025-09-21</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://lalluram.com/raisen-congress-workers-arrested-before-showing-black-flag-to-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/shivraj-singh-chouhan-says-govt-will-provide-all-possible-help-to-the-flood-affected-states-swm-1278520-2025-09-16</t>
+          <t>https://www.livehindustan.com/national/why-did-india-not-give-a-befitting-reply-to-america-on-tariffs-rajnath-singh-told-the-inside-story-201758531882767.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/shivraj-singh-chouhan-says-farm-sector-clocked-world-s-highest-growth-in-quarter-1-swm-1278382-2025-09-16</t>
+          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/india/shivraj-singh-chouhan-in-jammu-flood-affected-farmers-relief-announcement/</t>
+          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/khabar-junction/india-rural-agriculture-news-live-updates-shivraj-singh-chauhan-icar-narendra-modi-bihar-makhana</t>
+          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/shivraj-appeals-tractor-and-agri-machinery-makers-to-benefit-farmers-with-gst-rate-cut-1279937-2025-09-19</t>
+          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/delhi/any-shortage-food-grains-fruits-vegetables-country-make-india-food-basket-world-shivraj-singh/</t>
+          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/live/kheti-kisani/agriculture-and-rural-india-news-live-updates-shivraj-singh-chouhan-narendra-modi-farming-farmers-rural-yogi-adityanath-live-news-updates</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/national-rabi-agriculture-conference-2025-shivraj-singh-chouhan-1278609-2025-09-16</t>
+          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/union-agriculture-minister-shivraj-singh-chouhan-met-farmers-in-sehore-issued-immediate-instructions-collector</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://hindi.latestly.com/india/110-road-works-approved-in-udhampur-jitendra-singh-expresses-gratitude-to-union-minister-shivraj-singh-chouhan-2759210.html</t>
+          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/nku-leader-rakesh-tikait-raised-many-question-on-genome-edited-rice-written-letter-shivraj-singh-chouhan-nvs-1278250-2025-09-16</t>
+          <t>https://sundayguardianlive.com/news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654-140171/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://samacharnama.com/gadgetsandtech/hindi-we-will-make-india-food-basket-of-the-world-minister/cid17422327.htm</t>
+          <t>https://www.thehansindia.com/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-state-pralhad-joshi-1008474</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=union-minister-shivraj-shared-modi-story-page-and-told-a-wonderful-story-576739</t>
+          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/agri-minister-shivraj-announces-compensation-for-crop-and-livestock-loss-in-jammu-kashmir-1279968-2025-09-19</t>
+          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/centre-to-compensate-farmers-for-crop-losses-says-agri-minister-we-wont-let-their-lives-be-destroyed-by-disaster</t>
+          <t>https://www.freepressjournal.in/business/agriculture-minister-urges-tractor-makers-to-pass-gst-benefits-to-farmers-promises-price-cut-of-63000-from-september-22</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/beneficiaries-on-list-700-but-150-could-not-be-contacted-158-did-not-receive-subsidy-reveals-shivraj</t>
+          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rabi-conference-250-lakh-metric-tonnes-of-seeds-ready-for-rabi-season-agriculture-minister-sets-target-of-re</t>
+          <t>https://www.easternmirrornagaland.com/salhoutuonuo-kruse-seeks-centre-of-excellence-for-horticulture-in-nagaland</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/politics/story/pm-modi-at-75-agriculture-minister-shivraj-singh-chouhan-recalls-his-first-meeting-with-prime-minister-narendra-modi-1278717-2025-09-17</t>
+          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/launch-of-national-agriculture-conference-rabi-abhiyan-2025-two-day-brainstorming-begins-on-strategy-of-rabi-c</t>
+          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/farming-techniques/story/gst-reforms-to-make-farming-cheaper-and-profitable-prv-1280733-2025-09-21</t>
+          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/sarkari-yojana/story/pm-kisan-border-farmers-benefit-gst-cut-machinery-1280000-2025-09-19</t>
+          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://royalbulletin.in/business/gst-cut-tractor-price-reduction-benefit-farmers-india/article-107718</t>
+          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
+          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/atithi-shikshak-protest.html</t>
+          <t>https://www.technologyforyou.org/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/indias-agriculture-growth-at-3-7-highest-in-the-world-union-minister-shivraj-singh-chouhan/</t>
+          <t>https://ddnews.gov.in/one-nation-one-agriculture-one-team-national-agriculture-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/shivraj-singh-chouhan-plants-75-saplings-mark-pm-modis-birthday-453522</t>
+          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448</t>
+          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
+          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/agriculture-minister-shivraj-singh-chouhan-greets-prime-minister-narendra-modi-on-his-75th-birthday/</t>
+          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-held-in-delhi-under-the-chairmanship-of-union-agriculture-minister-shri-shivraj-singh-chouhan/</t>
+          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/09/this-is-bachat-utsav-shivraj-singh-chouhan-on-new-gst-rates-implementation/</t>
+          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/rajasthan/jodhpur-news/news-an-at-home-ceremony-was-held-to-mark-the-50th-birthday-of-shivraj-singh-chouhan-a-member-of-the-former-royal-family-news-hindi-1-753688-KKN.html</t>
+          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/guna-news/guna-nagar-nigam-status-delayed-shivraj-singh-chouhan-mp-news-19951215</t>
+          <t>https://hindi.ianslive.in/seva-pakhwada-pradhanmantri-modi-ke-75ven-janmdin-par-bjp-shasit-raajyon-mein-alag-alag-karyakramon-ka-aayojan--20250917113201</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://divyakirti.com/archives/5675</t>
+          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/jitu-patwari-accused-bjp-ministers-of-destabilizing-cm-mohan-yadav-19962245</t>
+          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.tractorjunction.com/tractor-news/gst-relief-will-reduce-tractor-prices-by-rs-23000-to-rs-63000/</t>
+          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/agriculture/agriculture-rural-news/story/gst-cut-tractor-harvester-farming-machines-cheap-shivraj-singh-lbs-dskc-2337363-2025-09-22</t>
+          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/after-vijayvargiya-meeting-with-home-minister-amit-shah-bjp-held-high-level-meeting-at-cm-house-madhya-pradesh-news-mps25092003187</t>
+          <t>https://mediawala.in/governance-hemant-will-be-able-to-form-his-team-on-the-decided-formula/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/punjab-floods-damage-5-lakh-acres-of-crops-demands-rs-151-crore-from-centre/</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/indias-food-grain-production-target-for-2025-26-is-362-5-million-tonnes-seed-availability-is-surplus/</t>
+          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
+          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/business/india-to-see-no-food-grain-fruit-or-vegetable-shortage-will-transform-into-a-global-food-basket-says-union-agriculture-minister-shivraj-chouhan</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-imd-weather-forecast-himachal-pradesh-weather-news-in-hindi-punjab-flood-latest-news-1277703-2025-09-15</t>
+          <t>https://www.knskashmir.com/jandk-flood-victims-to-get-comprehensive-package--lop-sunil-sharma-198290</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-clouds-prevail-in-delhi-ncr-heavy-rain-alert-in-up-bihar-1279668-2025-09-19</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467662-National-Agriculture-Conference-%E2%80%93-Rabi-Abhiyan-2025-held-in-Delhi-under-the-chairmanship-of-Shivra</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/govt-sets-rabis-crops-production-target-at-362-50-million-tonnes-shivraj-singh-chauhan/</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/sampla/news/bjps-state-level-team-formed-steffi-chauhan-appointed-as-member-135946135.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/national-agriculture-conference-rabi-campaign-2025-under-leadership-of-union-agriculture-minister-shivraj-singh-chouhan/</t>
+          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/aaj-ki-taaja-khabar-mukhya-samachar-hindi-news-today-17-18-september-live-updates-pm-narendra-modi-75th-birthday-bihar-election-bjp-amit-shah-rahul-gandhi-supreme-court/4145200/</t>
+          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/good-news-for-karnataka-farmers-the-central-government-will-buy-these-5-major-crops-at-msp/</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-amit-chauhan-raj-singh-lakhnamajra-bjp-fraud-haryana-135931816.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/centre-to-procure-green-gram-black-gram-sunflower-from-karnataka-pralhad-joshi-3737381</t>
+          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/19/over-5000-rural-houses-in-jk-to-get-pmay-support-minister/</t>
+          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/after-all-time-high-last-year-govt-aims-at-119-mn-tonnes-wheat-output-for-2025-26-10254259/</t>
+          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/centre-plans-state-specific-agriculture-roadmap-to-boost-crop-produce-enn25091703148</t>
+          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/navratri-gift-ktaka-farmers-centre-approves-procurement-5-crops-msp-454772</t>
+          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/karnataka/surjewala-urges-centre-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers-1007275</t>
+          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bulletins-detail/midday-news-545/</t>
+          <t>https://theindianawaaz.com/indias-agriculture-growth-at-3-7-highest-in-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/from-illegal-tagging-to-biostimulant-crackdown-first-viksit-krishi-sankalp-abhiyan-made-its-mark-across-india-second-phase-to-begin-october-3/</t>
+          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/globe-nation/punjab-police-clears-farmer-protest-sites-at-shambhu-and-khanauri-borders-arrests-leaders/14647/</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/defence-minister-rajnath-singh-shares-my-modi-story-on-pms-75th-birthday-praises-his-discipline-profound-knowledge20250917101654</t>
+          <t>https://rashtriyahindimail.in/posts/111216</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://blog.saginfotech.com/union-agriculture-minister-chair-meeting-gst-cut-farm-equipment</t>
+          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/front-page-2/centre-stands-with-jk-flood-victims-union-agriculture-minister/</t>
+          <t>https://khabardigital.com/madhya-pradesh/rahli-advocate-association-election-ramanand-patel-new-president/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
+          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/110-new-road-projects-sanctioned-in-udhampur-kathua-doda-under-pmgsy-4/</t>
+          <t>https://m.mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000?amp</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://kashmirlife.net/jammu-kashmir-centre-approves-110-road-projects-worth-rs-2000-crore-406293/</t>
+          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/coordination-meeting-held-at-mp-cm-mohan-yadav-house-lays-stress-on-joint-decisions</t>
+          <t>https://www.thehansindia.com/news/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal-1006573</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/udhampur-constituency-to-receive-highest-pmgsy-funds-under-phase-4/</t>
+          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2025/09/15/union-agri-minister-inaugurates-national-agriculture-conference-rabi-abhiyan-2025/</t>
+          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.bizzbuzz.news/industry/agriculture/viksit-krishi-sankalp-abhiyan-to-guide-prod-strategies-for-rabi-season-1371950</t>
+          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.news9live.com/business/biz-news/farm-sector-clocked-worlds-highest-growth-at-3-7-pc-in-q1-agri-min-shivraj-chouhan-2888973</t>
+          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-mps-at-parliament-during-monsoon-session-1186493</t>
+          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/with-the-blessings-of-the-prime-minister-the-central-and-jammu-and-kashmir-governments-will-rescue-the-farmers-from-the-flood-disaster-chauhan/870854/</t>
+          <t>https://www.wionews.com/business-economy/goods-and-services-tax-reforms-how-cheaper-will-tractors-get-minister-reveals-1758282747902</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/congress-allegation-on-the-central-govt-said-fertilizer-was-not-given-to-karnataka-as-per-demand-2025-09-17</t>
+          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-india-targets-36-million-tonnes-of-foodgrain-production-by-202526-24049540.html</t>
+          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://hindi.ianslive.in/maharaja-agrasen-jayanti-par-pradhanmantri-modi-samet-kai-netaon-ne-di-shraddhanjali--20250922133554</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/food-beverages/india-aims-for-3625-mt-foodgrain-production-target-by-2025-26/124037685</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/mp-lathi-charge-over-fertilizer-in-agriculture-ministers-home-district-3-farmers-injured/</t>
+          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation-11758032543012.html</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://hindi.business-standard.com/companies/industrial/pm-kisan-scheme-border-farmers-to-get-benefits-soon-after-state-certification-id-473218</t>
+          <t>https://indiaeducationdiary.in/national-agriculture-conference-rabi-abhiyan-2025-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/punjab-seeks-rs151-crore-aid-from-centre-for-flood-hit-farmland-restoration</t>
+          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/jammu-kashmir/the-central-government-announced-a-relief-package-for-the-flood-victims-of-jammu-and-kashmir/</t>
+          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.niharikatimes.com/central-government-agriculture-target-2025/</t>
+          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/rabi-abhiyan-2025-started-in-pusa-delhi-for-action-plan-on-rabi-crop-1278006-2025-09-15</t>
+          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://indianlooknews.com/?p=56810</t>
+          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/pm-modi-extends-greetings-on-maharaja-agrasen-jayanti-570286</t>
+          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/del35-pm-bday-leaders.html</t>
+          <t>https://hindi.theprint.in/india/economy/agriculture-minister-to-hold-meeting-with-farm-equipment-industry-tomorrow-on-gst-implementation/870347/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.knskashmir.com/jandk-flood-victims-to-get-comprehensive-package--lop-sunil-sharma-198290</t>
+          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/arrest-warrant-issued-against-bhojpur-mla-surendra-patwa-court-directs-bjp-leader-to-appear-after-repeated-absences-in-cheque-bounce-cases-135883039.html</t>
+          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/bjp-leader-accused-of-molesting-woman-constable-in-barwani-congress-mla-warns-protest-if-arrest-delayed-135958730.html</t>
+          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/aaj-subah/video/pm-modi-birthday-celebration-seva-pakhwada-blood-donation-drive-frvd-2335186-2025-09-17</t>
+          <t>https://hindi.news18.com/news/business/latest-how-much-money-save-on-tractor-price-after-gst-new-rate-impose-from-22-september-ws-kl-9641214.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/bjp-presidents-name-will-compete-in-four-veteran-ministers-as-soon-as-bhagwat-modi-is-united/146626</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/country/bjps-next-president-name-this-veteran-leader-is-leading-the-race-for-the-bjps-next-national-president-3259814.html</t>
+          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-why-rss-insisting-on-appointing-brahmin-party-president-balance-these-three-equations-1389609.html</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bjp-mla-rajeev-singh-parichha-and-mla-ravi-sharma-came-face-to-face-over-inspector-in-jhansi-uttar-pradesh-news-ups25091500787</t>
+          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/sub-inspector-sunil-kumar-rai-slaps-bjp-worker-in-mirzapur-ssp-suspended-departmental-inquiry-started-uttar-pradesh-news-ups25092003608</t>
+          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/why-mp-holds-special-place-for-pm-modi-birthday-celebrations-and-frequent-visits-explained-2025-09-17</t>
+          <t>https://vocaltv.in/national/n-a-conference-in-pusa-today-and-tomorrowphp/cid17416096.htm</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/bjp-president-election-two-tough-conditions-from-sangh-delayed-know-what-qualities-rss-prioritized-1387709.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168477</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-bjp-divisional-president-amit-chauhan-blame-naveen-dhul-haryana-135939831.html</t>
+          <t>https://cnin.co.in/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A4%BE%E0%A4%AE-%E0%A4%A8%E0%A4%88-%E0%A4%A6%E0%A4%BF%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%BF%E0%A4%A4.../70480</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/voluntary-conversion-is-not-a-crime-digvijay-singh-2214000</t>
+          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/gurugram/news/political-upheaval-7-rebel-councillors-return-bjp-gurugram-135982046.html</t>
+          <t>https://media24news.in/?p=90190</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bjp-president-who-are-frontrunners-for-next-bjp-national-chief-new-party-president-announce-update-1333133.html</t>
+          <t>https://www.kisantak.in/news/trending/story/national-agriculture-conference-organized-in-delhi-rabi-season-campaign-discussed-1277591-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/business/new-gst-rates-2025-leaders-reactions-gst-reform-india</t>
+          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/india/who-will-be-next-bjp-president-2025-delay-rss-relations-minister-nitin-gadkari-statement-1388863.html</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/india-may-impose-import-duties-on-pulses-to-protect-farmers-from-falling-prices</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.bhadas4media.com/vijay-rupani-antim-sanskar-bjp-expenses/</t>
+          <t>https://www.global-agriculture.com/india-region/production-target-of-362-50-million-tonnes-set-for-2025-26-mr-shivraj-singh/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/india/aaj-ki-taaja-khabar-17-september-2025-live-updates-today-latest-and-breaking-news-hindi-1357840.html</t>
+          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/surjewala-urges-union-government-to-quickly-release-pending-336-lakh-mt-urea-to-karnataka-farmers</t>
+          <t>https://krishijagran.com/news/govt-signs-mous-with-4-states-nirdpr-to-boost-rural-livelihoods-digital-innovations-under-day-nrlm/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
+          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
+          <t>https://www.divyahimachal.com/2025/09/the-central-government-will-run-kisan-train-from-kalka-the-agriculture-minister-raised-the-issue-in-the-national-conference-on-agriculture-rabi-campaign/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/india-will-soon-become-the-food-basket-of-the-world-union-agriculture-minister-shivraj-singh-chauhan/</t>
+          <t>https://ndtv.in/jammu-kashmir-news/jammu-flood-affected-farmers-these-announcements-to-provide-compensation-9311326</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
+          <t>https://www.yugwarta.com/Encyc/2025/9/15/Bhartiya-mazdoor-sangh-demands-national-labour-day.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/up-politics/photo-gallery-raja-bhaiya-sons-shivraj-or-brijraj-pratap-singh-profile-education-political-career-why-opposing-mother-bhanvi/2932290</t>
+          <t>https://www.bhaskar.com/local/mp/raisen/news/there-will-be-6-main-and-3-recreational-games-in-mp-sports-festival-registration-starts-today-135939182.html</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://rashtriyahindimail.in/posts/111216</t>
+          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.agniban.com/this-is-politics-my-love-37/</t>
+          <t>https://dainiknavajyoti.com/leads/the-central-governments-big-target-2025-26-started-the-agricultural-resolution/article-127055</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://firstindia.co.in/articles/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
+          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/google-trends/16092025/ladli-behna-yojana/</t>
+          <t>https://www.aajsamaaj.com/58-state-of-the-art-libraries-to-open-soon-in-punjab-sond/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/scindia-s-statement-regarding-the-roads-of-mp-2213041</t>
+          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.wionews.com/business-economy/goods-and-services-tax-reforms-how-cheaper-will-tractors-get-minister-reveals-1758282747902</t>
+          <t>https://www.jammulinksnews.com/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.thefinancialworld.com/centre-plans-strict-law-against-fake-fertilisers-pesticides-to-protect-farmers/</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2169327</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/how-to-effectively-pass-on-gst-benefits-to-farmers-agriculture-minister-to-deliberate-today/articleshow/123987171.cms</t>
+          <t>https://www.thehansindia.com/telangana/brs-leader-condemns-inhumane-treatment-of-muslims-demanding-graveyard-1006465</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal/</t>
+          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/centre-directs-farm-machinery-makers-to-cut-prices-after-gst-rate-reduction/article70070805.ece</t>
+          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.caclubindia.com/news/gst-cut-on-tractors-and-agricultural-equipment-govt-to-ensure-farmers-get-full-benefit-25486.asp</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/centre-sets-foodgrain-output-target-362-96-mt-2025-26-125091601264_1.html</t>
+          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/punjab-seeks-%E2%82%B9151-crore-central-assistance-after-floods-damage-5-lakh-acres-of-crops/</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-uttarakhand-government-schemes-review-cm-dhami-focuses-on-swift-implementation-24052708.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/india/news-ensure-gst-benefits-reach-farmers-agriculture-minister-tells-farm-equipment-tractor-makers-379191</t>
+          <t>https://timetv.news/national/2025/09/22/registration-of-cashless-treatment-up-to-rs-10-lakh-under-chief-ministers-health-scheme-will-start-from-september-23-cm-mann/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/economy/agri-minister-urges-tractor-makers-to-pass-on-gst-cut-to-farmers/56895</t>
+          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/news/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi-with-key-policy-resolutions/</t>
+          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/economy/foodgrain-production-crop-farming-sowing-agriculture-shivraj-singh-chouhan-monsoon-kharif-rabi-inflation-11758032543012.html</t>
+          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://ianslive.in/agricultural-machinery-and-tractors-to-become-cheaper-in-major-relief-for-farmers-minister--20250919175149</t>
+          <t>https://www.tv9hindi.com/state/haryana/haryana-lado-laxmi-yojana-launched-women-will-get-2100-rupees-per-month-from-25-september-3492755.html</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/national-conference-on-agriculture-rabi-campaign-2025-concludes-in-new-delhi/</t>
+          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/national/ghaziabad-farmer-neelam-tyagi-honoured-with-dr-norman-e-borlaug-innovative-farmer-award-2025.html</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.drishtiias.com/state-pcs-current-affairs/national-agriculture-conference-rabi-abhiyan-2025</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/two-day-national-agriculture-conference-rabi-abhiyan-2025-to-begin-in-new-delhi-tomorrow/</t>
+          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://arunachaltimes.in/index.php/2025/09/17/wangsu-for-state-specific-policy-interventions-for-himalayan-states/</t>
+          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.global-agriculture.com/india-region/india-sets-2025-26-foodgrain-production-target-at-362-5-million-tonnes-confirms-surplus-seed-availability/</t>
+          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://timelinedaily.com/india/2-day-national-agriculture-conference-kicks-off-in-delhi-tomorrow-fruitful-insights-expected</t>
+          <t>https://22scope.com/bihar-women-said-thanks-thanks-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://himachalheadlines.com/news/agriculture-minister-participates-in-national-conference-on-kharif-rabi-campaign/</t>
+          <t>https://hindikhabar.com/haryana-storage-capacity-increase-central-government-approval/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-agriculture-conference-for-rabi-campaign-2025-theme-one-nation-one-agriculture-one-team/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://kisansamadhan.com/from-september-22-farmers-will-get-tractors-harvesters-and-other-agricultural-equipment-at-such-cheap-rates/</t>
+          <t>https://a2ztaxcorp.net/agriculture-minister-shivraj-singh-chouhan-to-convene-key-meeting-on-gst-reforms-in-agricultural-machinery-with-tractor-and-farm-mechanisation-stakeholders-to-ensure-farmers-fully-benefit-from-gst-rat/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/rajasthan-will-become-indias-organic-hub-farmers-will-get-new-market-year-minister-dr-kirori-lal/</t>
+          <t>https://starsamachar.com/sidhi-sp-shailendra-singh-crime-control-police-action</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/15/N-A-Conference-in-Pusa-today-and-tomorrow.html</t>
+          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/national/two-day-national-agriculture-conference-on-rabi-abhiyan-begins-in-new-delhi.html</t>
+          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%A6%E0%A4%B0%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9%E0%A5%8B%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2</t>
+          <t>https://www.jagran.com/haryana/null-haryana-government-orders-police-officers-to-meet-people-for-one-hour-each-morning-and-evening-to-resolve-complaints-24052783.html</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/business/pm-kisan-gov-in-beneficiarystatus-new-farmer-registration-form-pm-kisan-ki-agali-kist-kab-aaegi-1390421.html</t>
+          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.zeebiz.com/hindi/economy/agriculture/pm-kisan-21st-installment-farmers-now-benefit-from-the-pm-kisan-scheme-even-if-they-do-not-have-land-documents-233431</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/lucknow/up-bjp-and-rss-meeting-before-panchayat-chunav-and-assembly-poll-3-leaders-gets-responsibility-news/articleshow/123899002.cms</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/tractors-cheaper-due-to-gst-cut-double-benefit-to-farmers-important-ministry-meeting-to-be-held-tomorrow/</t>
+          <t>https://www.bhaskar.com/local/bihar/kishanganj/kochadhaman/news/jeevikas-annual-general-meeting-held-at-altahat-kochadhaman-135950707.html</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/punjab/chandigarh-punjab/relief-to-punjab-central-government-released-second-installment-of-sdrf-in-advance-rs-240-crore-2025-09-17</t>
+          <t>https://www.abplive.com/states/haryana/haryana-cm-nayab-singh-saini-on-navratri-subsidy-to-farmers-paddy-procurement-adoption-of-swadeshi-3016726</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-gst-rate-reduction</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-gst-new-rates-uttarakhand-cm-launches-awareness-campaign-for-public-benefit-24055038.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/rabi-production-%E0%A4%B0%E0%A4%AC-%E0%A4%B8-%E0%A4%9C%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-171-%E0%A4%AE-%E0%A4%B2-%E0%A4%AF%E0%A4%A8-%E0%A4%9F%E0%A4%A8-%E0%A4%85%E0%A4%A8-%E0%A4%9C-%E0%A4%89%E0%A4%A4%E0%A5%8D%E0%A4%AA-%E0%A4%A6%E0%A4%A8-%E0%A4%95-%E0%A4%B2%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%96-%E0%A4%A6-%E0%A4%95-%E0%A4%89%E0%A4%AA%E0%A4%B2%E0%A4%AC%E0%A5%8D%E0%A4%A7%E0%A4%A4-%E0%A4%AC%E0%A4%A8-%E0%A4%AC%E0%A4%A1%E0%A4%BC-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%A4/ar-AA1MHKaX?ocid=finance-verthp-feeds</t>
+          <t>https://www.bhaskar.com/local/jharkhand/bokaro/news/pandal-on-the-lines-of-ashta-kastabhanjan-in-bokaro-135942281.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/national/n-a-conference-in-pusa-today-and-tomorrowphp/cid17416096.htm</t>
+          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90190</t>
+          <t>https://www.bhaskar.com/local/bihar/rohtas/nokha/news/jan-suraj-partys-public-relations-campaign-in-nokha-135969085.html</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://hindicurrentaffairs.adda247.com/rabi-abhiyan-2025-conference-begins-in-new-delhi/</t>
+          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-21-september-2025-in-hindi-todays-top-news</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/even-if-farmers-do-not-have-land-documents-they-will-now-get-the-benefit-of-pm-kisan-yojana/</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/reconstruction-of-disaster-affected-areas-is-top-priority/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/chhattisgarh/minister-ramvichar-netam-participated-in-the-national-rabi-conference-organized-in-new-delhi/</t>
+          <t>https://www.amarujala.com/dehradun/new-gst-rates-will-be-implemented-in-from-today-cm-dhami-said-state-economy-will-be-strengthened-uttarakhand-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://sehorehulchal.com/news/oh-god-farmers-are-worried-about-their-crops-no-solution-is-being-found/</t>
+          <t>https://www.jagran.com/bihar/khagaria-nitish-kumars-khagaria-visit-statue-unveiling-and-development-projects-24051481.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/food-grain-production-expected-to-increase-by-24-percent-despite-floods-and-disasters-1278860-2025-09-17</t>
+          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://nayanjagriti.com/krishi-mantralaya-2025-26-khadya-utpadan-lakshya/18357/</t>
+          <t>https://www.prabhatkhabar.com/state/bihar/khagaria/preparations-in-full-swing-in-pansalwa</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/india-may-impose-import-duties-on-pulses-to-protect-farmers-from-falling-prices</t>
+          <t>https://hindi.moneycontrol.com/jobs/sarkari-naukri-government-jobs-in-himachal-recruitment-in-electricity-revenue-health-and-panchayati-raj-departments-article-2162823.html</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/latest-news/centre-approves-110-pmgsy-road-projects-worth-rs-2000-cr-in-udhampur/</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-holds-review-meeting-with-public-representatives-on-new-gst-rates-and-swadeshi-campaign-expresses-gratitude-to-pm-modi-and-finance-minister/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/hi/%E0%A4%89%E0%A4%A7%E0%A4%AE%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%95%E0%A4%A0%E0%A5%81%E0%A4%86-%E0%A4%A1%E0%A5%8B%E0%A4%A1%E0%A4%BE-%E0%A4%AE%E0%A5%87%E0%A4%82-110-%E0%A4%A8%E0%A4%88-%E0%A4%B8%E0%A4%A1/</t>
+          <t>https://acn18.com/%E0%A4%B8%E0%A4%9A%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%BE%E0%A4%AF%E0%A4%B2%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan-1006836</t>
+          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/state/ap-govt-offers-rs-800-incentive-per-bag-to-farmers-who-cut-urea-use.html</t>
+          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/india-world-breaking-news-h1b-visa-zubeen-garg-pm-modi-trump-putin-weather-update-gaza-palestine-russia-ukraine/liveblog/124023294.cms</t>
+          <t>https://newsarenaindia.com/nation/rajnath-shares-my-modi-story-praises-discipline-knowledge/56623</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india-plans-rs-2-billion-fund-to-boost-infrastructure-finance/78815</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/pawan-singh-will-be-active-in-bihar-elections-2025-135981717.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://statetimes.in/cbi-chargesheets-anil-ambani-rana-kapoor-in-rs-2796-crore-corruption-case/</t>
+          <t>https://www.amarujala.com/india-news/bihar-politics-will-the-combination-of-rahul-and-tejashwi-be-a-hit-how-strongly-will-nitish-kumar-fight-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/gst-rationalisation-solar-pumps-farmers-cost-cut-pralhad-joshi-125091900897_1.html</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/instructions-to-remove-ai-video-of-pms-mother-135941376.html</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/hisar-haryana-government-is-preparing-to-make-lado-laxmi-yojana-a-festival-cm-will-launch-the-app-on-the-third-navratri-24056323.html</t>
+          <t>https://www.bhaskar.com/local/haryana/jind/news/devendra-atri-vs-brijendra-singh-high-court-petition-uchana-vote-recounting-case-135957437.html</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-government-giving-5000-rupees-extra-to-pm-vishwakarma-yojana-beneficiaries/articleshow/123963914.cms</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/vidisha/stone-pelting-news-on-maa-kali-tableau-in-muslim-locality-committee-resolved-matter-amicably/articleshow/124053496.cms</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/haryana/haryana-lado-laxmi-yojana-launched-women-will-get-2100-rupees-per-month-from-25-september-3492755.html</t>
+          <t>https://www.krishakjagat.org/news/animal-husbandry-farmers-benefited-from-the-chief-ministers-dairy-plus-scheme/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/punjab-and-haryana/chandigarh/registration-for-cashless-treatment-rs-10-lakh-under-chief-minister-health-scheme-will-start-from-september-23-bhagwant-mann-announces/articleshow/124050803.cms</t>
+          <t>https://www.kisantak.in/knowledge/story/know-all-about-chili-variety-kashi-anmol-which-gives-higher-yield-to-farmers-1278361-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-uttarakhand-government-schemes-review-cm-dhami-focuses-on-swift-implementation-24052708.html</t>
+          <t>https://ianslive.in/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal--20250915134402</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/government-schemes/haryana/haryana-2100-rupees-scheme-lado-laxmi-yojana-latest-update-news-proposal-sent-to-cm-nayab-singh-saini/articleshow/122820720.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/17/chief-minister-nayab-singh-saini-launches-mukhyamantri-vishwakarma-samman-yojana/</t>
+          <t>https://www.freepressjournal.in/bhopal/uttar-pradesh-man-who-walks-3600-km-to-promote-organic-food-fight-junk-diet-reaches-bhopal</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/career/news/union-cabinet-approves-bio-ride-scheme-atishi-will-take-oath-as-chief-minister-on-september-21-133669316.html</t>
+          <t>https://www.freepressjournal.in/bhopal/bhopal-gandhi-medical-college-students-raise-concern-over-language-mismatch-in-internal-exams</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/madhya-pradesh/congress-leader-accuses-bjp-of-misusing-cm-teerth-darshan-yojana-includes-family-members-3483525.html</t>
+          <t>https://www.freepressjournal.in/bhopal/bhopal-animal-birth-control-centre-accused-of-keeping-dogs-captive-for-over-a-month</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bihar-rajya-kinnar-kalyan-board-member-rajan-singh-said-transgender-can-become-cm-of-bihar-bihar-news-brs25091802012</t>
+          <t>https://mp.punjabkesari.in/national/news/farmers-protest-with-bowls-on-pm-modi-s-birthday-2214166</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://awaaz24x7india.com/news/haryana-chief-minister-nayab-singh-saini-gave-the-message-of-sabka-saath-sabka-vikas-on-maharaja-agrasen-jayanti-in-panchkula</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/guest-teachers-want-regularization-as-guru-dakshina-135933602.html</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://thetruefact.com/rbi-governor-sanjay-malhotra-offered-courtesy-to-big-breaking-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/awareness-campaign-of-chief-minister-women-employment-scheme-started-135925182.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://nayaharyana.com/latest-update/haryana-news-haryana-government-has-started-a-new/cid17425099.htm</t>
+          <t>https://www.bhaskar.com/local/mp/bhopal/news/organizations-protested-saying-the-government-used-societies-135963056.html</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-pm-modi-address-nation-new-gst-rates-live-updates-gst-slabs-reduction-tax-nirmala-sitharaman-taxation-reforms-date-22-september-2025-3984613/</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://argusenglish.in/national/pm-modi-to-inaugurate-purnea-airport-launch-rs-45000-crore-projects-in-bihar-on-sep-15</t>
+          <t>https://hindi.oneindia.com/news/bhopal/bjp-mp-alok-sharma-sharp-statement-ban-on-non-veg-shops-is-right-1390405.html</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/maharashtra-indian-railways-renames-ahmednagar-railway-station-as-ahilyanagar/</t>
+          <t>https://hindi.oneindia.com/news/bhopal/demonstration-of-mp-guest-teachers-gathered-in-bhopal-ambedkar-park-demand-for-regularization-1386979.html</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://starsamachar.com/sidhi-sp-shailendra-singh-crime-control-police-action</t>
+          <t>https://www.krishakjagat.org/news/onions-sold-at-just-rs-50-quintal-in-this-madhya-pradesh-market-know-todays-latest-rates/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/darbhanga/news/darbhanga-cricket-associations-annual-general-meeting-was-held-new-district-committee-was-elected-135989912.html</t>
+          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/uttarakhand-chief-minister-pushkar-singh-dhami-held-a-virtual-dialogue-with-the-public-at-the-tehsil-levelsaying-that-rebuilding-the-disaster-affected-areas-is-the-top-priority-of-the-state-government/</t>
+          <t>https://www.freepressjournal.in/bhopal/watch-behno-chappal-taiyar-rakhna-mp-cm-mohan-yadav-advices-ladli-behna-slams-congress-over-liquor-remark-in-ashoknagar</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-cm-dhami-directs-strict-action-against-land-encroachment-and-disaster-management-initiatives-201758024113510.html</t>
+          <t>https://www.bhopalsamachar.com/2025/09/bhopal-rss.html</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-gst-new-rates-uttarakhand-cm-launches-awareness-campaign-for-public-benefit-24055038.html</t>
+          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/chandigarh/celebrating-maharaja-agrasen-jayanti-at-government-level-is-a-historic-decision-vipul-goyal/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/prime-minister-narendra-modi-at-75-years-time-line-of-major-events-in-modi-life-hindi-news-hin25091604966</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/16/the-chief-minister-held-a-meeting-with-the-union-food-and-supplies-minister-regarding-the-welfare-of-farmers-and-discussed-various-issues/</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/kabirdham/news/dharna-in-kawardha-against-fir-against-journalist-135970021.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/rohtas/nokha/news/jan-suraj-partys-public-relations-campaign-in-nokha-135969085.html</t>
+          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/indore/bureaucracy-is-dominating-in-mp-why-is-the-conflict-between-officers-and-mlas-and-ministers-increasing-2025-09-15</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ashoknagar/congress-mla-gopal-singh-chauhan-secretly-met-with-the-cm-mohan-yadav-in-ashok-nagar-sparking-speculation-about-his-entry-into-the-bjp-/articleshow/124019641.cms</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/government-jobs-in-himachal-2600-posts-to-be-filled-in-himachal-electricity-board-himachal-pradesh-news-hps25092103062</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/jharkhand/bokaro/news/pandal-on-the-lines-of-ashta-kastabhanjan-in-bokaro-135942281.html</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/charkhi-dadri/news/charkhi-dadri-mla-sunil-satpal-sangwan-monsoon-session-assembly-dadri-rohtak-road-tender-construction-issue-public-works-department-minister-ranbir-gangwa-135735700.html</t>
+          <t>https://www.indiatv.in/bihar/tejashwi-will-be-cm-face-no-second-option-congress-mp-big-statement-for-bihar-election-2025-09-20-1163974</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189812</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://bolchhattisgarh.in/divisional-level-nuakhai-milan-ceremony-of-dhurwa-samaj-in-jagdalpur-and-the-inauguration-program-of-newly-constructed-social-building-olerse/</t>
+          <t>https://mbmnewsnetwork.com/himachal-pradesh/854552/%E0%A4%B0%E0%A4%BF%E0%A4%9C-%E0%A4%AA%E0%A4%B0-13-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%95%E0%A5%8B-%E0%A4%B9%E0%A5%8B%E0%A4%97%E0%A4%BE-%E0%A4%B5%E0%A5%80%E0%A4%B0</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/uttarakhand-chief-minister-pushkar-singh-dhami-conducted-a-field-inspection-of-heavy-rainfall/</t>
+          <t>https://www.prabhatkhabar.com/state/bihar/khagaria/on-25th-the-c-m-will-address-a-meeting-in-pansalwa</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://janpakshaajkal.com/rbi-governor-sanjay-malhotra-reacted-courtesy-in-rural-areas-of-chief-minister-pushkar-singh-dhami/</t>
+          <t>https://navbharatlive.com/maharashtra/garchiroli/gadchiroli-samruddha-panchayat-abhiyan-launch-1360071.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://thenewswave.com/chhattisgarh-chief-minister-inaugurated-the-newly-constructed-social-building-of-mahara-community/</t>
+          <t>https://www.etvbharat.com/hi/!state/rewa-pandit-srinivas-tiwari-100th-birth-anniversary-statue-unveiling-congress-convention-madhya-pradesh-news-mps25091800671</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/business/2025/09/19/dcm13-biz-chouhan-gst.html</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://eng.ruralvoice.in/cooperatives/kribhco-elects-v-sudhakar-chowdary-chairman-chandrapal-singh-yadav-vice-chairman.html</t>
+          <t>https://humarabikaner.com/india/pm-modi-birthday-prime-ministers-75th-birthday-today/cid17427895.htm</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/new-delhi-one-nation-one-election-entrepreneurs-traders-programme-1187394</t>
+          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/raisen-became-the-first-district-in-the-country-to-support-one-nation-one-election-135980706.html</t>
+          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/alirajpur-district-renamed-aalirajpur-in-hindi-official-notification-issued-lcln-strc-2334595-2025-09-16</t>
+          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/petition-challenging-the-election-of-bhopal-zilla-panchayat-president-dismissed-135961416.html</t>
+          <t>https://www.gyanwani.com/33520/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/pawan-singh-will-be-active-in-bihar-elections-2025-135981717.html</t>
+          <t>https://khabarwani.com/tour-program-of-honorable-shri-digvijay-singh-ji-rajya-sabha-mp-and-former-chief-minister-madhya-pradesh/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/farmers-rally-in-ujjain-took-to-the-streets-with-1000-tractors-started-protest-against-land-pooling-in-simhastha/articleshow/123924628.cms</t>
+          <t>https://www.bhaskar.com/local/bihar/kaimur/news/bihar-has-taken-a-new-direction-under-the-leadership-of-chief-minister-nitish-135966397.html</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://thebharatnow.in/madhya-pradesh/raisen-district-passed-the-resolution-of-one-nation-and-one-election/</t>
+          <t>https://www.bhaskar.com/local/bihar/katihar/news/dainik-bhaskar-bhagalpur-tuesday-september-16-2025-18-135930944.html</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bhopal-artist-anjan-unique-gift-pm-narendra-modi-75th-birthday-1-painting-depicts-entire-life-madhya-pradesh-news-mps25091702758</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/today-is-the-24th-anniversary-of-the-bihar-state-womens-commission-135956535.html</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/ashoknagar-woman-slapped-patwari-removal-cm-helpline-complaint-land-demarcation-case-madhya-pradesh-news-mps25091902940</t>
+          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-protest-against-rajya-sabha-mp-ramchandra-jangra-meham-haryana-135924292.html</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/balaghat-naxalites-kidnapping-youth-suspicion-informer-police-hawk-force-searching-forest-madhya-pradesh-news-mps25091703326</t>
+          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-potholes-roads-premix-material-135970302.html</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/rajasthan-manganiyar-singer-roze-khan-talk-etv-bharat-save-folk-music-madhya-pradesh-news-mps25091905402</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/the-mayor-sent-a-245-page-reply-to-the-department-135936659.html</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/ratlam-vijay-shah-kalika-mata-darshan-tree-planting-gabbar-style-dialogues-madhya-pradesh-news-mps25091801698</t>
+          <t>https://janpakshaajkal.com/the-wife-of-senior-journalist-pankaj-panwar-passed-away-by-chief-minister-pushkar-singh-dhami-and-director-general-information-banshidhar-tiwari/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/ratlam-theft-case-thief-trapped-in-chiller-unit-pipe-police-saves-life-madhya-pradesh-news-mps25091900829</t>
+          <t>https://www.bhaskar.com/local/haryana/karnal/news/haryana-congress-controversy-biraendra-singh-kumari-selja-bhupinder-singh-hooda-135961908.html</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://ianslive.in/shivraj-singh-chouhan-recalls-heartfelt-encounter-between-pm-modi-senior-party-leader-in-bhopal--20250915134402</t>
+          <t>https://www.bhaskar.com/local/bihar/patna/news/hearing-on-sir-in-supreme-court-in-today-135923491.html</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/bhopal/madhya-pradesh-government-transfers-twenty-ias-officers-in-administrative-reshuffle/articleshow/123920453.cms</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-news-digvijay-singh-s-reply-to-siddharth-tiwari-s-statement-son-can-be-son-or-daughter-father-is-not-ang-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/bhopal-gandhi-medical-college-students-raise-concern-over-language-mismatch-in-internal-exams</t>
+          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/morena-mp-live-news-today-21-september-2025-madhya-pradesh-breaking-update-crime-education-politics-samachar-aaj-ki-taza-khabar-livenews-9648356.html</t>
+          <t>https://www.prabhatkhabar.com/business/new-gst-rates-2025-leaders-reactions-gst-reform-india</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/guest-teachers-want-regularization-as-guru-dakshina-135933602.html</t>
+          <t>https://www.bhaskar.com/local/himachal/mandi/news/himachal-news-mandi-maha-yagya-mp-kangana-ranaut-pm-modi-135940705.html</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/mp/bhopal/news/organizations-protested-saying-the-government-used-societies-135963056.html</t>
+          <t>https://www.tv9hindi.com/india/raja-bhaiya-wife-bhanvi-singh-dispute-son-statement-big-reveals-3492379.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/cm-will-inaugurate-the-buildings-of-animal-science-university-tomorrow-135971701.html</t>
+          <t>https://www.bhaskar.com/local/himachal/shimla/news/mandi-mp-kangana-ranaut-visit-disaster-affected-kullu-manikaran-pm-modi-birthday-himachal-135957922.html</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/bathinda/news/on-the-birthday-of-shaheed-bhagat-singh-we-will-surround-the-chief-ministers-residence-hakam-singh-dhanetha-135947665.html</t>
+          <t>https://www.bhaskar.com/local/bihar/motihari/news/mlas-controversial-statement-on-lord-chitragupta-135953638.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/bjp-mp-alok-sharma-sharp-statement-ban-on-non-veg-shops-is-right-1390405.html</t>
+          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/khagaria/news/awareness-campaign-of-chief-minister-women-employment-scheme-started-135925182.html</t>
+          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/demonstration-of-mp-guest-teachers-gathered-in-bhopal-ambedkar-park-demand-for-regularization-1386979.html</t>
+          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/onions-sold-at-just-rs-50-quintal-in-this-madhya-pradesh-market-know-todays-latest-rates/</t>
+          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/rajasthan/amrita-haat-will-be-inaugurated-on-sundayphp/cid17448002.htm</t>
+          <t>https://www.thehawk.in/news/india/cm-mohan-yadav-inaugurates-sandipani-school-in-katni-joins-cleanliness-drive-in-jabalpur</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://vocaltv.in/bihar/safety-standards-checked-operation-of-patna-metrophp/cid17426826.htm</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.bhopalsamachar.com/2025/09/msp-khula-khat.html</t>
+          <t>https://www.amarujala.com/bihar/patna/bihar-goa-cm-and-several-other-leaders-attended-the-naman-bankipur-event-nitin-naveen-targeted-the-rjd-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.newspuran.com/preparations-for-payment-of-more-than-rs-2-crore-to-acss-favorite-firm-ey</t>
+          <t>https://www.deshsewak.org/hindi/news/218872</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.eurasiareview.com/19092025-modi-at-75-the-statesman-the-swayamsevak-and-the-question-of-succession-oped/</t>
+          <t>https://www.bhaskar.com/local/haryana/sonipat/gohana/news/sonipat-murthal-dcrust-cm-nayab-saini-visit-preparations-update-135958608.html</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/15/rss-associated-bharatiya-kisan-sangh-protests-against-farmers-issues-across-madhya-pradesh</t>
+          <t>https://www.dainiktribuneonline.com/news/nation/pm-modi-turns-75-haryana-cm-saini-launches-seva-pakhwada-in-rohtak/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/16/50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=50000-screenings-of-chalo-jeete-hain-on-pm-modis-early-life-planned-across-bihar-nityanand-rai</t>
+          <t>https://www.etvbharat.com/hi/!state/cm-nitish-kumar-to-inaugurate-development-projects-in-bihar-worth-crores-bihar-news-brs25092201132</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/pune/congress-harshwardhan-sapkal-devendra-fadnavis-rss-constitution-statement-1362143.html</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B2%C2%B0%C3%8E%C2%B1%C2%B8%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/20/2025</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/kabirdham/news/dharna-in-kawardha-against-fir-against-journalist-135970021.html</t>
+          <t>https://www.bhaskar.com/local/bihar/motihari/news/cm-nitish-kumar-will-come-to-motihari-tomorrow-135984378.html</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/opinion/the-missing-sense-of-rationalism-3729333</t>
+          <t>https://www.tv9hindi.com/india/cm-nitish-kumar-patna-mauryalok-comprehensive-urban-development-schemes-3493262.html</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/durg-bhilai/news/big-meetings-of-bjp-and-congress-on-the-same-day-in-durg-135965362.html</t>
+          <t>https://www.livehindustan.com/bihar/bhagalpur/story-bihar-cm-launches-development-projects-worth-15-crores-in-kishanganj-201758545934858.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ashoknagar/congress-mla-gopal-singh-chauhan-secretly-met-with-the-cm-mohan-yadav-in-ashok-nagar-sparking-speculation-about-his-entry-into-the-bjp-/articleshow/124019641.cms</t>
+          <t>https://www.livemint.com/hindi/money/rs-10000-will-be-deposited-in-accounts-of-50-lakh-women-on-september-22nd-under-bihar-mukhyamantri-mahila-rojgar-yojana-241758295360592.html</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/digvijaya-singh-religious-conversion-by-faith-not-a-crime-lcln-dskc-2335138-2025-09-17</t>
+          <t>https://www.munaadi.com/news-details/Chief-Minister-to-inaugurate-51-Mahatari-Sadans-on-September-23-state-level-event-to-be-held-in-village-Karelibari-of-Dhamtari-district-Dhamtari-to-get-development-works-worth-Rs-246-crore</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/bihar/tejashwi-will-be-cm-face-no-second-option-congress-mp-big-statement-for-bihar-election-2025-09-20-1163974</t>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/news/cm-nitish-to-visit-west-champaran-on-september-23-135969700.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/bjp-will-celebrate-seva-pakhwada-like-a-political-mega-show/</t>
+          <t>https://haryana.punjabkesari.in/haryana/news/haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-2214274</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/rewa-pandit-srinivas-tiwari-100th-birth-anniversary-statue-unveiling-congress-convention-madhya-pradesh-news-mps25091800671</t>
+          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-elections-mahagathbandhan-patna-news-bihar-news-bihar-legislative-assembly-elections-2025-1189296</t>
+          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/bhopal-mp-news-live-15-september-mohan-yadav-bhopal-madhya-pradesh-breaking-update-politics-crime-samachar-aaj-ki-taza-khabar-livenews-9623118.html</t>
+          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189355</t>
+          <t>https://vasundharadeep.news/two-day-programs-dedicated-to-public-service-and-cleanliness-started-in-the-vending-zone/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/bihar/patna-bihar-chunav-2025-news-live-updates-tejashwi-yadav-cm-nitish-kumar-prashant-kishor-tej-pratap-nda-rjd-bjp-livenews-local18-9627638.html</t>
+          <t>https://uttarakhandcitynews.com/bade-kadidehradun-chief-minister-made-craftsmen-of-11-places-including-halduchod-haldwani-nainital-with-uttarakhand-shilp-ratna-award/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/rewa-politics-news-srinivas-tiwari-centenary-siddharth-missing-digvijay-attack/</t>
+          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://humarabikaner.com/india/pm-modi-birthday-prime-ministers-75th-birthday-today/cid17427895.htm</t>
+          <t>https://garimatimes.in/a-big-gift-to-artisans-in-haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-rohtak-news-updates/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://mradubhashi.com/news.php?id=just-like-there-are-four-dhams-at-the-feet-of-a-mother-similarly-there-is-anand-dham-in-the-lap-of-mother-tongue-chief-minister-dr-yadav-576696</t>
+          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://ganadesh.com/salute-to-sadanand-singhs-legacy-cm-nitish-will-unveil-the-statue-on-september-25/</t>
+          <t>https://insiderlive.in/jp-ganga-path-koilwar-expansion-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://brightpost.in/2025/09/15/cm-dhami-honored-the-litterateurs-there-will-be-no-celebration-on-the-birthday/</t>
+          <t>https://delhiuptodate.com/mukhyamantri-vishwakarma-samman-yojana-launch-artisans-will-get-a-topup-incentive-of-%E2%82%B9-5000/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.gyanwani.com/33520/</t>
+          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nashik/trimbakeshwar-parking-dispute-journalist-attack-case-nashik-1362570.html</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-announces-formation-of-monitoring-committees/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttarakhand/haridwar-haridwar-news-saints-donate-34-lakh-to-cm-relief-fund-24055800.html</t>
+          <t>https://rewariupdate.com/haryana-gets-a-gift-of-rs-117-crore/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/madhya-pradesh/katni-who-is-katni-barwara-mla-dhirendra-singh-dhiru-gifted-gold-ring-cm-mohan-yadav-9643451.html</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/c-dot-joins-pnb-to-drive-it-upgrade-and-digital-banking/78763</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/state/jharkhand/khunti/cm-and-chief-justice-in-khunti-today</t>
+          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/indian-real-estate-draws--80bn-in-15-years--57-per-cent-from-foreigners/78892</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/kaimur/news/bihar-has-taken-a-new-direction-under-the-leadership-of-chief-minister-nitish-135966397.html</t>
+          <t>https://www.arthparkash.com/initiative-to-strengthen-road-infrastructure-in-haryana</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/today-is-the-24th-anniversary-of-the-bihar-state-womens-commission-135956535.html</t>
+          <t>https://ddnews.gov.in/200-students-rescued-from-submerged-institute-in-dehradun-after-heavy-rains-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-potholes-roads-premix-material-135970302.html</t>
+          <t>https://www.punjabkesari.in/national/news/foundation-stone-laid-for-eight-major-connectivity-road-projects-2216961</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/hisar/hansi/news/hisar-hansi-market-encroachment-removal-drive-municipal-council-update-135951308.html</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/himachal/shimla/news/himachal-cabinet-meeting-decision-cm-sukhvinder-sukhu-doctor-staff-nurses-recruitment-shimla-135923978.html</t>
+          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-praadeshik-sadak-utthaan-pariyojana-inauguration-update-135976694.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/bihar-election/news/pappu-yadav-talks-to-pm-on-stage-both-laugh-out-loud-135932167.html</t>
+          <t>https://www.tv9hindi.com/state/bihar/bihar-cm-nitish-kumar-mukhyamantri-gramin-setu-yojana-construction-of-703-new-bridges-started-across-the-state-3491602.html</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/rohtak/news/rohtak-protest-against-rajya-sabha-mp-ramchandra-jangra-meham-haryana-135924292.html</t>
+          <t>https://krantiodishanews.in/post/13872</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-launched-the-web-portal-of-mukhyamantri-pratiya-yojana-under-bihar-bhavan-and-other-construction-workers-welfare-board/</t>
+          <t>https://devbhoomimedia.com/mla-meat-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
+          <t>https://navpradesh.com/chhattisgarh-silver-jubilee-2/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/up-uk/kunda-mla-raja-bhaiya-and-bhanvi-singh-controversy-now-son-shivraj-pratap-singh-statement-3016302</t>
+          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-news-digvijay-singh-s-reply-to-siddharth-tiwari-s-statement-son-can-be-son-or-daughter-father-is-not-ang-2025-09-21</t>
+          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/patna/news/education-minister-sunil-kumars-big-statement-on-tre-4-135982974.html</t>
+          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/raja-bhaiya-wife-bhanvi-singh-dispute-son-statement-big-reveals-3492379.html</t>
+          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/himachal/mandi/news/himachal-news-mandi-maha-yagya-mp-kangana-ranaut-pm-modi-135940705.html</t>
+          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/himachal/shimla/news/mandi-mp-kangana-ranaut-visit-disaster-affected-kullu-manikaran-pm-modi-birthday-himachal-135957922.html</t>
+          <t>https://scroll.in/latest/1086674/how-bjp-governments-companies-celebrated-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/pcc-chief-jitu-patwari-raced-to-the-platform-to-catch-the-vande-bharat-express-19964475</t>
+          <t>https://ommcomnews.com/india-news/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/sonipat/news/harsh-chhikara-supports-uttar-kumar-rape-allegation-statement-135965440.html</t>
+          <t>https://smestreet.in/sectors/agriculture/gst-on-agricultural-machinery-tractors-tillers-harvesters-slashed-to-5-from-sept-22-10479641</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-harshita-soni-missing-case-update-harshita-found-delhi-135957260.html</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/inox-neo-energies-to-acquire-640-mw-hybrid-portfolio-from-evergreen-group-/78793</t>
+          <t>https://www.jagran.com/jammu-and-kashmir/srinagar-jk-disaster-pm-modi-will-visit-the-devastation-in-jammu-and-kashmir-omar-abdullah-looking-at-the-relief-package-24054487.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/pm-modi-launches-development-projects-worth-rs-36-000-crore-in-bihar/ar-AA1MzM9A</t>
+          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/psp-projects-sets-world-record-with-umiya-dham-foundation/79013</t>
+          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/wastewater-and-sewage-treatment/ramky-wins-rs-20.85-billion-godavari-water-project/79057</t>
+          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/latest-construction-technology/tekla-user-days-2025-highlights-collaboration-and-tech-led-construction-/78852</t>
+          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/ntpc-plans-nuclear-power-projects-via-jv-and-standalone-routes/78900</t>
+          <t>https://www.dainiktribuneonline.com/news/gurugram/labour-service-and-awareness-function-on-28th-cm-will-be-the-chief-guest/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/highways-and-roads-infrastructure/govt-approves-rs-4.45-billion-mokama-munger-highway-project/78743</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/goa-approves-rs-1.92-billion-mapusa-bus-stand-projec/78876</t>
+          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/metro-rail-and-railways-infrastructure/gwalior-railway-station-redevelopment-set-for-swift-completion/78894</t>
+          <t>https://www.etvbharat.com/hi/!state/delhi-government-will-give-six-thousand-rupees-every-month-to-those-who-take-care-of-disabled-delhi-news-dls25091603962</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/cm-mohan-yadav-inaugurates-sandipani-school-in-katni-joins-cleanliness-drive-in-jabalpur</t>
+          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/pm-modi-arunachal-tripura-hydropower-project-itanagar-tripura-sundari-temple-135981681.html</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-lado-lakshmi-yojana-app-will-be-launched-from-25-september-trial-will-start-haryana-news-hrs25091603418</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B3%C2%B7%C2%B6&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/19/2025</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/rohtak/vishwakarma-jayanti-haryana-chief-minister-vishwakarma-samman-yojana-benefits-647004</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://timetv.news/national/2025/09/22/chief-minister-nayab-singh-saini-inaugurated-557-projects-worth-rs-117-crore/</t>
+          <t>https://www.ibc24.in/uttarakhand/cm-pushkar-singh-dhami-birthday-2025-wishes-from-amit-shah-yogi-no-celebration-announced-3254134.html</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.deshsewak.org/hindi/news/218872</t>
+          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/ghaziabad-ncr-ghaziabad-news-robot-assisted-sewer-cleaning-pilot-project-launched-24053307.html</t>
+          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/motihari/news/cm-nitish-kumar-will-come-to-motihari-tomorrow-135984378.html</t>
+          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/nation/pm-modi-turns-75-haryana-cm-saini-launches-seva-pakhwada-in-rohtak/</t>
+          <t>https://22scope.com/the-chief-minister-transferred-through-dbt-in-the-bank-account-of-students-under-various-welfare-schemes-of-the-education-department/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://samvadjanhvi.com/dehradun-cm-dhami-attended-the-program-organized-by-the-uttarakhand-handloom-and-handicraft-development-council11-people-were-honored-with-the-uttarakhand-shilp-ratna-award/</t>
+          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.chinimandi.com/gujarat-handles-49-of-total-national-cargo-chief-minister-bhupendra-patel-lauds-pm-modis-vision-for-the-maritime-sector-in-hindi/</t>
+          <t>https://www.bhaskar.com/local/chhattisgarh/balrampur/news/30-crore-government-building-became-dilapidated-135927497.html</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-nayab-singh-saini-launched-haryana-state-environment-scheme-from-panchkula-haryana-news-hrs25091602693</t>
+          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/money/rs-10000-will-be-deposited-in-accounts-of-50-lakh-women-on-september-22nd-under-bihar-mukhyamantri-mahila-rojgar-yojana-241758295360592.html</t>
+          <t>https://www.outlookbusiness.com/planet/industry/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-chouhan</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bihar/bihar-today-news-in-hindi-21-september-2025-bihar-assembly-elections-2025-latest-update-nitish-kumar-1390369.html</t>
+          <t>https://www.newsgram.com/india/2025/09/16/sc-seeks-statess-responses-on-pleas-against-anti-conversion-laws</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://haryana.punjabkesari.in/haryana/news/haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-2214274</t>
+          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/hisar/agriculture-university-hau-rabi-fair-cm-nayab-singh-saini-647591</t>
+          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://mirroruttarakhand.com/news-uttarakhand-chief-minister-gives-financial-approval-for-various-development-schemes-worth-rs-72-62-crore-grant-of-rs-1-crore-for-doon-library-and-research-centre/</t>
+          <t>https://www.lokmattimes.com/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://shikharhimalaya.com/dehradun-expedite-implementation-of-development-plans-cm/</t>
+          <t>https://www.newsonair.gov.in/pm-modis-vision-realised-as-gst-council-slashes-tax-on-agricultural-equipment/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://gurugramnewsnetwork.com/haryana-news-haryana-gets-a-gift-of-projects-worth-rs-117-crore-cm-saini-inaugurates-557-schemes/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://vasundharadeep.news/two-day-programs-dedicated-to-public-service-and-cleanliness-started-in-the-vending-zone/</t>
+          <t>https://www.jansatta.com/videos/news-video/muslim-side-happy-with-supreme-courts-decision-on-waqf-act-2025/4144695/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://uttarakhandpost.com/dehradun/chief-minister-gives-financial-approval-for-various/cid17417142.htm</t>
+          <t>https://www.ptinews.com/story/national/karnataka-hc-infers-consent-of-biological-father-in-minors-adoption-case/2939691</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://devbhoomidarshan.in/cm-dhami-honored-the-artisans-and-weavers-of-uttarakhand/</t>
+          <t>https://www.ptinews.com/story/national/pm-arrives-in-tripura-to-inaugurate-redeveloped-tripureswari-temple/2937934</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://uttarakhandcitynews.com/bade-kadidehradun-chief-minister-made-craftsmen-of-11-places-including-halduchod-haldwani-nainital-with-uttarakhand-shilp-ratna-award/</t>
+          <t>https://www.ptinews.com/story/national/70-arrested-with-illegal-arms-drugs-under-delhi-polices-operation-aaghat/2933128</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-today-19-september-program-in-hindi/</t>
+          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/loans-provided-to-the-beneficiaries-of-chief-minister-youth-entrepreneur-scheme/</t>
+          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/a-big-gift-to-artisans-in-haryana-cm-saini-launched-chief-minister-vishwakarma-samman-yojana-rohtak-news-updates/</t>
+          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/first-meeting-of-disha-committee-cm-pushkar-singh-dhami-thoroughly-reviews-progress-of-various-schemes/</t>
+          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/entrepreneur-conference-chief-minister-naib-singh-saini-said-self-reliance-campaign-will-gain-momentum-only-from-msme/</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.kadwaghut.com/?p=260635</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://insiderlive.in/jp-ganga-path-koilwar-expansion-inauguration/</t>
+          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://dailysamvad.com/2025/09/15/cm-announces-formation-of-monitoring-committees/</t>
+          <t>https://www.jagran.com/himachal-pradesh/shimla-himachal-cm-sukhu-disgruntled-with-punjab-and-haryana-over-bbmb-and-shanan-project-24047696.html</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/transrail-expands-footprint-in-africa-with-new-epc-project/78806</t>
+          <t>https://www.punjabkesari.com/top-news/cm-vishnu-deo-sai/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/smart-cities-projects/global-south-diplomats-visit-bhubaneswar-smart-city/78934</t>
+          <t>https://www.patrika.com/raipur-news/pm-modi-visit-cg-pm-modi-will-visit-chhattisgarh-on-october-31-19951838</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/cerc-proposes-stricter-grid-deviation-rules-for-renewable-projects-/78995</t>
+          <t>https://www.krishakjagat.org/news/distribution-of-dap-and-npk-fertilizers-started-from-committees-in-guna-district/</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/c-dot-joins-pnb-to-drive-it-upgrade-and-digital-banking/78763</t>
+          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/coal-and-mining/government-to-promote-underground-coal-gasification-in-auctions/79070</t>
+          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-ldb-2.0-to-boost-digital-logistics-tracking/79079</t>
+          <t>https://thebikanernews.in/rajasthan/to-address-the-legitimate-demands-of-the-employees-working/cid17435615.htm</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/defence/indian-army-rolls-out-first-overhauled-arv-vt-72b-with-jcbl-group-partnership/79056</t>
+          <t>https://22scope.com/on-september-22-the-fight-for-the-rights-of-pacs-employees-intensified-on-22-september/</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/urban-infrastructure/warehouse-and-logistics/india-launches-leads-2025-to-benchmark-state-logistics/79078</t>
+          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/vikram-solar-secures-200-mw-order-to-expand-india---s-solar-capacity/78863</t>
+          <t>https://www.thehansindia.com/andhra-pradesh/womens-empowerment-conference-calls-for-action-beyond-slogans-1006774</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/permanent-infrastructure-for-simhastha-will-be-built-only-with-consensus-farmers-will-be-protected-chief-minister-yadav/869129/</t>
+          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-government-will-spend-4827-crore-to-repair-and-upgrade-4227-roads-covering-9410-kilometre-haryana-news-hrs25092103320</t>
+          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/hisar/news/haryana-hisar-praadeshik-sadak-utthaan-pariyojana-inauguration-update-135976694.html</t>
+          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/himachal-pradesh/himachal-floods-rs-20000-crore-loss-cm-sukhvinder-singh-sukhu-statement-on-relief-efforts-ann-3013837</t>
+          <t>https://www.abplive.com/states/up-uk/noida-news-grand-launch-of-mission-shakti-phase-5-noida-resonated-with-the-message-of-women-empowerment-ann-3016602</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/200-students-rescued-from-submerged-institute-in-dehradun-after-heavy-rains-in-uttarakhand/</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/pratapgarh-kunda/story-mission-shakti-phase-5-launched-for-women-s-empowerment-and-safety-in-pratapgarh-201758463458936.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-ayey-film-based-of-life-of-cm-yogi-adityanath-got-good-response-of-first-day-in-up-24052698.html</t>
+          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.dainikjagranmpcg.com/opinion/prime-minister-narendra-modi-is-the-champion-of-technology/article-33454</t>
+          <t>https://mp.punjabkesari.in/national/news/pm-modi-said-dhar-s-textiles-will-shine-in-the-world-pm-mitra-park-will-become-2214028</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/khandwa-news/museum-worth-rs-2195-crore-is-being-built-in-omkareshwar-in-mp-19964359</t>
+          <t>https://www.punjabkesari.com/uttar-pradesh/mission-shakti-5-0/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/madhya-pradesh/bhopal/engineer-s-day-will-be-celebrated-with-the-resolution-of-public-welfare-survey-app-and-public-project-manage-2025-09-15</t>
+          <t>https://vocaltv.in/rajasthan/launch-ceremony-of-healthy-womenphp/cid17431249.htm</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/haryana/hisar-news/news-public-money-will-be-used-for-the-public-good-nayab-singh-saini-news-hindi-1-754587-KKN.html</t>
+          <t>https://www.etvbharat.com/hi/!state/healthy-women-empowered-family-campaign-will-be-run-across-country-on-pms-birthday-jharkhand-news-jhs25091600888</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/bihar/bihar-cm-nitish-kumar-mukhyamantri-gramin-setu-yojana-construction-of-703-new-bridges-started-across-the-state-3491602.html</t>
+          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/business/chief-minister-omar-abdullah-asks-telecom-companies-to-focus-on-remote-villages-3254913.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167813</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/jammu-and-kashmir-flood-damage-report-cm-asks-officials-to-speed-up-assessment-ahead-of-pms-expected-visit-hindi-news-hin25092204098</t>
+          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/foundation-stone-laid-for-8-link-road-projects-worth-rs-1215-crore-135988387.html</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/ballia/news/women-empowerment-campaign-started-in-ballia-135968817.html</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://krantiodishanews.in/post/13872</t>
+          <t>https://www.etvbharat.com/hi/!state/chief-minister-yogi-adityanath-in-lucknow-kick-starts-mission-shakti-5-former-govts-jobs-to-females-uttar-pradesh-news-ups25092003463</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/will-protect-the-interests-of-commission-agents-of-punjab-mann/</t>
+          <t>https://www.bhaskar.com/local/uttar-pradesh/barabanki/ramsnehi-ghat/news/mission-shakti-50-launched-135966763.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://devbhoomimedia.com/mla-meat-chief-minister/</t>
+          <t>https://www.livehindustan.com/bihar/banka/story-nda-workers-grand-meeting-in-shambhugan-bihar-development-and-women-empowerment-highlighted-201758491360340.html</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/news/trending/story/agriculture-news-live-updates-weather-alert-rain-alert-uttarakhan-himachal-pradesh-monsoon-2025-1280851-2025-09-22</t>
+          <t>https://www.amarujala.com/lucknow/mission-shakti-5-0-launched-in-up-cm-yogi-releases-sop-booklets-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://navpradesh.com/chhattisgarh-silver-jubilee-2/</t>
+          <t>https://hindi.opindia.com/reports/mission-shakti-phase-5-begin-in-uttar-pradesh-during-navratri-cm-yogi-announces/</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://dainiksaveratimes.com/national/himachal/himachal-pradesh-suffered-a-loss-of-rs-20000-crore-in-three-years-due-to-floods-and-rain-related-disasters-cm-sukhu/</t>
+          <t>https://www.etvbharat.com/hi/!state/rps-passing-out-pared-cm-attend-the-function-in-jaipur-rajasthan-news-rjs25091901773</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://hindikhabar.com/punjab-launches-rural-flood-relief-rehabilitation-plan-2025/</t>
+          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://navyugsandesh.com/uttarakhand-gets-revenue-surplus-cm-dhami-calls-cag-report-proof-of-success/</t>
+          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/news/shivraj-singh-chouhan-assesses-flood-damage-in-jammu-announces-relief-measures-for-farmers-workers20250920025448-143406/</t>
+          <t>https://clipper28.com/union-women-and-child-development-minister-annapurna-devi-paid-a-courtesy-call-on-chief-minister-vishnu-dev-sai/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/shivraj-singh-chouhan-jammu-flood-relief-farmers/</t>
+          <t>https://vlesociety.com/bihar-mukhyamantri-mahila-rojgar-yojana-kist-update/</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1086674/how-bjp-governments-companies-celebrated-pm-modis-75th-birthday</t>
+          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167679</t>
+          <t>https://garimatimes.in/uttarakhand-cm-dhami-inaugurated-exhibition-in-dehradun-as-part-of-seva-pakhwada/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/pm-modis-vision-realised-as-gst-council-slashes-tax-on-agricultural-equipment/</t>
+          <t>https://upkiran.org/Uttarakhand-BJP-new-team-announced-Woman-general-secretary-for-first-time-know-full-list</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://therahnuma.com/navratri-gift-for-ktaka-farmers-centre-approves-procurement-of-5-crops-at-msp/</t>
+          <t>https://bastitimes24.in/2025/09/20/fifth-phase-of-mission-shakti/</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/jammu-and-kashmir/srinagar-jk-disaster-pm-modi-will-visit-the-devastation-in-jammu-and-kashmir-omar-abdullah-looking-at-the-relief-package-24054487.html</t>
+          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/purnia/news/pm-will-inaugurate-airport-and-hold-public-meeting-in-3-hours-135923374.html</t>
+          <t>https://samridhjharkhand.com/state/jharkhand/ranchi/initiative-of-chief-minister-hemant-soren-launched-economic-upliftment-of/article-16278</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/bettiah/news/modi-government-reduced-gst-rates-135928493.html</t>
+          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/career/news/pm-modi-launches-odisha-governments-subhadra-yojana-education-minister-atishi-marlena-will-be-the-new-chief-minister-of-delhi-133658792.html</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
+          <t>https://www.bhaskar.com/local/bihar/siwan/news/beneficiaries-of-pm-kisan-samman-nidhi-yojana-should-get-their-kyc-done-135962013.html</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://mp.punjabkesari.in/national/news/pm-modi-said-dhar-s-textiles-will-shine-in-the-world-pm-mitra-park-will-become-2214028</t>
+          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/jehanabad/news/tejashwi-bihar-adhikar-yatra-start-from-jehanabad-135927540.html</t>
+          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
+          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://krishijagran.com/blog/indian-agriculture-in-transition-from-policy-promises-to-ground-realities-on-the-road-to-viksit-bharat/</t>
+          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.in/business/news/3-7-growth-in-agriculture-sector-in-first-quarter-is-highest-2213431</t>
+          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/national-workshop-organized-to-tackle-agricultural-disasters-emphasis-on-new-technologies-and-policy-reforms/</t>
+          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
+          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.ruralvoice.in/agribusiness/mother-dairy-reduces-prices-to-pass-on-gst-benefits-to-consumers.html</t>
+          <t>https://www.kisantak.in/knowledge/story/pm-modi-at-75-how-pm-kisan-samman-nidhi-launched-by-pm-modi-becomes-the-biggest-support-for-farmers-1278751-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://cnin.co.in/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A4%BE%E0%A4%AE-%E0%A4%A8%E0%A4%88-%E0%A4%A6%E0%A4%BF%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%80-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%86%E0%A4%AF%E0%A5%8B%E0%A4%9C%E0%A4%BF%E0%A4%A4.../70480</t>
+          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/knowledge/story/why-bonuses-for-paddy-are-hurting-india-food-goals-1278307-2025-09-16</t>
+          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90140</t>
+          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://media24news.in/?p=90048</t>
+          <t>https://www.chinimandi.com/gujarat-handles-49-of-total-national-cargo-chief-minister-bhupendra-patel-lauds-pm-modis-vision-for-the-maritime-sector-in-hindi/</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/ghazipur/cm-samuhik-vivah-yojana-marriage-done-only-after-biometric-verification-know-new-rules-up-news/articleshow/124013599.cms</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189781</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B8%C3%8E%C2%B1%C2%B4%C2%B9&amp;fontname=%C3%8D%C3%A1%C3%AE%C3%A7%C3%A1%C3%AC&amp;LocID=32&amp;pubdate=09/18/2025</t>
+          <t>https://mradubhashi.com/news.php?id=india-can-achieve-8-growth-target-with-artificial-intelligence-niti-aayog-report-576577</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://hindi.krishijagran.com/news/rabi-crop-campaign-2025-shivraj-singh-launches-viksit-krishi-sankalp-abhiyan/</t>
+          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/haryana/panchkula-deen-dayal-ladli-lakshmi-yojana-haryana-launches-app-for-women-empowerment-cm-nayab-singh-saini-will-head-monitoring-commitee-24051710.html</t>
+          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/uttar-pradesh/story/viksit-uttar-pradesh-summit-2025-yogi-adityanath-brajesh-pathak-malini-awasthi-ntc-dskc-2339107-2025-09-22</t>
+          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/chief-minister-vishnu-deo-sai-announces-75-lakh-for-dhuruva-community-development-social-hall-inauguration-chhattisgarh-3492055.html</t>
+          <t>https://www.patrika.com/patrika-special/mp-politics-wave-rises-demand-to-make-this-leader-cm-intensifies-19948637</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/gurugram/labour-service-and-awareness-function-on-28th-cm-will-be-the-chief-guest/</t>
+          <t>https://www.amarujala.com/madhya-pradesh/bhopal/mp-news-meeting-between-cm-dr-yadav-and-assembly-speaker-tomar-discussion-continued-in-a-closed-room-for-ha-2025-09-19</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/gurgaon/story-haryana-government-hosts-state-level-labor-awareness-event-in-gurugram-201758462192593.html</t>
+          <t>https://www.jagran.com/bihar/patna-city-nitish-kumar-meets-amit-shah-rjd-calls-it-surrender-24052024.html</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-lado-lakshmi-yojana-app-will-be-launched-from-25-september-trial-will-start-haryana-news-hrs25091603418</t>
+          <t>https://hindi.news18.com/news/punjab/chandigarh-punjab-punjab-floods-remembered-for-generations-cm-bhagwant-mann-attack-congress-bjp-akali-dal-9646875.html</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.newstak.in/bihar/story/bihar-vishwakarma-puja-nitish-kumar-workers-scheme-2025-3202938-2025-09-19</t>
+          <t>https://www.statemirror.com/state/bihar/lalu-yadav-brainchild-bhura-baal-returns-in-bihar-election-2025-what-impact-on-cast-politics-151176</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://school.careers360.com/hi/articles/anuprati-coaching-yojana</t>
+          <t>https://www.amarujala.com/photo-gallery/madhya-pradesh/bhopal/dynasty-politics-nepotism-has-deep-roots-in-congress-too-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://delhiuptodate.com/mukhyamantri-vishwakarma-samman-yojana-launch-artisans-will-get-a-topup-incentive-of-%E2%82%B9-5000/</t>
+          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://uttarakhandmorningpost.com/nainital-news-chief-minister-pushkar-singh-dhami-held-multipurpose-camps-all-over-the-district/</t>
+          <t>https://www.patrika.com/bhopal-news/nepotism-in-mp-politics-many-leaders-including-scindia-digvijay-inherited-politics-adr-report-19949471</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
+          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://22scope.com/chief-minister-launched-a-program-organized-on-24th-foundation-day-of-bihar-state-womens-commission/</t>
+          <t>https://www.gnttv.com/india/story/bihar-politics-lalu-prasad-yadav-did-not-get-the-cms-chair-easily-ram-sundar-das-and-raghunath-jha-were-also-in-the-race-to-become-the-chief-minister-1279641-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://22scope.com/labor-welfare-day-was-honored-on-the-occasion-of-vishwakarma-puja-77-workers-of-a-total-of-11-factories-of-the-state/</t>
+          <t>https://www.bbc.com/hindi/articles/cj6xr010dldo</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.theprintlines.com/national-news/states-news/uttar-pradesh/yogi-government-will-now-gift-branded-items-to-the-bride-and-groom-under-the-chief-ministers-mass-marriage-scheme-440894</t>
+          <t>https://hindi.news18.com/news/haryana/chandigarh-city-rahul-gandhi-habit-of-making-false-allegations-then-running-away-haryana-cm-nayab-singh-saini-on-vote-chori-9647747.html</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/balaghat-news/work-done-towards-women-empowerment-and-social-change-received-many-honors-19966328</t>
+          <t>https://www.etvbharat.com/hi/!bharat/kosi-in-bihar-election-it-is-nitish-kumar-who-wins-not-lalu-yadav-story-of-three-yadavs-of-politics-hindi-news-brn25091602128</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/balrampur/news/30-crore-government-building-became-dilapidated-135927497.html</t>
+          <t>https://www.bhaskarhindi.com/other/news-1188206</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.outlookbusiness.com/planet/industry/farm-sector-clocked-worlds-highest-growth-at-37-in-q1-chouhan</t>
+          <t>https://www.etvbharat.com/hi/!state/former-chief-minister-ashok-gehlot-raised-questions-on-election-commission-rajasthan-news-rjs25092001128</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.newsgram.com/india/2025/09/16/sc-seeks-statess-responses-on-pleas-against-anti-conversion-laws</t>
+          <t>https://www.etvbharat.com/hi/!bharat/politics-on-bhura-baal-saaf-karo-in-bihar-election-2025-hindi-news-brn25091604889</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/congress-workers-call-for-singhar-as-cm-in-anuppur-lop-claims-many-bjp-leaders-are-in-contact-135928489.html</t>
+          <t>https://www.bhaskarhindi.com/other/delhi-cm-rekha-gupta-inaugurates-first-large-scale-biogas-plant-at-nangli-dairy-targets-kejriwal-1189076</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://www.gnttv.com/india/story/madhya-pradesh-alirajpur-district-has-been-renamed-as-aalirajpur-1278540-2025-09-16</t>
+          <t>https://www.timesnowhindi.com/elections/tejashwi-yadav-will-be-cm-face-of-mahagathbandhan-in-bihar-elections-says-congress-mp-akhilesh-prasad-singh-article-152861720</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/jabalpur-news/jabalpur-high-court-issues-notice-to-government-on-arrears-in-mp-19963694</t>
+          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/madhya-pradesh/ujjain/bhartiya-kisan-sangh-warns-mohan-government-stop-supply-of-milk-and-vegetables-in-ujjain-city/articleshow/123897186.cms</t>
+          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://www.aajsamaaj.com/lado-laxmi-yojana-update-women-will-receive-2100-rupees-every-month-applications-will-begin-on-september-25/</t>
+          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/we-will-make-india-food-basket-of-the-world-shivraj-singh-chouhan/</t>
+          <t>https://khabarsameeksha.com/increased-facilities-in-doon-hospital-within-two-days-on-the-instructions-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/economy/gst-new-rates-india-live-updates-two-slab-system-september-22-nirmala-sitharaman-gst-2-0-itc-council-reforms-5-18-40-pc-liveblog-19681684.htm</t>
+          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/questions-raised-on-hsvps-private-property-policy-advisors-met-the-chief-minister/</t>
+          <t>https://khabarsameeksha.com/cm-dhami-reached-kesarwala-maldevata-on-inspection/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/gwalior-news/gwalior-high-court-decision-on-transfer-and-posting-of-patwari-19963499</t>
+          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-revises-top-official-vehicle-price-limits-removes-cap-for-governor-and-chief-minister-and-judges-govt-issues-new-gr-know-all/articleshow/123979866.cms</t>
+          <t>https://dailysamvad.com/2025/09/15/cm-mann-warned-the-pm-modi/</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/videos/news-video/muslim-side-happy-with-supreme-courts-decision-on-waqf-act-2025/4144695/</t>
+          <t>https://www.rewariyasat.com/rewa/rewa-bjp-mla-siddharth-tiwari-digvijay-singh-political-controversy-484217</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2169327</t>
+          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/environment/story/recovery-punjab-amritsar-rice-wheat-steep-climate-change-pm-narendra-modi-aap-bjp-insurance-floods-2788708-2025-09-17</t>
+          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/agriculture/rice-stocks-climb-14-to-hit-record-wheat-at-four-year-high-shows-data-125091701284_1.html</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/government-teachers-marched-to-the-chief-ministers-residence-to-raise-their-demands/</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-vijay-kumar-sinha-said-at-dainik-jagran-agriculture-export-seminar-agriculture-is-based-on-culture-deputy-chief-minister-24052950.html</t>
+          <t>https://www.bhaskarhindi.com/state/chhattisgarh/cm-vishnu-deo-chhattisgarh-news-raipur-news-chhattisgarh-latest-news-1189494</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!business/andhra-pradesh-shrimp-export-loss-us-tariffs-cm-naidu-request-hin25091503292</t>
+          <t>https://krantiodishanews.in/post/13875</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/business/business-diary/andhra-shrimp-exports-may-suffer-losses-of-25000-crore-due-to-tariff-cm-naidu-seeks-centre-help-2025-09-15</t>
+          <t>https://statetimes.in/cente-jk-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/bhopal-bharatiya-kisan-sangh-protest-against-land-acquisition-ujjain-simhastha-2028-mohan-yadav-assured-madhya-pradesh-news-mps25091505407</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/animal-husbandry/story/us-tariffs-hit-andhra-s-shrimp-exports-tax-of-rs-600-crore-imposed-on-2000-containers-swm-1277905-2025-09-16</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.kisantak.in/crops/story/central-govt-acceptes-proposal-of-haryana-cm-nayab-singh-saini-of-crop-procurement-before-1st-october-1278237-2025-09-16</t>
+          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/govt-sets-rabis-crops-production-target-at-36250-million-tonnes-shivraj-singh-chauhan-1/</t>
+          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/piyush-goyal-to-visit-uae-for-13th-india-uae-high-level-task-force-on-investments/78929</t>
+          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/punjab-and-haryana-should-play-the-role-of-elder-brother-chief-minister/</t>
+          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cooperation-in-cooperation-programme-organised-at-raj-bhavan/</t>
+          <t>https://www.etvbharat.com/hi/!state/cm-mewat-upliftment-scheme-benefits-on-passing-competitive-exams-scholarship-in-nuh-haryana-news-hrs25091803715</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://www.naidunia.com/madhya-pradesh/bhopal-mp-faces-fertilizer-shortage-amidst-rising-demand-and-distribution-issues-8406114</t>
+          <t>https://www.bhaskar.com/local/bihar/aurangabad/news/reduction-in-gst-rates-will-increase-purchasing-135936513.html</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://www.divyahimachal.com/2025/09/punjab-and-haryana-should-cooperate-like-elder-brothers-on-shanan-sukhu/</t>
+          <t>https://timesofindia.indiatimes.com/business/india-business/reduced-prices-of-farm-equipment-under-gst-2-0-will-help-air-pollution-abatement-efforts/articleshow/124001260.cms</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/himachal-pradesh/shimla-himachal-cm-sukhu-disgruntled-with-punjab-and-haryana-over-bbmb-and-shanan-project-24047696.html</t>
+          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/first-meeting-of-the-high-level-committee-of-nabard-held-in-delhi/</t>
+          <t>https://www.jagran.com/haryana/panchkula-13-solid-waste-management-plants-to-be-set-up-in-haryana-e-waste-collection-centres-in-every-district-375-electric-buses-to-arrive-24049075.html</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/himachal-pradesh/solan/mukesh-sharma-chairman-of-jogindra-bank-took-charge-solan-news-c-176-1-ssml1040-152870-2025-09-16</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/chief-minister-naib-singh-saini-launched-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://www.punjabkesari.com/top-news/cm-vishnu-deo-sai/</t>
+          <t>https://www.abplive.com/states/maharashtra/devendra-fadnavis-launched-various-csr-projects-of-hyundai-motor-india-ltd-in-mumbai-meeting-with-md-unsoo-kim-3013038</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://www.gaonjunction.com/khabar-junction/himachal-cm-sukhu-announces-one-time-settlement-policy-for-small-farmers-focus-on-cooperative-sector</t>
+          <t>https://www.bhaskar.com/local/haryana/panchkula/news/cm-launched-haryana-state-environment-plan-2025-135934095.html</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/himachal-pradesh/cooperative-societies-cm-sukhvinder-singh-sukhuone-time-settlement-policy-sahkar-taxi-scheme</t>
+          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://newsghat.in/cm-sukhu-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%95%E0%A5%87-%E0%A4%B9%E0%A4%BF%E0%A4%A4%E0%A5%8B%E0%A4%82-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A4%B9%E0%A4%AF%E0%A5%8B/</t>
+          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://pahadprabhat.com/haldwani-aanchal-distributed-82-86-lakh-bonus-in-seven-committees-of-kaladhungi-region/</t>
+          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://newsheight.com/big-breaking-chief-minister-pushkar-singh-dhami-impressed-by-the-overflows/</t>
+          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/north/madhya-pradesh/pm-modi-birthday-mitra-park-launch-madhya-pradesh-206968</t>
+          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://ibgnews.com/2025/09/20/shri-h-m-bangur-chairman-shree-cement-conferred-honorary-doctorate-by-kiit-university/</t>
+          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/pm-modi-in-madhya-pradesh-foundation-of-dhar-pm-mitra-park-garments-export-via-gujarat-kandla-port-135940383.html</t>
+          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/chhattisgarh/sukma/news/awareness-was-also-created-about-women-empowerment-in-the-workshop-135978839.html</t>
+          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/bihar/patna-city-sashakt-bihar-nitish-government-emphasis-on-development-and-empowerment-24050850.html</t>
+          <t>https://www.etvbharat.com/hi/!state/pm-narendra-modi-birthday-uttarakhand-bjp-swachhotsav-abhiyan-program-uttarakhand-news-uts25091701295</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-ladki-behen-scheme-cm-fadnavis-assured-financial-help-says-women-empowerment-mahayuti-govt-resolve-2025-09-17</t>
+          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttar-pradesh/balia/story-mission-shakti-5-0-launched-by-cm-yogi-adityanath-for-women-s-empowerment-and-safety-201758389817293.html</t>
+          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://suryasamachar.com/2025/09/17/nayab-singh-saini-gift-to-haryana-breast-cancer-screening-van-dispatched-from-panchkula-on-pm-modi-birthday/</t>
+          <t>https://www.jagran.com/haryana/panchkula-haryana-state-environment-plan-2025-launched-by-cm-nayab-singh-saini-know-benefits-24048895.html</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/khagaria/news/chief-minister-women-employment-scheme-launched-in-bihar-135977950.html</t>
+          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!state/chief-minister-yogi-adityanath-in-lucknow-kick-starts-mission-shakti-5-former-govts-jobs-to-females-uttar-pradesh-news-ups25092003463</t>
+          <t>https://www.bhaskar.com/local/bihar/bettiah/jogapatti/news/one-tree-in-the-name-of-mother-tree-plantation-program-in-machhargaon-135969599.html</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167813</t>
+          <t>https://suryasamachar.com/2025/09/18/cm-rekha-gupta-planted-sapling-in-mother-name-diplomats-from-70-countries-participated-one-tree-in-mother-name/</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/uttar-pradesh/lucknow-city-mission-shakti-5-up-government-focuses-on-women-safety-and-empowerment-24050834.html</t>
+          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/uttarakhand/dehradun/story-uttarakhand-chief-minister-launches-exhibition-for-service-fortnight-focused-on-cleanliness-and-social-awareness-201758271216564.html</t>
+          <t>https://himachal.punjabkesari.in/himachal-pradesh/news/forest-friends-will-be-appointed-to-overcome-the-shortage-of-staff-in-the-forest-2214886</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/lucknow/mission-shakti-5-0-launched-in-up-cm-yogi-releases-sop-booklets-2025-09-20</t>
+          <t>https://www.etvbharat.com/hi/!state/first-meeting-of-the-state-level-disha-committee-was-held-under-the-chairmanship-of-the-chief-minister-uttarakhand-news-uts25092000523</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/auraiya/bela/news/new-initiative-for-women-empowerment-in-up-135967229.html</t>
+          <t>https://panchjanya.com/2025/09/17/435757/bharat/uttarakhand/cm-dhami-launched-a-cleanliness-drive-on-pm-modi-birthday/</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/uttar-pradesh/barabanki/ramsnehi-ghat/news/mission-shakti-50-launched-135966763.html</t>
+          <t>https://www.etvbharat.com/hi/!state/haryana-cm-nayab-saini-seva-pakhwada-swachhata-abhiyan-on-pm-modi-birthday-in-rohtak-mdu-haryana-news-hrs25091700782</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/haryana/sonipat/news/sonipat-updates-haryana-cm-saaini-seva-pakhwada-dcrsut-murahtal-program-135981755.html</t>
+          <t>https://www.khaskhabar.com/local/rajasthan/jaipur-news/news-cm-bhajanlal-sharma-planted-a-tree-at-the-chief-minister-residence-and-gave-the-message-of-environmental-protection-news-hindi-1-754747-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://infouttarakhand.com/far-away-from-the-ground-chief-minister-womens-sustainable-livelihood-scheme-300-women-did-not-get-garima-dasouni/</t>
+          <t>https://www.khaskhabar.com/local/haryana/chandigarh-news/news-haryana-government-working-to-modernize-healthcare-facilities-in-the-state-nayab-singh-saini-news-hindi-1-754146-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://bastitimes24.in/2025/09/20/basti-mission-shakti-5-0-begins/</t>
+          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://www.joharlive.com/news/the-healthy-women-strong-family-campaign-was-launched-in-a-grand-manner-in-ranchi-attended-by-the-chief-minister-and-the-governor/</t>
+          <t>https://garimatimes.in/chief-minister-nayab-singh-saini-launched-state-environment-plan-2025-appealed-to-citizens-to-save-water-plant-trees-and-keep-environment-clean/</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://clipper28.com/union-women-and-child-development-minister-annapurna-devi-paid-a-courtesy-call-on-chief-minister-vishnu-dev-sai/</t>
+          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://crimejasoos.in/news/up-news/82978/</t>
+          <t>https://garimatimes.in/on-pm-modis-birthday-cm-saini-did-cleanliness-work-in-rohtak-planted-a-tree-and-flagged-off-namo-marathon/</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/uttarakhand-cm-dhami-inaugurated-exhibition-in-dehradun-as-part-of-seva-pakhwada/</t>
+          <t>https://www.haryanaekhabar.com/gurugram/haryana-to-become-medical-hub-mbbs-seats-to-increase-from-700-to-2600-know-the-target-after-four-years/</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://khatpatnews.com/?p=61931</t>
+          <t>https://nayabharat.live/uttarakhand-news-the-first-meeting-of-the-state-level-direction-committee-in-the-secretariat-chaired-by-chief-minister-dhami-said-that-the-implementation-of-the-schemes/</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://tejastoday.com/mission-shakti-phase-5-0-launched/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/19/del27-jk-chouhan-farmers.html</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://garimatimes.in/rps-convocation-ceremony-chief-minister-bhajan-lal-sharma-announced-construction-of-a-new-training-building-at-rajasthan-police-academy/</t>
+          <t>https://www.jagran.com/punjab/chandigarh-chandigarh-news-punjab-flood-declared-severe-disaster-by-central-government-state-will-receive-a-loan-of-rs-590-crore-for-reconstruction-24051525.html</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://creativenewsexpress.com/pushpa-padhalani-wrote-new-recitation-of-6-lakhs-annually-6-lakhs/</t>
+          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://devbhoomisamvad.com/uttarakhand/healthy-women-strong-families-womens-health-and-empowerment-in-uttarakhand/</t>
+          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-get-this-work-done-before-diwali-kisan-pm-modi-2025-09-20</t>
+          <t>https://orissadiary.com/union-agriculture-minister-shivraj-singh-chouhan-visits-flood-affected-border-village-of-badyal-brahmana-in-rs-pura-jammu-also-visits-farm-lands-to-assess-damage-to-crops/</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/local/bihar/siwan/news/beneficiaries-of-pm-kisan-samman-nidhi-yojana-should-get-their-kyc-done-135962013.html</t>
+          <t>https://media24news.in/?p=90048</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/pm-kisan-samman-nidhi-yojana-21st-installment-21st-installment-likely-to-arrive-before-diwali-kisan-news-2025-09-18</t>
+          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://hindi.financialexpress.com/investment-saving-news/pm-kisan-2000-installment-for-28-lakh-farmers-in-jammu-himachal-punjab-when-will-other-states-receive-it-10488423</t>
+          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/who-will-get-rs-6000-from-the-delhi-government-just-have-to-do-this-work-delhi-govt-scheme-cm-rekha-2025-09-18</t>
+          <t>https://www.kisantak.in/crops/story/yogi-government-will-run-rabi-season-campaign-2025-in-all-75-districts-of-uttar-pradesh-nvs-1278737-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/animal-husbandry-farmers-benefited-from-the-chief-ministers-dairy-plus-scheme/</t>
+          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-last-date-extended-last-date-for-filing-itr-has-been-extended-know-what-is-the-update-breaking-n-2025-09-16</t>
+          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/gst-new-rates-prices-of-chips-biscuits-and-soap-will-not-decrease-how-will-the-common-man-benefit-gst-refo-2025-09-15</t>
+          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/indian-railways-new-rule-you-will-easily-get-train-tickets-for-diwali-chhath-this-rule-has-changed-irctc-2025-09-16</t>
+          <t>https://www.ruralvoice.in/latest-news/target-of-food-grain-production-of-36.25-crore-tonnes-in-year-2025-26-brainstorming-with-the-states-in-rabi-conference.html</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/itr-filing-update-didn-t-file-itr-now-you-will-be-fined-up-to-rs-5000-income-tax-return-breaking-2025-09-17</t>
+          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/news/cm-yadav-went-to-the-fields-and-inspected-the-affected-crops-said-farmers-should-not-worry-every-field-will-be-surveyed/</t>
+          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-update-details-aadhaar-is-10-years-old-update-it-for-free-till-this-date-uidai-amar-ujala-2025-09-15</t>
+          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/utility/aadhaar-lpg-link-link-your-lpg-connection-with-aadhaar-in-this-way-otherwise-you-will-not-get-subsidy-2025-09-17</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://www.krishakjagat.org/national-news/todays-weather-very-heavy-rain-alert-in-northeast-and-maharashtra-monsoon-returns-to-rajasthan-punjab-gujarat/</t>
+          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/utilities/ladli-behna-yojana-is-the-ladli-behna-scheme-about-to-end-the-1250-installment-will-not-be-available-from-october-10476808</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2168645</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-india-us-agree-to-step-up-efforts-for-early-bta-3979894/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167786</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/india--new-zealand-fta-talks-advance-in-queenstown/79087</t>
+          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/policy/economy-import-duties-may-be-imposed-on-key-varieties-of-pulses-3984751/</t>
+          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/chhattisgarh/special-focus-on-bastar-in-new-industrial-policy-said-cm-vishnu-dev-sai-3482248.html</t>
+          <t>https://www.hindustantimes.com/india-news/arunachal-minister-pushes-for-state-specific-policies-youth-training-in-agriculture-101758033324922.html</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>https://bolpanipat.com/chief-minister-naib-singh-saini-participated-in-the-national-convention-organized-by-laghu-udyog-bharati-at-sadhna-and-gram-vikas-kendra-in-samalkha/</t>
+          <t>https://makdaiexpress24.com/aaj-ka-rashifal-today-know-the-horoscope-of-september-16/</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>https://hillspost.com/%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B9%E0%A4%BF%E0%A4%AE%E0%A4%BE%E0%A4%9A%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%96%E0%A4%B0%E0%A5%80%E0%A4%A6/57360/</t>
+          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BBCnewsHindi/posts/%E0%A4%9C%E0%A4%AF%E0%A4%B0%E0%A4%BE%E0%A4%AE-%E0%A4%B0%E0%A4%AE%E0%A5%87%E0%A4%B6-%E0%A4%AC%E0%A5%8B%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A5%80%E0%A4%8F%E0%A4%B8%E0%A4%9F%E0%A5%80-%E0%A4%95%E0%A4%BE-%E0%A4%B5%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7-%E0%A4%95%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A5%87-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%87%E0%A4%95%E0%A4%BC%E0%A4%B2%E0%A5%8C%E0%A4%A4%E0%A5%87-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%80-%E0%A4%A5%E0%A5%87%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%80-%E0%A4%96%E0%A4%BC%E0%A4%AC%E0%A4%B0-h/905180755408570/</t>
+          <t>https://www.kisantak.in/latest-news/story/agriculture-news-live-updates-departure-of-monsoon-another-round-of-rain-begun-alert-issued-1279157-2025-09-18</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/uttarakhand/nainital/youth-congress-national-secretary-mimansa-who-was-protesting-against-cm-dhami-visit-was-detained-in-haldwani-2025-09-20</t>
+          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>https://4pm.co.in/rahul-gandhis-punjab-tour-took-stock-of-flood-affected-areas/146471</t>
+          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>https://viratvasundhara.in/2025/09/20/rewa-mp-digvijay-singh-was-called-maulana-as-bhadki-karni-sena-said-siddharth-tiwari-apologized/</t>
+          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167220</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3628917-farm-sector-clocked-worlds-highest-growth-at-37-pc-in-q1-chouhan?amp</t>
+          <t>https://jantaserishta.com/national/we-will-make-india-the-food-basket-of-the-world-shivraj-singh-chouhan-4267969</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/chief-minister-nitish-kumar-met-union-home-minister-amit-shah-and-discussed-election-strategy/</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/himachal-pradesh/hamirpur-hp-anurag-thakurs-tarpaulin-politics-criticized-in-hamirpur-24052156.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/sultanpur/ex-minister-op-singh-meets-yogi-will-political-equations-change-in-sultanpur-stir-in-bsp-congress-bjp/articleshow/124053101.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/bhopal-news/nepotism-in-mp-politics-many-leaders-including-scindia-digvijay-inherited-politics-adr-report-19949471</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/politics/story/pm-narendra-modi-counter-caste-based-politics-lalu-mulayam-jat-maratha-bjp-ntcpkb-dskc-2335430-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/india-news/goa-politics-murder-social-worker-ram-kankonkar-opposition-parties-march-to-chief-minister-residence-2025-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/haryana/panchkula-haryana-politics-birendra-singh-created-an-atmosphere-for-kumari-selja-bhupendra-hooda-turned-tables-said-neither-tired-nor-retired-24056405.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/nitish-kumar-showed-power-of-political-chanakya-warned-lalan-singh-in-gestures-from-pm-modi-stage/articleshow/123926248.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/mp-politics/digvijay-singh-younger-brother-laxman-singh-started-political-yatra-in-mp-expelled-from-congress/2923537</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/hindi/zeephh/himachal-pradesh/it-is-unfortunate-to-do-politics-on-disaster-in-himachal-says-naresh-chauhan/2927269</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/uttar-pradesh/pratapgarh/know-about-raja-bhaiya-twin-son-shivraj-pratap-singh-and-brijraj-pratap-singh/articleshow/124040972.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/news-1189152</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/bihar-assembly-election-2025-giriraj-singh-ignited-another-fire-in-the-mahagathbandhan-saying-rahul-took-political-advantage-of-tejashwi/articleshow/123979673.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/haryana/panchkula/news/chandigarh-asks-haryana-school-teachers-135958903.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>https://www.gnttv.com/india/story/bihar-politics-lalu-prasad-yadav-did-not-get-the-cms-chair-easily-ram-sundar-das-and-raghunath-jha-were-also-in-the-race-to-become-the-chief-minister-1279641-2025-09-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/politics/bihar-mukhyamantree-nitish-kumar-kendreey-grh-mantree-amit-shah-se-milane-patna-ke-ek-hotel-mein-pahunche-1188246</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/marathon-in-kurukshetra-namo-youth-run-2025-cm-nayab-saini-on-parivarvad-haryana-news-hrs25092100814</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/delhi-cm-rekha-gupta-inaugurates-first-large-scale-biogas-plant-at-nangli-dairy-targets-kejriwal-1189076</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>https://www.timesnowhindi.com/elections/tejashwi-yadav-will-be-cm-face-of-mahagathbandhan-in-bihar-elections-says-congress-mp-akhilesh-prasad-singh-article-152861720</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/uttarakhand-cm-meets-prime-minister-modi-in-new-delhi-1187432</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/other/news-1186498</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/bhopal/mp-govt-employees-lakhs-of-mp-employees-will-get-promotion-reservation-issue-will-be-resolved-soon-1389571.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>https://22scope.com/chief-minister-hemant-soren-master-plan-somesh-soren-will-soon-take-minister-oath-ghatsila-by-election/</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>https://ind24.tv/news/scindia_MP</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>https://ghamasan.com/india/madhya-pradesh/political-turmoil-is-increasing-in-mp-politics-suddenl-demand-to-make-this-leader-chief-minister-of-madhya-pradesh-650728</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>https://npg.news/madhya-pradesh/mp-kee-siyaasat-mein-vanshavaad-ka-dabadaba-politikal-phaimilee-se-har-chautha-saansad-vidhaayak-madhya-pradesh-politics-news-1295562</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>https://www.ultranewstv.com/hi/personality/pushkar-singh-dhami</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>https://www.thejbt.com/india/there-was-a-ruckus-between-rjd-and-congress-over-seat-sharing-and-the-post-of-chief-minister-there-was-a-ruckus-in-kutumba-assembly-news-295226</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>https://www.awazthevoice.in/india-news/modi-at-global-leaders-nation-unite-in-celebrations-41616.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>https://www.thestatesman.com/india/defence-minister-rajnath-singh-hails-pm-modi-as-a-visionary-leader-on-his-75th-birthday-1503487779.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>https://www.aninews.in/news/national/general-news/kharge-rahul-gandhi-kejriwal-extend-birthday-greetings-to-pm-modi20250917110456</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/government-teachers-marched-to-the-chief-ministers-residence-to-raise-their-demands/</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>https://krantiodishanews.in/post/13875</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarenglish.in/local/mp/news/kolaras-sugar-factory-shuts-down-115-workers-dead-unpaid-dues-families-face-distress-forced-to-live-in-damaged-quarters-135957427.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-conference-on-agriculture-rabi-campaign-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>https://starsamachar.com/farmers-protest-satna-tractor-rally-memorandum-to-pm-cm</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-nabha-farmers-protest-dispute-female-dsp-mandeep-news-135984706.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/wcd-ministry-to-organise-main-function-in-Raipur.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/punjab/ludhiana/news/punjab-bathinda-court-again-issues-summons-bjp-mp-actor-kangana-ranaut-news-135933597.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Administration-released-the-list-of-dead-missing.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/farmers-protest-against-land-pooling-scheme-in-ujjain-simhastha-2028-madhya-pradesh-news-mps25091604176</t>
-        </is>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/bhopal/farmers-agitation-against-land-pooling-act-demonstration-by-bharatiya-kisan-sangh-and-karni-sena-1386239.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/Ayush-Department-will-receive-the-prestigious-Scot.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/shimla/cm-sukhvinder-sukhu-said-state-cooperative-bank-will-bring-one-time-settlement-policy-for-small-farmers-2025-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>https://www.yugwarta.com/Encyc/2025/9/16/CG-Bastar-Division-54-adult-minor-girls-missing.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>https://inanews.org/lucknow-agriculture-minister-attended-the-national-agriculture-conference--rabi-abhiyan-2025-in-new-delhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/krishi-vyapar/haryana-govt-announces-procurement-of-kharif-crops-from-september-22-cm-saini-assures-farmers-of-msp-support</t>
-        </is>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/sharad-pawar-warns-fadnavis-to-learn-from-nepal-supriya-sule-demands-complete-farm-loan-waiver-in-maharashtra</t>
-        </is>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>https://krishijagran.com/news/dr-jitendra-singh-calls-biotechnology-india-s-next-industrial-revolution-highlights-bio-e3-policy-and-ai-healthcare-initiative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>https://www.constructionworld.in/latest-construction-news/real-estate-news/indian-real-estate-draws--80bn-in-15-years--57-per-cent-from-foreigners/78892</t>
-        </is>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>https://www.financialexpress.com/policy/economy-khaif-output-to-match-last-years-level-secretary-3978830/</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-projects-a-modest-2-4-growth-in-foodgrains-production-in-2025-26-3979861/</t>
-        </is>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>https://www.financialexpress.com/policy/economy-govt-moots-state-panels-to-curb-fertiliser-diversion-3979999/</t>
-        </is>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/niti-aayog-launches-ai-roadmap-and-frontier-tech-repository/78832</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/asm-tech-to-invest-rs-2.50-bn-in-tamil-nadu/78907</t>
-        </is>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/godrej-finance--muthoot-join-hands-to-boost-msme-lending/79061</t>
-        </is>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/madhya-pradesh/story/mohan-yadav-blog-praises-pm-modi-leadership-on-his-birthday-lcln-dskc-2335245-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>https://bharatsamachartv.in/akhilesh-yadav-attacks-yogi-government-expresses-displeasure-over-issues-ranging-from-films-to-foreign-policy/</t>
-        </is>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/punjab/amritsar/news/amritsar-durgiana-temple-langoor-mela-navratri-2025-135978487.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/himachal/controversy-erupts-over-sukhus-foreign-tour-government-defends-him/</t>
-        </is>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>https://dainikdehat.com/states/uttar-pradesh/problems-of-farmers-cows-and-h1b-visa-holders-persist-akhilesh-targets-bjp</t>
-        </is>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/small-biz/sustainability/govt-aid-corporate-funds-can-be-used-to-finance-msmes-measures-to-cut-emission-experts/articleshow/124037953.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>https://eng.ruralvoice.in/latest-news/india-bioenergy-tech-expo-2025-to-focus-on-scaling-up-green-energy-initiatives.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278591275/union-minister-shivraj-singh-chouhan-participates-in-cleanliness-drive-in-raisen-under-seva-pakhwada-initiative</t>
-        </is>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/haryana/panchkula-13-solid-waste-management-plants-to-be-set-up-in-haryana-e-waste-collection-centres-in-every-district-375-electric-buses-to-arrive-24049075.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/chief-minister-naib-singh-saini-launched-state-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/haryana/panchkula/news/cm-launched-haryana-state-environment-plan-2025-135934095.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>https://www.divyahimachal.com/2025/09/a-balance-must-be-struck-between-development-and-the-environment-the-cm-said-adding-that-methods-will-have-to-change-in-the-era-of-disasters-and-climate-change/</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>https://www.haribhoomi.com/state-local/haryana/panchkula/haryana-green-plan-cm-saini-electric-buses-stubble-management-646820</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/haryana/panchkula-news/news-chief-minister-naib-singh-saini-launched-state-environment-plan-2025-government-aims-to-set-up-e-waste-collection-centers-in-every-district-news-hindi-1-753254-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>https://suryasamachar.com/2025/09/16/major-step-by-haryana-government-for-pollution-control-cm-saini-launched-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/dehradun/cm-dhami-wishes-pm-modi-on-his-birthday-launches-swachh-utsav-2025-program-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/chief-minister-dhami-launched-swachh-utsav-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>https://firstindianews.com/news/chief-minister-bhajanlal-sharma-planted-a-tree</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-embarks-on-green-mission-cm-nayab-saini-launches-state-environment-plan-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/delhi/new-delhi-city-ncr-plantation-drive-75-trees-planted-on-pm-modis-birthday-24050882.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/haryana/jhajjar/bahadurgarh/news/jhajjar-bahadurgarh-municipal-council-utensils-bank-135983940.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/uttarakhand/dehradun-city-pm-modi-birthday-cleanliness-campaign-launched-by-cm-dhami-in-uttarakhand-swachh-utsav2025-24050015.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>https://www.bhaskar.com/local/bihar/bettiah/jogapatti/news/one-tree-in-the-name-of-mother-tree-plantation-program-in-machhargaon-135969599.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/haryana/haryana-news-rao-narbir-singh-said-namo-van-will-be-established-at-75-places-in-haryana-during-seva-pakhwada/</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>https://www.jagran.com/haryana/panchkula-haryana-state-environment-plan-2025-launched-by-cm-nayab-singh-saini-know-benefits-24048895.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>https://www.dainiktribuneonline.com/news/karnal/union-health-minister-and-chief-minister-will-participate-in-various-programs-prime-minister-modi-will-join-live/</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>https://www.indiatv.in/delhi/seva-pakhwada-72-countries-delegates-attended-one-tree-for-mother-programme-2025-09-18-1163540</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>https://avikaluttarakhand.com/uttarakhand/cms-emphasis-on-speeding-up-implementation-of-schemes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>https://suryasamachar.com/2025/09/19/transcon-2025-50-years-of-isbti-completed-cm-saini-made-these-important-remarks/</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>https://panchjanya.com/2025/09/17/435757/bharat/uttarakhand/cm-dhami-launched-a-cleanliness-drive-on-pm-modi-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/haryana-cm-nayab-saini-seva-pakhwada-swachhata-abhiyan-on-pm-modi-birthday-in-rohtak-mdu-haryana-news-hrs25091700782</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>https://kalikumaunkhabar.com/national/haryana-new-initiative-of-haryana-government-these-districts-get-this-big-gift</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>https://garimatimes.in/chief-minister-nayab-singh-saini-launched-state-environment-plan-2025-appealed-to-citizens-to-save-water-plant-trees-and-keep-environment-clean/</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/rs20000-crore-mous-to-be-signed-at-mumbai-international-bamboo-summit-focus-on-green-economy-and-sustainable-development</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/uttarakhand/pm-modi-birthday-swachhotsav-campaign-in-dehradun-cm-dhami-and-other-leaders-extended-their-best-wishes-53-819606</t>
-        </is>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>https://dailyuttarakhand.com/india-became-the-fourth-largest-economy-in-the-world-under-the-leadership-of-pm-modi-dhami/</t>
-        </is>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/cente-j-k-govt-will-bring-farmers-out-of-flood-disaster-with-pms-blessings-chouhan/2929985</t>
-        </is>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>https://dailysamvad.com/2025/09/16/minister-khudian-appealed-to-the-central-govt/</t>
-        </is>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/chandigarh/himachal-minister-chander-kumar-to-centre-run-train-to-transport-farm-produce/articleshow/123952835.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>https://www.tribuneindia.com/news/business/agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/gst-cut-agri-minister-meets-farm-equipment-industry/33889220250918</t>
-        </is>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>https://www.latestly.com/agency-news/business-news-agriculture-minister-asks-farm-equipment-tractor-makers-to-pass-on-gst-cut-benefits-to-farmers-7118810.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>https://ianslive.in/we-will-make-india-food-basket-of-the-world-minister--20250916091123</t>
-        </is>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>https://hindi.business-standard.com/commodities/crops-damaged-by-floods-yet-government-sets-higher-food-grain-production-target-for-fy-2025-26-id-472424</t>
-        </is>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/uttar-pradesh-preparations-for-rabi-season-in-full-swing-yogi-government-to-launch-viksit-krishi-sankalp-abhiy</t>
-        </is>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>https://samarsaleel.com/agriculture-minister-surya-pratap-shahi-joined-national-agricultural-conference-rabi-abhiyan-2025/496856</t>
-        </is>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/record-wheat-output-target-set-at-119-million-tons/33771920250916</t>
-        </is>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>https://money.rediff.com/news/market/india-farm-growth-highest-globally-chouhan/33725320250915</t>
-        </is>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/dap-shortage-for-rabi-crops-agra-agriculture-officer-says-npk-provide-better-yield-uttar-pradesh-news-ups25091900464</t>
-        </is>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/business/business-diary/union-government-set-record-wheat-production-target-of-119-million-tonnes-for-2025-26-crop-year-2025-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>https://www.prabhatkhabar.com/national/agriculture-seeds-and-fertilizers</t>
-        </is>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167392</t>
-        </is>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/national/kerala/aidak-seeks-ban-on-spurious-herbicides-sold-online/article70077811.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>https://saachibaat.com/politics/todays-top-news-17-september-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2167390</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>https://www.humsamvet.com/mp-info/rainfall-has-become-a-headache-for-farmers-in-sehore-with-waterlogging-causing-heavy-damage-to-soybean-crops-34980</t>
-        </is>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/kheti-kisani/govt-plans-state-panels-tech-push-to-curb-fertiliser-diversion-ensure-farmer-supply</t>
-        </is>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
-        <is>
-          <t>https://eng.ruralvoice.in/latest-news/10-eminent-agricultural-scientists-urge-pm-modi-to-expedite-clearance-for-gm-mustard.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/agriculture-secretary-said-despite-crop-loss-kharif-production-will-remain-same-as-last-year-said-a-big-thi</t>
-        </is>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!state/panchkula-self-reliant-india-resolution-campaign-haryana-cm-nayab-saini-haryana-news-hrs25092101142</t>
-        </is>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
-        <is>
-          <t>https://cg24news.in/bjp-20925</t>
-        </is>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
-        <is>
-          <t>https://www.gaonjunction.com/khabar-junction/gst-rate-on-agricultural-machinery-reduced-to-5-which-equipment-has-become-cheaper-see-list</t>
-        </is>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
-        <is>
-          <t>https://www.mpinfo.org/Home/TodaysNews?newsid=%C2%B2%C2%B0%C2%B2%C2%B5%C2%B0%C2%B9%C2%B1%C2%B9%C3%8E%C2%B5%C2%B3%C2%B7&amp;fontname=Mangal&amp;LocID=32&amp;pubdate=19%20Sep%202025</t>
-        </is>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/video/news/gst-rate-cut-to-benefit-farmers-shivraj-singh-chouhan-says-on-tax-benefits/videoshow/123994517.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
-        <is>
-          <t>https://ndtv.in/india/what-became-cheaper-due-to-reduction-in-gst-on-agricultural-machinery-9311879</t>
-        </is>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
-        <is>
-          <t>https://hindi.news18.com/news/business/latest-list-of-agricultural-equipment-which-will-be-cheaper-after-gst-rate-cut-like-tractors-harvesting-machines-threshers-drip-irrigation-parts-sprayers-ws-kl-9650177.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
-        <is>
-          <t>https://khabardigital.com/madhya-pradesh/cm-mohan-yadav-visit-tyonthar-rewa-administration-alert/</t>
-        </is>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleseDetailm.aspx?PRID=2166972</t>
-        </is>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
-        <is>
-          <t>https://www.drishtiias.com/statepcs/16-09-2025/bihar</t>
-        </is>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>https://www.tractorjunction.com/agriculture-news/national-agriculture-conference-2025-concludes-with-focus-on-rabi-season/</t>
-        </is>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
           <t>https://www.etvbharat.com/hi/!state/mata-mansa-devi-temple-lit-up-with-colourful-lights-on-the-first-navratri-haryana-news-hrs25092205734</t>
-        </is>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>https://www.tv9hindi.com/india/aaj-ki-taaja-khabar-live-updates-latest-news-hindi-samachar-daily-breaking-22-september-2025-3492207.html</t>
         </is>
       </c>
     </row>
